--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD29452E-BB03-4385-9ED3-37740982FF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB35B12-2258-43A7-9114-0496E6C514FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="1995" windowWidth="27180" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27450" yWindow="2460" windowWidth="27180" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="49">
-  <si>
-    <t>苹果</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
   <si>
     <t>사과</t>
   </si>
@@ -130,12 +127,6 @@
   <si>
     <t>二</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>斤</t>
-  </si>
-  <si>
-    <t>个</t>
   </si>
   <si>
     <t>양사</t>
@@ -246,6 +237,26 @@
       </rPr>
       <t>萝</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>바나나</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>香蕉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>斤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>个</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>苹果</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -385,7 +396,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -394,26 +405,23 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="보통" xfId="1" builtinId="28"/>
@@ -708,36 +716,36 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="10" t="s">
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>10</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>501</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>0</v>
+      <c r="B2" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="7" t="s">
         <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="E2" s="6" t="str">
         <f>B2</f>
@@ -753,13 +761,13 @@
         <v>504</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="E3" s="6" t="str">
         <f>B3</f>
@@ -775,16 +783,16 @@
         <v>505</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>5</v>
       </c>
       <c r="E4" s="6" t="str">
-        <f t="shared" ref="E4:F67" si="1">B4</f>
+        <f t="shared" ref="E4:E67" si="1">B4</f>
         <v>西瓜</v>
       </c>
       <c r="F4" s="6" t="str">
@@ -796,14 +804,14 @@
       <c r="A5">
         <v>506</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>48</v>
+      <c r="B5" t="s">
+        <v>45</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="E5" s="6" t="str">
         <f t="shared" si="1"/>
@@ -819,13 +827,13 @@
         <v>507</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="E6" s="6" t="str">
         <f t="shared" si="1"/>
@@ -840,14 +848,14 @@
       <c r="A7">
         <v>508</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>47</v>
+      <c r="B7" t="s">
+        <v>44</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="E7" s="6" t="str">
         <f t="shared" si="1"/>
@@ -862,14 +870,14 @@
       <c r="A8">
         <v>509</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>34</v>
+      <c r="B8" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="E8" s="6" t="str">
         <f t="shared" si="1"/>
@@ -881,22 +889,31 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A9">
+        <v>510</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>香蕉</v>
+      </c>
+      <c r="F9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>香蕉</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="8"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="3"/>
       <c r="E10" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -909,7 +926,7 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -920,9 +937,9 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="8"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="3"/>
       <c r="E12" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -935,7 +952,7 @@
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
+      <c r="D13" s="3"/>
       <c r="E13" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -950,12 +967,12 @@
         <v>1000</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="7">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="3">
         <v>1</v>
       </c>
       <c r="E14" s="6" t="str">
@@ -972,13 +989,13 @@
         <v>1001</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E15" s="6" t="str">
         <f t="shared" si="1"/>
@@ -994,10 +1011,10 @@
         <v>1002</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1016,10 +1033,10 @@
         <v>1003</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1038,10 +1055,10 @@
         <v>1004</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3">
         <v>4</v>
@@ -1060,10 +1077,10 @@
         <v>1005</v>
       </c>
       <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
         <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>20</v>
       </c>
       <c r="D19" s="3">
         <v>5</v>
@@ -1082,10 +1099,10 @@
         <v>1006</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="3">
         <v>6</v>
@@ -1104,10 +1121,10 @@
         <v>1007</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" s="3">
         <v>7</v>
@@ -1126,10 +1143,10 @@
         <v>1008</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" s="3">
         <v>8</v>
@@ -1148,10 +1165,10 @@
         <v>1009</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" s="3">
         <v>9</v>
@@ -1170,10 +1187,10 @@
         <v>1010</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>10</v>
@@ -1192,10 +1209,10 @@
         <v>1011</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="3">
         <v>11</v>
@@ -1214,10 +1231,10 @@
         <v>1012</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D26" s="3">
         <v>12</v>
@@ -1236,10 +1253,10 @@
         <v>1013</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27" s="3">
         <v>13</v>
@@ -1249,7 +1266,7 @@
         <v>十三</v>
       </c>
       <c r="F27" s="6" t="str">
-        <f>B27</f>
+        <f t="shared" ref="F27:F34" si="2">B27</f>
         <v>十三</v>
       </c>
     </row>
@@ -1258,20 +1275,20 @@
         <v>1014</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D28" s="3">
         <v>14</v>
       </c>
       <c r="E28" s="6" t="str">
-        <f>B28</f>
+        <f t="shared" ref="E28:E34" si="3">B28</f>
         <v>十四</v>
       </c>
       <c r="F28" s="6" t="str">
-        <f>B28</f>
+        <f t="shared" si="2"/>
         <v>十四</v>
       </c>
     </row>
@@ -1280,20 +1297,20 @@
         <v>1015</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D29" s="3">
         <v>15</v>
       </c>
       <c r="E29" s="6" t="str">
-        <f>B29</f>
+        <f t="shared" si="3"/>
         <v>十五</v>
       </c>
       <c r="F29" s="6" t="str">
-        <f>B29</f>
+        <f t="shared" si="2"/>
         <v>十五</v>
       </c>
     </row>
@@ -1302,20 +1319,20 @@
         <v>1016</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30" s="3">
         <v>16</v>
       </c>
       <c r="E30" s="6" t="str">
-        <f>B30</f>
+        <f t="shared" si="3"/>
         <v>十六</v>
       </c>
       <c r="F30" s="6" t="str">
-        <f>B30</f>
+        <f t="shared" si="2"/>
         <v>十六</v>
       </c>
     </row>
@@ -1324,20 +1341,20 @@
         <v>1017</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D31" s="3">
         <v>17</v>
       </c>
       <c r="E31" s="6" t="str">
-        <f>B31</f>
+        <f t="shared" si="3"/>
         <v>十七</v>
       </c>
       <c r="F31" s="6" t="str">
-        <f>B31</f>
+        <f t="shared" si="2"/>
         <v>十七</v>
       </c>
     </row>
@@ -1346,20 +1363,20 @@
         <v>1018</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D32" s="3">
         <v>18</v>
       </c>
       <c r="E32" s="6" t="str">
-        <f>B32</f>
+        <f t="shared" si="3"/>
         <v>十八</v>
       </c>
       <c r="F32" s="6" t="str">
-        <f>B32</f>
+        <f t="shared" si="2"/>
         <v>十八</v>
       </c>
     </row>
@@ -1368,20 +1385,20 @@
         <v>1019</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D33" s="3">
         <v>19</v>
       </c>
       <c r="E33" s="6" t="str">
-        <f>B33</f>
+        <f t="shared" si="3"/>
         <v>十九</v>
       </c>
       <c r="F33" s="6" t="str">
-        <f>B33</f>
+        <f t="shared" si="2"/>
         <v>十九</v>
       </c>
     </row>
@@ -1390,20 +1407,20 @@
         <v>1020</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D34" s="3">
         <v>20</v>
       </c>
       <c r="E34" s="6" t="str">
-        <f>B34</f>
+        <f t="shared" si="3"/>
         <v>二十</v>
       </c>
       <c r="F34" s="6" t="str">
-        <f>B34</f>
+        <f t="shared" si="2"/>
         <v>二十</v>
       </c>
     </row>
@@ -1422,13 +1439,13 @@
         <v>2021</v>
       </c>
       <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" t="s">
         <v>27</v>
-      </c>
-      <c r="C37" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" t="s">
-        <v>30</v>
       </c>
       <c r="E37" s="6" t="str">
         <f>B37</f>
@@ -1443,14 +1460,14 @@
       <c r="A38">
         <v>2022</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" t="s">
         <v>28</v>
-      </c>
-      <c r="C38" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" t="s">
-        <v>31</v>
       </c>
       <c r="E38" s="6" t="str">
         <f>B38</f>
@@ -1747,1913 +1764,1913 @@
         <v>0</v>
       </c>
       <c r="F67" s="6">
-        <f t="shared" ref="F67:F130" si="2">B67</f>
+        <f t="shared" ref="F67:F130" si="4">B67</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E68" s="6">
-        <f t="shared" ref="E68:E131" si="3">B68</f>
+        <f t="shared" ref="E68:E131" si="5">B68</f>
         <v>0</v>
       </c>
       <c r="F68" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E69" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F69" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E70" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F70" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E71" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F71" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E72" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F72" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E73" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F73" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E74" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F74" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E75" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F75" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E76" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F76" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E77" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F77" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E78" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F78" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E79" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F79" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E80" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F80" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E81" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F81" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E82" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F82" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E83" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F83" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E84" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F84" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E85" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F85" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E86" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F86" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E87" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F87" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E88" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F88" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E89" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F89" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E90" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F90" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E91" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F91" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E92" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F92" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E93" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F93" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E94" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F94" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E95" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F95" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E96" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F96" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E97" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F97" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E98" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F98" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E99" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F99" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E100" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F100" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E101" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F101" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E102" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F102" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E103" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F103" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E104" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F104" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E105" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F105" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E106" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F106" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E107" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F107" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E108" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F108" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E109" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F109" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E110" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F110" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E111" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F111" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E112" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F112" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E113" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F113" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E114" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F114" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E115" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F115" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E116" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F116" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E117" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F117" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E118" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F118" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E119" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F119" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E120" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F120" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E121" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F121" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E122" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F122" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E123" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F123" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E124" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F124" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E125" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F125" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E126" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F126" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E127" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F127" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E128" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F128" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E129" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F129" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E130" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F130" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E131" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F131" s="6">
-        <f t="shared" ref="F131:F194" si="4">B131</f>
+        <f t="shared" ref="F131:F194" si="6">B131</f>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E132" s="6">
-        <f t="shared" ref="E132:E195" si="5">B132</f>
+        <f t="shared" ref="E132:E195" si="7">B132</f>
         <v>0</v>
       </c>
       <c r="F132" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E133" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F133" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E134" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F134" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E135" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F135" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E136" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F136" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E137" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F137" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E138" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F138" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E139" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F139" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E140" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F140" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E141" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F141" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E142" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F142" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E143" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F143" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E144" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F144" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E145" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F145" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E146" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F146" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E147" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F147" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E148" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F148" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E149" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F149" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E150" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F150" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E151" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F151" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E152" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F152" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E153" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F153" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E154" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F154" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E155" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F155" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E156" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F156" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E157" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F157" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E158" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F158" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E159" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F159" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E160" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F160" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E161" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F161" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E162" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F162" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E163" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F163" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E164" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F164" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="165" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E165" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F165" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E166" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F166" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E167" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F167" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E168" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F168" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="169" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E169" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F169" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E170" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F170" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E171" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F171" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E172" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F172" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E173" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F173" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E174" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F174" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E175" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F175" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E176" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F176" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E177" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F177" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E178" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F178" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E179" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F179" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E180" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F180" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E181" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F181" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E182" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F182" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E183" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F183" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E184" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F184" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E185" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F185" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E186" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F186" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E187" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F187" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E188" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F188" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E189" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F189" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E190" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F190" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E191" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F191" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E192" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F192" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="193" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E193" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F193" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E194" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F194" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E195" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F195" s="6">
-        <f t="shared" ref="F195:F257" si="6">B195</f>
+        <f t="shared" ref="F195:F257" si="8">B195</f>
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E196" s="6">
-        <f t="shared" ref="E196:E258" si="7">B196</f>
+        <f t="shared" ref="E196:E258" si="9">B196</f>
         <v>0</v>
       </c>
       <c r="F196" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="197" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E197" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F197" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E198" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F198" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="199" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E199" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F199" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="200" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E200" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F200" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="201" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E201" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F201" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="202" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E202" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F202" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="203" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E203" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F203" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="204" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E204" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F204" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="205" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E205" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F205" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="206" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E206" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F206" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="207" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E207" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F207" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="208" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E208" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F208" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="209" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E209" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F209" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="210" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E210" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F210" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="211" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E211" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F211" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="212" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E212" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F212" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="213" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E213" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F213" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="214" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E214" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F214" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="215" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E215" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F215" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="216" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E216" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F216" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E217" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F217" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E218" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F218" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="219" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E219" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F219" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E220" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F220" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="221" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E221" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F221" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E222" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F222" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="223" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E223" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F223" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E224" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F224" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="225" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E225" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F225" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E226" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F226" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="227" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E227" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F227" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="228" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E228" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F228" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E229" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F229" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E230" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F230" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="231" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E231" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F231" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="232" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E232" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F232" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="233" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E233" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F233" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E234" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F234" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E235" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F235" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="236" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E236" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F236" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="237" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E237" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F237" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E238" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F238" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="239" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E239" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F239" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="240" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E240" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F240" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E241" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F241" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="242" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E242" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F242" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="243" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E243" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F243" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="244" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E244" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F244" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E245" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F245" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E246" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F246" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E247" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F247" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="248" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E248" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F248" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="249" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E249" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F249" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E250" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F250" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E251" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F251" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E252" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F252" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E253" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F253" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="254" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E254" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F254" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E255" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F255" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E256" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F256" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E257" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F257" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E258" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB35B12-2258-43A7-9114-0496E6C514FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639DA935-FE9D-4B75-8CC0-53414015FC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27450" yWindow="2460" windowWidth="27180" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30105" yWindow="2625" windowWidth="27180" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>사과</t>
   </si>
@@ -258,6 +258,9 @@
   <si>
     <t>苹果</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
@@ -1447,9 +1450,8 @@
       <c r="D37" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="6" t="str">
-        <f>B37</f>
-        <v>斤</v>
+      <c r="E37" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="F37" s="6" t="str">
         <f>B37</f>
@@ -1469,9 +1471,8 @@
       <c r="D38" t="s">
         <v>28</v>
       </c>
-      <c r="E38" s="6" t="str">
-        <f>B38</f>
-        <v>个</v>
+      <c r="E38" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="F38" s="6" t="str">
         <f>B38</f>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,12 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639DA935-FE9D-4B75-8CC0-53414015FC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE629257-802F-4E6A-A60A-151AD2BCED13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30105" yWindow="2625" windowWidth="27180" windowHeight="15570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="수사" sheetId="4" r:id="rId1"/>
+    <sheet name="기타" sheetId="5" r:id="rId2"/>
+    <sheet name="대명사" sheetId="6" r:id="rId3"/>
+    <sheet name="명사" sheetId="1" r:id="rId4"/>
+    <sheet name="동사" sheetId="3" r:id="rId5"/>
+    <sheet name="형용사" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="194">
   <si>
     <t>사과</t>
   </si>
@@ -262,12 +267,648 @@
   <si>
     <t>none</t>
   </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>동사</t>
+  </si>
+  <si>
+    <t>吗</t>
+  </si>
+  <si>
+    <t>我</t>
+  </si>
+  <si>
+    <t>대명사</t>
+  </si>
+  <si>
+    <t>您</t>
+  </si>
+  <si>
+    <t>他</t>
+  </si>
+  <si>
+    <t>她</t>
+  </si>
+  <si>
+    <t>我们</t>
+  </si>
+  <si>
+    <t>你们</t>
+  </si>
+  <si>
+    <t>他们</t>
+  </si>
+  <si>
+    <t>她们</t>
+  </si>
+  <si>
+    <t>나, 저</t>
+  </si>
+  <si>
+    <t>너, 당신</t>
+  </si>
+  <si>
+    <t>그</t>
+  </si>
+  <si>
+    <t>그녀</t>
+  </si>
+  <si>
+    <t>그들</t>
+  </si>
+  <si>
+    <t>그녀들</t>
+  </si>
+  <si>
+    <t>~이다</t>
+  </si>
+  <si>
+    <t>어기조사</t>
+  </si>
+  <si>
+    <t>~인가요? (의문문 표시)</t>
+  </si>
+  <si>
+    <t>上班族</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>명사</t>
+  </si>
+  <si>
+    <t>직장인, 회사원</t>
+  </si>
+  <si>
+    <t>公司职员</t>
+  </si>
+  <si>
+    <t>회사원 (보다 공식적 표현)</t>
+  </si>
+  <si>
+    <t>졸업생</t>
+  </si>
+  <si>
+    <t>요리사</t>
+  </si>
+  <si>
+    <t>가수</t>
+  </si>
+  <si>
+    <t>학생</t>
+  </si>
+  <si>
+    <t>중국인</t>
+  </si>
+  <si>
+    <t>한국인</t>
+  </si>
+  <si>
+    <t>프로그래머, 개발자</t>
+  </si>
+  <si>
+    <r>
+      <t>程序</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>员</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>工程师</t>
+  </si>
+  <si>
+    <t>엔지니어</t>
+  </si>
+  <si>
+    <t>선생님</t>
+  </si>
+  <si>
+    <t>医生</t>
+  </si>
+  <si>
+    <t>의사</t>
+  </si>
+  <si>
+    <r>
+      <t>公</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>务员</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计师</t>
+  </si>
+  <si>
+    <t>律师</t>
+  </si>
+  <si>
+    <t>공무원</t>
+  </si>
+  <si>
+    <t>디자이너</t>
+  </si>
+  <si>
+    <t>변호사</t>
+  </si>
+  <si>
+    <t>会计</t>
+  </si>
+  <si>
+    <t>회계사, 회계 담당자</t>
+  </si>
+  <si>
+    <t>银行职员</t>
+  </si>
+  <si>
+    <t>은행원</t>
+  </si>
+  <si>
+    <t>你</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毕业</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>生</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>老</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>师</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不</t>
+  </si>
+  <si>
+    <t>부정 부사</t>
+  </si>
+  <si>
+    <t>아니다, ~하지 않다</t>
+  </si>
+  <si>
+    <t>歌手</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>厨师</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>学</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>生</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>韩国</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>人</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>国</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>人</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在</t>
+  </si>
+  <si>
+    <t>去</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>~에 있다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>~에 가다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지시대명사</t>
+  </si>
+  <si>
+    <t>여기</t>
+  </si>
+  <si>
+    <t>거기 / 저기</t>
+  </si>
+  <si>
+    <t>어디</t>
+  </si>
+  <si>
+    <t>哪儿</t>
+  </si>
+  <si>
+    <t>의문대명사</t>
+  </si>
+  <si>
+    <t>工作</t>
+  </si>
+  <si>
+    <t>일, 직업</t>
+  </si>
+  <si>
+    <t>银行</t>
+  </si>
+  <si>
+    <t>은행</t>
+  </si>
+  <si>
+    <t>有</t>
+  </si>
+  <si>
+    <t>等</t>
+  </si>
+  <si>
+    <t>있다, 가지다</t>
+  </si>
+  <si>
+    <t>기다리다</t>
+  </si>
+  <si>
+    <t>일하다</t>
+  </si>
+  <si>
+    <t>那</t>
+  </si>
+  <si>
+    <t>这</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지시대명사|지시형용사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것|이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것|저</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这儿</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>儿</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>本</t>
+  </si>
+  <si>
+    <t>양사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>권 (책류 세는 단위)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>的</t>
+  </si>
+  <si>
+    <t>조사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>~의 / ~한</t>
+  </si>
+  <si>
+    <t>手机</t>
+  </si>
+  <si>
+    <t>핸드폰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>책</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>书</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>개</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>닭</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>돼지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>只</t>
+  </si>
+  <si>
+    <t>마리 ( 동물을 세는 단위)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>masking</t>
+  </si>
+  <si>
+    <t>"1"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>狗</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸡肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>猪肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸭肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊肉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>양</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>돼지고기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소고기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오리고기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>양고기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>닭고기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵</t>
+  </si>
+  <si>
+    <t>好</t>
+  </si>
+  <si>
+    <t>吃</t>
+  </si>
+  <si>
+    <t>좋다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>형용사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀한</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>맛있는</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신 (존칭)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대명사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너희, 여러분</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리, 저희</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好吃</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,6 +1011,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -399,7 +1047,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -425,6 +1073,14 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="보통" xfId="1" builtinId="28"/>
@@ -705,19 +1361,1125 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD933C08-AB0D-4C1A-BC48-5A53A606CA65}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f>B2</f>
+        <v>一</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <f>B2</f>
+        <v>一</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <f>B3</f>
+        <v>两</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <f>B3</f>
+        <v>两</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="str">
+        <f>B4</f>
+        <v>二</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <f>B4</f>
+        <v>二</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1003</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f>B5</f>
+        <v>三</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <f>B5</f>
+        <v>三</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6" t="str">
+        <f>B6</f>
+        <v>四</v>
+      </c>
+      <c r="F6" s="6" t="str">
+        <f>B6</f>
+        <v>四</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1005</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f>B7</f>
+        <v>五</v>
+      </c>
+      <c r="F7" s="6" t="str">
+        <f>B7</f>
+        <v>五</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1006</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="6" t="str">
+        <f>B8</f>
+        <v>六</v>
+      </c>
+      <c r="F8" s="6" t="str">
+        <f>B8</f>
+        <v>六</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1007</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7</v>
+      </c>
+      <c r="E9" s="6" t="str">
+        <f>B9</f>
+        <v>七</v>
+      </c>
+      <c r="F9" s="6" t="str">
+        <f>B9</f>
+        <v>七</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1008</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6" t="str">
+        <f>B10</f>
+        <v>八</v>
+      </c>
+      <c r="F10" s="6" t="str">
+        <f>B10</f>
+        <v>八</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1009</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3">
+        <v>9</v>
+      </c>
+      <c r="E11" s="6" t="str">
+        <f>B11</f>
+        <v>九</v>
+      </c>
+      <c r="F11" s="6" t="str">
+        <f>B11</f>
+        <v>九</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1010</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="3">
+        <v>10</v>
+      </c>
+      <c r="E12" s="6" t="str">
+        <f>B12</f>
+        <v>十</v>
+      </c>
+      <c r="F12" s="6" t="str">
+        <f>B12</f>
+        <v>十</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1011</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="3">
+        <v>11</v>
+      </c>
+      <c r="E13" s="6" t="str">
+        <f>B13</f>
+        <v>十一</v>
+      </c>
+      <c r="F13" s="6" t="str">
+        <f>B13</f>
+        <v>十一</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1012</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="3">
+        <v>12</v>
+      </c>
+      <c r="E14" s="6" t="str">
+        <f>B14</f>
+        <v>十二</v>
+      </c>
+      <c r="F14" s="6" t="str">
+        <f>B14</f>
+        <v>十二</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1013</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="3">
+        <v>13</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f>B15</f>
+        <v>十三</v>
+      </c>
+      <c r="F15" s="6" t="str">
+        <f>B15</f>
+        <v>十三</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1014</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="3">
+        <v>14</v>
+      </c>
+      <c r="E16" s="6" t="str">
+        <f>B16</f>
+        <v>十四</v>
+      </c>
+      <c r="F16" s="6" t="str">
+        <f>B16</f>
+        <v>十四</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1015</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="3">
+        <v>15</v>
+      </c>
+      <c r="E17" s="6" t="str">
+        <f>B17</f>
+        <v>十五</v>
+      </c>
+      <c r="F17" s="6" t="str">
+        <f>B17</f>
+        <v>十五</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1016</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="3">
+        <v>16</v>
+      </c>
+      <c r="E18" s="6" t="str">
+        <f>B18</f>
+        <v>十六</v>
+      </c>
+      <c r="F18" s="6" t="str">
+        <f>B18</f>
+        <v>十六</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1017</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="3">
+        <v>17</v>
+      </c>
+      <c r="E19" s="6" t="str">
+        <f>B19</f>
+        <v>十七</v>
+      </c>
+      <c r="F19" s="6" t="str">
+        <f>B19</f>
+        <v>十七</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1018</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3">
+        <v>18</v>
+      </c>
+      <c r="E20" s="6" t="str">
+        <f>B20</f>
+        <v>十八</v>
+      </c>
+      <c r="F20" s="6" t="str">
+        <f>B20</f>
+        <v>十八</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1019</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="3">
+        <v>19</v>
+      </c>
+      <c r="E21" s="6" t="str">
+        <f>B21</f>
+        <v>十九</v>
+      </c>
+      <c r="F21" s="6" t="str">
+        <f>B21</f>
+        <v>十九</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1020</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="3">
+        <v>20</v>
+      </c>
+      <c r="E22" s="6" t="str">
+        <f>B22</f>
+        <v>二十</v>
+      </c>
+      <c r="F22" s="6" t="str">
+        <f>B22</f>
+        <v>二十</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5446ED6D-53FB-4D62-B605-3F28DA373B37}">
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2021</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <f>B2</f>
+        <v>斤</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2022</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <f>B3</f>
+        <v>个</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2023</v>
+      </c>
+      <c r="B4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <f>B4</f>
+        <v>本</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2024</v>
+      </c>
+      <c r="B5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <f>B5</f>
+        <v>只</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>3000</v>
+      </c>
+      <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="6" t="str">
+        <f>B25</f>
+        <v>吗</v>
+      </c>
+      <c r="F25" s="6" t="str">
+        <f>B25</f>
+        <v>吗</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>3001</v>
+      </c>
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="6" t="str">
+        <f>B26</f>
+        <v>不</v>
+      </c>
+      <c r="F26" s="6" t="str">
+        <f>B26</f>
+        <v>不</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>3002</v>
+      </c>
+      <c r="B27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="6" t="str">
+        <f>B27</f>
+        <v>的</v>
+      </c>
+      <c r="F27" s="6" t="str">
+        <f>B27</f>
+        <v>的</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33B9A0D8-1595-42A1-869B-986F7DD96898}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.125" customWidth="1"/>
+    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3100</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <f>B2</f>
+        <v>这</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <f>B3</f>
+        <v>那</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3102</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <f>B4</f>
+        <v>这个</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3103</v>
+      </c>
+      <c r="B5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <f>B5</f>
+        <v>那个</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>3104</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="6" t="str">
+        <f>B6</f>
+        <v>这儿</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>3105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="6" t="str">
+        <f>B7</f>
+        <v>那儿</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3106</v>
+      </c>
+      <c r="B8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="6" t="str">
+        <f>B8</f>
+        <v>哪儿</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E9" s="6">
+        <f>B9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <f>B9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E10" s="6">
+        <f>B10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <f>B10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E11" s="6">
+        <f>B11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <f>B11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>4000</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="6" t="str">
+        <f>B12</f>
+        <v>我</v>
+      </c>
+      <c r="F12" s="6" t="str">
+        <f>B12</f>
+        <v>我</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>4001</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="6" t="str">
+        <f>B13</f>
+        <v>你</v>
+      </c>
+      <c r="F13" s="6" t="str">
+        <f>B13</f>
+        <v>你</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>4002</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="6" t="str">
+        <f>B14</f>
+        <v>您</v>
+      </c>
+      <c r="F14" s="6" t="str">
+        <f>B14</f>
+        <v>您</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>4003</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f>B15</f>
+        <v>他</v>
+      </c>
+      <c r="F15" s="6" t="str">
+        <f>B15</f>
+        <v>他</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>4004</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="6" t="str">
+        <f>B16</f>
+        <v>她</v>
+      </c>
+      <c r="F16" s="6" t="str">
+        <f>B16</f>
+        <v>她</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>4005</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="6" t="str">
+        <f>B17</f>
+        <v>我们</v>
+      </c>
+      <c r="F17" s="6" t="str">
+        <f>B17</f>
+        <v>我们</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>4006</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E18" s="6" t="str">
+        <f>B18</f>
+        <v>你们</v>
+      </c>
+      <c r="F18" s="6" t="str">
+        <f>B18</f>
+        <v>你们</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>4007</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="6" t="str">
+        <f>B19</f>
+        <v>他们</v>
+      </c>
+      <c r="F19" s="6" t="str">
+        <f>B19</f>
+        <v>他们</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>4008</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="6" t="str">
+        <f>B20</f>
+        <v>她们</v>
+      </c>
+      <c r="F20" s="6" t="str">
+        <f>B20</f>
+        <v>她们</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:G258"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.875" customWidth="1"/>
     <col min="2" max="2" width="25.25" customWidth="1"/>
-    <col min="3" max="3" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="21.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.5" customWidth="1"/>
     <col min="5" max="5" width="43.125" customWidth="1"/>
     <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -736,8 +2498,11 @@
       <c r="F1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>501</v>
       </c>
@@ -759,7 +2524,7 @@
         <v>苹果</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>504</v>
       </c>
@@ -777,11 +2542,11 @@
         <v>芒果</v>
       </c>
       <c r="F3" s="6" t="str">
-        <f t="shared" ref="F3:F66" si="0">B3</f>
+        <f>B3</f>
         <v>芒果</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>505</v>
       </c>
@@ -795,15 +2560,15 @@
         <v>5</v>
       </c>
       <c r="E4" s="6" t="str">
-        <f t="shared" ref="E4:E67" si="1">B4</f>
+        <f>B4</f>
         <v>西瓜</v>
       </c>
       <c r="F4" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>B4</f>
         <v>西瓜</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>506</v>
       </c>
@@ -817,15 +2582,15 @@
         <v>12</v>
       </c>
       <c r="E5" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>B5</f>
         <v>菠萝</v>
       </c>
       <c r="F5" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>B5</f>
         <v>菠萝</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>507</v>
       </c>
@@ -839,15 +2604,15 @@
         <v>13</v>
       </c>
       <c r="E6" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>B6</f>
         <v>草莓</v>
       </c>
       <c r="F6" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>B6</f>
         <v>草莓</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>508</v>
       </c>
@@ -861,15 +2626,15 @@
         <v>14</v>
       </c>
       <c r="E7" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>B7</f>
         <v>山竹</v>
       </c>
       <c r="F7" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>B7</f>
         <v>山竹</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>509</v>
       </c>
@@ -883,15 +2648,15 @@
         <v>29</v>
       </c>
       <c r="E8" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>B8</f>
         <v>樱桃</v>
       </c>
       <c r="F8" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>B8</f>
         <v>樱桃</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>510</v>
       </c>
@@ -905,2143 +2670,1695 @@
         <v>46</v>
       </c>
       <c r="E9" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>B9</f>
         <v>香蕉</v>
       </c>
       <c r="F9" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>B9</f>
         <v>香蕉</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
       <c r="D10" s="3"/>
       <c r="E10" s="6">
-        <f t="shared" si="1"/>
+        <f>B10</f>
         <v>0</v>
       </c>
       <c r="F10" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <f>B10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="3"/>
       <c r="E11" s="6">
-        <f t="shared" si="1"/>
+        <f>B11</f>
         <v>0</v>
       </c>
       <c r="F11" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <f>B11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
       <c r="D12" s="3"/>
       <c r="E12" s="6">
-        <f t="shared" si="1"/>
+        <f>B12</f>
         <v>0</v>
       </c>
       <c r="F12" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <f>B12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="3"/>
       <c r="E13" s="6">
-        <f t="shared" si="1"/>
+        <f>B13</f>
         <v>0</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>1000</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>一</v>
-      </c>
-      <c r="F14" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>一</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>1001</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>两</v>
-      </c>
-      <c r="F15" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>两</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>1002</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>二</v>
-      </c>
-      <c r="F16" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>二</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>1003</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>三</v>
-      </c>
-      <c r="F17" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>三</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>1004</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="3">
-        <v>4</v>
-      </c>
-      <c r="E18" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>四</v>
-      </c>
-      <c r="F18" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>四</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>1005</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="3">
-        <v>5</v>
-      </c>
-      <c r="E19" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>五</v>
-      </c>
-      <c r="F19" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>五</v>
+        <f>B13</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1006</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>20</v>
+        <v>20000</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="3">
-        <v>6</v>
+        <v>74</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
       </c>
       <c r="E20" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>六</v>
+        <f>B20</f>
+        <v>上班族</v>
       </c>
       <c r="F20" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>六</v>
+        <f>B20</f>
+        <v>上班族</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>1007</v>
+        <v>20001</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="3">
-        <v>7</v>
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
       </c>
       <c r="E21" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>七</v>
+        <f>B21</f>
+        <v>公司职员</v>
       </c>
       <c r="F21" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>七</v>
+        <f>B21</f>
+        <v>公司职员</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1008</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>22</v>
+        <v>20002</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="3">
-        <v>8</v>
+        <v>74</v>
+      </c>
+      <c r="D22" t="s">
+        <v>78</v>
       </c>
       <c r="E22" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>八</v>
+        <f>B22</f>
+        <v>毕业生</v>
       </c>
       <c r="F22" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>八</v>
+        <f>B22</f>
+        <v>毕业生</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1009</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>23</v>
+        <v>20003</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="3">
-        <v>9</v>
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>79</v>
       </c>
       <c r="E23" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>九</v>
+        <f>B23</f>
+        <v>厨师</v>
       </c>
       <c r="F23" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>九</v>
+        <f>B23</f>
+        <v>厨师</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1010</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>32</v>
+        <v>20004</v>
+      </c>
+      <c r="B24" t="s">
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="3">
-        <v>10</v>
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
       </c>
       <c r="E24" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>十</v>
+        <f>B24</f>
+        <v>歌手</v>
       </c>
       <c r="F24" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>十</v>
+        <f>B24</f>
+        <v>歌手</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1011</v>
-      </c>
-      <c r="B25" t="s">
-        <v>33</v>
+        <v>20005</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="3">
-        <v>11</v>
+        <v>74</v>
+      </c>
+      <c r="D25" t="s">
+        <v>83</v>
       </c>
       <c r="E25" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>十一</v>
+        <f>B25</f>
+        <v>韩国人</v>
       </c>
       <c r="F25" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>十一</v>
+        <f>B25</f>
+        <v>韩国人</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>1012</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>34</v>
+        <v>20006</v>
+      </c>
+      <c r="B26" t="s">
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="3">
-        <v>12</v>
+        <v>74</v>
+      </c>
+      <c r="D26" t="s">
+        <v>82</v>
       </c>
       <c r="E26" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>十二</v>
+        <f>B26</f>
+        <v>中国人</v>
       </c>
       <c r="F26" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>十二</v>
+        <f>B26</f>
+        <v>中国人</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1013</v>
+        <v>20007</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="3">
-        <v>13</v>
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>84</v>
       </c>
       <c r="E27" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>十三</v>
+        <f>B27</f>
+        <v>程序员</v>
       </c>
       <c r="F27" s="6" t="str">
-        <f t="shared" ref="F27:F34" si="2">B27</f>
-        <v>十三</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <f>B27</f>
+        <v>程序员</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>1014</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>36</v>
+        <v>20008</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="3">
-        <v>14</v>
+        <v>74</v>
+      </c>
+      <c r="D28" t="s">
+        <v>81</v>
       </c>
       <c r="E28" s="6" t="str">
-        <f t="shared" ref="E28:E34" si="3">B28</f>
-        <v>十四</v>
+        <f>B28</f>
+        <v>学生</v>
       </c>
       <c r="F28" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>十四</v>
+        <f>B28</f>
+        <v>学生</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1015</v>
+        <v>20009</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="3">
-        <v>15</v>
+        <v>74</v>
+      </c>
+      <c r="D29" t="s">
+        <v>87</v>
       </c>
       <c r="E29" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>十五</v>
+        <f>B29</f>
+        <v>工程师</v>
       </c>
       <c r="F29" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>十五</v>
+        <f>B27</f>
+        <v>程序员</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>1016</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>39</v>
+        <v>20010</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="3">
-        <v>16</v>
+        <v>74</v>
+      </c>
+      <c r="D30" t="s">
+        <v>88</v>
       </c>
       <c r="E30" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>十六</v>
+        <f>B30</f>
+        <v>老师</v>
       </c>
       <c r="F30" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>十六</v>
+        <f>B30</f>
+        <v>老师</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1017</v>
+        <v>20011</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="3">
-        <v>17</v>
+        <v>74</v>
+      </c>
+      <c r="D31" t="s">
+        <v>90</v>
       </c>
       <c r="E31" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>十七</v>
+        <f>B31</f>
+        <v>医生</v>
       </c>
       <c r="F31" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>十七</v>
+        <f>B31</f>
+        <v>医生</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>1018</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>40</v>
+        <v>20012</v>
+      </c>
+      <c r="B32" t="s">
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="3">
-        <v>18</v>
+        <v>74</v>
+      </c>
+      <c r="D32" t="s">
+        <v>94</v>
       </c>
       <c r="E32" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>十八</v>
+        <f>B32</f>
+        <v>公务员</v>
       </c>
       <c r="F32" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>十八</v>
+        <f>B32</f>
+        <v>公务员</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>1019</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>41</v>
+        <v>20013</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="3">
-        <v>19</v>
+        <v>74</v>
+      </c>
+      <c r="D33" t="s">
+        <v>95</v>
       </c>
       <c r="E33" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>十九</v>
+        <f>B33</f>
+        <v>设计师</v>
       </c>
       <c r="F33" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>十九</v>
+        <f>B33</f>
+        <v>设计师</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>1020</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>42</v>
+        <v>20014</v>
+      </c>
+      <c r="B34" t="s">
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="3">
-        <v>20</v>
+        <v>74</v>
+      </c>
+      <c r="D34" t="s">
+        <v>96</v>
       </c>
       <c r="E34" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>二十</v>
+        <f>B34</f>
+        <v>律师</v>
       </c>
       <c r="F34" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>二十</v>
+        <f>B34</f>
+        <v>律师</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>20015</v>
+      </c>
+      <c r="B35" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35" s="6" t="str">
+        <f>B35</f>
+        <v>会计</v>
+      </c>
+      <c r="F35" s="6" t="str">
+        <f>B35</f>
+        <v>会计</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A36">
+        <v>20016</v>
+      </c>
+      <c r="B36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" s="6" t="str">
+        <f>B36</f>
+        <v>银行职员</v>
+      </c>
+      <c r="F36" s="6" t="str">
+        <f>B36</f>
+        <v>银行职员</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>2021</v>
-      </c>
-      <c r="B37" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F37" s="6" t="str">
+      <c r="E37" s="6">
         <f>B37</f>
-        <v>斤</v>
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
+        <f>B37</f>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>2022</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D38" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F38" s="6" t="str">
+      <c r="E38" s="6">
         <f>B38</f>
-        <v>个</v>
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
+        <f>B38</f>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E39" s="6">
-        <f t="shared" si="1"/>
+        <f>B39</f>
         <v>0</v>
       </c>
       <c r="F39" s="6">
-        <f t="shared" si="0"/>
+        <f>B39</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E40" s="6">
-        <f t="shared" si="1"/>
+        <f>B40</f>
         <v>0</v>
       </c>
       <c r="F40" s="6">
-        <f t="shared" si="0"/>
+        <f>B40</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E41" s="6">
-        <f t="shared" si="1"/>
+        <f>B41</f>
         <v>0</v>
       </c>
       <c r="F41" s="6">
-        <f t="shared" si="0"/>
+        <f>B41</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E42" s="6">
-        <f t="shared" si="1"/>
+        <f>B42</f>
         <v>0</v>
       </c>
       <c r="F42" s="6">
-        <f t="shared" si="0"/>
+        <f>B42</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A43">
+        <v>20100</v>
+      </c>
+      <c r="B43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="6" t="str">
+        <f>B43</f>
+        <v>工作</v>
+      </c>
+      <c r="F43" s="6" t="str">
+        <f>B43</f>
+        <v>工作</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F44" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A44">
+        <v>20101</v>
+      </c>
+      <c r="B44" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="6" t="str">
+        <f>B44</f>
+        <v>银行</v>
+      </c>
+      <c r="F44" s="6" t="str">
+        <f>B44</f>
+        <v>银行</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A45">
+        <v>20101</v>
+      </c>
+      <c r="B45" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" t="s">
+        <v>74</v>
+      </c>
+      <c r="D45" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45" s="6" t="str">
+        <f>B45</f>
+        <v>手机</v>
+      </c>
+      <c r="F45" s="6" t="str">
+        <f>B45</f>
+        <v>手机</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A46">
+        <v>20102</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" s="6" t="str">
+        <f>B46</f>
+        <v>书</v>
+      </c>
+      <c r="F46" s="6" t="str">
+        <f>B46</f>
+        <v>书</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A47">
+        <v>20103</v>
+      </c>
+      <c r="B47" t="s">
+        <v>167</v>
+      </c>
+      <c r="C47" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" s="6" t="str">
+        <f>B47</f>
+        <v>狗</v>
+      </c>
+      <c r="F47" s="6" t="str">
+        <f>B47</f>
+        <v>狗</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E53" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F53" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E54" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F54" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E55" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E56" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F56" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E57" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E58" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E59" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F59" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E60" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F60" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E61" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F61" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E62" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E63" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F63" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E64" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F64" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E65" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F65" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A48">
+        <v>20104</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" t="s">
+        <v>157</v>
+      </c>
+      <c r="E48" s="6" t="str">
+        <f>B48</f>
+        <v>猫</v>
+      </c>
+      <c r="F48" s="6" t="str">
+        <f>B48</f>
+        <v>猫</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>20105</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C49" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" s="6" t="str">
+        <f>B49</f>
+        <v>鸡</v>
+      </c>
+      <c r="F49" s="6" t="str">
+        <f>B49</f>
+        <v>鸡</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>20106</v>
+      </c>
+      <c r="B50" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" s="6" t="str">
+        <f>B50</f>
+        <v>猪</v>
+      </c>
+      <c r="F50" s="6" t="str">
+        <f>B50</f>
+        <v>猪</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>20107</v>
+      </c>
+      <c r="B51" t="s">
+        <v>155</v>
+      </c>
+      <c r="C51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" t="s">
+        <v>160</v>
+      </c>
+      <c r="E51" s="6" t="str">
+        <f>B51</f>
+        <v>牛</v>
+      </c>
+      <c r="F51" s="6" t="str">
+        <f>B51</f>
+        <v>牛</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>20108</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D52" t="s">
+        <v>161</v>
+      </c>
+      <c r="E52" s="6" t="str">
+        <f>B52</f>
+        <v>鸭子</v>
+      </c>
+      <c r="F52" s="6" t="str">
+        <f>B52</f>
+        <v>鸭子</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>20109</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C53" t="s">
+        <v>74</v>
+      </c>
+      <c r="D53" t="s">
+        <v>174</v>
+      </c>
+      <c r="E53" s="6" t="str">
+        <f>B53</f>
+        <v>羊</v>
+      </c>
+      <c r="F53" s="6" t="str">
+        <f>B53</f>
+        <v>羊</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>20110</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" t="s">
+        <v>74</v>
+      </c>
+      <c r="D54" t="s">
+        <v>175</v>
+      </c>
+      <c r="E54" s="6" t="str">
+        <f>B54</f>
+        <v>猪肉</v>
+      </c>
+      <c r="F54" s="6" t="str">
+        <f>B54</f>
+        <v>猪肉</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>20111</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" t="s">
+        <v>176</v>
+      </c>
+      <c r="E55" s="6" t="str">
+        <f>B55</f>
+        <v>牛肉</v>
+      </c>
+      <c r="F55" s="6" t="str">
+        <f>B55</f>
+        <v>牛肉</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>20112</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56" t="s">
+        <v>177</v>
+      </c>
+      <c r="E56" s="6" t="str">
+        <f>B56</f>
+        <v>鸭肉</v>
+      </c>
+      <c r="F56" s="6" t="str">
+        <f>B56</f>
+        <v>鸭肉</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>20113</v>
+      </c>
+      <c r="B57" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" t="s">
+        <v>178</v>
+      </c>
+      <c r="E57" s="6" t="str">
+        <f>B57</f>
+        <v>羊肉</v>
+      </c>
+      <c r="F57" s="6" t="str">
+        <f>B57</f>
+        <v>羊肉</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>20114</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C58" t="s">
+        <v>74</v>
+      </c>
+      <c r="D58" t="s">
+        <v>179</v>
+      </c>
+      <c r="E58" s="6" t="str">
+        <f>B58</f>
+        <v>鸡肉</v>
+      </c>
+      <c r="F58" s="6" t="str">
+        <f>B58</f>
+        <v>鸡肉</v>
       </c>
     </row>
     <row r="66" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E66" s="6">
-        <f t="shared" si="1"/>
+        <f>B66</f>
         <v>0</v>
       </c>
       <c r="F66" s="6">
-        <f t="shared" si="0"/>
+        <f>B66</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E67" s="6">
-        <f t="shared" si="1"/>
+        <f>B67</f>
         <v>0</v>
       </c>
       <c r="F67" s="6">
-        <f t="shared" ref="F67:F130" si="4">B67</f>
+        <f t="shared" ref="F67:F78" si="0">B67</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E68" s="6">
-        <f t="shared" ref="E68:E131" si="5">B68</f>
+        <f t="shared" ref="E68:E78" si="1">B68</f>
         <v>0</v>
       </c>
       <c r="F68" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E69" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F69" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E70" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F70" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E71" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F71" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E72" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F72" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E73" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F73" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E74" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F74" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E75" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F75" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E76" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F76" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E77" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F77" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E78" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F78" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E79" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E80" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F80" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E81" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F81" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E82" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F82" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E83" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F83" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E84" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F84" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E85" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="E85:E131" si="2">B85</f>
         <v>0</v>
       </c>
       <c r="F85" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="F85:F130" si="3">B85</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E86" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F86" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E87" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F87" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E88" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F88" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E89" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F89" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E90" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F90" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E91" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F91" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E92" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F92" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E93" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F93" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E94" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F94" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E95" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F95" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E96" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F96" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E97" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F97" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E98" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F98" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E99" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F99" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E100" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F100" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E101" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F101" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E102" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F102" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E103" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F103" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E104" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F104" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E105" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F105" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E106" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F106" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E107" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F107" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E108" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F108" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E109" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F109" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E110" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F110" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E111" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F111" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E112" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F112" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E113" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F113" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E114" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F114" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E115" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F115" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E116" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F116" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E117" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F117" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E118" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F118" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E119" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F119" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E120" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F120" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E121" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F121" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E122" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F122" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E123" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F123" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E124" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F124" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E125" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F125" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E126" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F126" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E127" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F127" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E128" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F128" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E129" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F129" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E130" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F130" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E131" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F131" s="6">
-        <f t="shared" ref="F131:F194" si="6">B131</f>
+        <f t="shared" ref="F131:F194" si="4">B131</f>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E132" s="6">
-        <f t="shared" ref="E132:E195" si="7">B132</f>
+        <f t="shared" ref="E132:E195" si="5">B132</f>
         <v>0</v>
       </c>
       <c r="F132" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E133" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F133" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E134" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F134" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E135" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F135" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E136" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F136" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E137" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F137" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E138" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F138" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E139" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F139" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E140" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F140" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E141" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F141" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E142" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F142" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E143" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F143" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E144" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F144" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E145" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F145" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E146" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F146" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E147" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F147" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E148" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F148" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E149" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F149" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E150" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F150" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E151" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F151" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E152" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F152" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E153" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F153" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E154" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F154" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E155" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F155" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E156" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F156" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E157" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F157" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E158" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F158" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E159" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F159" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E160" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F160" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E161" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F161" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E162" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F162" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E163" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F163" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E164" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F164" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E165" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F165" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E166" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F166" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E167" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F167" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E168" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F168" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E169" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F169" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E170" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F170" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E171" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F171" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E172" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F172" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E173" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F173" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E174" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F174" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E175" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F175" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E176" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F176" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E177" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F177" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="5:6" x14ac:dyDescent="0.3">
-      <c r="E178" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F178" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E179" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="E173:E180" si="6">B179</f>
         <v>0</v>
       </c>
       <c r="F179" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F173:F180" si="7">B179</f>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E180" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F180" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F180" s="6">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E181" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F181" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E182" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F182" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E183" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F183" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E184" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F184" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E185" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F185" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E186" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F186" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E187" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F187" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E188" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F188" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E189" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F189" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E190" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F190" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E191" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F191" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E192" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F192" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="193" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E193" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F193" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E194" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F194" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E195" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F195" s="6">
@@ -3672,6 +4989,384 @@
     <row r="258" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E258" s="6">
         <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8850F99E-0402-4A76-81B6-EBA17C790D8C}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="5" max="5" width="13.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>10000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f t="shared" ref="E2:E9" si="0">B2</f>
+        <v>是</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <f t="shared" ref="F2:F9" si="1">B2</f>
+        <v>是</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>10001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>在</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>在</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>10002</v>
+      </c>
+      <c r="B4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>去</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>去</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>10003</v>
+      </c>
+      <c r="B5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>有</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>有</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>10004</v>
+      </c>
+      <c r="B6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>等</v>
+      </c>
+      <c r="F6" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>等</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>10005</v>
+      </c>
+      <c r="B7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>工作</v>
+      </c>
+      <c r="F7" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>工作</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>10006</v>
+      </c>
+      <c r="B8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>好</v>
+      </c>
+      <c r="F8" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>好</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>10007</v>
+      </c>
+      <c r="B9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>吃</v>
+      </c>
+      <c r="F9" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>吃</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98471DEA-DA11-4ED3-8CC2-751E4782F2C0}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C5" s="6"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C7" s="6"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="11"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C9" s="6"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>100000</v>
+      </c>
+      <c r="B10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" s="6" t="str">
+        <f t="shared" ref="E10:E13" si="0">B10</f>
+        <v>贵</v>
+      </c>
+      <c r="F10" s="6" t="str">
+        <f t="shared" ref="F10:F13" si="1">B10</f>
+        <v>贵</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>100001</v>
+      </c>
+      <c r="B11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>好吃</v>
+      </c>
+      <c r="F11" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>好吃</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="7"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B3796F-6DAF-49BD-B331-EFC457E156CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D23441-DF5B-4D6E-B07D-5770E5224066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="259">
   <si>
     <t>사과</t>
   </si>
@@ -1469,12 +1469,22 @@
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>tts_type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tts_voice</t>
+  </si>
+  <si>
+    <t>ko-KR-SunHiNeural</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1612,6 +1622,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1641,7 +1657,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1677,6 +1693,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="보통" xfId="1" builtinId="28"/>
@@ -11370,7 +11387,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6292A66C-4C4B-481A-9187-6C9DCCB37A7E}">
-  <dimension ref="A1:H467"/>
+  <dimension ref="A1:J467"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.875" customWidth="1"/>
@@ -11382,7 +11399,7 @@
     <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -11407,8 +11424,14 @@
       <c r="H1" s="8" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>30000</v>
       </c>
@@ -11417,7 +11440,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>30116</v>
       </c>
@@ -11439,7 +11462,7 @@
         <v>地铁站</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>30117</v>
       </c>
@@ -11461,7 +11484,7 @@
         <v>外滩</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>30118</v>
       </c>
@@ -11483,7 +11506,7 @@
         <v>喜茶</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>30119</v>
       </c>
@@ -11505,7 +11528,7 @@
         <v>海底捞</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>30120</v>
       </c>
@@ -11527,7 +11550,7 @@
         <v>瑞幸咖啡</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>30121</v>
       </c>
@@ -11549,7 +11572,7 @@
         <v>东方明珠</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>30122</v>
       </c>
@@ -11571,7 +11594,7 @@
         <v>迪士尼乐园</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>30123</v>
       </c>
@@ -11596,7 +11619,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>30124</v>
       </c>
@@ -11621,7 +11644,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>30125</v>
       </c>
@@ -11646,7 +11669,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>30126</v>
       </c>
@@ -11671,7 +11694,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>30127</v>
       </c>
@@ -11696,7 +11719,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>30128</v>
       </c>
@@ -11720,8 +11743,11 @@
       <c r="H15" s="14" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J15" s="19" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>30129</v>
       </c>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D23441-DF5B-4D6E-B07D-5770E5224066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C36CA2C-3B5C-4234-B86C-522ECB2EF2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="260">
   <si>
     <t>사과</t>
   </si>
@@ -1479,12 +1479,16 @@
   <si>
     <t>ko-KR-SunHiNeural</t>
   </si>
+  <si>
+    <t>video_path</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1628,6 +1632,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9.9"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1657,7 +1667,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1694,6 +1704,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="보통" xfId="1" builtinId="28"/>
@@ -11387,7 +11401,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6292A66C-4C4B-481A-9187-6C9DCCB37A7E}">
-  <dimension ref="A1:J467"/>
+  <dimension ref="A1:K467"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.875" customWidth="1"/>
@@ -11397,9 +11411,10 @@
     <col min="5" max="5" width="43.125" customWidth="1"/>
     <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="46.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -11424,14 +11439,17 @@
       <c r="H1" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="J1" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="K1" s="19" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>30000</v>
       </c>
@@ -11440,7 +11458,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>30116</v>
       </c>
@@ -11462,7 +11480,7 @@
         <v>地铁站</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>30117</v>
       </c>
@@ -11484,7 +11502,7 @@
         <v>外滩</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>30118</v>
       </c>
@@ -11506,7 +11524,7 @@
         <v>喜茶</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>30119</v>
       </c>
@@ -11528,7 +11546,7 @@
         <v>海底捞</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>30120</v>
       </c>
@@ -11550,7 +11568,7 @@
         <v>瑞幸咖啡</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>30121</v>
       </c>
@@ -11572,7 +11590,7 @@
         <v>东方明珠</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>30122</v>
       </c>
@@ -11594,7 +11612,7 @@
         <v>迪士尼乐园</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>30123</v>
       </c>
@@ -11618,8 +11636,9 @@
       <c r="H10" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="I10" s="21"/>
+    </row>
+    <row r="11" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>30124</v>
       </c>
@@ -11643,8 +11662,9 @@
       <c r="H11" s="11" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="I11" s="21"/>
+    </row>
+    <row r="12" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>30125</v>
       </c>
@@ -11668,8 +11688,9 @@
       <c r="H12" s="11" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="I12" s="21"/>
+    </row>
+    <row r="13" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>30126</v>
       </c>
@@ -11694,7 +11715,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>30127</v>
       </c>
@@ -11719,7 +11740,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>30128</v>
       </c>
@@ -11743,11 +11764,11 @@
       <c r="H15" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="K15" s="19" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>30129</v>
       </c>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C36CA2C-3B5C-4234-B86C-522ECB2EF2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AAD050-C011-4F9C-B483-A7D4A8E1BE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -21,8 +21,9 @@
     <sheet name="동사" sheetId="3" r:id="rId6"/>
     <sheet name="명사" sheetId="1" r:id="rId7"/>
     <sheet name="고유명사" sheetId="11" r:id="rId8"/>
-    <sheet name="형용사" sheetId="2" r:id="rId9"/>
-    <sheet name="전치사" sheetId="8" r:id="rId10"/>
+    <sheet name="작업용" sheetId="12" r:id="rId9"/>
+    <sheet name="형용사" sheetId="2" r:id="rId10"/>
+    <sheet name="전치사" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="289">
   <si>
     <t>사과</t>
   </si>
@@ -1481,6 +1482,251 @@
   </si>
   <si>
     <t>video_path</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛泽东</t>
+  </si>
+  <si>
+    <t>邓小平</t>
+  </si>
+  <si>
+    <t>周恩来</t>
+  </si>
+  <si>
+    <t>江泽民</t>
+  </si>
+  <si>
+    <t>习近平</t>
+  </si>
+  <si>
+    <t>마오쩌둥 (모택동)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>시진핑 (습근평)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장쩌민 (강택민)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>덩샤오핑 (등소평)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>저우언라이 (주은래)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>중화인민공화국의 창건자</t>
+  </si>
+  <si>
+    <t>현대 중국을 부유하게 만든 '개혁개방의 총설계자'</t>
+  </si>
+  <si>
+    <t>건국 초기부터 1976년 사망할 때까지 무려 27년간 총리직을 지키며 중국의 행정과 외교를 도맡은 2인자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국의 고속 경제 성장기를 이끈 실용주의 정치가</t>
+  </si>
+  <si>
+    <t>마오쩌둥 이후 가장 강력한 1인 지배 체제를 구축한 현직 주석</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>한시</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>침대 앞 밝은 달빛을 보고</t>
+  </si>
+  <si>
+    <t>서리인 줄 알았네</t>
+  </si>
+  <si>
+    <t>고개 들어 달을 바라보다가</t>
+  </si>
+  <si>
+    <t>고향을 생각한다</t>
+  </si>
+  <si>
+    <t>床前明月光</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑是地上霜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>床前明月光</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疑是地上霜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>举头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>望明月</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>思故</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>乡</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低头思故乡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>举头望明月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>당나라 시인 이백(李白)\n &lt;정야사(靜夜思) - 고요한 밤의 그리움&gt;</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2491,6 +2737,323 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98471DEA-DA11-4ED3-8CC2-751E4782F2C0}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>100000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f t="shared" ref="E2:E4" si="0">B2</f>
+        <v>贵</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <f t="shared" ref="F2:F4" si="1">B2</f>
+        <v>贵</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>100001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>好吃</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>好吃</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>100002</v>
+      </c>
+      <c r="B4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="E4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>对</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>对</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>100003</v>
+      </c>
+      <c r="B5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f t="shared" ref="E5:E17" si="2">B5</f>
+        <v>错</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <f t="shared" ref="F5:F17" si="3">B5</f>
+        <v>错</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>100004</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>100005</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>100006</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>100007</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>100008</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>100009</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>100010</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>100011</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>100012</v>
+      </c>
+      <c r="E14" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>100013</v>
+      </c>
+      <c r="E15" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>100014</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>100015</v>
+      </c>
+      <c r="E17" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669360A0-5660-4C1B-A0E2-B39C4C67F52C}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -11410,7 +11973,7 @@
     <col min="4" max="4" width="42.5" customWidth="1"/>
     <col min="5" max="5" width="43.125" customWidth="1"/>
     <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="90.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="46.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11772,84 +12335,128 @@
       <c r="A16">
         <v>30129</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" t="s">
+        <v>260</v>
+      </c>
       <c r="C16" t="s">
         <v>250</v>
       </c>
-      <c r="E16" s="6">
+      <c r="D16" t="s">
+        <v>265</v>
+      </c>
+      <c r="E16" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
+        <v>毛泽东</v>
+      </c>
+      <c r="F16" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>毛泽东</v>
+      </c>
+      <c r="H16" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>30130</v>
       </c>
+      <c r="B17" t="s">
+        <v>262</v>
+      </c>
       <c r="C17" t="s">
         <v>250</v>
       </c>
-      <c r="E17" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E17" s="6" t="str">
+        <f>B18</f>
+        <v>邓小平</v>
+      </c>
+      <c r="F17" s="6" t="str">
+        <f>B18</f>
+        <v>邓小平</v>
+      </c>
+      <c r="H17" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>30131</v>
       </c>
+      <c r="B18" t="s">
+        <v>261</v>
+      </c>
       <c r="C18" t="s">
         <v>250</v>
       </c>
-      <c r="E18" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>268</v>
+      </c>
+      <c r="E18" s="6" t="str">
+        <f>B17</f>
+        <v>周恩来</v>
+      </c>
+      <c r="F18" s="6" t="str">
+        <f>B17</f>
+        <v>周恩来</v>
+      </c>
+      <c r="H18" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>30132</v>
       </c>
+      <c r="B19" t="s">
+        <v>263</v>
+      </c>
       <c r="C19" t="s">
         <v>250</v>
       </c>
-      <c r="E19" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>267</v>
+      </c>
+      <c r="E19" s="6" t="str">
+        <f>B18</f>
+        <v>邓小平</v>
+      </c>
+      <c r="F19" s="6" t="str">
+        <f>B18</f>
+        <v>邓小平</v>
+      </c>
+      <c r="H19" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>30133</v>
       </c>
+      <c r="B20" t="s">
+        <v>264</v>
+      </c>
       <c r="C20" t="s">
         <v>250</v>
       </c>
-      <c r="E20" s="6">
+      <c r="D20" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
+        <v>习近平</v>
+      </c>
+      <c r="F20" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>习近平</v>
+      </c>
+      <c r="H20" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>30134</v>
       </c>
@@ -11865,7 +12472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>30135</v>
       </c>
@@ -11881,7 +12488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>30136</v>
       </c>
@@ -11898,7 +12505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>30137</v>
       </c>
@@ -11915,7 +12522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>30138</v>
       </c>
@@ -11931,7 +12538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>30139</v>
       </c>
@@ -11947,7 +12554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>30140</v>
       </c>
@@ -11963,7 +12570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>30141</v>
       </c>
@@ -11979,7 +12586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>30142</v>
       </c>
@@ -11995,7 +12602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30143</v>
       </c>
@@ -12011,7 +12618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30144</v>
       </c>
@@ -12027,7 +12634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30145</v>
       </c>
@@ -15950,17 +16557,21 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98471DEA-DA11-4ED3-8CC2-751E4782F2C0}">
-  <dimension ref="A1:H17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E61A85-9E37-4DCB-B2F7-E83A50F42F3E}">
+  <dimension ref="A1:K467"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="22.875" customWidth="1"/>
-    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="25.25" customWidth="1"/>
+    <col min="3" max="3" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.5" customWidth="1"/>
+    <col min="5" max="5" width="43.125" customWidth="1"/>
     <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="71" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -15982,286 +16593,4429 @@
       <c r="G1" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J1" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>192</v>
+        <v>280</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" t="s">
+        <v>276</v>
       </c>
       <c r="E2" s="6" t="str">
-        <f t="shared" ref="E2:E4" si="0">B2</f>
-        <v>贵</v>
+        <f t="shared" ref="E2:E20" si="0">B2</f>
+        <v>床前明月光</v>
       </c>
       <c r="F2" s="6" t="str">
-        <f t="shared" ref="F2:F4" si="1">B2</f>
-        <v>贵</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" ref="F2:F20" si="1">B2</f>
+        <v>床前明月光</v>
+      </c>
+      <c r="H2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>100001</v>
+        <v>50001</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>185</v>
+        <v>281</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" t="s">
+        <v>277</v>
       </c>
       <c r="E3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>好吃</v>
+        <v>疑是地上霜</v>
       </c>
       <c r="F3" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>好吃</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>疑是地上霜</v>
+      </c>
+      <c r="H3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>100002</v>
-      </c>
-      <c r="B4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>213</v>
+        <v>50002</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" t="s">
+        <v>278</v>
       </c>
       <c r="E4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>对</v>
+        <v>举头望明月</v>
       </c>
       <c r="F4" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>对</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>举头望明月</v>
+      </c>
+      <c r="H4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>100003</v>
+        <v>50003</v>
       </c>
       <c r="B5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>215</v>
+        <v>285</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" t="s">
+        <v>279</v>
       </c>
       <c r="E5" s="6" t="str">
-        <f t="shared" ref="E5:E17" si="2">B5</f>
-        <v>错</v>
+        <f t="shared" si="0"/>
+        <v>低头思故乡</v>
       </c>
       <c r="F5" s="6" t="str">
-        <f t="shared" ref="F5:F17" si="3">B5</f>
-        <v>错</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>低头思故乡</v>
+      </c>
+      <c r="H5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>100004</v>
-      </c>
-      <c r="B6" s="6"/>
+        <v>50004</v>
+      </c>
       <c r="C6" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" s="10"/>
+        <v>275</v>
+      </c>
       <c r="E6" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F6" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>100005</v>
+        <v>50005</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="10"/>
+        <v>275</v>
+      </c>
       <c r="E7" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F7" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>100006</v>
-      </c>
-      <c r="B8" s="11"/>
+        <v>50006</v>
+      </c>
       <c r="C8" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="10"/>
+        <v>275</v>
+      </c>
       <c r="E8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F8" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>100007</v>
+        <v>50007</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="10"/>
+        <v>275</v>
+      </c>
       <c r="E9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F9" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>100008</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>184</v>
+        <v>50008</v>
       </c>
       <c r="E10" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F10" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="21"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>100009</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>184</v>
-      </c>
+        <v>50009</v>
+      </c>
+      <c r="B11" s="17"/>
       <c r="E11" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F11" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="21"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>100010</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>184</v>
-      </c>
+        <v>50010</v>
+      </c>
+      <c r="B12" s="12"/>
       <c r="E12" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F12" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="21"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>100011</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>184</v>
+        <v>50011</v>
       </c>
       <c r="E13" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>100012</v>
-      </c>
+        <v>50012</v>
+      </c>
+      <c r="B14" s="17"/>
       <c r="E14" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F14" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A15">
-        <v>100013</v>
-      </c>
+        <v>50013</v>
+      </c>
+      <c r="B15" s="18"/>
       <c r="E15" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F15" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="K15" s="19"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>100014</v>
+        <v>50014</v>
       </c>
       <c r="E16" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F16" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>100015</v>
+        <v>50015</v>
       </c>
       <c r="E17" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>50016</v>
+      </c>
+      <c r="E18" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>50017</v>
+      </c>
+      <c r="E19" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>50018</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>50019</v>
+      </c>
+      <c r="C21" t="s">
+        <v>250</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" ref="E21:E73" si="2">B21</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
+        <f t="shared" ref="F21:F73" si="3">B21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>50020</v>
+      </c>
+      <c r="C22" t="s">
+        <v>250</v>
+      </c>
+      <c r="E22" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F22" s="6">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>50021</v>
+      </c>
+      <c r="C23" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>50022</v>
+      </c>
+      <c r="C24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>50023</v>
+      </c>
+      <c r="C25" t="s">
+        <v>250</v>
+      </c>
+      <c r="E25" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>50024</v>
+      </c>
+      <c r="C26" t="s">
+        <v>250</v>
+      </c>
+      <c r="E26" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>50025</v>
+      </c>
+      <c r="C27" t="s">
+        <v>250</v>
+      </c>
+      <c r="E27" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>50026</v>
+      </c>
+      <c r="C28" t="s">
+        <v>250</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>50027</v>
+      </c>
+      <c r="C29" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>50028</v>
+      </c>
+      <c r="C30" t="s">
+        <v>250</v>
+      </c>
+      <c r="E30" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>50029</v>
+      </c>
+      <c r="C31" t="s">
+        <v>250</v>
+      </c>
+      <c r="E31" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>50030</v>
+      </c>
+      <c r="C32" t="s">
+        <v>250</v>
+      </c>
+      <c r="E32" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>50031</v>
+      </c>
+      <c r="C33" t="s">
+        <v>250</v>
+      </c>
+      <c r="E33" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>50032</v>
+      </c>
+      <c r="C34" t="s">
+        <v>250</v>
+      </c>
+      <c r="E34" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>50033</v>
+      </c>
+      <c r="C35" t="s">
+        <v>250</v>
+      </c>
+      <c r="E35" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>50034</v>
+      </c>
+      <c r="C36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E36" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>50035</v>
+      </c>
+      <c r="C37" t="s">
+        <v>250</v>
+      </c>
+      <c r="E37" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>50036</v>
+      </c>
+      <c r="C38" t="s">
+        <v>250</v>
+      </c>
+      <c r="E38" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>50037</v>
+      </c>
+      <c r="C39" t="s">
+        <v>250</v>
+      </c>
+      <c r="E39" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>50038</v>
+      </c>
+      <c r="C40" t="s">
+        <v>250</v>
+      </c>
+      <c r="E40" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>50039</v>
+      </c>
+      <c r="C41" t="s">
+        <v>250</v>
+      </c>
+      <c r="E41" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>50040</v>
+      </c>
+      <c r="C42" t="s">
+        <v>250</v>
+      </c>
+      <c r="E42" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>50041</v>
+      </c>
+      <c r="C43" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>50042</v>
+      </c>
+      <c r="C44" t="s">
+        <v>250</v>
+      </c>
+      <c r="E44" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>50043</v>
+      </c>
+      <c r="C45" t="s">
+        <v>250</v>
+      </c>
+      <c r="E45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>50044</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" t="s">
+        <v>250</v>
+      </c>
+      <c r="E46" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>50045</v>
+      </c>
+      <c r="C47" t="s">
+        <v>250</v>
+      </c>
+      <c r="E47" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>50046</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" t="s">
+        <v>250</v>
+      </c>
+      <c r="E48" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>50047</v>
+      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" t="s">
+        <v>250</v>
+      </c>
+      <c r="E49" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>50048</v>
+      </c>
+      <c r="C50" t="s">
+        <v>250</v>
+      </c>
+      <c r="E50" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50049</v>
+      </c>
+      <c r="C51" t="s">
+        <v>250</v>
+      </c>
+      <c r="E51" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>50050</v>
+      </c>
+      <c r="B52" s="12"/>
+      <c r="C52" t="s">
+        <v>250</v>
+      </c>
+      <c r="E52" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>50051</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" t="s">
+        <v>250</v>
+      </c>
+      <c r="E53" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>50052</v>
+      </c>
+      <c r="B54" s="12"/>
+      <c r="C54" t="s">
+        <v>250</v>
+      </c>
+      <c r="E54" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>50053</v>
+      </c>
+      <c r="B55" s="12"/>
+      <c r="C55" t="s">
+        <v>250</v>
+      </c>
+      <c r="E55" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>50054</v>
+      </c>
+      <c r="B56" s="12"/>
+      <c r="C56" t="s">
+        <v>250</v>
+      </c>
+      <c r="E56" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>50055</v>
+      </c>
+      <c r="C57" t="s">
+        <v>250</v>
+      </c>
+      <c r="E57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>50056</v>
+      </c>
+      <c r="B58" s="12"/>
+      <c r="C58" t="s">
+        <v>250</v>
+      </c>
+      <c r="E58" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>50057</v>
+      </c>
+      <c r="C59" t="s">
+        <v>250</v>
+      </c>
+      <c r="E59" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F59" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>50058</v>
+      </c>
+      <c r="C60" t="s">
+        <v>250</v>
+      </c>
+      <c r="E60" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F60" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>50059</v>
+      </c>
+      <c r="C61" t="s">
+        <v>250</v>
+      </c>
+      <c r="E61" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>50060</v>
+      </c>
+      <c r="C62" t="s">
+        <v>250</v>
+      </c>
+      <c r="E62" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>50061</v>
+      </c>
+      <c r="C63" t="s">
+        <v>250</v>
+      </c>
+      <c r="E63" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>50062</v>
+      </c>
+      <c r="C64" t="s">
+        <v>250</v>
+      </c>
+      <c r="E64" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>50063</v>
+      </c>
+      <c r="C65" t="s">
+        <v>250</v>
+      </c>
+      <c r="E65" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>50064</v>
+      </c>
+      <c r="C66" t="s">
+        <v>250</v>
+      </c>
+      <c r="E66" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F66" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>50065</v>
+      </c>
+      <c r="C67" t="s">
+        <v>250</v>
+      </c>
+      <c r="E67" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F67" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>50066</v>
+      </c>
+      <c r="C68" t="s">
+        <v>250</v>
+      </c>
+      <c r="E68" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>50067</v>
+      </c>
+      <c r="C69" t="s">
+        <v>250</v>
+      </c>
+      <c r="E69" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>50068</v>
+      </c>
+      <c r="C70" t="s">
+        <v>250</v>
+      </c>
+      <c r="E70" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>50069</v>
+      </c>
+      <c r="B71" s="12"/>
+      <c r="C71" t="s">
+        <v>250</v>
+      </c>
+      <c r="E71" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F71" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>50070</v>
+      </c>
+      <c r="C72" t="s">
+        <v>250</v>
+      </c>
+      <c r="E72" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F72" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>50071</v>
+      </c>
+      <c r="C73" t="s">
+        <v>250</v>
+      </c>
+      <c r="E73" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>50072</v>
+      </c>
+      <c r="C74" t="s">
+        <v>250</v>
+      </c>
+      <c r="E74" s="6">
+        <f t="shared" ref="E74:E137" si="4">B74</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="6">
+        <f t="shared" ref="F74:F137" si="5">B74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>50073</v>
+      </c>
+      <c r="C75" t="s">
+        <v>250</v>
+      </c>
+      <c r="E75" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>50074</v>
+      </c>
+      <c r="C76" t="s">
+        <v>250</v>
+      </c>
+      <c r="E76" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>50075</v>
+      </c>
+      <c r="C77" t="s">
+        <v>250</v>
+      </c>
+      <c r="E77" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F77" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>50076</v>
+      </c>
+      <c r="C78" t="s">
+        <v>250</v>
+      </c>
+      <c r="E78" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F78" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>50077</v>
+      </c>
+      <c r="C79" t="s">
+        <v>250</v>
+      </c>
+      <c r="E79" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F79" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>50078</v>
+      </c>
+      <c r="C80" t="s">
+        <v>250</v>
+      </c>
+      <c r="E80" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>50079</v>
+      </c>
+      <c r="C81" t="s">
+        <v>250</v>
+      </c>
+      <c r="E81" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>50080</v>
+      </c>
+      <c r="C82" t="s">
+        <v>250</v>
+      </c>
+      <c r="E82" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>50081</v>
+      </c>
+      <c r="C83" t="s">
+        <v>250</v>
+      </c>
+      <c r="E83" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>50082</v>
+      </c>
+      <c r="C84" t="s">
+        <v>250</v>
+      </c>
+      <c r="E84" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>50083</v>
+      </c>
+      <c r="C85" t="s">
+        <v>250</v>
+      </c>
+      <c r="E85" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>50084</v>
+      </c>
+      <c r="C86" t="s">
+        <v>250</v>
+      </c>
+      <c r="E86" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F86" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>50085</v>
+      </c>
+      <c r="C87" t="s">
+        <v>250</v>
+      </c>
+      <c r="E87" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F87" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>50086</v>
+      </c>
+      <c r="C88" t="s">
+        <v>250</v>
+      </c>
+      <c r="E88" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>50087</v>
+      </c>
+      <c r="C89" t="s">
+        <v>250</v>
+      </c>
+      <c r="E89" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F89" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>50088</v>
+      </c>
+      <c r="C90" t="s">
+        <v>250</v>
+      </c>
+      <c r="E90" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F90" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>50089</v>
+      </c>
+      <c r="C91" t="s">
+        <v>250</v>
+      </c>
+      <c r="E91" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F91" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>50090</v>
+      </c>
+      <c r="C92" t="s">
+        <v>250</v>
+      </c>
+      <c r="E92" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F92" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>50091</v>
+      </c>
+      <c r="C93" t="s">
+        <v>250</v>
+      </c>
+      <c r="E93" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F93" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>50092</v>
+      </c>
+      <c r="C94" t="s">
+        <v>250</v>
+      </c>
+      <c r="E94" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>50093</v>
+      </c>
+      <c r="C95" t="s">
+        <v>250</v>
+      </c>
+      <c r="E95" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>50094</v>
+      </c>
+      <c r="C96" t="s">
+        <v>250</v>
+      </c>
+      <c r="E96" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F96" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>50095</v>
+      </c>
+      <c r="C97" t="s">
+        <v>250</v>
+      </c>
+      <c r="E97" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F97" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>50096</v>
+      </c>
+      <c r="C98" t="s">
+        <v>250</v>
+      </c>
+      <c r="E98" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F98" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>50097</v>
+      </c>
+      <c r="C99" t="s">
+        <v>250</v>
+      </c>
+      <c r="E99" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F99" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>50098</v>
+      </c>
+      <c r="C100" t="s">
+        <v>250</v>
+      </c>
+      <c r="E100" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F100" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>50099</v>
+      </c>
+      <c r="C101" t="s">
+        <v>250</v>
+      </c>
+      <c r="E101" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F101" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>50100</v>
+      </c>
+      <c r="C102" t="s">
+        <v>250</v>
+      </c>
+      <c r="E102" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F102" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>50101</v>
+      </c>
+      <c r="C103" t="s">
+        <v>250</v>
+      </c>
+      <c r="E103" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>50102</v>
+      </c>
+      <c r="C104" t="s">
+        <v>250</v>
+      </c>
+      <c r="E104" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F104" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>50103</v>
+      </c>
+      <c r="C105" t="s">
+        <v>250</v>
+      </c>
+      <c r="E105" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>50104</v>
+      </c>
+      <c r="C106" t="s">
+        <v>250</v>
+      </c>
+      <c r="E106" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F106" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>50105</v>
+      </c>
+      <c r="C107" t="s">
+        <v>250</v>
+      </c>
+      <c r="E107" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F107" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>50106</v>
+      </c>
+      <c r="C108" t="s">
+        <v>250</v>
+      </c>
+      <c r="E108" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F108" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>50107</v>
+      </c>
+      <c r="C109" t="s">
+        <v>250</v>
+      </c>
+      <c r="E109" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F109" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>50108</v>
+      </c>
+      <c r="C110" t="s">
+        <v>250</v>
+      </c>
+      <c r="E110" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F110" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>50109</v>
+      </c>
+      <c r="C111" t="s">
+        <v>250</v>
+      </c>
+      <c r="E111" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F111" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>50110</v>
+      </c>
+      <c r="C112" t="s">
+        <v>250</v>
+      </c>
+      <c r="E112" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F112" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>50111</v>
+      </c>
+      <c r="C113" t="s">
+        <v>250</v>
+      </c>
+      <c r="E113" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F113" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>50112</v>
+      </c>
+      <c r="C114" t="s">
+        <v>250</v>
+      </c>
+      <c r="E114" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F114" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>50113</v>
+      </c>
+      <c r="C115" t="s">
+        <v>250</v>
+      </c>
+      <c r="E115" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F115" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>50114</v>
+      </c>
+      <c r="C116" t="s">
+        <v>250</v>
+      </c>
+      <c r="E116" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F116" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>50115</v>
+      </c>
+      <c r="C117" t="s">
+        <v>250</v>
+      </c>
+      <c r="E117" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F117" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>50116</v>
+      </c>
+      <c r="C118" t="s">
+        <v>250</v>
+      </c>
+      <c r="E118" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F118" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>50117</v>
+      </c>
+      <c r="C119" t="s">
+        <v>250</v>
+      </c>
+      <c r="E119" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F119" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>50118</v>
+      </c>
+      <c r="C120" t="s">
+        <v>250</v>
+      </c>
+      <c r="E120" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F120" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>50119</v>
+      </c>
+      <c r="C121" t="s">
+        <v>250</v>
+      </c>
+      <c r="E121" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F121" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>50120</v>
+      </c>
+      <c r="C122" t="s">
+        <v>250</v>
+      </c>
+      <c r="E122" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F122" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>50121</v>
+      </c>
+      <c r="C123" t="s">
+        <v>250</v>
+      </c>
+      <c r="E123" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F123" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>50122</v>
+      </c>
+      <c r="C124" t="s">
+        <v>250</v>
+      </c>
+      <c r="E124" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F124" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>50123</v>
+      </c>
+      <c r="C125" t="s">
+        <v>250</v>
+      </c>
+      <c r="E125" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F125" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>50124</v>
+      </c>
+      <c r="C126" t="s">
+        <v>250</v>
+      </c>
+      <c r="E126" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F126" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>50125</v>
+      </c>
+      <c r="C127" t="s">
+        <v>250</v>
+      </c>
+      <c r="E127" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F127" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>50126</v>
+      </c>
+      <c r="C128" t="s">
+        <v>250</v>
+      </c>
+      <c r="E128" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F128" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>50127</v>
+      </c>
+      <c r="C129" t="s">
+        <v>250</v>
+      </c>
+      <c r="E129" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F129" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>50128</v>
+      </c>
+      <c r="C130" t="s">
+        <v>250</v>
+      </c>
+      <c r="E130" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F130" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>50129</v>
+      </c>
+      <c r="C131" t="s">
+        <v>250</v>
+      </c>
+      <c r="E131" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F131" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>50130</v>
+      </c>
+      <c r="C132" t="s">
+        <v>250</v>
+      </c>
+      <c r="E132" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F132" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>50131</v>
+      </c>
+      <c r="C133" t="s">
+        <v>250</v>
+      </c>
+      <c r="E133" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F133" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>50132</v>
+      </c>
+      <c r="C134" t="s">
+        <v>250</v>
+      </c>
+      <c r="E134" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F134" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>50133</v>
+      </c>
+      <c r="C135" t="s">
+        <v>250</v>
+      </c>
+      <c r="E135" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F135" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>50134</v>
+      </c>
+      <c r="C136" t="s">
+        <v>250</v>
+      </c>
+      <c r="E136" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F136" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>50135</v>
+      </c>
+      <c r="C137" t="s">
+        <v>250</v>
+      </c>
+      <c r="E137" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F137" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>50136</v>
+      </c>
+      <c r="C138" t="s">
+        <v>250</v>
+      </c>
+      <c r="E138" s="6">
+        <f t="shared" ref="E138:E201" si="6">B138</f>
+        <v>0</v>
+      </c>
+      <c r="F138" s="6">
+        <f t="shared" ref="F138:F201" si="7">B138</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>50137</v>
+      </c>
+      <c r="C139" t="s">
+        <v>250</v>
+      </c>
+      <c r="E139" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F139" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>50138</v>
+      </c>
+      <c r="C140" t="s">
+        <v>250</v>
+      </c>
+      <c r="E140" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F140" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>50139</v>
+      </c>
+      <c r="C141" t="s">
+        <v>250</v>
+      </c>
+      <c r="E141" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F141" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>50140</v>
+      </c>
+      <c r="C142" t="s">
+        <v>250</v>
+      </c>
+      <c r="E142" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F142" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>50141</v>
+      </c>
+      <c r="C143" t="s">
+        <v>250</v>
+      </c>
+      <c r="E143" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F143" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>50142</v>
+      </c>
+      <c r="C144" t="s">
+        <v>250</v>
+      </c>
+      <c r="E144" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F144" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>50143</v>
+      </c>
+      <c r="C145" t="s">
+        <v>250</v>
+      </c>
+      <c r="E145" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F145" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>50144</v>
+      </c>
+      <c r="C146" t="s">
+        <v>250</v>
+      </c>
+      <c r="E146" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F146" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>50145</v>
+      </c>
+      <c r="C147" t="s">
+        <v>250</v>
+      </c>
+      <c r="E147" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F147" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>50146</v>
+      </c>
+      <c r="C148" t="s">
+        <v>250</v>
+      </c>
+      <c r="E148" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F148" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>50147</v>
+      </c>
+      <c r="C149" t="s">
+        <v>250</v>
+      </c>
+      <c r="E149" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F149" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>50148</v>
+      </c>
+      <c r="C150" t="s">
+        <v>250</v>
+      </c>
+      <c r="E150" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F150" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>50149</v>
+      </c>
+      <c r="C151" t="s">
+        <v>250</v>
+      </c>
+      <c r="E151" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F151" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>50150</v>
+      </c>
+      <c r="C152" t="s">
+        <v>250</v>
+      </c>
+      <c r="E152" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F152" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>50151</v>
+      </c>
+      <c r="C153" t="s">
+        <v>250</v>
+      </c>
+      <c r="E153" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F153" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>50152</v>
+      </c>
+      <c r="C154" t="s">
+        <v>250</v>
+      </c>
+      <c r="E154" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F154" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>50153</v>
+      </c>
+      <c r="C155" t="s">
+        <v>250</v>
+      </c>
+      <c r="E155" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F155" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>50154</v>
+      </c>
+      <c r="C156" t="s">
+        <v>250</v>
+      </c>
+      <c r="E156" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F156" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>50155</v>
+      </c>
+      <c r="C157" t="s">
+        <v>250</v>
+      </c>
+      <c r="E157" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F157" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>50156</v>
+      </c>
+      <c r="C158" t="s">
+        <v>250</v>
+      </c>
+      <c r="E158" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F158" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>50157</v>
+      </c>
+      <c r="C159" t="s">
+        <v>250</v>
+      </c>
+      <c r="E159" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F159" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>50158</v>
+      </c>
+      <c r="C160" t="s">
+        <v>250</v>
+      </c>
+      <c r="E160" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F160" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>50159</v>
+      </c>
+      <c r="C161" t="s">
+        <v>250</v>
+      </c>
+      <c r="E161" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F161" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>50160</v>
+      </c>
+      <c r="C162" t="s">
+        <v>250</v>
+      </c>
+      <c r="E162" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F162" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>50161</v>
+      </c>
+      <c r="C163" t="s">
+        <v>250</v>
+      </c>
+      <c r="E163" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F163" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>50162</v>
+      </c>
+      <c r="C164" t="s">
+        <v>250</v>
+      </c>
+      <c r="E164" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F164" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>50163</v>
+      </c>
+      <c r="C165" t="s">
+        <v>250</v>
+      </c>
+      <c r="E165" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F165" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>50164</v>
+      </c>
+      <c r="C166" t="s">
+        <v>250</v>
+      </c>
+      <c r="E166" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F166" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>50165</v>
+      </c>
+      <c r="C167" t="s">
+        <v>250</v>
+      </c>
+      <c r="E167" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F167" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>50166</v>
+      </c>
+      <c r="C168" t="s">
+        <v>250</v>
+      </c>
+      <c r="E168" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F168" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>50167</v>
+      </c>
+      <c r="C169" t="s">
+        <v>250</v>
+      </c>
+      <c r="E169" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F169" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>50168</v>
+      </c>
+      <c r="C170" t="s">
+        <v>250</v>
+      </c>
+      <c r="E170" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F170" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>50169</v>
+      </c>
+      <c r="C171" t="s">
+        <v>250</v>
+      </c>
+      <c r="E171" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F171" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>50170</v>
+      </c>
+      <c r="C172" t="s">
+        <v>250</v>
+      </c>
+      <c r="E172" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F172" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>50171</v>
+      </c>
+      <c r="C173" t="s">
+        <v>250</v>
+      </c>
+      <c r="E173" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F173" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>50172</v>
+      </c>
+      <c r="C174" t="s">
+        <v>250</v>
+      </c>
+      <c r="E174" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F174" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>50173</v>
+      </c>
+      <c r="C175" t="s">
+        <v>250</v>
+      </c>
+      <c r="E175" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F175" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>50174</v>
+      </c>
+      <c r="C176" t="s">
+        <v>250</v>
+      </c>
+      <c r="E176" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F176" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>50175</v>
+      </c>
+      <c r="C177" t="s">
+        <v>250</v>
+      </c>
+      <c r="E177" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F177" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>50176</v>
+      </c>
+      <c r="C178" t="s">
+        <v>250</v>
+      </c>
+      <c r="E178" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F178" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>50177</v>
+      </c>
+      <c r="C179" t="s">
+        <v>250</v>
+      </c>
+      <c r="E179" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F179" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>50178</v>
+      </c>
+      <c r="C180" t="s">
+        <v>250</v>
+      </c>
+      <c r="E180" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F180" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>50179</v>
+      </c>
+      <c r="C181" t="s">
+        <v>250</v>
+      </c>
+      <c r="E181" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F181" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>50180</v>
+      </c>
+      <c r="C182" t="s">
+        <v>250</v>
+      </c>
+      <c r="E182" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F182" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>50181</v>
+      </c>
+      <c r="C183" t="s">
+        <v>250</v>
+      </c>
+      <c r="E183" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F183" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>50182</v>
+      </c>
+      <c r="C184" t="s">
+        <v>250</v>
+      </c>
+      <c r="E184" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F184" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>50183</v>
+      </c>
+      <c r="C185" t="s">
+        <v>250</v>
+      </c>
+      <c r="E185" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F185" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>50184</v>
+      </c>
+      <c r="C186" t="s">
+        <v>250</v>
+      </c>
+      <c r="E186" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F186" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>50185</v>
+      </c>
+      <c r="C187" t="s">
+        <v>250</v>
+      </c>
+      <c r="E187" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F187" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>50186</v>
+      </c>
+      <c r="C188" t="s">
+        <v>250</v>
+      </c>
+      <c r="E188" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F188" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>50187</v>
+      </c>
+      <c r="C189" t="s">
+        <v>250</v>
+      </c>
+      <c r="E189" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F189" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>50188</v>
+      </c>
+      <c r="C190" t="s">
+        <v>250</v>
+      </c>
+      <c r="E190" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F190" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>50189</v>
+      </c>
+      <c r="C191" t="s">
+        <v>250</v>
+      </c>
+      <c r="E191" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F191" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>50190</v>
+      </c>
+      <c r="C192" t="s">
+        <v>250</v>
+      </c>
+      <c r="E192" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F192" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>50191</v>
+      </c>
+      <c r="C193" t="s">
+        <v>250</v>
+      </c>
+      <c r="E193" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F193" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>50192</v>
+      </c>
+      <c r="C194" t="s">
+        <v>250</v>
+      </c>
+      <c r="E194" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F194" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>50193</v>
+      </c>
+      <c r="C195" t="s">
+        <v>250</v>
+      </c>
+      <c r="E195" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F195" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>50194</v>
+      </c>
+      <c r="C196" t="s">
+        <v>250</v>
+      </c>
+      <c r="E196" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F196" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>50195</v>
+      </c>
+      <c r="C197" t="s">
+        <v>250</v>
+      </c>
+      <c r="E197" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F197" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>50196</v>
+      </c>
+      <c r="C198" t="s">
+        <v>250</v>
+      </c>
+      <c r="E198" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F198" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>50197</v>
+      </c>
+      <c r="C199" t="s">
+        <v>250</v>
+      </c>
+      <c r="E199" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F199" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>50198</v>
+      </c>
+      <c r="C200" t="s">
+        <v>250</v>
+      </c>
+      <c r="E200" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F200" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>50199</v>
+      </c>
+      <c r="C201" t="s">
+        <v>250</v>
+      </c>
+      <c r="E201" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F201" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>50200</v>
+      </c>
+      <c r="C202" t="s">
+        <v>250</v>
+      </c>
+      <c r="E202" s="6">
+        <f t="shared" ref="E202:E210" si="8">B202</f>
+        <v>0</v>
+      </c>
+      <c r="F202" s="6">
+        <f t="shared" ref="F202:F210" si="9">B202</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>50201</v>
+      </c>
+      <c r="C203" t="s">
+        <v>250</v>
+      </c>
+      <c r="E203" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F203" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>50202</v>
+      </c>
+      <c r="C204" t="s">
+        <v>250</v>
+      </c>
+      <c r="E204" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F204" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>50203</v>
+      </c>
+      <c r="C205" t="s">
+        <v>250</v>
+      </c>
+      <c r="E205" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F205" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>50204</v>
+      </c>
+      <c r="C206" t="s">
+        <v>250</v>
+      </c>
+      <c r="E206" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F206" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>50205</v>
+      </c>
+      <c r="C207" t="s">
+        <v>250</v>
+      </c>
+      <c r="E207" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F207" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>50206</v>
+      </c>
+      <c r="C208" t="s">
+        <v>250</v>
+      </c>
+      <c r="E208" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F208" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>50207</v>
+      </c>
+      <c r="C209" t="s">
+        <v>250</v>
+      </c>
+      <c r="E209" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F209" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>50208</v>
+      </c>
+      <c r="C210" t="s">
+        <v>250</v>
+      </c>
+      <c r="E210" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F210" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E211" s="6"/>
+      <c r="F211" s="6"/>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E212" s="6"/>
+      <c r="F212" s="6"/>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E213" s="6"/>
+      <c r="F213" s="6"/>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E214" s="6"/>
+      <c r="F214" s="6"/>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E215" s="6"/>
+      <c r="F215" s="6"/>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E216" s="6"/>
+      <c r="F216" s="6"/>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E217" s="6"/>
+      <c r="F217" s="6"/>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E218" s="6"/>
+      <c r="F218" s="6"/>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E219" s="6"/>
+      <c r="F219" s="6"/>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E220" s="6"/>
+      <c r="F220" s="6"/>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E221" s="6"/>
+      <c r="F221" s="6"/>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E222" s="6"/>
+      <c r="F222" s="6"/>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E223" s="6"/>
+      <c r="F223" s="6"/>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E224" s="6"/>
+      <c r="F224" s="6"/>
+    </row>
+    <row r="225" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E225" s="6"/>
+      <c r="F225" s="6"/>
+    </row>
+    <row r="226" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E226" s="6"/>
+      <c r="F226" s="6"/>
+    </row>
+    <row r="227" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E227" s="6"/>
+      <c r="F227" s="6"/>
+    </row>
+    <row r="228" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E228" s="6"/>
+      <c r="F228" s="6"/>
+    </row>
+    <row r="229" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E229" s="6"/>
+      <c r="F229" s="6"/>
+    </row>
+    <row r="230" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E230" s="6"/>
+      <c r="F230" s="6"/>
+    </row>
+    <row r="231" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E231" s="6"/>
+      <c r="F231" s="6"/>
+    </row>
+    <row r="232" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E232" s="6"/>
+      <c r="F232" s="6"/>
+    </row>
+    <row r="233" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E233" s="6"/>
+      <c r="F233" s="6"/>
+    </row>
+    <row r="234" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E234" s="6"/>
+      <c r="F234" s="6"/>
+    </row>
+    <row r="235" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E235" s="6"/>
+      <c r="F235" s="6"/>
+    </row>
+    <row r="236" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E236" s="6"/>
+      <c r="F236" s="6"/>
+    </row>
+    <row r="237" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E237" s="6"/>
+      <c r="F237" s="6"/>
+    </row>
+    <row r="238" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E238" s="6"/>
+      <c r="F238" s="6"/>
+    </row>
+    <row r="239" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E239" s="6"/>
+      <c r="F239" s="6"/>
+    </row>
+    <row r="240" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E240" s="6"/>
+      <c r="F240" s="6"/>
+    </row>
+    <row r="241" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E241" s="6"/>
+      <c r="F241" s="6"/>
+    </row>
+    <row r="242" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E242" s="6"/>
+      <c r="F242" s="6"/>
+    </row>
+    <row r="243" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E243" s="6"/>
+      <c r="F243" s="6"/>
+    </row>
+    <row r="244" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E244" s="6"/>
+      <c r="F244" s="6"/>
+    </row>
+    <row r="245" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E245" s="6"/>
+      <c r="F245" s="6"/>
+    </row>
+    <row r="246" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E246" s="6"/>
+      <c r="F246" s="6"/>
+    </row>
+    <row r="247" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E247" s="6"/>
+      <c r="F247" s="6"/>
+    </row>
+    <row r="248" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E248" s="6"/>
+      <c r="F248" s="6"/>
+    </row>
+    <row r="249" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E249" s="6"/>
+      <c r="F249" s="6"/>
+    </row>
+    <row r="250" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E250" s="6"/>
+      <c r="F250" s="6"/>
+    </row>
+    <row r="251" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E251" s="6"/>
+      <c r="F251" s="6"/>
+    </row>
+    <row r="252" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E252" s="6"/>
+      <c r="F252" s="6"/>
+    </row>
+    <row r="253" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E253" s="6"/>
+      <c r="F253" s="6"/>
+    </row>
+    <row r="254" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E254" s="6"/>
+      <c r="F254" s="6"/>
+    </row>
+    <row r="255" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E255" s="6"/>
+      <c r="F255" s="6"/>
+    </row>
+    <row r="256" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E256" s="6"/>
+      <c r="F256" s="6"/>
+    </row>
+    <row r="257" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E257" s="6"/>
+      <c r="F257" s="6"/>
+    </row>
+    <row r="258" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E258" s="6"/>
+      <c r="F258" s="6"/>
+    </row>
+    <row r="259" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E259" s="6"/>
+      <c r="F259" s="6"/>
+    </row>
+    <row r="260" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E260" s="6"/>
+      <c r="F260" s="6"/>
+    </row>
+    <row r="261" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E261" s="6"/>
+      <c r="F261" s="6"/>
+    </row>
+    <row r="262" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E262" s="6"/>
+      <c r="F262" s="6"/>
+    </row>
+    <row r="263" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E263" s="6"/>
+      <c r="F263" s="6"/>
+    </row>
+    <row r="264" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E264" s="6"/>
+      <c r="F264" s="6"/>
+    </row>
+    <row r="265" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E265" s="6"/>
+      <c r="F265" s="6"/>
+    </row>
+    <row r="266" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E266" s="6"/>
+      <c r="F266" s="6"/>
+    </row>
+    <row r="267" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E267" s="6"/>
+      <c r="F267" s="6"/>
+    </row>
+    <row r="268" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E268" s="6"/>
+      <c r="F268" s="6"/>
+    </row>
+    <row r="269" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E269" s="6"/>
+      <c r="F269" s="6"/>
+    </row>
+    <row r="270" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E270" s="6"/>
+      <c r="F270" s="6"/>
+    </row>
+    <row r="271" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E271" s="6"/>
+      <c r="F271" s="6"/>
+    </row>
+    <row r="272" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E272" s="6"/>
+      <c r="F272" s="6"/>
+    </row>
+    <row r="273" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E273" s="6"/>
+      <c r="F273" s="6"/>
+    </row>
+    <row r="274" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E274" s="6"/>
+      <c r="F274" s="6"/>
+    </row>
+    <row r="275" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E275" s="6"/>
+      <c r="F275" s="6"/>
+    </row>
+    <row r="276" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E276" s="6"/>
+      <c r="F276" s="6"/>
+    </row>
+    <row r="277" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E277" s="6"/>
+      <c r="F277" s="6"/>
+    </row>
+    <row r="278" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E278" s="6"/>
+      <c r="F278" s="6"/>
+    </row>
+    <row r="279" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E279" s="6"/>
+      <c r="F279" s="6"/>
+    </row>
+    <row r="280" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E280" s="6"/>
+      <c r="F280" s="6"/>
+    </row>
+    <row r="281" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E281" s="6"/>
+      <c r="F281" s="6"/>
+    </row>
+    <row r="282" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E282" s="6"/>
+      <c r="F282" s="6"/>
+    </row>
+    <row r="283" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E283" s="6"/>
+      <c r="F283" s="6"/>
+    </row>
+    <row r="284" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E284" s="6"/>
+      <c r="F284" s="6"/>
+    </row>
+    <row r="285" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E285" s="6"/>
+      <c r="F285" s="6"/>
+    </row>
+    <row r="286" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E286" s="6"/>
+      <c r="F286" s="6"/>
+    </row>
+    <row r="287" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E287" s="6"/>
+      <c r="F287" s="6"/>
+    </row>
+    <row r="288" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E288" s="6"/>
+      <c r="F288" s="6"/>
+    </row>
+    <row r="289" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E289" s="6"/>
+      <c r="F289" s="6"/>
+    </row>
+    <row r="290" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E290" s="6"/>
+      <c r="F290" s="6"/>
+    </row>
+    <row r="291" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E291" s="6"/>
+      <c r="F291" s="6"/>
+    </row>
+    <row r="292" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E292" s="6"/>
+      <c r="F292" s="6"/>
+    </row>
+    <row r="293" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E293" s="6"/>
+      <c r="F293" s="6"/>
+    </row>
+    <row r="294" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E294" s="6"/>
+      <c r="F294" s="6"/>
+    </row>
+    <row r="295" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E295" s="6"/>
+      <c r="F295" s="6"/>
+    </row>
+    <row r="296" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E296" s="6"/>
+      <c r="F296" s="6"/>
+    </row>
+    <row r="297" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E297" s="6"/>
+      <c r="F297" s="6"/>
+    </row>
+    <row r="298" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E298" s="6"/>
+      <c r="F298" s="6"/>
+    </row>
+    <row r="299" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E299" s="6"/>
+      <c r="F299" s="6"/>
+    </row>
+    <row r="300" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E300" s="6"/>
+      <c r="F300" s="6"/>
+    </row>
+    <row r="301" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E301" s="6"/>
+      <c r="F301" s="6"/>
+    </row>
+    <row r="302" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E302" s="6"/>
+      <c r="F302" s="6"/>
+    </row>
+    <row r="303" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E303" s="6"/>
+      <c r="F303" s="6"/>
+    </row>
+    <row r="304" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E304" s="6"/>
+      <c r="F304" s="6"/>
+    </row>
+    <row r="305" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E305" s="6"/>
+      <c r="F305" s="6"/>
+    </row>
+    <row r="306" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E306" s="6"/>
+      <c r="F306" s="6"/>
+    </row>
+    <row r="307" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E307" s="6"/>
+      <c r="F307" s="6"/>
+    </row>
+    <row r="308" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E308" s="6"/>
+      <c r="F308" s="6"/>
+    </row>
+    <row r="309" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E309" s="6"/>
+      <c r="F309" s="6"/>
+    </row>
+    <row r="310" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E310" s="6"/>
+      <c r="F310" s="6"/>
+    </row>
+    <row r="311" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E311" s="6"/>
+      <c r="F311" s="6"/>
+    </row>
+    <row r="312" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E312" s="6"/>
+      <c r="F312" s="6"/>
+    </row>
+    <row r="313" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E313" s="6"/>
+      <c r="F313" s="6"/>
+    </row>
+    <row r="314" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E314" s="6"/>
+      <c r="F314" s="6"/>
+    </row>
+    <row r="315" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E315" s="6"/>
+      <c r="F315" s="6"/>
+    </row>
+    <row r="316" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E316" s="6"/>
+      <c r="F316" s="6"/>
+    </row>
+    <row r="317" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E317" s="6"/>
+      <c r="F317" s="6"/>
+    </row>
+    <row r="318" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E318" s="6"/>
+      <c r="F318" s="6"/>
+    </row>
+    <row r="319" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E319" s="6"/>
+      <c r="F319" s="6"/>
+    </row>
+    <row r="320" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E320" s="6"/>
+      <c r="F320" s="6"/>
+    </row>
+    <row r="321" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E321" s="6"/>
+      <c r="F321" s="6"/>
+    </row>
+    <row r="322" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E322" s="6"/>
+      <c r="F322" s="6"/>
+    </row>
+    <row r="323" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E323" s="6"/>
+      <c r="F323" s="6"/>
+    </row>
+    <row r="324" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E324" s="6"/>
+      <c r="F324" s="6"/>
+    </row>
+    <row r="325" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E325" s="6"/>
+      <c r="F325" s="6"/>
+    </row>
+    <row r="326" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E326" s="6"/>
+      <c r="F326" s="6"/>
+    </row>
+    <row r="327" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E327" s="6"/>
+      <c r="F327" s="6"/>
+    </row>
+    <row r="328" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E328" s="6"/>
+      <c r="F328" s="6"/>
+    </row>
+    <row r="329" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E329" s="6"/>
+      <c r="F329" s="6"/>
+    </row>
+    <row r="330" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E330" s="6"/>
+      <c r="F330" s="6"/>
+    </row>
+    <row r="331" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E331" s="6"/>
+      <c r="F331" s="6"/>
+    </row>
+    <row r="332" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E332" s="6"/>
+      <c r="F332" s="6"/>
+    </row>
+    <row r="333" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E333" s="6"/>
+      <c r="F333" s="6"/>
+    </row>
+    <row r="334" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E334" s="6"/>
+      <c r="F334" s="6"/>
+    </row>
+    <row r="335" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E335" s="6"/>
+      <c r="F335" s="6"/>
+    </row>
+    <row r="336" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E336" s="6"/>
+      <c r="F336" s="6"/>
+    </row>
+    <row r="337" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E337" s="6"/>
+      <c r="F337" s="6"/>
+    </row>
+    <row r="338" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E338" s="6"/>
+      <c r="F338" s="6"/>
+    </row>
+    <row r="339" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E339" s="6"/>
+      <c r="F339" s="6"/>
+    </row>
+    <row r="340" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E340" s="6"/>
+      <c r="F340" s="6"/>
+    </row>
+    <row r="341" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E341" s="6"/>
+      <c r="F341" s="6"/>
+    </row>
+    <row r="342" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E342" s="6"/>
+      <c r="F342" s="6"/>
+    </row>
+    <row r="343" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E343" s="6"/>
+      <c r="F343" s="6"/>
+    </row>
+    <row r="344" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E344" s="6"/>
+      <c r="F344" s="6"/>
+    </row>
+    <row r="345" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E345" s="6"/>
+      <c r="F345" s="6"/>
+    </row>
+    <row r="346" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E346" s="6"/>
+      <c r="F346" s="6"/>
+    </row>
+    <row r="347" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E347" s="6"/>
+      <c r="F347" s="6"/>
+    </row>
+    <row r="348" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E348" s="6"/>
+      <c r="F348" s="6"/>
+    </row>
+    <row r="349" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E349" s="6"/>
+      <c r="F349" s="6"/>
+    </row>
+    <row r="350" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E350" s="6"/>
+      <c r="F350" s="6"/>
+    </row>
+    <row r="351" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E351" s="6"/>
+      <c r="F351" s="6"/>
+    </row>
+    <row r="352" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E352" s="6"/>
+      <c r="F352" s="6"/>
+    </row>
+    <row r="353" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E353" s="6"/>
+      <c r="F353" s="6"/>
+    </row>
+    <row r="354" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E354" s="6"/>
+      <c r="F354" s="6"/>
+    </row>
+    <row r="355" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E355" s="6"/>
+      <c r="F355" s="6"/>
+    </row>
+    <row r="356" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E356" s="6"/>
+      <c r="F356" s="6"/>
+    </row>
+    <row r="357" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E357" s="6"/>
+      <c r="F357" s="6"/>
+    </row>
+    <row r="358" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E358" s="6"/>
+      <c r="F358" s="6"/>
+    </row>
+    <row r="359" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E359" s="6"/>
+      <c r="F359" s="6"/>
+    </row>
+    <row r="360" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E360" s="6"/>
+      <c r="F360" s="6"/>
+    </row>
+    <row r="361" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E361" s="6"/>
+      <c r="F361" s="6"/>
+    </row>
+    <row r="362" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E362" s="6"/>
+      <c r="F362" s="6"/>
+    </row>
+    <row r="363" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E363" s="6"/>
+      <c r="F363" s="6"/>
+    </row>
+    <row r="364" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E364" s="6"/>
+      <c r="F364" s="6"/>
+    </row>
+    <row r="365" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E365" s="6"/>
+      <c r="F365" s="6"/>
+    </row>
+    <row r="366" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E366" s="6"/>
+      <c r="F366" s="6"/>
+    </row>
+    <row r="367" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E367" s="6"/>
+      <c r="F367" s="6"/>
+    </row>
+    <row r="368" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E368" s="6"/>
+      <c r="F368" s="6"/>
+    </row>
+    <row r="369" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E369" s="6"/>
+      <c r="F369" s="6"/>
+    </row>
+    <row r="370" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E370" s="6"/>
+      <c r="F370" s="6"/>
+    </row>
+    <row r="371" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E371" s="6"/>
+      <c r="F371" s="6"/>
+    </row>
+    <row r="372" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E372" s="6"/>
+      <c r="F372" s="6"/>
+    </row>
+    <row r="373" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E373" s="6"/>
+      <c r="F373" s="6"/>
+    </row>
+    <row r="374" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E374" s="6"/>
+      <c r="F374" s="6"/>
+    </row>
+    <row r="375" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E375" s="6"/>
+      <c r="F375" s="6"/>
+    </row>
+    <row r="376" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E376" s="6"/>
+      <c r="F376" s="6"/>
+    </row>
+    <row r="377" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E377" s="6"/>
+      <c r="F377" s="6"/>
+    </row>
+    <row r="378" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E378" s="6"/>
+      <c r="F378" s="6"/>
+    </row>
+    <row r="379" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E379" s="6"/>
+      <c r="F379" s="6"/>
+    </row>
+    <row r="380" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E380" s="6"/>
+      <c r="F380" s="6"/>
+    </row>
+    <row r="381" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E381" s="6"/>
+      <c r="F381" s="6"/>
+    </row>
+    <row r="382" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E382" s="6"/>
+      <c r="F382" s="6"/>
+    </row>
+    <row r="383" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E383" s="6"/>
+      <c r="F383" s="6"/>
+    </row>
+    <row r="384" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E384" s="6"/>
+      <c r="F384" s="6"/>
+    </row>
+    <row r="385" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E385" s="6"/>
+      <c r="F385" s="6"/>
+    </row>
+    <row r="386" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E386" s="6"/>
+      <c r="F386" s="6"/>
+    </row>
+    <row r="387" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E387" s="6"/>
+      <c r="F387" s="6"/>
+    </row>
+    <row r="388" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E388" s="6"/>
+      <c r="F388" s="6"/>
+    </row>
+    <row r="389" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E389" s="6"/>
+      <c r="F389" s="6"/>
+    </row>
+    <row r="390" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E390" s="6"/>
+      <c r="F390" s="6"/>
+    </row>
+    <row r="391" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E391" s="6"/>
+      <c r="F391" s="6"/>
+    </row>
+    <row r="392" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E392" s="6"/>
+      <c r="F392" s="6"/>
+    </row>
+    <row r="393" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E393" s="6"/>
+      <c r="F393" s="6"/>
+    </row>
+    <row r="394" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E394" s="6"/>
+      <c r="F394" s="6"/>
+    </row>
+    <row r="395" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E395" s="6"/>
+      <c r="F395" s="6"/>
+    </row>
+    <row r="396" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E396" s="6"/>
+      <c r="F396" s="6"/>
+    </row>
+    <row r="397" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E397" s="6"/>
+      <c r="F397" s="6"/>
+    </row>
+    <row r="398" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E398" s="6"/>
+      <c r="F398" s="6"/>
+    </row>
+    <row r="399" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E399" s="6"/>
+      <c r="F399" s="6"/>
+    </row>
+    <row r="400" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E400" s="6"/>
+      <c r="F400" s="6"/>
+    </row>
+    <row r="401" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E401" s="6"/>
+      <c r="F401" s="6"/>
+    </row>
+    <row r="402" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E402" s="6"/>
+      <c r="F402" s="6"/>
+    </row>
+    <row r="403" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E403" s="6"/>
+      <c r="F403" s="6"/>
+    </row>
+    <row r="404" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E404" s="6"/>
+      <c r="F404" s="6"/>
+    </row>
+    <row r="405" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E405" s="6"/>
+      <c r="F405" s="6"/>
+    </row>
+    <row r="406" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E406" s="6"/>
+      <c r="F406" s="6"/>
+    </row>
+    <row r="407" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E407" s="6"/>
+      <c r="F407" s="6"/>
+    </row>
+    <row r="408" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E408" s="6"/>
+      <c r="F408" s="6"/>
+    </row>
+    <row r="409" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E409" s="6"/>
+      <c r="F409" s="6"/>
+    </row>
+    <row r="410" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E410" s="6"/>
+      <c r="F410" s="6"/>
+    </row>
+    <row r="411" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E411" s="6"/>
+      <c r="F411" s="6"/>
+    </row>
+    <row r="412" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E412" s="6"/>
+      <c r="F412" s="6"/>
+    </row>
+    <row r="413" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E413" s="6"/>
+      <c r="F413" s="6"/>
+    </row>
+    <row r="414" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E414" s="6"/>
+      <c r="F414" s="6"/>
+    </row>
+    <row r="415" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E415" s="6"/>
+      <c r="F415" s="6"/>
+    </row>
+    <row r="416" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E416" s="6"/>
+      <c r="F416" s="6"/>
+    </row>
+    <row r="417" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E417" s="6"/>
+      <c r="F417" s="6"/>
+    </row>
+    <row r="418" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E418" s="6"/>
+      <c r="F418" s="6"/>
+    </row>
+    <row r="419" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E419" s="6"/>
+      <c r="F419" s="6"/>
+    </row>
+    <row r="420" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E420" s="6"/>
+      <c r="F420" s="6"/>
+    </row>
+    <row r="421" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E421" s="6"/>
+      <c r="F421" s="6"/>
+    </row>
+    <row r="422" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E422" s="6"/>
+      <c r="F422" s="6"/>
+    </row>
+    <row r="423" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E423" s="6"/>
+      <c r="F423" s="6"/>
+    </row>
+    <row r="424" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E424" s="6"/>
+      <c r="F424" s="6"/>
+    </row>
+    <row r="425" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E425" s="6"/>
+      <c r="F425" s="6"/>
+    </row>
+    <row r="426" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E426" s="6"/>
+      <c r="F426" s="6"/>
+    </row>
+    <row r="427" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E427" s="6"/>
+      <c r="F427" s="6"/>
+    </row>
+    <row r="428" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E428" s="6"/>
+      <c r="F428" s="6"/>
+    </row>
+    <row r="429" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E429" s="6"/>
+      <c r="F429" s="6"/>
+    </row>
+    <row r="430" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E430" s="6"/>
+      <c r="F430" s="6"/>
+    </row>
+    <row r="431" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E431" s="6"/>
+      <c r="F431" s="6"/>
+    </row>
+    <row r="432" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E432" s="6"/>
+      <c r="F432" s="6"/>
+    </row>
+    <row r="433" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E433" s="6"/>
+      <c r="F433" s="6"/>
+    </row>
+    <row r="434" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E434" s="6"/>
+      <c r="F434" s="6"/>
+    </row>
+    <row r="435" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E435" s="6"/>
+      <c r="F435" s="6"/>
+    </row>
+    <row r="436" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E436" s="6"/>
+      <c r="F436" s="6"/>
+    </row>
+    <row r="437" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E437" s="6"/>
+      <c r="F437" s="6"/>
+    </row>
+    <row r="438" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E438" s="6"/>
+      <c r="F438" s="6"/>
+    </row>
+    <row r="439" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E439" s="6"/>
+      <c r="F439" s="6"/>
+    </row>
+    <row r="440" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E440" s="6"/>
+      <c r="F440" s="6"/>
+    </row>
+    <row r="441" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E441" s="6"/>
+      <c r="F441" s="6"/>
+    </row>
+    <row r="442" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E442" s="6"/>
+      <c r="F442" s="6"/>
+    </row>
+    <row r="443" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E443" s="6"/>
+      <c r="F443" s="6"/>
+    </row>
+    <row r="444" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E444" s="6"/>
+      <c r="F444" s="6"/>
+    </row>
+    <row r="445" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B445" s="6"/>
+      <c r="D445" s="3"/>
+      <c r="E445" s="6"/>
+      <c r="F445" s="6"/>
+    </row>
+    <row r="446" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B446" s="6"/>
+      <c r="D446" s="9"/>
+      <c r="E446" s="6"/>
+      <c r="F446" s="6"/>
+    </row>
+    <row r="447" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B447" s="6"/>
+      <c r="D447" s="9"/>
+      <c r="E447" s="6"/>
+      <c r="F447" s="6"/>
+    </row>
+    <row r="448" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D448" s="10"/>
+      <c r="E448" s="6"/>
+      <c r="F448" s="6"/>
+    </row>
+    <row r="449" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B449" s="6"/>
+      <c r="D449" s="10"/>
+      <c r="E449" s="6"/>
+      <c r="F449" s="6"/>
+    </row>
+    <row r="450" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D450" s="10"/>
+      <c r="E450" s="6"/>
+      <c r="F450" s="6"/>
+    </row>
+    <row r="451" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B451" s="11"/>
+      <c r="D451" s="10"/>
+      <c r="E451" s="6"/>
+      <c r="F451" s="6"/>
+    </row>
+    <row r="452" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D452" s="10"/>
+      <c r="E452" s="6"/>
+      <c r="F452" s="6"/>
+    </row>
+    <row r="453" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E453" s="6"/>
+      <c r="F453" s="6"/>
+    </row>
+    <row r="454" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E454" s="6"/>
+      <c r="F454" s="6"/>
+    </row>
+    <row r="455" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E455" s="6"/>
+      <c r="F455" s="6"/>
+    </row>
+    <row r="456" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E456" s="6"/>
+      <c r="F456" s="6"/>
+    </row>
+    <row r="457" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E457" s="6"/>
+      <c r="F457" s="6"/>
+    </row>
+    <row r="458" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E458" s="6"/>
+      <c r="F458" s="6"/>
+    </row>
+    <row r="459" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E459" s="6"/>
+      <c r="F459" s="6"/>
+    </row>
+    <row r="460" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E460" s="6"/>
+      <c r="F460" s="6"/>
+    </row>
+    <row r="461" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E461" s="6"/>
+      <c r="F461" s="6"/>
+    </row>
+    <row r="462" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E462" s="6"/>
+      <c r="F462" s="6"/>
+    </row>
+    <row r="463" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E463" s="6"/>
+      <c r="F463" s="6"/>
+    </row>
+    <row r="464" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E464" s="6"/>
+      <c r="F464" s="6"/>
+    </row>
+    <row r="465" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E465" s="6"/>
+      <c r="F465" s="6"/>
+    </row>
+    <row r="466" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E466" s="6"/>
+      <c r="F466" s="6"/>
+    </row>
+    <row r="467" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E467" s="6"/>
+      <c r="F467" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AAD050-C011-4F9C-B483-A7D4A8E1BE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA9041D-9CBC-4346-85F6-3782AA4E52E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15180" yWindow="5445" windowWidth="32745" windowHeight="12480" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="288">
   <si>
     <t>사과</t>
   </si>
@@ -1723,10 +1723,6 @@
       </rPr>
       <t>.mp4</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>당나라 시인 이백(李白)\n &lt;정야사(靜夜思) - 고요한 밤의 그리움&gt;</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -16568,7 +16564,7 @@
     <col min="5" max="5" width="43.125" customWidth="1"/>
     <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="71" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -16696,9 +16692,6 @@
       </c>
       <c r="H5" t="s">
         <v>286</v>
-      </c>
-      <c r="I5" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA9041D-9CBC-4346-85F6-3782AA4E52E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038E6642-70F9-4206-A439-76459D869B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15180" yWindow="5445" windowWidth="32745" windowHeight="12480" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10260" yWindow="3885" windowWidth="32745" windowHeight="12480" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -21,9 +21,11 @@
     <sheet name="동사" sheetId="3" r:id="rId6"/>
     <sheet name="명사" sheetId="1" r:id="rId7"/>
     <sheet name="고유명사" sheetId="11" r:id="rId8"/>
-    <sheet name="작업용" sheetId="12" r:id="rId9"/>
-    <sheet name="형용사" sheetId="2" r:id="rId10"/>
-    <sheet name="전치사" sheetId="8" r:id="rId11"/>
+    <sheet name="표현" sheetId="14" r:id="rId9"/>
+    <sheet name="작업용" sheetId="12" r:id="rId10"/>
+    <sheet name="형용사" sheetId="2" r:id="rId11"/>
+    <sheet name="전치사" sheetId="8" r:id="rId12"/>
+    <sheet name="부사" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="330">
   <si>
     <t>사과</t>
   </si>
@@ -1537,10 +1539,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>한시</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>침대 앞 밝은 달빛을 보고</t>
   </si>
   <si>
@@ -1725,12 +1723,348 @@
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>这样</t>
+  </si>
+  <si>
+    <t>哪样</t>
+  </si>
+  <si>
+    <t>이렇게</t>
+  </si>
+  <si>
+    <t>그렇게</t>
+  </si>
+  <si>
+    <t>어떤 식으로</t>
+  </si>
+  <si>
+    <t>헤어스타일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>型</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장원영</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지시대명사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>样</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>元英</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>高胤祯</t>
+  </si>
+  <si>
+    <t>고윤정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런 종류</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>짧은 머리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국식, 한국 스타일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>韩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>式</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这种</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>短</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수온, 물 온도</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>有点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>부사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금, 약간</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>温</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>烫</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>热</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>凉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>뜨겁다(매우 뜨거움)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>덥다(따뜻~뜨거움)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서늘하다(약간 시원함)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>춥다(차가움)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太</t>
+  </si>
+  <si>
+    <t>아주</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>了</t>
+  </si>
+  <si>
+    <t>완료를 나타냄</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>표현</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太冰了</t>
+  </si>
+  <si>
+    <r>
+      <t>太</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>了</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太 + 형용사 + 了 : 너무 뜨겁다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太 + 형용사 + 了 : 너무 차갑다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1880,6 +2214,24 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Noto Sans KR"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Noto Sans KR"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1909,7 +2261,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1950,6 +2302,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="보통" xfId="1" builtinId="28"/>
@@ -2733,6 +3087,4456 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E61A85-9E37-4DCB-B2F7-E83A50F42F3E}">
+  <dimension ref="A1:K467"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="25.25" customWidth="1"/>
+    <col min="3" max="3" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.5" customWidth="1"/>
+    <col min="5" max="5" width="43.125" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>50000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f t="shared" ref="E2:E20" si="0">B2</f>
+        <v>床前明月光</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <f t="shared" ref="F2:F20" si="1">B2</f>
+        <v>床前明月光</v>
+      </c>
+      <c r="H2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>50001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>疑是地上霜</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>疑是地上霜</v>
+      </c>
+      <c r="H3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>50002</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>举头望明月</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>举头望明月</v>
+      </c>
+      <c r="H4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>50003</v>
+      </c>
+      <c r="B5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" t="s">
+        <v>278</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>低头思故乡</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>低头思故乡</v>
+      </c>
+      <c r="H5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>50004</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="E6" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>50005</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>50006</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="E8" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>50007</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="E9" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>50008</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="21"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>50009</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="E11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="21"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>50010</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="E12" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="21"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>50011</v>
+      </c>
+      <c r="E13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>50012</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="E14" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>50013</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="E15" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="K15" s="19"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>50014</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>50015</v>
+      </c>
+      <c r="E17" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>50016</v>
+      </c>
+      <c r="E18" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>50017</v>
+      </c>
+      <c r="E19" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>50018</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>50019</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" ref="E21:E73" si="2">B21</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
+        <f t="shared" ref="F21:F73" si="3">B21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>50020</v>
+      </c>
+      <c r="C22" t="s">
+        <v>324</v>
+      </c>
+      <c r="E22" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>50021</v>
+      </c>
+      <c r="C23" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>50022</v>
+      </c>
+      <c r="C24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>50023</v>
+      </c>
+      <c r="C25" t="s">
+        <v>250</v>
+      </c>
+      <c r="E25" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>50024</v>
+      </c>
+      <c r="C26" t="s">
+        <v>250</v>
+      </c>
+      <c r="E26" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>50025</v>
+      </c>
+      <c r="C27" t="s">
+        <v>250</v>
+      </c>
+      <c r="E27" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>50026</v>
+      </c>
+      <c r="C28" t="s">
+        <v>250</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>50027</v>
+      </c>
+      <c r="C29" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>50028</v>
+      </c>
+      <c r="C30" t="s">
+        <v>250</v>
+      </c>
+      <c r="E30" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>50029</v>
+      </c>
+      <c r="C31" t="s">
+        <v>250</v>
+      </c>
+      <c r="E31" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>50030</v>
+      </c>
+      <c r="C32" t="s">
+        <v>250</v>
+      </c>
+      <c r="E32" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>50031</v>
+      </c>
+      <c r="C33" t="s">
+        <v>250</v>
+      </c>
+      <c r="E33" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>50032</v>
+      </c>
+      <c r="C34" t="s">
+        <v>250</v>
+      </c>
+      <c r="E34" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>50033</v>
+      </c>
+      <c r="C35" t="s">
+        <v>250</v>
+      </c>
+      <c r="E35" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>50034</v>
+      </c>
+      <c r="C36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E36" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>50035</v>
+      </c>
+      <c r="C37" t="s">
+        <v>250</v>
+      </c>
+      <c r="E37" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>50036</v>
+      </c>
+      <c r="C38" t="s">
+        <v>250</v>
+      </c>
+      <c r="E38" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>50037</v>
+      </c>
+      <c r="C39" t="s">
+        <v>250</v>
+      </c>
+      <c r="E39" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>50038</v>
+      </c>
+      <c r="C40" t="s">
+        <v>250</v>
+      </c>
+      <c r="E40" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>50039</v>
+      </c>
+      <c r="C41" t="s">
+        <v>250</v>
+      </c>
+      <c r="E41" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>50040</v>
+      </c>
+      <c r="C42" t="s">
+        <v>250</v>
+      </c>
+      <c r="E42" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>50041</v>
+      </c>
+      <c r="C43" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>50042</v>
+      </c>
+      <c r="C44" t="s">
+        <v>250</v>
+      </c>
+      <c r="E44" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>50043</v>
+      </c>
+      <c r="C45" t="s">
+        <v>250</v>
+      </c>
+      <c r="E45" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>50044</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" t="s">
+        <v>250</v>
+      </c>
+      <c r="E46" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>50045</v>
+      </c>
+      <c r="C47" t="s">
+        <v>250</v>
+      </c>
+      <c r="E47" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>50046</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" t="s">
+        <v>250</v>
+      </c>
+      <c r="E48" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>50047</v>
+      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" t="s">
+        <v>250</v>
+      </c>
+      <c r="E49" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>50048</v>
+      </c>
+      <c r="C50" t="s">
+        <v>250</v>
+      </c>
+      <c r="E50" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50049</v>
+      </c>
+      <c r="C51" t="s">
+        <v>250</v>
+      </c>
+      <c r="E51" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>50050</v>
+      </c>
+      <c r="B52" s="12"/>
+      <c r="C52" t="s">
+        <v>250</v>
+      </c>
+      <c r="E52" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>50051</v>
+      </c>
+      <c r="B53" s="12"/>
+      <c r="C53" t="s">
+        <v>250</v>
+      </c>
+      <c r="E53" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>50052</v>
+      </c>
+      <c r="B54" s="12"/>
+      <c r="C54" t="s">
+        <v>250</v>
+      </c>
+      <c r="E54" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>50053</v>
+      </c>
+      <c r="B55" s="12"/>
+      <c r="C55" t="s">
+        <v>250</v>
+      </c>
+      <c r="E55" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>50054</v>
+      </c>
+      <c r="B56" s="12"/>
+      <c r="C56" t="s">
+        <v>250</v>
+      </c>
+      <c r="E56" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>50055</v>
+      </c>
+      <c r="C57" t="s">
+        <v>250</v>
+      </c>
+      <c r="E57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>50056</v>
+      </c>
+      <c r="B58" s="12"/>
+      <c r="C58" t="s">
+        <v>250</v>
+      </c>
+      <c r="E58" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>50057</v>
+      </c>
+      <c r="C59" t="s">
+        <v>250</v>
+      </c>
+      <c r="E59" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F59" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>50058</v>
+      </c>
+      <c r="C60" t="s">
+        <v>250</v>
+      </c>
+      <c r="E60" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F60" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>50059</v>
+      </c>
+      <c r="C61" t="s">
+        <v>250</v>
+      </c>
+      <c r="E61" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>50060</v>
+      </c>
+      <c r="C62" t="s">
+        <v>250</v>
+      </c>
+      <c r="E62" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>50061</v>
+      </c>
+      <c r="C63" t="s">
+        <v>250</v>
+      </c>
+      <c r="E63" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>50062</v>
+      </c>
+      <c r="C64" t="s">
+        <v>250</v>
+      </c>
+      <c r="E64" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>50063</v>
+      </c>
+      <c r="C65" t="s">
+        <v>250</v>
+      </c>
+      <c r="E65" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F65" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>50064</v>
+      </c>
+      <c r="C66" t="s">
+        <v>250</v>
+      </c>
+      <c r="E66" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F66" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>50065</v>
+      </c>
+      <c r="C67" t="s">
+        <v>250</v>
+      </c>
+      <c r="E67" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F67" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>50066</v>
+      </c>
+      <c r="C68" t="s">
+        <v>250</v>
+      </c>
+      <c r="E68" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>50067</v>
+      </c>
+      <c r="C69" t="s">
+        <v>250</v>
+      </c>
+      <c r="E69" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>50068</v>
+      </c>
+      <c r="C70" t="s">
+        <v>250</v>
+      </c>
+      <c r="E70" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F70" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>50069</v>
+      </c>
+      <c r="B71" s="12"/>
+      <c r="C71" t="s">
+        <v>250</v>
+      </c>
+      <c r="E71" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F71" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>50070</v>
+      </c>
+      <c r="C72" t="s">
+        <v>250</v>
+      </c>
+      <c r="E72" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F72" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>50071</v>
+      </c>
+      <c r="C73" t="s">
+        <v>250</v>
+      </c>
+      <c r="E73" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>50072</v>
+      </c>
+      <c r="C74" t="s">
+        <v>250</v>
+      </c>
+      <c r="E74" s="6">
+        <f t="shared" ref="E74:E137" si="4">B74</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="6">
+        <f t="shared" ref="F74:F137" si="5">B74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>50073</v>
+      </c>
+      <c r="C75" t="s">
+        <v>250</v>
+      </c>
+      <c r="E75" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>50074</v>
+      </c>
+      <c r="C76" t="s">
+        <v>250</v>
+      </c>
+      <c r="E76" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F76" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>50075</v>
+      </c>
+      <c r="C77" t="s">
+        <v>250</v>
+      </c>
+      <c r="E77" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F77" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>50076</v>
+      </c>
+      <c r="C78" t="s">
+        <v>250</v>
+      </c>
+      <c r="E78" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F78" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>50077</v>
+      </c>
+      <c r="C79" t="s">
+        <v>250</v>
+      </c>
+      <c r="E79" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F79" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>50078</v>
+      </c>
+      <c r="C80" t="s">
+        <v>250</v>
+      </c>
+      <c r="E80" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>50079</v>
+      </c>
+      <c r="C81" t="s">
+        <v>250</v>
+      </c>
+      <c r="E81" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F81" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>50080</v>
+      </c>
+      <c r="C82" t="s">
+        <v>250</v>
+      </c>
+      <c r="E82" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>50081</v>
+      </c>
+      <c r="C83" t="s">
+        <v>250</v>
+      </c>
+      <c r="E83" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>50082</v>
+      </c>
+      <c r="C84" t="s">
+        <v>250</v>
+      </c>
+      <c r="E84" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F84" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>50083</v>
+      </c>
+      <c r="C85" t="s">
+        <v>250</v>
+      </c>
+      <c r="E85" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>50084</v>
+      </c>
+      <c r="C86" t="s">
+        <v>250</v>
+      </c>
+      <c r="E86" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F86" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>50085</v>
+      </c>
+      <c r="C87" t="s">
+        <v>250</v>
+      </c>
+      <c r="E87" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F87" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>50086</v>
+      </c>
+      <c r="C88" t="s">
+        <v>250</v>
+      </c>
+      <c r="E88" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>50087</v>
+      </c>
+      <c r="C89" t="s">
+        <v>250</v>
+      </c>
+      <c r="E89" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F89" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>50088</v>
+      </c>
+      <c r="C90" t="s">
+        <v>250</v>
+      </c>
+      <c r="E90" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F90" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>50089</v>
+      </c>
+      <c r="C91" t="s">
+        <v>250</v>
+      </c>
+      <c r="E91" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F91" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>50090</v>
+      </c>
+      <c r="C92" t="s">
+        <v>250</v>
+      </c>
+      <c r="E92" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F92" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>50091</v>
+      </c>
+      <c r="C93" t="s">
+        <v>250</v>
+      </c>
+      <c r="E93" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F93" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>50092</v>
+      </c>
+      <c r="C94" t="s">
+        <v>250</v>
+      </c>
+      <c r="E94" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>50093</v>
+      </c>
+      <c r="C95" t="s">
+        <v>250</v>
+      </c>
+      <c r="E95" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>50094</v>
+      </c>
+      <c r="C96" t="s">
+        <v>250</v>
+      </c>
+      <c r="E96" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F96" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>50095</v>
+      </c>
+      <c r="C97" t="s">
+        <v>250</v>
+      </c>
+      <c r="E97" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F97" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>50096</v>
+      </c>
+      <c r="C98" t="s">
+        <v>250</v>
+      </c>
+      <c r="E98" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F98" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>50097</v>
+      </c>
+      <c r="C99" t="s">
+        <v>250</v>
+      </c>
+      <c r="E99" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F99" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>50098</v>
+      </c>
+      <c r="C100" t="s">
+        <v>250</v>
+      </c>
+      <c r="E100" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F100" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>50099</v>
+      </c>
+      <c r="C101" t="s">
+        <v>250</v>
+      </c>
+      <c r="E101" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F101" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>50100</v>
+      </c>
+      <c r="C102" t="s">
+        <v>250</v>
+      </c>
+      <c r="E102" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F102" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>50101</v>
+      </c>
+      <c r="C103" t="s">
+        <v>250</v>
+      </c>
+      <c r="E103" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>50102</v>
+      </c>
+      <c r="C104" t="s">
+        <v>250</v>
+      </c>
+      <c r="E104" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F104" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>50103</v>
+      </c>
+      <c r="C105" t="s">
+        <v>250</v>
+      </c>
+      <c r="E105" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>50104</v>
+      </c>
+      <c r="C106" t="s">
+        <v>250</v>
+      </c>
+      <c r="E106" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F106" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>50105</v>
+      </c>
+      <c r="C107" t="s">
+        <v>250</v>
+      </c>
+      <c r="E107" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F107" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>50106</v>
+      </c>
+      <c r="C108" t="s">
+        <v>250</v>
+      </c>
+      <c r="E108" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F108" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>50107</v>
+      </c>
+      <c r="C109" t="s">
+        <v>250</v>
+      </c>
+      <c r="E109" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F109" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>50108</v>
+      </c>
+      <c r="C110" t="s">
+        <v>250</v>
+      </c>
+      <c r="E110" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F110" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>50109</v>
+      </c>
+      <c r="C111" t="s">
+        <v>250</v>
+      </c>
+      <c r="E111" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F111" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>50110</v>
+      </c>
+      <c r="C112" t="s">
+        <v>250</v>
+      </c>
+      <c r="E112" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F112" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>50111</v>
+      </c>
+      <c r="C113" t="s">
+        <v>250</v>
+      </c>
+      <c r="E113" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F113" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>50112</v>
+      </c>
+      <c r="C114" t="s">
+        <v>250</v>
+      </c>
+      <c r="E114" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F114" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>50113</v>
+      </c>
+      <c r="C115" t="s">
+        <v>250</v>
+      </c>
+      <c r="E115" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F115" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>50114</v>
+      </c>
+      <c r="C116" t="s">
+        <v>250</v>
+      </c>
+      <c r="E116" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F116" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>50115</v>
+      </c>
+      <c r="C117" t="s">
+        <v>250</v>
+      </c>
+      <c r="E117" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F117" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>50116</v>
+      </c>
+      <c r="C118" t="s">
+        <v>250</v>
+      </c>
+      <c r="E118" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F118" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>50117</v>
+      </c>
+      <c r="C119" t="s">
+        <v>250</v>
+      </c>
+      <c r="E119" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F119" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>50118</v>
+      </c>
+      <c r="C120" t="s">
+        <v>250</v>
+      </c>
+      <c r="E120" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F120" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>50119</v>
+      </c>
+      <c r="C121" t="s">
+        <v>250</v>
+      </c>
+      <c r="E121" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F121" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>50120</v>
+      </c>
+      <c r="C122" t="s">
+        <v>250</v>
+      </c>
+      <c r="E122" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F122" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>50121</v>
+      </c>
+      <c r="C123" t="s">
+        <v>250</v>
+      </c>
+      <c r="E123" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F123" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>50122</v>
+      </c>
+      <c r="C124" t="s">
+        <v>250</v>
+      </c>
+      <c r="E124" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F124" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>50123</v>
+      </c>
+      <c r="C125" t="s">
+        <v>250</v>
+      </c>
+      <c r="E125" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F125" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>50124</v>
+      </c>
+      <c r="C126" t="s">
+        <v>250</v>
+      </c>
+      <c r="E126" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F126" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>50125</v>
+      </c>
+      <c r="C127" t="s">
+        <v>250</v>
+      </c>
+      <c r="E127" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F127" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>50126</v>
+      </c>
+      <c r="C128" t="s">
+        <v>250</v>
+      </c>
+      <c r="E128" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F128" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>50127</v>
+      </c>
+      <c r="C129" t="s">
+        <v>250</v>
+      </c>
+      <c r="E129" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F129" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>50128</v>
+      </c>
+      <c r="C130" t="s">
+        <v>250</v>
+      </c>
+      <c r="E130" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F130" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>50129</v>
+      </c>
+      <c r="C131" t="s">
+        <v>250</v>
+      </c>
+      <c r="E131" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F131" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>50130</v>
+      </c>
+      <c r="C132" t="s">
+        <v>250</v>
+      </c>
+      <c r="E132" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F132" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>50131</v>
+      </c>
+      <c r="C133" t="s">
+        <v>250</v>
+      </c>
+      <c r="E133" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F133" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>50132</v>
+      </c>
+      <c r="C134" t="s">
+        <v>250</v>
+      </c>
+      <c r="E134" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F134" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>50133</v>
+      </c>
+      <c r="C135" t="s">
+        <v>250</v>
+      </c>
+      <c r="E135" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F135" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>50134</v>
+      </c>
+      <c r="C136" t="s">
+        <v>250</v>
+      </c>
+      <c r="E136" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F136" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>50135</v>
+      </c>
+      <c r="C137" t="s">
+        <v>250</v>
+      </c>
+      <c r="E137" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F137" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>50136</v>
+      </c>
+      <c r="C138" t="s">
+        <v>250</v>
+      </c>
+      <c r="E138" s="6">
+        <f t="shared" ref="E138:E201" si="6">B138</f>
+        <v>0</v>
+      </c>
+      <c r="F138" s="6">
+        <f t="shared" ref="F138:F201" si="7">B138</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>50137</v>
+      </c>
+      <c r="C139" t="s">
+        <v>250</v>
+      </c>
+      <c r="E139" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F139" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>50138</v>
+      </c>
+      <c r="C140" t="s">
+        <v>250</v>
+      </c>
+      <c r="E140" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F140" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>50139</v>
+      </c>
+      <c r="C141" t="s">
+        <v>250</v>
+      </c>
+      <c r="E141" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F141" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>50140</v>
+      </c>
+      <c r="C142" t="s">
+        <v>250</v>
+      </c>
+      <c r="E142" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F142" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>50141</v>
+      </c>
+      <c r="C143" t="s">
+        <v>250</v>
+      </c>
+      <c r="E143" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F143" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>50142</v>
+      </c>
+      <c r="C144" t="s">
+        <v>250</v>
+      </c>
+      <c r="E144" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F144" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>50143</v>
+      </c>
+      <c r="C145" t="s">
+        <v>250</v>
+      </c>
+      <c r="E145" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F145" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>50144</v>
+      </c>
+      <c r="C146" t="s">
+        <v>250</v>
+      </c>
+      <c r="E146" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F146" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>50145</v>
+      </c>
+      <c r="C147" t="s">
+        <v>250</v>
+      </c>
+      <c r="E147" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F147" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>50146</v>
+      </c>
+      <c r="C148" t="s">
+        <v>250</v>
+      </c>
+      <c r="E148" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F148" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>50147</v>
+      </c>
+      <c r="C149" t="s">
+        <v>250</v>
+      </c>
+      <c r="E149" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F149" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>50148</v>
+      </c>
+      <c r="C150" t="s">
+        <v>250</v>
+      </c>
+      <c r="E150" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F150" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>50149</v>
+      </c>
+      <c r="C151" t="s">
+        <v>250</v>
+      </c>
+      <c r="E151" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F151" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>50150</v>
+      </c>
+      <c r="C152" t="s">
+        <v>250</v>
+      </c>
+      <c r="E152" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F152" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>50151</v>
+      </c>
+      <c r="C153" t="s">
+        <v>250</v>
+      </c>
+      <c r="E153" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F153" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>50152</v>
+      </c>
+      <c r="C154" t="s">
+        <v>250</v>
+      </c>
+      <c r="E154" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F154" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>50153</v>
+      </c>
+      <c r="C155" t="s">
+        <v>250</v>
+      </c>
+      <c r="E155" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F155" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>50154</v>
+      </c>
+      <c r="C156" t="s">
+        <v>250</v>
+      </c>
+      <c r="E156" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F156" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>50155</v>
+      </c>
+      <c r="C157" t="s">
+        <v>250</v>
+      </c>
+      <c r="E157" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F157" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>50156</v>
+      </c>
+      <c r="C158" t="s">
+        <v>250</v>
+      </c>
+      <c r="E158" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F158" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>50157</v>
+      </c>
+      <c r="C159" t="s">
+        <v>250</v>
+      </c>
+      <c r="E159" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F159" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>50158</v>
+      </c>
+      <c r="C160" t="s">
+        <v>250</v>
+      </c>
+      <c r="E160" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F160" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>50159</v>
+      </c>
+      <c r="C161" t="s">
+        <v>250</v>
+      </c>
+      <c r="E161" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F161" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>50160</v>
+      </c>
+      <c r="C162" t="s">
+        <v>250</v>
+      </c>
+      <c r="E162" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F162" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>50161</v>
+      </c>
+      <c r="C163" t="s">
+        <v>250</v>
+      </c>
+      <c r="E163" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F163" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>50162</v>
+      </c>
+      <c r="C164" t="s">
+        <v>250</v>
+      </c>
+      <c r="E164" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F164" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>50163</v>
+      </c>
+      <c r="C165" t="s">
+        <v>250</v>
+      </c>
+      <c r="E165" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F165" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>50164</v>
+      </c>
+      <c r="C166" t="s">
+        <v>250</v>
+      </c>
+      <c r="E166" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F166" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>50165</v>
+      </c>
+      <c r="C167" t="s">
+        <v>250</v>
+      </c>
+      <c r="E167" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F167" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>50166</v>
+      </c>
+      <c r="C168" t="s">
+        <v>250</v>
+      </c>
+      <c r="E168" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F168" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>50167</v>
+      </c>
+      <c r="C169" t="s">
+        <v>250</v>
+      </c>
+      <c r="E169" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F169" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>50168</v>
+      </c>
+      <c r="C170" t="s">
+        <v>250</v>
+      </c>
+      <c r="E170" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F170" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>50169</v>
+      </c>
+      <c r="C171" t="s">
+        <v>250</v>
+      </c>
+      <c r="E171" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F171" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>50170</v>
+      </c>
+      <c r="C172" t="s">
+        <v>250</v>
+      </c>
+      <c r="E172" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F172" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>50171</v>
+      </c>
+      <c r="C173" t="s">
+        <v>250</v>
+      </c>
+      <c r="E173" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F173" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>50172</v>
+      </c>
+      <c r="C174" t="s">
+        <v>250</v>
+      </c>
+      <c r="E174" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F174" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>50173</v>
+      </c>
+      <c r="C175" t="s">
+        <v>250</v>
+      </c>
+      <c r="E175" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F175" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>50174</v>
+      </c>
+      <c r="C176" t="s">
+        <v>250</v>
+      </c>
+      <c r="E176" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F176" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>50175</v>
+      </c>
+      <c r="C177" t="s">
+        <v>250</v>
+      </c>
+      <c r="E177" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F177" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>50176</v>
+      </c>
+      <c r="C178" t="s">
+        <v>250</v>
+      </c>
+      <c r="E178" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F178" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>50177</v>
+      </c>
+      <c r="C179" t="s">
+        <v>250</v>
+      </c>
+      <c r="E179" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F179" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>50178</v>
+      </c>
+      <c r="C180" t="s">
+        <v>250</v>
+      </c>
+      <c r="E180" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F180" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>50179</v>
+      </c>
+      <c r="C181" t="s">
+        <v>250</v>
+      </c>
+      <c r="E181" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F181" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>50180</v>
+      </c>
+      <c r="C182" t="s">
+        <v>250</v>
+      </c>
+      <c r="E182" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F182" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>50181</v>
+      </c>
+      <c r="C183" t="s">
+        <v>250</v>
+      </c>
+      <c r="E183" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F183" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>50182</v>
+      </c>
+      <c r="C184" t="s">
+        <v>250</v>
+      </c>
+      <c r="E184" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F184" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>50183</v>
+      </c>
+      <c r="C185" t="s">
+        <v>250</v>
+      </c>
+      <c r="E185" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F185" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>50184</v>
+      </c>
+      <c r="C186" t="s">
+        <v>250</v>
+      </c>
+      <c r="E186" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F186" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>50185</v>
+      </c>
+      <c r="C187" t="s">
+        <v>250</v>
+      </c>
+      <c r="E187" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F187" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>50186</v>
+      </c>
+      <c r="C188" t="s">
+        <v>250</v>
+      </c>
+      <c r="E188" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F188" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>50187</v>
+      </c>
+      <c r="C189" t="s">
+        <v>250</v>
+      </c>
+      <c r="E189" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F189" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>50188</v>
+      </c>
+      <c r="C190" t="s">
+        <v>250</v>
+      </c>
+      <c r="E190" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F190" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>50189</v>
+      </c>
+      <c r="C191" t="s">
+        <v>250</v>
+      </c>
+      <c r="E191" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F191" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>50190</v>
+      </c>
+      <c r="C192" t="s">
+        <v>250</v>
+      </c>
+      <c r="E192" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F192" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>50191</v>
+      </c>
+      <c r="C193" t="s">
+        <v>250</v>
+      </c>
+      <c r="E193" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F193" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>50192</v>
+      </c>
+      <c r="C194" t="s">
+        <v>250</v>
+      </c>
+      <c r="E194" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F194" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>50193</v>
+      </c>
+      <c r="C195" t="s">
+        <v>250</v>
+      </c>
+      <c r="E195" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F195" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>50194</v>
+      </c>
+      <c r="C196" t="s">
+        <v>250</v>
+      </c>
+      <c r="E196" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F196" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>50195</v>
+      </c>
+      <c r="C197" t="s">
+        <v>250</v>
+      </c>
+      <c r="E197" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F197" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>50196</v>
+      </c>
+      <c r="C198" t="s">
+        <v>250</v>
+      </c>
+      <c r="E198" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F198" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>50197</v>
+      </c>
+      <c r="C199" t="s">
+        <v>250</v>
+      </c>
+      <c r="E199" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F199" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>50198</v>
+      </c>
+      <c r="C200" t="s">
+        <v>250</v>
+      </c>
+      <c r="E200" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F200" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>50199</v>
+      </c>
+      <c r="C201" t="s">
+        <v>250</v>
+      </c>
+      <c r="E201" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F201" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>50200</v>
+      </c>
+      <c r="C202" t="s">
+        <v>250</v>
+      </c>
+      <c r="E202" s="6">
+        <f t="shared" ref="E202:E210" si="8">B202</f>
+        <v>0</v>
+      </c>
+      <c r="F202" s="6">
+        <f t="shared" ref="F202:F210" si="9">B202</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>50201</v>
+      </c>
+      <c r="C203" t="s">
+        <v>250</v>
+      </c>
+      <c r="E203" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F203" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>50202</v>
+      </c>
+      <c r="C204" t="s">
+        <v>250</v>
+      </c>
+      <c r="E204" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F204" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>50203</v>
+      </c>
+      <c r="C205" t="s">
+        <v>250</v>
+      </c>
+      <c r="E205" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F205" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>50204</v>
+      </c>
+      <c r="C206" t="s">
+        <v>250</v>
+      </c>
+      <c r="E206" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F206" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>50205</v>
+      </c>
+      <c r="C207" t="s">
+        <v>250</v>
+      </c>
+      <c r="E207" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F207" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>50206</v>
+      </c>
+      <c r="C208" t="s">
+        <v>250</v>
+      </c>
+      <c r="E208" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F208" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>50207</v>
+      </c>
+      <c r="C209" t="s">
+        <v>250</v>
+      </c>
+      <c r="E209" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F209" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>50208</v>
+      </c>
+      <c r="C210" t="s">
+        <v>250</v>
+      </c>
+      <c r="E210" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F210" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E211" s="6"/>
+      <c r="F211" s="6"/>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E212" s="6"/>
+      <c r="F212" s="6"/>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E213" s="6"/>
+      <c r="F213" s="6"/>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E214" s="6"/>
+      <c r="F214" s="6"/>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E215" s="6"/>
+      <c r="F215" s="6"/>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E216" s="6"/>
+      <c r="F216" s="6"/>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E217" s="6"/>
+      <c r="F217" s="6"/>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E218" s="6"/>
+      <c r="F218" s="6"/>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E219" s="6"/>
+      <c r="F219" s="6"/>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E220" s="6"/>
+      <c r="F220" s="6"/>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E221" s="6"/>
+      <c r="F221" s="6"/>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E222" s="6"/>
+      <c r="F222" s="6"/>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E223" s="6"/>
+      <c r="F223" s="6"/>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E224" s="6"/>
+      <c r="F224" s="6"/>
+    </row>
+    <row r="225" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E225" s="6"/>
+      <c r="F225" s="6"/>
+    </row>
+    <row r="226" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E226" s="6"/>
+      <c r="F226" s="6"/>
+    </row>
+    <row r="227" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E227" s="6"/>
+      <c r="F227" s="6"/>
+    </row>
+    <row r="228" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E228" s="6"/>
+      <c r="F228" s="6"/>
+    </row>
+    <row r="229" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E229" s="6"/>
+      <c r="F229" s="6"/>
+    </row>
+    <row r="230" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E230" s="6"/>
+      <c r="F230" s="6"/>
+    </row>
+    <row r="231" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E231" s="6"/>
+      <c r="F231" s="6"/>
+    </row>
+    <row r="232" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E232" s="6"/>
+      <c r="F232" s="6"/>
+    </row>
+    <row r="233" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E233" s="6"/>
+      <c r="F233" s="6"/>
+    </row>
+    <row r="234" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E234" s="6"/>
+      <c r="F234" s="6"/>
+    </row>
+    <row r="235" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E235" s="6"/>
+      <c r="F235" s="6"/>
+    </row>
+    <row r="236" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E236" s="6"/>
+      <c r="F236" s="6"/>
+    </row>
+    <row r="237" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E237" s="6"/>
+      <c r="F237" s="6"/>
+    </row>
+    <row r="238" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E238" s="6"/>
+      <c r="F238" s="6"/>
+    </row>
+    <row r="239" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E239" s="6"/>
+      <c r="F239" s="6"/>
+    </row>
+    <row r="240" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E240" s="6"/>
+      <c r="F240" s="6"/>
+    </row>
+    <row r="241" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E241" s="6"/>
+      <c r="F241" s="6"/>
+    </row>
+    <row r="242" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E242" s="6"/>
+      <c r="F242" s="6"/>
+    </row>
+    <row r="243" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E243" s="6"/>
+      <c r="F243" s="6"/>
+    </row>
+    <row r="244" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E244" s="6"/>
+      <c r="F244" s="6"/>
+    </row>
+    <row r="245" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E245" s="6"/>
+      <c r="F245" s="6"/>
+    </row>
+    <row r="246" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E246" s="6"/>
+      <c r="F246" s="6"/>
+    </row>
+    <row r="247" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E247" s="6"/>
+      <c r="F247" s="6"/>
+    </row>
+    <row r="248" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E248" s="6"/>
+      <c r="F248" s="6"/>
+    </row>
+    <row r="249" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E249" s="6"/>
+      <c r="F249" s="6"/>
+    </row>
+    <row r="250" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E250" s="6"/>
+      <c r="F250" s="6"/>
+    </row>
+    <row r="251" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E251" s="6"/>
+      <c r="F251" s="6"/>
+    </row>
+    <row r="252" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E252" s="6"/>
+      <c r="F252" s="6"/>
+    </row>
+    <row r="253" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E253" s="6"/>
+      <c r="F253" s="6"/>
+    </row>
+    <row r="254" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E254" s="6"/>
+      <c r="F254" s="6"/>
+    </row>
+    <row r="255" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E255" s="6"/>
+      <c r="F255" s="6"/>
+    </row>
+    <row r="256" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E256" s="6"/>
+      <c r="F256" s="6"/>
+    </row>
+    <row r="257" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E257" s="6"/>
+      <c r="F257" s="6"/>
+    </row>
+    <row r="258" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E258" s="6"/>
+      <c r="F258" s="6"/>
+    </row>
+    <row r="259" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E259" s="6"/>
+      <c r="F259" s="6"/>
+    </row>
+    <row r="260" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E260" s="6"/>
+      <c r="F260" s="6"/>
+    </row>
+    <row r="261" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E261" s="6"/>
+      <c r="F261" s="6"/>
+    </row>
+    <row r="262" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E262" s="6"/>
+      <c r="F262" s="6"/>
+    </row>
+    <row r="263" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E263" s="6"/>
+      <c r="F263" s="6"/>
+    </row>
+    <row r="264" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E264" s="6"/>
+      <c r="F264" s="6"/>
+    </row>
+    <row r="265" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E265" s="6"/>
+      <c r="F265" s="6"/>
+    </row>
+    <row r="266" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E266" s="6"/>
+      <c r="F266" s="6"/>
+    </row>
+    <row r="267" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E267" s="6"/>
+      <c r="F267" s="6"/>
+    </row>
+    <row r="268" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E268" s="6"/>
+      <c r="F268" s="6"/>
+    </row>
+    <row r="269" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E269" s="6"/>
+      <c r="F269" s="6"/>
+    </row>
+    <row r="270" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E270" s="6"/>
+      <c r="F270" s="6"/>
+    </row>
+    <row r="271" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E271" s="6"/>
+      <c r="F271" s="6"/>
+    </row>
+    <row r="272" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E272" s="6"/>
+      <c r="F272" s="6"/>
+    </row>
+    <row r="273" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E273" s="6"/>
+      <c r="F273" s="6"/>
+    </row>
+    <row r="274" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E274" s="6"/>
+      <c r="F274" s="6"/>
+    </row>
+    <row r="275" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E275" s="6"/>
+      <c r="F275" s="6"/>
+    </row>
+    <row r="276" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E276" s="6"/>
+      <c r="F276" s="6"/>
+    </row>
+    <row r="277" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E277" s="6"/>
+      <c r="F277" s="6"/>
+    </row>
+    <row r="278" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E278" s="6"/>
+      <c r="F278" s="6"/>
+    </row>
+    <row r="279" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E279" s="6"/>
+      <c r="F279" s="6"/>
+    </row>
+    <row r="280" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E280" s="6"/>
+      <c r="F280" s="6"/>
+    </row>
+    <row r="281" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E281" s="6"/>
+      <c r="F281" s="6"/>
+    </row>
+    <row r="282" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E282" s="6"/>
+      <c r="F282" s="6"/>
+    </row>
+    <row r="283" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E283" s="6"/>
+      <c r="F283" s="6"/>
+    </row>
+    <row r="284" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E284" s="6"/>
+      <c r="F284" s="6"/>
+    </row>
+    <row r="285" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E285" s="6"/>
+      <c r="F285" s="6"/>
+    </row>
+    <row r="286" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E286" s="6"/>
+      <c r="F286" s="6"/>
+    </row>
+    <row r="287" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E287" s="6"/>
+      <c r="F287" s="6"/>
+    </row>
+    <row r="288" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E288" s="6"/>
+      <c r="F288" s="6"/>
+    </row>
+    <row r="289" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E289" s="6"/>
+      <c r="F289" s="6"/>
+    </row>
+    <row r="290" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E290" s="6"/>
+      <c r="F290" s="6"/>
+    </row>
+    <row r="291" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E291" s="6"/>
+      <c r="F291" s="6"/>
+    </row>
+    <row r="292" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E292" s="6"/>
+      <c r="F292" s="6"/>
+    </row>
+    <row r="293" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E293" s="6"/>
+      <c r="F293" s="6"/>
+    </row>
+    <row r="294" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E294" s="6"/>
+      <c r="F294" s="6"/>
+    </row>
+    <row r="295" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E295" s="6"/>
+      <c r="F295" s="6"/>
+    </row>
+    <row r="296" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E296" s="6"/>
+      <c r="F296" s="6"/>
+    </row>
+    <row r="297" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E297" s="6"/>
+      <c r="F297" s="6"/>
+    </row>
+    <row r="298" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E298" s="6"/>
+      <c r="F298" s="6"/>
+    </row>
+    <row r="299" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E299" s="6"/>
+      <c r="F299" s="6"/>
+    </row>
+    <row r="300" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E300" s="6"/>
+      <c r="F300" s="6"/>
+    </row>
+    <row r="301" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E301" s="6"/>
+      <c r="F301" s="6"/>
+    </row>
+    <row r="302" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E302" s="6"/>
+      <c r="F302" s="6"/>
+    </row>
+    <row r="303" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E303" s="6"/>
+      <c r="F303" s="6"/>
+    </row>
+    <row r="304" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E304" s="6"/>
+      <c r="F304" s="6"/>
+    </row>
+    <row r="305" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E305" s="6"/>
+      <c r="F305" s="6"/>
+    </row>
+    <row r="306" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E306" s="6"/>
+      <c r="F306" s="6"/>
+    </row>
+    <row r="307" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E307" s="6"/>
+      <c r="F307" s="6"/>
+    </row>
+    <row r="308" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E308" s="6"/>
+      <c r="F308" s="6"/>
+    </row>
+    <row r="309" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E309" s="6"/>
+      <c r="F309" s="6"/>
+    </row>
+    <row r="310" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E310" s="6"/>
+      <c r="F310" s="6"/>
+    </row>
+    <row r="311" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E311" s="6"/>
+      <c r="F311" s="6"/>
+    </row>
+    <row r="312" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E312" s="6"/>
+      <c r="F312" s="6"/>
+    </row>
+    <row r="313" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E313" s="6"/>
+      <c r="F313" s="6"/>
+    </row>
+    <row r="314" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E314" s="6"/>
+      <c r="F314" s="6"/>
+    </row>
+    <row r="315" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E315" s="6"/>
+      <c r="F315" s="6"/>
+    </row>
+    <row r="316" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E316" s="6"/>
+      <c r="F316" s="6"/>
+    </row>
+    <row r="317" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E317" s="6"/>
+      <c r="F317" s="6"/>
+    </row>
+    <row r="318" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E318" s="6"/>
+      <c r="F318" s="6"/>
+    </row>
+    <row r="319" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E319" s="6"/>
+      <c r="F319" s="6"/>
+    </row>
+    <row r="320" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E320" s="6"/>
+      <c r="F320" s="6"/>
+    </row>
+    <row r="321" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E321" s="6"/>
+      <c r="F321" s="6"/>
+    </row>
+    <row r="322" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E322" s="6"/>
+      <c r="F322" s="6"/>
+    </row>
+    <row r="323" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E323" s="6"/>
+      <c r="F323" s="6"/>
+    </row>
+    <row r="324" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E324" s="6"/>
+      <c r="F324" s="6"/>
+    </row>
+    <row r="325" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E325" s="6"/>
+      <c r="F325" s="6"/>
+    </row>
+    <row r="326" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E326" s="6"/>
+      <c r="F326" s="6"/>
+    </row>
+    <row r="327" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E327" s="6"/>
+      <c r="F327" s="6"/>
+    </row>
+    <row r="328" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E328" s="6"/>
+      <c r="F328" s="6"/>
+    </row>
+    <row r="329" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E329" s="6"/>
+      <c r="F329" s="6"/>
+    </row>
+    <row r="330" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E330" s="6"/>
+      <c r="F330" s="6"/>
+    </row>
+    <row r="331" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E331" s="6"/>
+      <c r="F331" s="6"/>
+    </row>
+    <row r="332" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E332" s="6"/>
+      <c r="F332" s="6"/>
+    </row>
+    <row r="333" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E333" s="6"/>
+      <c r="F333" s="6"/>
+    </row>
+    <row r="334" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E334" s="6"/>
+      <c r="F334" s="6"/>
+    </row>
+    <row r="335" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E335" s="6"/>
+      <c r="F335" s="6"/>
+    </row>
+    <row r="336" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E336" s="6"/>
+      <c r="F336" s="6"/>
+    </row>
+    <row r="337" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E337" s="6"/>
+      <c r="F337" s="6"/>
+    </row>
+    <row r="338" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E338" s="6"/>
+      <c r="F338" s="6"/>
+    </row>
+    <row r="339" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E339" s="6"/>
+      <c r="F339" s="6"/>
+    </row>
+    <row r="340" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E340" s="6"/>
+      <c r="F340" s="6"/>
+    </row>
+    <row r="341" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E341" s="6"/>
+      <c r="F341" s="6"/>
+    </row>
+    <row r="342" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E342" s="6"/>
+      <c r="F342" s="6"/>
+    </row>
+    <row r="343" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E343" s="6"/>
+      <c r="F343" s="6"/>
+    </row>
+    <row r="344" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E344" s="6"/>
+      <c r="F344" s="6"/>
+    </row>
+    <row r="345" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E345" s="6"/>
+      <c r="F345" s="6"/>
+    </row>
+    <row r="346" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E346" s="6"/>
+      <c r="F346" s="6"/>
+    </row>
+    <row r="347" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E347" s="6"/>
+      <c r="F347" s="6"/>
+    </row>
+    <row r="348" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E348" s="6"/>
+      <c r="F348" s="6"/>
+    </row>
+    <row r="349" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E349" s="6"/>
+      <c r="F349" s="6"/>
+    </row>
+    <row r="350" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E350" s="6"/>
+      <c r="F350" s="6"/>
+    </row>
+    <row r="351" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E351" s="6"/>
+      <c r="F351" s="6"/>
+    </row>
+    <row r="352" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E352" s="6"/>
+      <c r="F352" s="6"/>
+    </row>
+    <row r="353" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E353" s="6"/>
+      <c r="F353" s="6"/>
+    </row>
+    <row r="354" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E354" s="6"/>
+      <c r="F354" s="6"/>
+    </row>
+    <row r="355" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E355" s="6"/>
+      <c r="F355" s="6"/>
+    </row>
+    <row r="356" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E356" s="6"/>
+      <c r="F356" s="6"/>
+    </row>
+    <row r="357" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E357" s="6"/>
+      <c r="F357" s="6"/>
+    </row>
+    <row r="358" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E358" s="6"/>
+      <c r="F358" s="6"/>
+    </row>
+    <row r="359" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E359" s="6"/>
+      <c r="F359" s="6"/>
+    </row>
+    <row r="360" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E360" s="6"/>
+      <c r="F360" s="6"/>
+    </row>
+    <row r="361" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E361" s="6"/>
+      <c r="F361" s="6"/>
+    </row>
+    <row r="362" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E362" s="6"/>
+      <c r="F362" s="6"/>
+    </row>
+    <row r="363" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E363" s="6"/>
+      <c r="F363" s="6"/>
+    </row>
+    <row r="364" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E364" s="6"/>
+      <c r="F364" s="6"/>
+    </row>
+    <row r="365" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E365" s="6"/>
+      <c r="F365" s="6"/>
+    </row>
+    <row r="366" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E366" s="6"/>
+      <c r="F366" s="6"/>
+    </row>
+    <row r="367" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E367" s="6"/>
+      <c r="F367" s="6"/>
+    </row>
+    <row r="368" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E368" s="6"/>
+      <c r="F368" s="6"/>
+    </row>
+    <row r="369" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E369" s="6"/>
+      <c r="F369" s="6"/>
+    </row>
+    <row r="370" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E370" s="6"/>
+      <c r="F370" s="6"/>
+    </row>
+    <row r="371" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E371" s="6"/>
+      <c r="F371" s="6"/>
+    </row>
+    <row r="372" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E372" s="6"/>
+      <c r="F372" s="6"/>
+    </row>
+    <row r="373" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E373" s="6"/>
+      <c r="F373" s="6"/>
+    </row>
+    <row r="374" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E374" s="6"/>
+      <c r="F374" s="6"/>
+    </row>
+    <row r="375" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E375" s="6"/>
+      <c r="F375" s="6"/>
+    </row>
+    <row r="376" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E376" s="6"/>
+      <c r="F376" s="6"/>
+    </row>
+    <row r="377" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E377" s="6"/>
+      <c r="F377" s="6"/>
+    </row>
+    <row r="378" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E378" s="6"/>
+      <c r="F378" s="6"/>
+    </row>
+    <row r="379" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E379" s="6"/>
+      <c r="F379" s="6"/>
+    </row>
+    <row r="380" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E380" s="6"/>
+      <c r="F380" s="6"/>
+    </row>
+    <row r="381" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E381" s="6"/>
+      <c r="F381" s="6"/>
+    </row>
+    <row r="382" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E382" s="6"/>
+      <c r="F382" s="6"/>
+    </row>
+    <row r="383" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E383" s="6"/>
+      <c r="F383" s="6"/>
+    </row>
+    <row r="384" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E384" s="6"/>
+      <c r="F384" s="6"/>
+    </row>
+    <row r="385" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E385" s="6"/>
+      <c r="F385" s="6"/>
+    </row>
+    <row r="386" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E386" s="6"/>
+      <c r="F386" s="6"/>
+    </row>
+    <row r="387" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E387" s="6"/>
+      <c r="F387" s="6"/>
+    </row>
+    <row r="388" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E388" s="6"/>
+      <c r="F388" s="6"/>
+    </row>
+    <row r="389" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E389" s="6"/>
+      <c r="F389" s="6"/>
+    </row>
+    <row r="390" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E390" s="6"/>
+      <c r="F390" s="6"/>
+    </row>
+    <row r="391" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E391" s="6"/>
+      <c r="F391" s="6"/>
+    </row>
+    <row r="392" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E392" s="6"/>
+      <c r="F392" s="6"/>
+    </row>
+    <row r="393" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E393" s="6"/>
+      <c r="F393" s="6"/>
+    </row>
+    <row r="394" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E394" s="6"/>
+      <c r="F394" s="6"/>
+    </row>
+    <row r="395" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E395" s="6"/>
+      <c r="F395" s="6"/>
+    </row>
+    <row r="396" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E396" s="6"/>
+      <c r="F396" s="6"/>
+    </row>
+    <row r="397" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E397" s="6"/>
+      <c r="F397" s="6"/>
+    </row>
+    <row r="398" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E398" s="6"/>
+      <c r="F398" s="6"/>
+    </row>
+    <row r="399" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E399" s="6"/>
+      <c r="F399" s="6"/>
+    </row>
+    <row r="400" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E400" s="6"/>
+      <c r="F400" s="6"/>
+    </row>
+    <row r="401" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E401" s="6"/>
+      <c r="F401" s="6"/>
+    </row>
+    <row r="402" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E402" s="6"/>
+      <c r="F402" s="6"/>
+    </row>
+    <row r="403" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E403" s="6"/>
+      <c r="F403" s="6"/>
+    </row>
+    <row r="404" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E404" s="6"/>
+      <c r="F404" s="6"/>
+    </row>
+    <row r="405" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E405" s="6"/>
+      <c r="F405" s="6"/>
+    </row>
+    <row r="406" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E406" s="6"/>
+      <c r="F406" s="6"/>
+    </row>
+    <row r="407" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E407" s="6"/>
+      <c r="F407" s="6"/>
+    </row>
+    <row r="408" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E408" s="6"/>
+      <c r="F408" s="6"/>
+    </row>
+    <row r="409" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E409" s="6"/>
+      <c r="F409" s="6"/>
+    </row>
+    <row r="410" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E410" s="6"/>
+      <c r="F410" s="6"/>
+    </row>
+    <row r="411" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E411" s="6"/>
+      <c r="F411" s="6"/>
+    </row>
+    <row r="412" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E412" s="6"/>
+      <c r="F412" s="6"/>
+    </row>
+    <row r="413" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E413" s="6"/>
+      <c r="F413" s="6"/>
+    </row>
+    <row r="414" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E414" s="6"/>
+      <c r="F414" s="6"/>
+    </row>
+    <row r="415" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E415" s="6"/>
+      <c r="F415" s="6"/>
+    </row>
+    <row r="416" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E416" s="6"/>
+      <c r="F416" s="6"/>
+    </row>
+    <row r="417" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E417" s="6"/>
+      <c r="F417" s="6"/>
+    </row>
+    <row r="418" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E418" s="6"/>
+      <c r="F418" s="6"/>
+    </row>
+    <row r="419" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E419" s="6"/>
+      <c r="F419" s="6"/>
+    </row>
+    <row r="420" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E420" s="6"/>
+      <c r="F420" s="6"/>
+    </row>
+    <row r="421" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E421" s="6"/>
+      <c r="F421" s="6"/>
+    </row>
+    <row r="422" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E422" s="6"/>
+      <c r="F422" s="6"/>
+    </row>
+    <row r="423" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E423" s="6"/>
+      <c r="F423" s="6"/>
+    </row>
+    <row r="424" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E424" s="6"/>
+      <c r="F424" s="6"/>
+    </row>
+    <row r="425" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E425" s="6"/>
+      <c r="F425" s="6"/>
+    </row>
+    <row r="426" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E426" s="6"/>
+      <c r="F426" s="6"/>
+    </row>
+    <row r="427" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E427" s="6"/>
+      <c r="F427" s="6"/>
+    </row>
+    <row r="428" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E428" s="6"/>
+      <c r="F428" s="6"/>
+    </row>
+    <row r="429" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E429" s="6"/>
+      <c r="F429" s="6"/>
+    </row>
+    <row r="430" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E430" s="6"/>
+      <c r="F430" s="6"/>
+    </row>
+    <row r="431" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E431" s="6"/>
+      <c r="F431" s="6"/>
+    </row>
+    <row r="432" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E432" s="6"/>
+      <c r="F432" s="6"/>
+    </row>
+    <row r="433" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E433" s="6"/>
+      <c r="F433" s="6"/>
+    </row>
+    <row r="434" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E434" s="6"/>
+      <c r="F434" s="6"/>
+    </row>
+    <row r="435" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E435" s="6"/>
+      <c r="F435" s="6"/>
+    </row>
+    <row r="436" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E436" s="6"/>
+      <c r="F436" s="6"/>
+    </row>
+    <row r="437" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E437" s="6"/>
+      <c r="F437" s="6"/>
+    </row>
+    <row r="438" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E438" s="6"/>
+      <c r="F438" s="6"/>
+    </row>
+    <row r="439" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E439" s="6"/>
+      <c r="F439" s="6"/>
+    </row>
+    <row r="440" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E440" s="6"/>
+      <c r="F440" s="6"/>
+    </row>
+    <row r="441" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E441" s="6"/>
+      <c r="F441" s="6"/>
+    </row>
+    <row r="442" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E442" s="6"/>
+      <c r="F442" s="6"/>
+    </row>
+    <row r="443" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E443" s="6"/>
+      <c r="F443" s="6"/>
+    </row>
+    <row r="444" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E444" s="6"/>
+      <c r="F444" s="6"/>
+    </row>
+    <row r="445" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B445" s="6"/>
+      <c r="D445" s="3"/>
+      <c r="E445" s="6"/>
+      <c r="F445" s="6"/>
+    </row>
+    <row r="446" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B446" s="6"/>
+      <c r="D446" s="9"/>
+      <c r="E446" s="6"/>
+      <c r="F446" s="6"/>
+    </row>
+    <row r="447" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B447" s="6"/>
+      <c r="D447" s="9"/>
+      <c r="E447" s="6"/>
+      <c r="F447" s="6"/>
+    </row>
+    <row r="448" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D448" s="10"/>
+      <c r="E448" s="6"/>
+      <c r="F448" s="6"/>
+    </row>
+    <row r="449" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B449" s="6"/>
+      <c r="D449" s="10"/>
+      <c r="E449" s="6"/>
+      <c r="F449" s="6"/>
+    </row>
+    <row r="450" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D450" s="10"/>
+      <c r="E450" s="6"/>
+      <c r="F450" s="6"/>
+    </row>
+    <row r="451" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B451" s="11"/>
+      <c r="D451" s="10"/>
+      <c r="E451" s="6"/>
+      <c r="F451" s="6"/>
+    </row>
+    <row r="452" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D452" s="10"/>
+      <c r="E452" s="6"/>
+      <c r="F452" s="6"/>
+    </row>
+    <row r="453" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E453" s="6"/>
+      <c r="F453" s="6"/>
+    </row>
+    <row r="454" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E454" s="6"/>
+      <c r="F454" s="6"/>
+    </row>
+    <row r="455" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E455" s="6"/>
+      <c r="F455" s="6"/>
+    </row>
+    <row r="456" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E456" s="6"/>
+      <c r="F456" s="6"/>
+    </row>
+    <row r="457" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E457" s="6"/>
+      <c r="F457" s="6"/>
+    </row>
+    <row r="458" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E458" s="6"/>
+      <c r="F458" s="6"/>
+    </row>
+    <row r="459" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E459" s="6"/>
+      <c r="F459" s="6"/>
+    </row>
+    <row r="460" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E460" s="6"/>
+      <c r="F460" s="6"/>
+    </row>
+    <row r="461" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E461" s="6"/>
+      <c r="F461" s="6"/>
+    </row>
+    <row r="462" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E462" s="6"/>
+      <c r="F462" s="6"/>
+    </row>
+    <row r="463" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E463" s="6"/>
+      <c r="F463" s="6"/>
+    </row>
+    <row r="464" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E464" s="6"/>
+      <c r="F464" s="6"/>
+    </row>
+    <row r="465" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E465" s="6"/>
+      <c r="F465" s="6"/>
+    </row>
+    <row r="466" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E466" s="6"/>
+      <c r="F466" s="6"/>
+    </row>
+    <row r="467" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E467" s="6"/>
+      <c r="F467" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98471DEA-DA11-4ED3-8CC2-751E4782F2C0}">
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2861,70 +7665,88 @@
       <c r="A6">
         <v>100004</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="12" t="s">
+        <v>312</v>
+      </c>
       <c r="C6" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="6">
+      <c r="D6" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="E6" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
+        <v>烫</v>
+      </c>
+      <c r="F6" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>烫</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>100005</v>
       </c>
+      <c r="B7" s="12" t="s">
+        <v>313</v>
+      </c>
       <c r="C7" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="6">
+      <c r="D7" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="E7" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
+        <v>热</v>
+      </c>
+      <c r="F7" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>热</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>100006</v>
       </c>
-      <c r="B8" s="11"/>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
       <c r="C8" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="6">
+      <c r="D8" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="E8" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
+        <v>凉</v>
+      </c>
+      <c r="F8" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>凉</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>100007</v>
       </c>
+      <c r="B9" t="s">
+        <v>315</v>
+      </c>
       <c r="C9" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="6">
+      <c r="D9" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
+        <v>冷</v>
+      </c>
+      <c r="F9" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>冷</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -3049,7 +7871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669360A0-5660-4C1B-A0E2-B39C4C67F52C}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3121,6 +7943,145 @@
       <c r="F3" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="7"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="6"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="11"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="6"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C1B3F7-54F4-4D6B-B9DF-C355C73B066C}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>300000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f t="shared" ref="E2:E5" si="0">B2</f>
+        <v>有点</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <f t="shared" ref="F2:F5" si="1">B2</f>
+        <v>有点</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>300001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>太</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>太</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3424,8 +8385,26 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="A5">
+        <v>3003</v>
+      </c>
+      <c r="B5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f>B5</f>
+        <v>了</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <f>B5</f>
+        <v>了</v>
+      </c>
       <c r="G5" s="16"/>
     </row>
   </sheetData>
@@ -3885,46 +8864,128 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E10" s="6">
-        <f t="shared" ref="E10:E11" si="1">B10</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="A10">
+        <v>5018</v>
+      </c>
+      <c r="B10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" t="s">
+        <v>289</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>这样</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E11" s="6">
+      <c r="A11">
+        <v>5019</v>
+      </c>
+      <c r="B11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>那样</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>5020</v>
+      </c>
+      <c r="B12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C12" t="s">
+        <v>295</v>
+      </c>
+      <c r="D12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="6" t="str">
+        <f t="shared" ref="F12:F16" si="1">B12</f>
+        <v>哪样</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>5021</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C13" t="s">
+        <v>295</v>
+      </c>
+      <c r="D13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="12"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+        <v>这种</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>5022</v>
+      </c>
       <c r="D14" s="13"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="E14" s="6">
+        <f t="shared" ref="E13:E16" si="2">B14</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="A15">
+        <v>5023</v>
+      </c>
+      <c r="E15" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="A16">
+        <v>5024</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D17" s="13"/>
@@ -5101,7 +10162,7 @@
         <v>猫</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>20105</v>
       </c>
@@ -5123,7 +10184,7 @@
         <v>鸡</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>20106</v>
       </c>
@@ -5145,7 +10206,7 @@
         <v>猪</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>20107</v>
       </c>
@@ -5167,7 +10228,7 @@
         <v>牛</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>20108</v>
       </c>
@@ -5189,7 +10250,7 @@
         <v>鸭子</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>20109</v>
       </c>
@@ -5211,7 +10272,7 @@
         <v>羊</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>20110</v>
       </c>
@@ -5233,7 +10294,7 @@
         <v>猪肉</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>20111</v>
       </c>
@@ -5255,7 +10316,7 @@
         <v>牛肉</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>20112</v>
       </c>
@@ -5277,7 +10338,7 @@
         <v>鸭肉</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>20113</v>
       </c>
@@ -5299,7 +10360,7 @@
         <v>羊肉</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>20114</v>
       </c>
@@ -5321,7 +10382,7 @@
         <v>鸡肉</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>20115</v>
       </c>
@@ -5343,7 +10404,7 @@
         <v>洗手间</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>20116</v>
       </c>
@@ -5365,68 +10426,98 @@
         <v>地铁站</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>20117</v>
       </c>
+      <c r="B61" s="11" t="s">
+        <v>293</v>
+      </c>
       <c r="C61" t="s">
         <v>73</v>
       </c>
-      <c r="E61" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F61" s="6">
+      <c r="D61" t="s">
+        <v>292</v>
+      </c>
+      <c r="E61" s="6" t="str">
+        <f>B61</f>
+        <v>发型</v>
+      </c>
+      <c r="F61" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+        <v>发型</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>20118</v>
       </c>
+      <c r="B62" t="s">
+        <v>306</v>
+      </c>
       <c r="C62" t="s">
         <v>73</v>
       </c>
-      <c r="E62" s="6">
+      <c r="D62" t="s">
+        <v>302</v>
+      </c>
+      <c r="E62" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="6">
+        <v>短发</v>
+      </c>
+      <c r="F62" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+        <v>短发</v>
+      </c>
+      <c r="G62" s="23" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>20119</v>
       </c>
+      <c r="B63" s="11" t="s">
+        <v>304</v>
+      </c>
       <c r="C63" t="s">
         <v>73</v>
       </c>
-      <c r="E63" s="6">
+      <c r="D63" t="s">
+        <v>303</v>
+      </c>
+      <c r="E63" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F63" s="6">
+        <v>韩式</v>
+      </c>
+      <c r="F63" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+        <v>韩式</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>20120</v>
       </c>
+      <c r="B64" t="s">
+        <v>311</v>
+      </c>
       <c r="C64" t="s">
         <v>73</v>
       </c>
-      <c r="E64" s="6">
+      <c r="D64" t="s">
+        <v>307</v>
+      </c>
+      <c r="E64" s="6" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F64" s="6">
+        <v>水温</v>
+      </c>
+      <c r="F64" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>水温</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -12452,36 +17543,48 @@
         <v>274</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>30134</v>
       </c>
+      <c r="B21" s="22" t="s">
+        <v>297</v>
+      </c>
       <c r="C21" t="s">
         <v>250</v>
       </c>
-      <c r="E21" s="6">
+      <c r="D21" t="s">
+        <v>294</v>
+      </c>
+      <c r="E21" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
+        <v>张元英</v>
+      </c>
+      <c r="F21" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>张元英</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>30135</v>
       </c>
+      <c r="B22" t="s">
+        <v>299</v>
+      </c>
       <c r="C22" t="s">
         <v>250</v>
       </c>
-      <c r="E22" s="6">
+      <c r="D22" t="s">
+        <v>300</v>
+      </c>
+      <c r="E22" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
+        <v>高胤祯</v>
+      </c>
+      <c r="F22" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>高胤祯</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -16553,7 +21656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E61A85-9E37-4DCB-B2F7-E83A50F42F3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94FA983A-9B85-4041-AF3F-1812E14E028A}">
   <dimension ref="A1:K467"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16604,103 +21707,82 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="B2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C2" s="6"/>
+        <v>326</v>
+      </c>
+      <c r="C2" t="s">
+        <v>324</v>
+      </c>
       <c r="D2" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="E2" s="6" t="str">
-        <f t="shared" ref="E2:E20" si="0">B2</f>
-        <v>床前明月光</v>
+        <f t="shared" ref="E2:E65" si="0">B2</f>
+        <v>太烫了</v>
       </c>
       <c r="F2" s="6" t="str">
-        <f t="shared" ref="F2:F20" si="1">B2</f>
-        <v>床前明月光</v>
-      </c>
-      <c r="H2" t="s">
-        <v>282</v>
+        <f t="shared" ref="F2:F65" si="1">B2</f>
+        <v>太烫了</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>50001</v>
+        <v>40001</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C3" s="6"/>
+        <v>325</v>
+      </c>
+      <c r="C3" t="s">
+        <v>324</v>
+      </c>
       <c r="D3" t="s">
-        <v>277</v>
+        <v>328</v>
       </c>
       <c r="E3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>疑是地上霜</v>
+        <v>太冰了</v>
       </c>
       <c r="F3" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>疑是地上霜</v>
-      </c>
-      <c r="H3" t="s">
-        <v>283</v>
+        <v>太冰了</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>50002</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>284</v>
-      </c>
+        <v>40002</v>
+      </c>
+      <c r="B4" s="11"/>
       <c r="C4" s="6"/>
-      <c r="D4" t="s">
-        <v>278</v>
-      </c>
-      <c r="E4" s="6" t="str">
+      <c r="E4" s="6">
         <f t="shared" si="0"/>
-        <v>举头望明月</v>
-      </c>
-      <c r="F4" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
         <f t="shared" si="1"/>
-        <v>举头望明月</v>
-      </c>
-      <c r="H4" t="s">
-        <v>287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>50003</v>
       </c>
-      <c r="B5" t="s">
-        <v>285</v>
-      </c>
       <c r="C5" s="6"/>
-      <c r="D5" t="s">
-        <v>279</v>
-      </c>
-      <c r="E5" s="6" t="str">
+      <c r="E5" s="6">
         <f t="shared" si="0"/>
-        <v>低头思故乡</v>
-      </c>
-      <c r="F5" s="6" t="str">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
         <f t="shared" si="1"/>
-        <v>低头思故乡</v>
-      </c>
-      <c r="H5" t="s">
-        <v>286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>50004</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>275</v>
-      </c>
+      <c r="C6" s="6"/>
       <c r="E6" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -16714,9 +21796,7 @@
       <c r="A7">
         <v>50005</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>275</v>
-      </c>
+      <c r="C7" s="6"/>
       <c r="E7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -16730,9 +21810,7 @@
       <c r="A8">
         <v>50006</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>275</v>
-      </c>
+      <c r="C8" s="6"/>
       <c r="E8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -16746,9 +21824,7 @@
       <c r="A9">
         <v>50007</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>275</v>
-      </c>
+      <c r="C9" s="6"/>
       <c r="E9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -16917,15 +21993,12 @@
       <c r="A21">
         <v>50019</v>
       </c>
-      <c r="C21" t="s">
-        <v>250</v>
-      </c>
       <c r="E21" s="6">
-        <f t="shared" ref="E21:E73" si="2">B21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F21" s="6">
-        <f t="shared" ref="F21:F73" si="3">B21</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -16934,14 +22007,14 @@
         <v>50020</v>
       </c>
       <c r="C22" t="s">
-        <v>250</v>
+        <v>324</v>
       </c>
       <c r="E22" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F22" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -16954,11 +22027,11 @@
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F23" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -16971,11 +22044,11 @@
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F24" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -16987,11 +22060,11 @@
         <v>250</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F25" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17003,11 +22076,11 @@
         <v>250</v>
       </c>
       <c r="E26" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F26" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17019,11 +22092,11 @@
         <v>250</v>
       </c>
       <c r="E27" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F27" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17035,11 +22108,11 @@
         <v>250</v>
       </c>
       <c r="E28" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F28" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17051,11 +22124,11 @@
         <v>250</v>
       </c>
       <c r="E29" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F29" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17067,11 +22140,11 @@
         <v>250</v>
       </c>
       <c r="E30" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17083,11 +22156,11 @@
         <v>250</v>
       </c>
       <c r="E31" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17099,11 +22172,11 @@
         <v>250</v>
       </c>
       <c r="E32" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F32" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17115,11 +22188,11 @@
         <v>250</v>
       </c>
       <c r="E33" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F33" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17131,11 +22204,11 @@
         <v>250</v>
       </c>
       <c r="E34" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F34" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17147,11 +22220,11 @@
         <v>250</v>
       </c>
       <c r="E35" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F35" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17163,11 +22236,11 @@
         <v>250</v>
       </c>
       <c r="E36" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F36" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17179,11 +22252,11 @@
         <v>250</v>
       </c>
       <c r="E37" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F37" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17195,11 +22268,11 @@
         <v>250</v>
       </c>
       <c r="E38" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F38" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17211,11 +22284,11 @@
         <v>250</v>
       </c>
       <c r="E39" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F39" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17227,11 +22300,11 @@
         <v>250</v>
       </c>
       <c r="E40" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F40" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17243,11 +22316,11 @@
         <v>250</v>
       </c>
       <c r="E41" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F41" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17259,11 +22332,11 @@
         <v>250</v>
       </c>
       <c r="E42" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F42" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17275,11 +22348,11 @@
         <v>250</v>
       </c>
       <c r="E43" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F43" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17291,11 +22364,11 @@
         <v>250</v>
       </c>
       <c r="E44" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F44" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17307,11 +22380,11 @@
         <v>250</v>
       </c>
       <c r="E45" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F45" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17324,11 +22397,11 @@
         <v>250</v>
       </c>
       <c r="E46" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F46" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17340,11 +22413,11 @@
         <v>250</v>
       </c>
       <c r="E47" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F47" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17357,11 +22430,11 @@
         <v>250</v>
       </c>
       <c r="E48" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F48" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17374,11 +22447,11 @@
         <v>250</v>
       </c>
       <c r="E49" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F49" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17390,11 +22463,11 @@
         <v>250</v>
       </c>
       <c r="E50" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F50" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17406,11 +22479,11 @@
         <v>250</v>
       </c>
       <c r="E51" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F51" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17423,11 +22496,11 @@
         <v>250</v>
       </c>
       <c r="E52" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F52" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17440,11 +22513,11 @@
         <v>250</v>
       </c>
       <c r="E53" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F53" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17457,11 +22530,11 @@
         <v>250</v>
       </c>
       <c r="E54" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F54" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17474,11 +22547,11 @@
         <v>250</v>
       </c>
       <c r="E55" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F55" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17491,11 +22564,11 @@
         <v>250</v>
       </c>
       <c r="E56" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F56" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17507,11 +22580,11 @@
         <v>250</v>
       </c>
       <c r="E57" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F57" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17524,11 +22597,11 @@
         <v>250</v>
       </c>
       <c r="E58" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F58" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17540,11 +22613,11 @@
         <v>250</v>
       </c>
       <c r="E59" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F59" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17556,11 +22629,11 @@
         <v>250</v>
       </c>
       <c r="E60" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F60" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17572,11 +22645,11 @@
         <v>250</v>
       </c>
       <c r="E61" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F61" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17588,11 +22661,11 @@
         <v>250</v>
       </c>
       <c r="E62" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F62" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17604,11 +22677,11 @@
         <v>250</v>
       </c>
       <c r="E63" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F63" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17620,11 +22693,11 @@
         <v>250</v>
       </c>
       <c r="E64" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F64" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17636,11 +22709,11 @@
         <v>250</v>
       </c>
       <c r="E65" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F65" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -17652,11 +22725,11 @@
         <v>250</v>
       </c>
       <c r="E66" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E66:E129" si="2">B66</f>
         <v>0</v>
       </c>
       <c r="F66" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F66:F129" si="3">B66</f>
         <v>0</v>
       </c>
     </row>
@@ -17781,11 +22854,11 @@
         <v>250</v>
       </c>
       <c r="E74" s="6">
-        <f t="shared" ref="E74:E137" si="4">B74</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F74" s="6">
-        <f t="shared" ref="F74:F137" si="5">B74</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17797,11 +22870,11 @@
         <v>250</v>
       </c>
       <c r="E75" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F75" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17813,11 +22886,11 @@
         <v>250</v>
       </c>
       <c r="E76" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F76" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17829,11 +22902,11 @@
         <v>250</v>
       </c>
       <c r="E77" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F77" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17845,11 +22918,11 @@
         <v>250</v>
       </c>
       <c r="E78" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F78" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17861,11 +22934,11 @@
         <v>250</v>
       </c>
       <c r="E79" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F79" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17877,11 +22950,11 @@
         <v>250</v>
       </c>
       <c r="E80" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F80" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17893,11 +22966,11 @@
         <v>250</v>
       </c>
       <c r="E81" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F81" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17909,11 +22982,11 @@
         <v>250</v>
       </c>
       <c r="E82" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F82" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17925,11 +22998,11 @@
         <v>250</v>
       </c>
       <c r="E83" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F83" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17941,11 +23014,11 @@
         <v>250</v>
       </c>
       <c r="E84" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F84" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17957,11 +23030,11 @@
         <v>250</v>
       </c>
       <c r="E85" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F85" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17973,11 +23046,11 @@
         <v>250</v>
       </c>
       <c r="E86" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F86" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -17989,11 +23062,11 @@
         <v>250</v>
       </c>
       <c r="E87" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F87" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18005,11 +23078,11 @@
         <v>250</v>
       </c>
       <c r="E88" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F88" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18021,11 +23094,11 @@
         <v>250</v>
       </c>
       <c r="E89" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F89" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18037,11 +23110,11 @@
         <v>250</v>
       </c>
       <c r="E90" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F90" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18053,11 +23126,11 @@
         <v>250</v>
       </c>
       <c r="E91" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F91" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18069,11 +23142,11 @@
         <v>250</v>
       </c>
       <c r="E92" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F92" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18085,11 +23158,11 @@
         <v>250</v>
       </c>
       <c r="E93" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F93" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18101,11 +23174,11 @@
         <v>250</v>
       </c>
       <c r="E94" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F94" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18117,11 +23190,11 @@
         <v>250</v>
       </c>
       <c r="E95" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F95" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18133,11 +23206,11 @@
         <v>250</v>
       </c>
       <c r="E96" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F96" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18149,11 +23222,11 @@
         <v>250</v>
       </c>
       <c r="E97" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F97" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18165,11 +23238,11 @@
         <v>250</v>
       </c>
       <c r="E98" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F98" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18181,11 +23254,11 @@
         <v>250</v>
       </c>
       <c r="E99" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F99" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18197,11 +23270,11 @@
         <v>250</v>
       </c>
       <c r="E100" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F100" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18213,11 +23286,11 @@
         <v>250</v>
       </c>
       <c r="E101" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F101" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18229,11 +23302,11 @@
         <v>250</v>
       </c>
       <c r="E102" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F102" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18245,11 +23318,11 @@
         <v>250</v>
       </c>
       <c r="E103" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F103" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18261,11 +23334,11 @@
         <v>250</v>
       </c>
       <c r="E104" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F104" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18277,11 +23350,11 @@
         <v>250</v>
       </c>
       <c r="E105" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F105" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18293,11 +23366,11 @@
         <v>250</v>
       </c>
       <c r="E106" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F106" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18309,11 +23382,11 @@
         <v>250</v>
       </c>
       <c r="E107" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F107" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18325,11 +23398,11 @@
         <v>250</v>
       </c>
       <c r="E108" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F108" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18341,11 +23414,11 @@
         <v>250</v>
       </c>
       <c r="E109" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F109" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18357,11 +23430,11 @@
         <v>250</v>
       </c>
       <c r="E110" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F110" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18373,11 +23446,11 @@
         <v>250</v>
       </c>
       <c r="E111" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F111" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18389,11 +23462,11 @@
         <v>250</v>
       </c>
       <c r="E112" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F112" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18405,11 +23478,11 @@
         <v>250</v>
       </c>
       <c r="E113" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F113" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18421,11 +23494,11 @@
         <v>250</v>
       </c>
       <c r="E114" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F114" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18437,11 +23510,11 @@
         <v>250</v>
       </c>
       <c r="E115" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F115" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18453,11 +23526,11 @@
         <v>250</v>
       </c>
       <c r="E116" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F116" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18469,11 +23542,11 @@
         <v>250</v>
       </c>
       <c r="E117" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F117" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18485,11 +23558,11 @@
         <v>250</v>
       </c>
       <c r="E118" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F118" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18501,11 +23574,11 @@
         <v>250</v>
       </c>
       <c r="E119" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F119" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18517,11 +23590,11 @@
         <v>250</v>
       </c>
       <c r="E120" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F120" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18533,11 +23606,11 @@
         <v>250</v>
       </c>
       <c r="E121" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F121" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18549,11 +23622,11 @@
         <v>250</v>
       </c>
       <c r="E122" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F122" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18565,11 +23638,11 @@
         <v>250</v>
       </c>
       <c r="E123" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F123" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18581,11 +23654,11 @@
         <v>250</v>
       </c>
       <c r="E124" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F124" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18597,11 +23670,11 @@
         <v>250</v>
       </c>
       <c r="E125" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F125" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18613,11 +23686,11 @@
         <v>250</v>
       </c>
       <c r="E126" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F126" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18629,11 +23702,11 @@
         <v>250</v>
       </c>
       <c r="E127" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F127" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18645,11 +23718,11 @@
         <v>250</v>
       </c>
       <c r="E128" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F128" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18661,11 +23734,11 @@
         <v>250</v>
       </c>
       <c r="E129" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F129" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -18677,11 +23750,11 @@
         <v>250</v>
       </c>
       <c r="E130" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E130:E193" si="4">B130</f>
         <v>0</v>
       </c>
       <c r="F130" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="F130:F193" si="5">B130</f>
         <v>0</v>
       </c>
     </row>
@@ -18805,11 +23878,11 @@
         <v>250</v>
       </c>
       <c r="E138" s="6">
-        <f t="shared" ref="E138:E201" si="6">B138</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F138" s="6">
-        <f t="shared" ref="F138:F201" si="7">B138</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18821,11 +23894,11 @@
         <v>250</v>
       </c>
       <c r="E139" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F139" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18837,11 +23910,11 @@
         <v>250</v>
       </c>
       <c r="E140" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F140" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18853,11 +23926,11 @@
         <v>250</v>
       </c>
       <c r="E141" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F141" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18869,11 +23942,11 @@
         <v>250</v>
       </c>
       <c r="E142" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F142" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18885,11 +23958,11 @@
         <v>250</v>
       </c>
       <c r="E143" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F143" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18901,11 +23974,11 @@
         <v>250</v>
       </c>
       <c r="E144" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F144" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18917,11 +23990,11 @@
         <v>250</v>
       </c>
       <c r="E145" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F145" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18933,11 +24006,11 @@
         <v>250</v>
       </c>
       <c r="E146" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F146" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18949,11 +24022,11 @@
         <v>250</v>
       </c>
       <c r="E147" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F147" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18965,11 +24038,11 @@
         <v>250</v>
       </c>
       <c r="E148" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F148" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18981,11 +24054,11 @@
         <v>250</v>
       </c>
       <c r="E149" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F149" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -18997,11 +24070,11 @@
         <v>250</v>
       </c>
       <c r="E150" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F150" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19013,11 +24086,11 @@
         <v>250</v>
       </c>
       <c r="E151" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F151" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19029,11 +24102,11 @@
         <v>250</v>
       </c>
       <c r="E152" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F152" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19045,11 +24118,11 @@
         <v>250</v>
       </c>
       <c r="E153" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F153" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19061,11 +24134,11 @@
         <v>250</v>
       </c>
       <c r="E154" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F154" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19077,11 +24150,11 @@
         <v>250</v>
       </c>
       <c r="E155" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F155" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19093,11 +24166,11 @@
         <v>250</v>
       </c>
       <c r="E156" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F156" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19109,11 +24182,11 @@
         <v>250</v>
       </c>
       <c r="E157" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F157" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19125,11 +24198,11 @@
         <v>250</v>
       </c>
       <c r="E158" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F158" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19141,11 +24214,11 @@
         <v>250</v>
       </c>
       <c r="E159" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F159" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19157,11 +24230,11 @@
         <v>250</v>
       </c>
       <c r="E160" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F160" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19173,11 +24246,11 @@
         <v>250</v>
       </c>
       <c r="E161" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F161" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19189,11 +24262,11 @@
         <v>250</v>
       </c>
       <c r="E162" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F162" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19205,11 +24278,11 @@
         <v>250</v>
       </c>
       <c r="E163" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F163" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19221,11 +24294,11 @@
         <v>250</v>
       </c>
       <c r="E164" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F164" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19237,11 +24310,11 @@
         <v>250</v>
       </c>
       <c r="E165" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F165" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19253,11 +24326,11 @@
         <v>250</v>
       </c>
       <c r="E166" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F166" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19269,11 +24342,11 @@
         <v>250</v>
       </c>
       <c r="E167" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F167" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19285,11 +24358,11 @@
         <v>250</v>
       </c>
       <c r="E168" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F168" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19301,11 +24374,11 @@
         <v>250</v>
       </c>
       <c r="E169" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F169" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19317,11 +24390,11 @@
         <v>250</v>
       </c>
       <c r="E170" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F170" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19333,11 +24406,11 @@
         <v>250</v>
       </c>
       <c r="E171" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F171" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19349,11 +24422,11 @@
         <v>250</v>
       </c>
       <c r="E172" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F172" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19365,11 +24438,11 @@
         <v>250</v>
       </c>
       <c r="E173" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F173" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19381,11 +24454,11 @@
         <v>250</v>
       </c>
       <c r="E174" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F174" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19397,11 +24470,11 @@
         <v>250</v>
       </c>
       <c r="E175" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F175" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19413,11 +24486,11 @@
         <v>250</v>
       </c>
       <c r="E176" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F176" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19429,11 +24502,11 @@
         <v>250</v>
       </c>
       <c r="E177" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F177" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19445,11 +24518,11 @@
         <v>250</v>
       </c>
       <c r="E178" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F178" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19461,11 +24534,11 @@
         <v>250</v>
       </c>
       <c r="E179" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F179" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19477,11 +24550,11 @@
         <v>250</v>
       </c>
       <c r="E180" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F180" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19493,11 +24566,11 @@
         <v>250</v>
       </c>
       <c r="E181" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F181" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19509,11 +24582,11 @@
         <v>250</v>
       </c>
       <c r="E182" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F182" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19525,11 +24598,11 @@
         <v>250</v>
       </c>
       <c r="E183" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F183" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19541,11 +24614,11 @@
         <v>250</v>
       </c>
       <c r="E184" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F184" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19557,11 +24630,11 @@
         <v>250</v>
       </c>
       <c r="E185" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F185" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19573,11 +24646,11 @@
         <v>250</v>
       </c>
       <c r="E186" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F186" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19589,11 +24662,11 @@
         <v>250</v>
       </c>
       <c r="E187" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F187" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19605,11 +24678,11 @@
         <v>250</v>
       </c>
       <c r="E188" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F188" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19621,11 +24694,11 @@
         <v>250</v>
       </c>
       <c r="E189" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F189" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19637,11 +24710,11 @@
         <v>250</v>
       </c>
       <c r="E190" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F190" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19653,11 +24726,11 @@
         <v>250</v>
       </c>
       <c r="E191" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F191" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19669,11 +24742,11 @@
         <v>250</v>
       </c>
       <c r="E192" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F192" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19685,11 +24758,11 @@
         <v>250</v>
       </c>
       <c r="E193" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F193" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -19701,11 +24774,11 @@
         <v>250</v>
       </c>
       <c r="E194" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="E194:E257" si="6">B194</f>
         <v>0</v>
       </c>
       <c r="F194" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="F194:F257" si="7">B194</f>
         <v>0</v>
       </c>
     </row>
@@ -19829,11 +24902,11 @@
         <v>250</v>
       </c>
       <c r="E202" s="6">
-        <f t="shared" ref="E202:E210" si="8">B202</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F202" s="6">
-        <f t="shared" ref="F202:F210" si="9">B202</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19845,11 +24918,11 @@
         <v>250</v>
       </c>
       <c r="E203" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F203" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19861,11 +24934,11 @@
         <v>250</v>
       </c>
       <c r="E204" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F204" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19877,11 +24950,11 @@
         <v>250</v>
       </c>
       <c r="E205" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F205" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19893,11 +24966,11 @@
         <v>250</v>
       </c>
       <c r="E206" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F206" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19909,11 +24982,11 @@
         <v>250</v>
       </c>
       <c r="E207" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F207" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19925,11 +24998,11 @@
         <v>250</v>
       </c>
       <c r="E208" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F208" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19941,11 +25014,11 @@
         <v>250</v>
       </c>
       <c r="E209" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F209" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -19957,11 +25030,11 @@
         <v>250</v>
       </c>
       <c r="E210" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F210" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038E6642-70F9-4206-A439-76459D869B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD96CE48-CB92-4749-9344-A62B944C9746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10260" yWindow="3885" windowWidth="32745" windowHeight="12480" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="6">
-        <f t="shared" ref="E13:E16" si="2">B14</f>
+        <f t="shared" ref="E14:E16" si="2">B14</f>
         <v>0</v>
       </c>
       <c r="F14" s="6">
@@ -24774,11 +24774,11 @@
         <v>250</v>
       </c>
       <c r="E194" s="6">
-        <f t="shared" ref="E194:E257" si="6">B194</f>
+        <f t="shared" ref="E194:E210" si="6">B194</f>
         <v>0</v>
       </c>
       <c r="F194" s="6">
-        <f t="shared" ref="F194:F257" si="7">B194</f>
+        <f t="shared" ref="F194:F210" si="7">B194</f>
         <v>0</v>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD96CE48-CB92-4749-9344-A62B944C9746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B640C65A-49F0-40B4-B425-4D297DD054A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25845" yWindow="3840" windowWidth="32745" windowHeight="17535" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -1730,12 +1730,6 @@
     <t>哪样</t>
   </si>
   <si>
-    <t>이렇게</t>
-  </si>
-  <si>
-    <t>그렇게</t>
-  </si>
-  <si>
     <t>어떤 식으로</t>
   </si>
   <si>
@@ -1989,9 +1983,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>太冰了</t>
-  </si>
-  <si>
     <r>
       <t>太</t>
     </r>
@@ -2057,6 +2048,18 @@
       </rPr>
       <t>"</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그런</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太冷了</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3457,7 +3460,7 @@
         <v>50020</v>
       </c>
       <c r="C22" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="2"/>
@@ -7666,13 +7669,13 @@
         <v>100004</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E6" s="6" t="str">
         <f t="shared" si="2"/>
@@ -7688,13 +7691,13 @@
         <v>100005</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E7" s="6" t="str">
         <f t="shared" si="2"/>
@@ -7710,13 +7713,13 @@
         <v>100006</v>
       </c>
       <c r="B8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E8" s="6" t="str">
         <f t="shared" si="2"/>
@@ -7732,13 +7735,13 @@
         <v>100007</v>
       </c>
       <c r="B9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E9" s="6" t="str">
         <f t="shared" si="2"/>
@@ -8045,13 +8048,13 @@
         <v>300000</v>
       </c>
       <c r="B2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2" t="s">
         <v>308</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D2" t="s">
-        <v>310</v>
       </c>
       <c r="E2" s="6" t="str">
         <f t="shared" ref="E2:E5" si="0">B2</f>
@@ -8067,13 +8070,13 @@
         <v>300001</v>
       </c>
       <c r="B3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E3" s="6" t="str">
         <f t="shared" si="0"/>
@@ -8389,13 +8392,13 @@
         <v>3003</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C5" t="s">
         <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E5" s="6" t="str">
         <f>B5</f>
@@ -8874,7 +8877,7 @@
         <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -8889,13 +8892,13 @@
         <v>5019</v>
       </c>
       <c r="B11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C11" t="s">
         <v>115</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>50</v>
@@ -8913,10 +8916,10 @@
         <v>288</v>
       </c>
       <c r="C12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>50</v>
@@ -8931,13 +8934,13 @@
         <v>5021</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>50</v>
@@ -10431,13 +10434,13 @@
         <v>20117</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C61" t="s">
         <v>73</v>
       </c>
       <c r="D61" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E61" s="6" t="str">
         <f>B61</f>
@@ -10448,7 +10451,7 @@
         <v>发型</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -10456,13 +10459,13 @@
         <v>20118</v>
       </c>
       <c r="B62" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C62" t="s">
         <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E62" s="6" t="str">
         <f t="shared" si="5"/>
@@ -10473,7 +10476,7 @@
         <v>短发</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -10481,16 +10484,16 @@
         <v>20119</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C63" t="s">
         <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E63" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f>B63</f>
         <v>韩式</v>
       </c>
       <c r="F63" s="6" t="str">
@@ -10503,16 +10506,16 @@
         <v>20120</v>
       </c>
       <c r="B64" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C64" t="s">
         <v>73</v>
       </c>
       <c r="D64" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E64" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f>B64</f>
         <v>水温</v>
       </c>
       <c r="F64" s="6" t="str">
@@ -17548,13 +17551,13 @@
         <v>30134</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C21" t="s">
         <v>250</v>
       </c>
       <c r="D21" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E21" s="6" t="str">
         <f t="shared" si="2"/>
@@ -17570,13 +17573,13 @@
         <v>30135</v>
       </c>
       <c r="B22" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
         <v>250</v>
       </c>
       <c r="D22" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E22" s="6" t="str">
         <f t="shared" si="2"/>
@@ -21710,13 +21713,13 @@
         <v>40000</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D2" t="s">
         <v>324</v>
-      </c>
-      <c r="D2" t="s">
-        <v>327</v>
       </c>
       <c r="E2" s="6" t="str">
         <f t="shared" ref="E2:E65" si="0">B2</f>
@@ -21732,21 +21735,21 @@
         <v>40001</v>
       </c>
       <c r="B3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D3" t="s">
         <v>325</v>
-      </c>
-      <c r="C3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D3" t="s">
-        <v>328</v>
       </c>
       <c r="E3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>太冰了</v>
+        <v>太冷了</v>
       </c>
       <c r="F3" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>太冰了</v>
+        <v>太冷了</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -22007,7 +22010,7 @@
         <v>50020</v>
       </c>
       <c r="C22" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="0"/>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B640C65A-49F0-40B4-B425-4D297DD054A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F49DFA3-BC60-40A1-8625-D8736CEA6974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25845" yWindow="3840" windowWidth="32745" windowHeight="17535" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F49DFA3-BC60-40A1-8625-D8736CEA6974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBEF167-4D15-4819-8926-936BD55E7EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="338">
   <si>
     <t>사과</t>
   </si>
@@ -2060,6 +2060,136 @@
   </si>
   <si>
     <t>太冷了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>山</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>月明夜</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>上戍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>楼抚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>大刀</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>深愁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时何处</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>어디선가 들려오는 피리 소리가 시름을 더하는구나</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>声</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>羌笛更添愁</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>깊은 시름에 잠긴 이때</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수루에 올라 큰 칼을 어루만지니</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>한산섬 달 밝은 밤에</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3099,7 +3229,7 @@
     <col min="3" max="3" width="21.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.5" customWidth="1"/>
     <col min="5" max="5" width="43.125" customWidth="1"/>
-    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30.375" bestFit="1" customWidth="1"/>
   </cols>
@@ -3249,55 +3379,79 @@
       <c r="A7">
         <v>50005</v>
       </c>
+      <c r="B7" s="11" t="s">
+        <v>330</v>
+      </c>
       <c r="C7" s="6"/>
-      <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="D7" t="s">
+        <v>337</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f>B7</f>
+        <v>闲山岛月明夜</v>
+      </c>
+      <c r="F7" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>闲山岛月明夜</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>50006</v>
       </c>
+      <c r="B8" t="s">
+        <v>331</v>
+      </c>
       <c r="C8" s="6"/>
-      <c r="E8" s="6">
+      <c r="D8" t="s">
+        <v>336</v>
+      </c>
+      <c r="E8" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
+        <v>上戍楼抚大刀</v>
+      </c>
+      <c r="F8" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>上戍楼抚大刀</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>50007</v>
       </c>
+      <c r="B9" t="s">
+        <v>332</v>
+      </c>
       <c r="C9" s="6"/>
-      <c r="E9" s="6">
+      <c r="D9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E9" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
+        <v>深愁时何处</v>
+      </c>
+      <c r="F9" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>深愁时何处</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>50008</v>
       </c>
-      <c r="E10" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="B10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D10" t="s">
+        <v>333</v>
+      </c>
+      <c r="E10" s="6" t="str">
+        <f>B10</f>
+        <v>一声羌笛更添愁</v>
+      </c>
+      <c r="F10" s="6" t="str">
+        <f>B10</f>
+        <v>一声羌笛更添愁</v>
       </c>
       <c r="I10" s="21"/>
     </row>
@@ -3305,7 +3459,7 @@
       <c r="A11">
         <v>50009</v>
       </c>
-      <c r="B11" s="17"/>
+      <c r="B11" s="12"/>
       <c r="E11" s="6">
         <f t="shared" si="0"/>
         <v>0</v>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBEF167-4D15-4819-8926-936BD55E7EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8B6DBC-3618-416C-B31A-C33730C86563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38250" yWindow="1635" windowWidth="32745" windowHeight="17535" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -2059,10 +2059,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>太冷了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2190,6 +2186,10 @@
   </si>
   <si>
     <t>한산섬 달 밝은 밤에</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太凉了</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3380,11 +3380,11 @@
         <v>50005</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E7" s="6" t="str">
         <f>B7</f>
@@ -3400,11 +3400,11 @@
         <v>50006</v>
       </c>
       <c r="B8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E8" s="6" t="str">
         <f t="shared" si="0"/>
@@ -3420,11 +3420,11 @@
         <v>50007</v>
       </c>
       <c r="B9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E9" s="6" t="str">
         <f t="shared" si="0"/>
@@ -3440,10 +3440,10 @@
         <v>50008</v>
       </c>
       <c r="B10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E10" s="6" t="str">
         <f>B10</f>
@@ -21889,7 +21889,7 @@
         <v>40001</v>
       </c>
       <c r="B3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C3" t="s">
         <v>322</v>
@@ -21899,11 +21899,11 @@
       </c>
       <c r="E3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>太冷了</v>
+        <v>太凉了</v>
       </c>
       <c r="F3" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>太冷了</v>
+        <v>太凉了</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8B6DBC-3618-416C-B31A-C33730C86563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED4CF18-A320-4D31-B4C8-93557E29DF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38250" yWindow="1635" windowWidth="32745" windowHeight="17535" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34725" yWindow="8310" windowWidth="32745" windowHeight="17535" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="343">
   <si>
     <t>사과</t>
   </si>
@@ -2190,6 +2190,114 @@
   </si>
   <si>
     <t>太凉了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闲山岛月明夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上戍楼抚大刀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深愁时何处</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一声羌笛更添愁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3276,7 +3384,9 @@
       <c r="B2" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="D2" t="s">
         <v>275</v>
       </c>
@@ -3299,7 +3409,9 @@
       <c r="B3" t="s">
         <v>280</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="D3" t="s">
         <v>276</v>
       </c>
@@ -3322,7 +3434,9 @@
       <c r="B4" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="D4" t="s">
         <v>277</v>
       </c>
@@ -3345,7 +3459,9 @@
       <c r="B5" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="D5" t="s">
         <v>278</v>
       </c>
@@ -3365,7 +3481,9 @@
       <c r="A6">
         <v>50004</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="E6" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3382,7 +3500,9 @@
       <c r="B7" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="D7" t="s">
         <v>336</v>
       </c>
@@ -3394,6 +3514,9 @@
         <f t="shared" si="1"/>
         <v>闲山岛月明夜</v>
       </c>
+      <c r="H7" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -3402,7 +3525,9 @@
       <c r="B8" t="s">
         <v>330</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="D8" t="s">
         <v>335</v>
       </c>
@@ -3414,6 +3539,9 @@
         <f t="shared" si="1"/>
         <v>上戍楼抚大刀</v>
       </c>
+      <c r="H8" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -3422,7 +3550,9 @@
       <c r="B9" t="s">
         <v>331</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="D9" t="s">
         <v>334</v>
       </c>
@@ -3434,6 +3564,9 @@
         <f t="shared" si="1"/>
         <v>深愁时何处</v>
       </c>
+      <c r="H9" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A10">
@@ -3442,6 +3575,9 @@
       <c r="B10" t="s">
         <v>333</v>
       </c>
+      <c r="C10" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="D10" t="s">
         <v>332</v>
       </c>
@@ -3452,6 +3588,9 @@
       <c r="F10" s="6" t="str">
         <f>B10</f>
         <v>一声羌笛更添愁</v>
+      </c>
+      <c r="H10" t="s">
+        <v>342</v>
       </c>
       <c r="I10" s="21"/>
     </row>
@@ -21876,11 +22015,11 @@
         <v>324</v>
       </c>
       <c r="E2" s="6" t="str">
-        <f t="shared" ref="E2:E65" si="0">B2</f>
+        <f t="shared" ref="E2:E4" si="0">B2</f>
         <v>太烫了</v>
       </c>
       <c r="F2" s="6" t="str">
-        <f t="shared" ref="F2:F65" si="1">B2</f>
+        <f t="shared" ref="F2:F4" si="1">B2</f>
         <v>太烫了</v>
       </c>
     </row>
@@ -21922,3332 +22061,911 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>50003</v>
-      </c>
       <c r="C5" s="6"/>
-      <c r="E5" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>50004</v>
-      </c>
       <c r="C6" s="6"/>
-      <c r="E6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>50005</v>
-      </c>
       <c r="C7" s="6"/>
-      <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>50006</v>
-      </c>
       <c r="C8" s="6"/>
-      <c r="E8" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>50007</v>
-      </c>
       <c r="C9" s="6"/>
-      <c r="E9" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>50008</v>
-      </c>
-      <c r="E10" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
       <c r="I10" s="21"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>50009</v>
-      </c>
       <c r="B11" s="17"/>
-      <c r="E11" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
       <c r="H11" s="11"/>
       <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>50010</v>
-      </c>
       <c r="B12" s="12"/>
-      <c r="E12" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
       <c r="H12" s="11"/>
       <c r="I12" s="21"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>50011</v>
-      </c>
-      <c r="E13" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>50012</v>
-      </c>
       <c r="B14" s="17"/>
-      <c r="E14" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
       <c r="H14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A15">
-        <v>50013</v>
-      </c>
       <c r="B15" s="18"/>
-      <c r="E15" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
       <c r="H15" s="14"/>
       <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>50014</v>
-      </c>
-      <c r="E16" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>50015</v>
-      </c>
-      <c r="E17" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>50016</v>
-      </c>
-      <c r="E18" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>50017</v>
-      </c>
-      <c r="E19" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>50018</v>
-      </c>
-      <c r="E20" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>50019</v>
-      </c>
-      <c r="E21" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>50020</v>
-      </c>
-      <c r="C22" t="s">
-        <v>322</v>
-      </c>
-      <c r="E22" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>50021</v>
-      </c>
-      <c r="C23" t="s">
-        <v>250</v>
-      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D23" s="13"/>
-      <c r="E23" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>50022</v>
-      </c>
-      <c r="C24" t="s">
-        <v>250</v>
-      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D24" s="13"/>
-      <c r="E24" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>50023</v>
-      </c>
-      <c r="C25" t="s">
-        <v>250</v>
-      </c>
-      <c r="E25" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>50024</v>
-      </c>
-      <c r="C26" t="s">
-        <v>250</v>
-      </c>
-      <c r="E26" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>50025</v>
-      </c>
-      <c r="C27" t="s">
-        <v>250</v>
-      </c>
-      <c r="E27" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>50026</v>
-      </c>
-      <c r="C28" t="s">
-        <v>250</v>
-      </c>
-      <c r="E28" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>50027</v>
-      </c>
-      <c r="C29" t="s">
-        <v>250</v>
-      </c>
-      <c r="E29" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>50028</v>
-      </c>
-      <c r="C30" t="s">
-        <v>250</v>
-      </c>
-      <c r="E30" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>50029</v>
-      </c>
-      <c r="C31" t="s">
-        <v>250</v>
-      </c>
-      <c r="E31" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>50030</v>
-      </c>
-      <c r="C32" t="s">
-        <v>250</v>
-      </c>
-      <c r="E32" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>50031</v>
-      </c>
-      <c r="C33" t="s">
-        <v>250</v>
-      </c>
-      <c r="E33" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>50032</v>
-      </c>
-      <c r="C34" t="s">
-        <v>250</v>
-      </c>
-      <c r="E34" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>50033</v>
-      </c>
-      <c r="C35" t="s">
-        <v>250</v>
-      </c>
-      <c r="E35" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>50034</v>
-      </c>
-      <c r="C36" t="s">
-        <v>250</v>
-      </c>
-      <c r="E36" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>50035</v>
-      </c>
-      <c r="C37" t="s">
-        <v>250</v>
-      </c>
-      <c r="E37" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>50036</v>
-      </c>
-      <c r="C38" t="s">
-        <v>250</v>
-      </c>
-      <c r="E38" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>50037</v>
-      </c>
-      <c r="C39" t="s">
-        <v>250</v>
-      </c>
-      <c r="E39" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>50038</v>
-      </c>
-      <c r="C40" t="s">
-        <v>250</v>
-      </c>
-      <c r="E40" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>50039</v>
-      </c>
-      <c r="C41" t="s">
-        <v>250</v>
-      </c>
-      <c r="E41" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>50040</v>
-      </c>
-      <c r="C42" t="s">
-        <v>250</v>
-      </c>
-      <c r="E42" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>50041</v>
-      </c>
-      <c r="C43" t="s">
-        <v>250</v>
-      </c>
-      <c r="E43" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>50042</v>
-      </c>
-      <c r="C44" t="s">
-        <v>250</v>
-      </c>
-      <c r="E44" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>50043</v>
-      </c>
-      <c r="C45" t="s">
-        <v>250</v>
-      </c>
-      <c r="E45" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>50044</v>
-      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="12"/>
-      <c r="C46" t="s">
-        <v>250</v>
-      </c>
-      <c r="E46" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>50045</v>
-      </c>
-      <c r="C47" t="s">
-        <v>250</v>
-      </c>
-      <c r="E47" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>50046</v>
-      </c>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="13"/>
-      <c r="C48" t="s">
-        <v>250</v>
-      </c>
-      <c r="E48" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>50047</v>
-      </c>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="12"/>
-      <c r="C49" t="s">
-        <v>250</v>
-      </c>
-      <c r="E49" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>50048</v>
-      </c>
-      <c r="C50" t="s">
-        <v>250</v>
-      </c>
-      <c r="E50" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>50049</v>
-      </c>
-      <c r="C51" t="s">
-        <v>250</v>
-      </c>
-      <c r="E51" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>50050</v>
-      </c>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="12"/>
-      <c r="C52" t="s">
-        <v>250</v>
-      </c>
-      <c r="E52" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>50051</v>
-      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="12"/>
-      <c r="C53" t="s">
-        <v>250</v>
-      </c>
-      <c r="E53" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F53" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>50052</v>
-      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="12"/>
-      <c r="C54" t="s">
-        <v>250</v>
-      </c>
-      <c r="E54" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F54" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>50053</v>
-      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="12"/>
-      <c r="C55" t="s">
-        <v>250</v>
-      </c>
-      <c r="E55" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F55" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>50054</v>
-      </c>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="12"/>
-      <c r="C56" t="s">
-        <v>250</v>
-      </c>
-      <c r="E56" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F56" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>50055</v>
-      </c>
-      <c r="C57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E57" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F57" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>50056</v>
-      </c>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="12"/>
-      <c r="C58" t="s">
-        <v>250</v>
-      </c>
-      <c r="E58" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F58" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>50057</v>
-      </c>
-      <c r="C59" t="s">
-        <v>250</v>
-      </c>
-      <c r="E59" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F59" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>50058</v>
-      </c>
-      <c r="C60" t="s">
-        <v>250</v>
-      </c>
-      <c r="E60" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F60" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>50059</v>
-      </c>
-      <c r="C61" t="s">
-        <v>250</v>
-      </c>
-      <c r="E61" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F61" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>50060</v>
-      </c>
-      <c r="C62" t="s">
-        <v>250</v>
-      </c>
-      <c r="E62" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F62" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>50061</v>
-      </c>
-      <c r="C63" t="s">
-        <v>250</v>
-      </c>
-      <c r="E63" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F63" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>50062</v>
-      </c>
-      <c r="C64" t="s">
-        <v>250</v>
-      </c>
-      <c r="E64" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F64" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>50063</v>
-      </c>
-      <c r="C65" t="s">
-        <v>250</v>
-      </c>
-      <c r="E65" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F65" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>50064</v>
-      </c>
-      <c r="C66" t="s">
-        <v>250</v>
-      </c>
-      <c r="E66" s="6">
-        <f t="shared" ref="E66:E129" si="2">B66</f>
-        <v>0</v>
-      </c>
-      <c r="F66" s="6">
-        <f t="shared" ref="F66:F129" si="3">B66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>50065</v>
-      </c>
-      <c r="C67" t="s">
-        <v>250</v>
-      </c>
-      <c r="E67" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F67" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>50066</v>
-      </c>
-      <c r="C68" t="s">
-        <v>250</v>
-      </c>
-      <c r="E68" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F68" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>50067</v>
-      </c>
-      <c r="C69" t="s">
-        <v>250</v>
-      </c>
-      <c r="E69" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F69" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>50068</v>
-      </c>
-      <c r="C70" t="s">
-        <v>250</v>
-      </c>
-      <c r="E70" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F70" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>50069</v>
-      </c>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B71" s="12"/>
-      <c r="C71" t="s">
-        <v>250</v>
-      </c>
-      <c r="E71" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F71" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>50070</v>
-      </c>
-      <c r="C72" t="s">
-        <v>250</v>
-      </c>
-      <c r="E72" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F72" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>50071</v>
-      </c>
-      <c r="C73" t="s">
-        <v>250</v>
-      </c>
-      <c r="E73" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F73" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>50072</v>
-      </c>
-      <c r="C74" t="s">
-        <v>250</v>
-      </c>
-      <c r="E74" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F74" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>50073</v>
-      </c>
-      <c r="C75" t="s">
-        <v>250</v>
-      </c>
-      <c r="E75" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F75" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>50074</v>
-      </c>
-      <c r="C76" t="s">
-        <v>250</v>
-      </c>
-      <c r="E76" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>50075</v>
-      </c>
-      <c r="C77" t="s">
-        <v>250</v>
-      </c>
-      <c r="E77" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F77" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>50076</v>
-      </c>
-      <c r="C78" t="s">
-        <v>250</v>
-      </c>
-      <c r="E78" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F78" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>50077</v>
-      </c>
-      <c r="C79" t="s">
-        <v>250</v>
-      </c>
-      <c r="E79" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>50078</v>
-      </c>
-      <c r="C80" t="s">
-        <v>250</v>
-      </c>
-      <c r="E80" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F80" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>50079</v>
-      </c>
-      <c r="C81" t="s">
-        <v>250</v>
-      </c>
-      <c r="E81" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F81" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>50080</v>
-      </c>
-      <c r="C82" t="s">
-        <v>250</v>
-      </c>
-      <c r="E82" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F82" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <v>50081</v>
-      </c>
-      <c r="C83" t="s">
-        <v>250</v>
-      </c>
-      <c r="E83" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F83" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <v>50082</v>
-      </c>
-      <c r="C84" t="s">
-        <v>250</v>
-      </c>
-      <c r="E84" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F84" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <v>50083</v>
-      </c>
-      <c r="C85" t="s">
-        <v>250</v>
-      </c>
-      <c r="E85" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <v>50084</v>
-      </c>
-      <c r="C86" t="s">
-        <v>250</v>
-      </c>
-      <c r="E86" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F86" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>50085</v>
-      </c>
-      <c r="C87" t="s">
-        <v>250</v>
-      </c>
-      <c r="E87" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F87" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>50086</v>
-      </c>
-      <c r="C88" t="s">
-        <v>250</v>
-      </c>
-      <c r="E88" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F88" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>50087</v>
-      </c>
-      <c r="C89" t="s">
-        <v>250</v>
-      </c>
-      <c r="E89" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F89" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>50088</v>
-      </c>
-      <c r="C90" t="s">
-        <v>250</v>
-      </c>
-      <c r="E90" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F90" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>50089</v>
-      </c>
-      <c r="C91" t="s">
-        <v>250</v>
-      </c>
-      <c r="E91" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F91" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>50090</v>
-      </c>
-      <c r="C92" t="s">
-        <v>250</v>
-      </c>
-      <c r="E92" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F92" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>50091</v>
-      </c>
-      <c r="C93" t="s">
-        <v>250</v>
-      </c>
-      <c r="E93" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F93" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>50092</v>
-      </c>
-      <c r="C94" t="s">
-        <v>250</v>
-      </c>
-      <c r="E94" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F94" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>50093</v>
-      </c>
-      <c r="C95" t="s">
-        <v>250</v>
-      </c>
-      <c r="E95" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F95" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <v>50094</v>
-      </c>
-      <c r="C96" t="s">
-        <v>250</v>
-      </c>
-      <c r="E96" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F96" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>50095</v>
-      </c>
-      <c r="C97" t="s">
-        <v>250</v>
-      </c>
-      <c r="E97" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F97" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <v>50096</v>
-      </c>
-      <c r="C98" t="s">
-        <v>250</v>
-      </c>
-      <c r="E98" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F98" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <v>50097</v>
-      </c>
-      <c r="C99" t="s">
-        <v>250</v>
-      </c>
-      <c r="E99" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F99" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <v>50098</v>
-      </c>
-      <c r="C100" t="s">
-        <v>250</v>
-      </c>
-      <c r="E100" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F100" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>50099</v>
-      </c>
-      <c r="C101" t="s">
-        <v>250</v>
-      </c>
-      <c r="E101" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F101" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>50100</v>
-      </c>
-      <c r="C102" t="s">
-        <v>250</v>
-      </c>
-      <c r="E102" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F102" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>50101</v>
-      </c>
-      <c r="C103" t="s">
-        <v>250</v>
-      </c>
-      <c r="E103" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <v>50102</v>
-      </c>
-      <c r="C104" t="s">
-        <v>250</v>
-      </c>
-      <c r="E104" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F104" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <v>50103</v>
-      </c>
-      <c r="C105" t="s">
-        <v>250</v>
-      </c>
-      <c r="E105" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F105" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106">
-        <v>50104</v>
-      </c>
-      <c r="C106" t="s">
-        <v>250</v>
-      </c>
-      <c r="E106" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F106" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>50105</v>
-      </c>
-      <c r="C107" t="s">
-        <v>250</v>
-      </c>
-      <c r="E107" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F107" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108">
-        <v>50106</v>
-      </c>
-      <c r="C108" t="s">
-        <v>250</v>
-      </c>
-      <c r="E108" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F108" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <v>50107</v>
-      </c>
-      <c r="C109" t="s">
-        <v>250</v>
-      </c>
-      <c r="E109" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F109" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <v>50108</v>
-      </c>
-      <c r="C110" t="s">
-        <v>250</v>
-      </c>
-      <c r="E110" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F110" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>50109</v>
-      </c>
-      <c r="C111" t="s">
-        <v>250</v>
-      </c>
-      <c r="E111" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F111" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <v>50110</v>
-      </c>
-      <c r="C112" t="s">
-        <v>250</v>
-      </c>
-      <c r="E112" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F112" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <v>50111</v>
-      </c>
-      <c r="C113" t="s">
-        <v>250</v>
-      </c>
-      <c r="E113" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F113" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114">
-        <v>50112</v>
-      </c>
-      <c r="C114" t="s">
-        <v>250</v>
-      </c>
-      <c r="E114" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F114" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115">
-        <v>50113</v>
-      </c>
-      <c r="C115" t="s">
-        <v>250</v>
-      </c>
-      <c r="E115" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F115" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116">
-        <v>50114</v>
-      </c>
-      <c r="C116" t="s">
-        <v>250</v>
-      </c>
-      <c r="E116" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F116" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117">
-        <v>50115</v>
-      </c>
-      <c r="C117" t="s">
-        <v>250</v>
-      </c>
-      <c r="E117" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F117" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118">
-        <v>50116</v>
-      </c>
-      <c r="C118" t="s">
-        <v>250</v>
-      </c>
-      <c r="E118" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F118" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119">
-        <v>50117</v>
-      </c>
-      <c r="C119" t="s">
-        <v>250</v>
-      </c>
-      <c r="E119" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F119" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120">
-        <v>50118</v>
-      </c>
-      <c r="C120" t="s">
-        <v>250</v>
-      </c>
-      <c r="E120" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F120" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121">
-        <v>50119</v>
-      </c>
-      <c r="C121" t="s">
-        <v>250</v>
-      </c>
-      <c r="E121" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F121" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122">
-        <v>50120</v>
-      </c>
-      <c r="C122" t="s">
-        <v>250</v>
-      </c>
-      <c r="E122" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F122" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123">
-        <v>50121</v>
-      </c>
-      <c r="C123" t="s">
-        <v>250</v>
-      </c>
-      <c r="E123" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F123" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124">
-        <v>50122</v>
-      </c>
-      <c r="C124" t="s">
-        <v>250</v>
-      </c>
-      <c r="E124" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F124" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125">
-        <v>50123</v>
-      </c>
-      <c r="C125" t="s">
-        <v>250</v>
-      </c>
-      <c r="E125" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F125" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126">
-        <v>50124</v>
-      </c>
-      <c r="C126" t="s">
-        <v>250</v>
-      </c>
-      <c r="E126" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F126" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127">
-        <v>50125</v>
-      </c>
-      <c r="C127" t="s">
-        <v>250</v>
-      </c>
-      <c r="E127" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F127" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128">
-        <v>50126</v>
-      </c>
-      <c r="C128" t="s">
-        <v>250</v>
-      </c>
-      <c r="E128" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F128" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129">
-        <v>50127</v>
-      </c>
-      <c r="C129" t="s">
-        <v>250</v>
-      </c>
-      <c r="E129" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F129" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130">
-        <v>50128</v>
-      </c>
-      <c r="C130" t="s">
-        <v>250</v>
-      </c>
-      <c r="E130" s="6">
-        <f t="shared" ref="E130:E193" si="4">B130</f>
-        <v>0</v>
-      </c>
-      <c r="F130" s="6">
-        <f t="shared" ref="F130:F193" si="5">B130</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131">
-        <v>50129</v>
-      </c>
-      <c r="C131" t="s">
-        <v>250</v>
-      </c>
-      <c r="E131" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F131" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132">
-        <v>50130</v>
-      </c>
-      <c r="C132" t="s">
-        <v>250</v>
-      </c>
-      <c r="E132" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F132" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133">
-        <v>50131</v>
-      </c>
-      <c r="C133" t="s">
-        <v>250</v>
-      </c>
-      <c r="E133" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F133" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134">
-        <v>50132</v>
-      </c>
-      <c r="C134" t="s">
-        <v>250</v>
-      </c>
-      <c r="E134" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F134" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135">
-        <v>50133</v>
-      </c>
-      <c r="C135" t="s">
-        <v>250</v>
-      </c>
-      <c r="E135" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F135" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136">
-        <v>50134</v>
-      </c>
-      <c r="C136" t="s">
-        <v>250</v>
-      </c>
-      <c r="E136" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F136" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137">
-        <v>50135</v>
-      </c>
-      <c r="C137" t="s">
-        <v>250</v>
-      </c>
-      <c r="E137" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F137" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138">
-        <v>50136</v>
-      </c>
-      <c r="C138" t="s">
-        <v>250</v>
-      </c>
-      <c r="E138" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F138" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139">
-        <v>50137</v>
-      </c>
-      <c r="C139" t="s">
-        <v>250</v>
-      </c>
-      <c r="E139" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F139" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140">
-        <v>50138</v>
-      </c>
-      <c r="C140" t="s">
-        <v>250</v>
-      </c>
-      <c r="E140" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F140" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141">
-        <v>50139</v>
-      </c>
-      <c r="C141" t="s">
-        <v>250</v>
-      </c>
-      <c r="E141" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F141" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142">
-        <v>50140</v>
-      </c>
-      <c r="C142" t="s">
-        <v>250</v>
-      </c>
-      <c r="E142" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F142" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143">
-        <v>50141</v>
-      </c>
-      <c r="C143" t="s">
-        <v>250</v>
-      </c>
-      <c r="E143" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F143" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144">
-        <v>50142</v>
-      </c>
-      <c r="C144" t="s">
-        <v>250</v>
-      </c>
-      <c r="E144" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F144" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145">
-        <v>50143</v>
-      </c>
-      <c r="C145" t="s">
-        <v>250</v>
-      </c>
-      <c r="E145" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F145" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146">
-        <v>50144</v>
-      </c>
-      <c r="C146" t="s">
-        <v>250</v>
-      </c>
-      <c r="E146" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F146" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147">
-        <v>50145</v>
-      </c>
-      <c r="C147" t="s">
-        <v>250</v>
-      </c>
-      <c r="E147" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F147" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148">
-        <v>50146</v>
-      </c>
-      <c r="C148" t="s">
-        <v>250</v>
-      </c>
-      <c r="E148" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F148" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149">
-        <v>50147</v>
-      </c>
-      <c r="C149" t="s">
-        <v>250</v>
-      </c>
-      <c r="E149" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F149" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150">
-        <v>50148</v>
-      </c>
-      <c r="C150" t="s">
-        <v>250</v>
-      </c>
-      <c r="E150" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F150" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151">
-        <v>50149</v>
-      </c>
-      <c r="C151" t="s">
-        <v>250</v>
-      </c>
-      <c r="E151" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F151" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152">
-        <v>50150</v>
-      </c>
-      <c r="C152" t="s">
-        <v>250</v>
-      </c>
-      <c r="E152" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F152" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153">
-        <v>50151</v>
-      </c>
-      <c r="C153" t="s">
-        <v>250</v>
-      </c>
-      <c r="E153" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F153" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154">
-        <v>50152</v>
-      </c>
-      <c r="C154" t="s">
-        <v>250</v>
-      </c>
-      <c r="E154" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F154" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155">
-        <v>50153</v>
-      </c>
-      <c r="C155" t="s">
-        <v>250</v>
-      </c>
-      <c r="E155" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F155" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156">
-        <v>50154</v>
-      </c>
-      <c r="C156" t="s">
-        <v>250</v>
-      </c>
-      <c r="E156" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F156" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157">
-        <v>50155</v>
-      </c>
-      <c r="C157" t="s">
-        <v>250</v>
-      </c>
-      <c r="E157" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F157" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158">
-        <v>50156</v>
-      </c>
-      <c r="C158" t="s">
-        <v>250</v>
-      </c>
-      <c r="E158" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F158" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159">
-        <v>50157</v>
-      </c>
-      <c r="C159" t="s">
-        <v>250</v>
-      </c>
-      <c r="E159" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F159" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160">
-        <v>50158</v>
-      </c>
-      <c r="C160" t="s">
-        <v>250</v>
-      </c>
-      <c r="E160" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F160" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161">
-        <v>50159</v>
-      </c>
-      <c r="C161" t="s">
-        <v>250</v>
-      </c>
-      <c r="E161" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F161" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162">
-        <v>50160</v>
-      </c>
-      <c r="C162" t="s">
-        <v>250</v>
-      </c>
-      <c r="E162" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F162" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163">
-        <v>50161</v>
-      </c>
-      <c r="C163" t="s">
-        <v>250</v>
-      </c>
-      <c r="E163" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F163" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A164">
-        <v>50162</v>
-      </c>
-      <c r="C164" t="s">
-        <v>250</v>
-      </c>
-      <c r="E164" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F164" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A165">
-        <v>50163</v>
-      </c>
-      <c r="C165" t="s">
-        <v>250</v>
-      </c>
-      <c r="E165" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F165" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A166">
-        <v>50164</v>
-      </c>
-      <c r="C166" t="s">
-        <v>250</v>
-      </c>
-      <c r="E166" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F166" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167">
-        <v>50165</v>
-      </c>
-      <c r="C167" t="s">
-        <v>250</v>
-      </c>
-      <c r="E167" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F167" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A168">
-        <v>50166</v>
-      </c>
-      <c r="C168" t="s">
-        <v>250</v>
-      </c>
-      <c r="E168" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F168" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A169">
-        <v>50167</v>
-      </c>
-      <c r="C169" t="s">
-        <v>250</v>
-      </c>
-      <c r="E169" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F169" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A170">
-        <v>50168</v>
-      </c>
-      <c r="C170" t="s">
-        <v>250</v>
-      </c>
-      <c r="E170" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F170" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A171">
-        <v>50169</v>
-      </c>
-      <c r="C171" t="s">
-        <v>250</v>
-      </c>
-      <c r="E171" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F171" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A172">
-        <v>50170</v>
-      </c>
-      <c r="C172" t="s">
-        <v>250</v>
-      </c>
-      <c r="E172" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F172" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173">
-        <v>50171</v>
-      </c>
-      <c r="C173" t="s">
-        <v>250</v>
-      </c>
-      <c r="E173" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F173" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A174">
-        <v>50172</v>
-      </c>
-      <c r="C174" t="s">
-        <v>250</v>
-      </c>
-      <c r="E174" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F174" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A175">
-        <v>50173</v>
-      </c>
-      <c r="C175" t="s">
-        <v>250</v>
-      </c>
-      <c r="E175" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F175" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A176">
-        <v>50174</v>
-      </c>
-      <c r="C176" t="s">
-        <v>250</v>
-      </c>
-      <c r="E176" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F176" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177">
-        <v>50175</v>
-      </c>
-      <c r="C177" t="s">
-        <v>250</v>
-      </c>
-      <c r="E177" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F177" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A178">
-        <v>50176</v>
-      </c>
-      <c r="C178" t="s">
-        <v>250</v>
-      </c>
-      <c r="E178" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F178" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A179">
-        <v>50177</v>
-      </c>
-      <c r="C179" t="s">
-        <v>250</v>
-      </c>
-      <c r="E179" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F179" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A180">
-        <v>50178</v>
-      </c>
-      <c r="C180" t="s">
-        <v>250</v>
-      </c>
-      <c r="E180" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F180" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A181">
-        <v>50179</v>
-      </c>
-      <c r="C181" t="s">
-        <v>250</v>
-      </c>
-      <c r="E181" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F181" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A182">
-        <v>50180</v>
-      </c>
-      <c r="C182" t="s">
-        <v>250</v>
-      </c>
-      <c r="E182" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F182" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A183">
-        <v>50181</v>
-      </c>
-      <c r="C183" t="s">
-        <v>250</v>
-      </c>
-      <c r="E183" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F183" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A184">
-        <v>50182</v>
-      </c>
-      <c r="C184" t="s">
-        <v>250</v>
-      </c>
-      <c r="E184" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F184" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A185">
-        <v>50183</v>
-      </c>
-      <c r="C185" t="s">
-        <v>250</v>
-      </c>
-      <c r="E185" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F185" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186">
-        <v>50184</v>
-      </c>
-      <c r="C186" t="s">
-        <v>250</v>
-      </c>
-      <c r="E186" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F186" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187">
-        <v>50185</v>
-      </c>
-      <c r="C187" t="s">
-        <v>250</v>
-      </c>
-      <c r="E187" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F187" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188">
-        <v>50186</v>
-      </c>
-      <c r="C188" t="s">
-        <v>250</v>
-      </c>
-      <c r="E188" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F188" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189">
-        <v>50187</v>
-      </c>
-      <c r="C189" t="s">
-        <v>250</v>
-      </c>
-      <c r="E189" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F189" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A190">
-        <v>50188</v>
-      </c>
-      <c r="C190" t="s">
-        <v>250</v>
-      </c>
-      <c r="E190" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F190" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191">
-        <v>50189</v>
-      </c>
-      <c r="C191" t="s">
-        <v>250</v>
-      </c>
-      <c r="E191" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F191" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A192">
-        <v>50190</v>
-      </c>
-      <c r="C192" t="s">
-        <v>250</v>
-      </c>
-      <c r="E192" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F192" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193">
-        <v>50191</v>
-      </c>
-      <c r="C193" t="s">
-        <v>250</v>
-      </c>
-      <c r="E193" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="F193" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A194">
-        <v>50192</v>
-      </c>
-      <c r="C194" t="s">
-        <v>250</v>
-      </c>
-      <c r="E194" s="6">
-        <f t="shared" ref="E194:E210" si="6">B194</f>
-        <v>0</v>
-      </c>
-      <c r="F194" s="6">
-        <f t="shared" ref="F194:F210" si="7">B194</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A195">
-        <v>50193</v>
-      </c>
-      <c r="C195" t="s">
-        <v>250</v>
-      </c>
-      <c r="E195" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F195" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A196">
-        <v>50194</v>
-      </c>
-      <c r="C196" t="s">
-        <v>250</v>
-      </c>
-      <c r="E196" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F196" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A197">
-        <v>50195</v>
-      </c>
-      <c r="C197" t="s">
-        <v>250</v>
-      </c>
-      <c r="E197" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F197" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A198">
-        <v>50196</v>
-      </c>
-      <c r="C198" t="s">
-        <v>250</v>
-      </c>
-      <c r="E198" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F198" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A199">
-        <v>50197</v>
-      </c>
-      <c r="C199" t="s">
-        <v>250</v>
-      </c>
-      <c r="E199" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F199" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A200">
-        <v>50198</v>
-      </c>
-      <c r="C200" t="s">
-        <v>250</v>
-      </c>
-      <c r="E200" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F200" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A201">
-        <v>50199</v>
-      </c>
-      <c r="C201" t="s">
-        <v>250</v>
-      </c>
-      <c r="E201" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F201" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A202">
-        <v>50200</v>
-      </c>
-      <c r="C202" t="s">
-        <v>250</v>
-      </c>
-      <c r="E202" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F202" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A203">
-        <v>50201</v>
-      </c>
-      <c r="C203" t="s">
-        <v>250</v>
-      </c>
-      <c r="E203" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F203" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A204">
-        <v>50202</v>
-      </c>
-      <c r="C204" t="s">
-        <v>250</v>
-      </c>
-      <c r="E204" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F204" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A205">
-        <v>50203</v>
-      </c>
-      <c r="C205" t="s">
-        <v>250</v>
-      </c>
-      <c r="E205" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F205" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A206">
-        <v>50204</v>
-      </c>
-      <c r="C206" t="s">
-        <v>250</v>
-      </c>
-      <c r="E206" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F206" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A207">
-        <v>50205</v>
-      </c>
-      <c r="C207" t="s">
-        <v>250</v>
-      </c>
-      <c r="E207" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F207" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A208">
-        <v>50206</v>
-      </c>
-      <c r="C208" t="s">
-        <v>250</v>
-      </c>
-      <c r="E208" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F208" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A209">
-        <v>50207</v>
-      </c>
-      <c r="C209" t="s">
-        <v>250</v>
-      </c>
-      <c r="E209" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F209" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A210">
-        <v>50208</v>
-      </c>
-      <c r="C210" t="s">
-        <v>250</v>
-      </c>
-      <c r="E210" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F210" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+    </row>
+    <row r="81" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+    </row>
+    <row r="82" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+    </row>
+    <row r="83" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+    </row>
+    <row r="84" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+    </row>
+    <row r="85" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+    </row>
+    <row r="87" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+    </row>
+    <row r="88" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+    </row>
+    <row r="90" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+    </row>
+    <row r="91" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+    </row>
+    <row r="93" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+    </row>
+    <row r="94" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+    </row>
+    <row r="95" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+    </row>
+    <row r="97" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+    </row>
+    <row r="98" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+    </row>
+    <row r="99" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+    </row>
+    <row r="100" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+    </row>
+    <row r="101" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+    </row>
+    <row r="102" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+    </row>
+    <row r="103" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+    </row>
+    <row r="104" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+    </row>
+    <row r="105" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+    </row>
+    <row r="106" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+    </row>
+    <row r="107" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+    </row>
+    <row r="108" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+    </row>
+    <row r="109" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+    </row>
+    <row r="110" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+    </row>
+    <row r="111" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+    </row>
+    <row r="112" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+    </row>
+    <row r="113" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+    </row>
+    <row r="114" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+    </row>
+    <row r="115" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+    </row>
+    <row r="116" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+    </row>
+    <row r="117" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
+    </row>
+    <row r="118" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+    </row>
+    <row r="119" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+    </row>
+    <row r="120" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E120" s="6"/>
+      <c r="F120" s="6"/>
+    </row>
+    <row r="121" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E121" s="6"/>
+      <c r="F121" s="6"/>
+    </row>
+    <row r="122" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
+    </row>
+    <row r="123" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E123" s="6"/>
+      <c r="F123" s="6"/>
+    </row>
+    <row r="124" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
+    </row>
+    <row r="125" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
+    </row>
+    <row r="126" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+    </row>
+    <row r="127" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+    </row>
+    <row r="128" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
+    </row>
+    <row r="129" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+    </row>
+    <row r="130" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
+    </row>
+    <row r="131" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
+    </row>
+    <row r="132" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+    </row>
+    <row r="133" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+    </row>
+    <row r="134" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+    </row>
+    <row r="135" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+    </row>
+    <row r="136" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+    </row>
+    <row r="137" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+    </row>
+    <row r="138" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
+    </row>
+    <row r="139" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
+    </row>
+    <row r="140" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+    </row>
+    <row r="141" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
+    </row>
+    <row r="142" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+    </row>
+    <row r="143" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+    </row>
+    <row r="144" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E144" s="6"/>
+      <c r="F144" s="6"/>
+    </row>
+    <row r="145" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E145" s="6"/>
+      <c r="F145" s="6"/>
+    </row>
+    <row r="146" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E146" s="6"/>
+      <c r="F146" s="6"/>
+    </row>
+    <row r="147" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
+    </row>
+    <row r="148" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E148" s="6"/>
+      <c r="F148" s="6"/>
+    </row>
+    <row r="149" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
+    </row>
+    <row r="150" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E150" s="6"/>
+      <c r="F150" s="6"/>
+    </row>
+    <row r="151" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E151" s="6"/>
+      <c r="F151" s="6"/>
+    </row>
+    <row r="152" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E152" s="6"/>
+      <c r="F152" s="6"/>
+    </row>
+    <row r="153" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
+    </row>
+    <row r="154" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E154" s="6"/>
+      <c r="F154" s="6"/>
+    </row>
+    <row r="155" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E155" s="6"/>
+      <c r="F155" s="6"/>
+    </row>
+    <row r="156" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E156" s="6"/>
+      <c r="F156" s="6"/>
+    </row>
+    <row r="157" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E157" s="6"/>
+      <c r="F157" s="6"/>
+    </row>
+    <row r="158" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E158" s="6"/>
+      <c r="F158" s="6"/>
+    </row>
+    <row r="159" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E159" s="6"/>
+      <c r="F159" s="6"/>
+    </row>
+    <row r="160" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E160" s="6"/>
+      <c r="F160" s="6"/>
+    </row>
+    <row r="161" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E161" s="6"/>
+      <c r="F161" s="6"/>
+    </row>
+    <row r="162" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E162" s="6"/>
+      <c r="F162" s="6"/>
+    </row>
+    <row r="163" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E163" s="6"/>
+      <c r="F163" s="6"/>
+    </row>
+    <row r="164" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E164" s="6"/>
+      <c r="F164" s="6"/>
+    </row>
+    <row r="165" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E165" s="6"/>
+      <c r="F165" s="6"/>
+    </row>
+    <row r="166" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E166" s="6"/>
+      <c r="F166" s="6"/>
+    </row>
+    <row r="167" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
+    </row>
+    <row r="168" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E168" s="6"/>
+      <c r="F168" s="6"/>
+    </row>
+    <row r="169" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E169" s="6"/>
+      <c r="F169" s="6"/>
+    </row>
+    <row r="170" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E170" s="6"/>
+      <c r="F170" s="6"/>
+    </row>
+    <row r="171" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E171" s="6"/>
+      <c r="F171" s="6"/>
+    </row>
+    <row r="172" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E172" s="6"/>
+      <c r="F172" s="6"/>
+    </row>
+    <row r="173" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E173" s="6"/>
+      <c r="F173" s="6"/>
+    </row>
+    <row r="174" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E174" s="6"/>
+      <c r="F174" s="6"/>
+    </row>
+    <row r="175" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E175" s="6"/>
+      <c r="F175" s="6"/>
+    </row>
+    <row r="176" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E176" s="6"/>
+      <c r="F176" s="6"/>
+    </row>
+    <row r="177" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E177" s="6"/>
+      <c r="F177" s="6"/>
+    </row>
+    <row r="178" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E178" s="6"/>
+      <c r="F178" s="6"/>
+    </row>
+    <row r="179" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E179" s="6"/>
+      <c r="F179" s="6"/>
+    </row>
+    <row r="180" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E180" s="6"/>
+      <c r="F180" s="6"/>
+    </row>
+    <row r="181" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E181" s="6"/>
+      <c r="F181" s="6"/>
+    </row>
+    <row r="182" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E182" s="6"/>
+      <c r="F182" s="6"/>
+    </row>
+    <row r="183" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E183" s="6"/>
+      <c r="F183" s="6"/>
+    </row>
+    <row r="184" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E184" s="6"/>
+      <c r="F184" s="6"/>
+    </row>
+    <row r="185" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E185" s="6"/>
+      <c r="F185" s="6"/>
+    </row>
+    <row r="186" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E186" s="6"/>
+      <c r="F186" s="6"/>
+    </row>
+    <row r="187" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E187" s="6"/>
+      <c r="F187" s="6"/>
+    </row>
+    <row r="188" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E188" s="6"/>
+      <c r="F188" s="6"/>
+    </row>
+    <row r="189" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E189" s="6"/>
+      <c r="F189" s="6"/>
+    </row>
+    <row r="190" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E190" s="6"/>
+      <c r="F190" s="6"/>
+    </row>
+    <row r="191" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E191" s="6"/>
+      <c r="F191" s="6"/>
+    </row>
+    <row r="192" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E192" s="6"/>
+      <c r="F192" s="6"/>
+    </row>
+    <row r="193" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E193" s="6"/>
+      <c r="F193" s="6"/>
+    </row>
+    <row r="194" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E194" s="6"/>
+      <c r="F194" s="6"/>
+    </row>
+    <row r="195" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E195" s="6"/>
+      <c r="F195" s="6"/>
+    </row>
+    <row r="196" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E196" s="6"/>
+      <c r="F196" s="6"/>
+    </row>
+    <row r="197" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E197" s="6"/>
+      <c r="F197" s="6"/>
+    </row>
+    <row r="198" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E198" s="6"/>
+      <c r="F198" s="6"/>
+    </row>
+    <row r="199" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E199" s="6"/>
+      <c r="F199" s="6"/>
+    </row>
+    <row r="200" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E200" s="6"/>
+      <c r="F200" s="6"/>
+    </row>
+    <row r="201" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E201" s="6"/>
+      <c r="F201" s="6"/>
+    </row>
+    <row r="202" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E202" s="6"/>
+      <c r="F202" s="6"/>
+    </row>
+    <row r="203" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E203" s="6"/>
+      <c r="F203" s="6"/>
+    </row>
+    <row r="204" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E204" s="6"/>
+      <c r="F204" s="6"/>
+    </row>
+    <row r="205" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E205" s="6"/>
+      <c r="F205" s="6"/>
+    </row>
+    <row r="206" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E206" s="6"/>
+      <c r="F206" s="6"/>
+    </row>
+    <row r="207" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E207" s="6"/>
+      <c r="F207" s="6"/>
+    </row>
+    <row r="208" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E208" s="6"/>
+      <c r="F208" s="6"/>
+    </row>
+    <row r="209" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E209" s="6"/>
+      <c r="F209" s="6"/>
+    </row>
+    <row r="210" spans="5:6" x14ac:dyDescent="0.3">
+      <c r="E210" s="6"/>
+      <c r="F210" s="6"/>
+    </row>
+    <row r="211" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E216" s="6"/>
       <c r="F216" s="6"/>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E217" s="6"/>
       <c r="F217" s="6"/>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E218" s="6"/>
       <c r="F218" s="6"/>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E219" s="6"/>
       <c r="F219" s="6"/>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E220" s="6"/>
       <c r="F220" s="6"/>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E221" s="6"/>
       <c r="F221" s="6"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E222" s="6"/>
       <c r="F222" s="6"/>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E223" s="6"/>
       <c r="F223" s="6"/>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED4CF18-A320-4D31-B4C8-93557E29DF3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCF86E5-0E4D-4351-B9E5-BF671072798C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34725" yWindow="8310" windowWidth="32745" windowHeight="17535" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCF86E5-0E4D-4351-B9E5-BF671072798C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F73E05-68B5-4415-AC7D-58EFC28E9746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="345">
   <si>
     <t>사과</t>
   </si>
@@ -2299,6 +2299,36 @@
       <t>.mp4</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>수루(戍樓):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 적을 살피기 위해 높이 지은 누각</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>일성호가(一聲胡笳):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 어디선가 들려오는 외마디 피리 소리</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3339,7 +3369,7 @@
     <col min="5" max="5" width="43.125" customWidth="1"/>
     <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="54.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -3542,6 +3572,9 @@
       <c r="H8" t="s">
         <v>340</v>
       </c>
+      <c r="I8" s="2" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -3592,7 +3625,9 @@
       <c r="H10" t="s">
         <v>342</v>
       </c>
-      <c r="I10" s="21"/>
+      <c r="I10" s="2" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F73E05-68B5-4415-AC7D-58EFC28E9746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF2C546-34C3-4310-91B2-885B645EFBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="432">
   <si>
     <t>사과</t>
   </si>
@@ -1913,10 +1913,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>조금, 약간</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>水</t>
     </r>
@@ -2302,6 +2298,96 @@
   </si>
   <si>
     <r>
+      <t>일성(一</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>声</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>): 한 가닥 소리\n羌笛 (강독): 강족의 피리 -&gt; 변방의 쓸쓸함</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>한산도(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闲山岛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통영의 섬 ( 삼도수군통제영 )</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>수루(戍樓):</t>
     </r>
     <r>
@@ -2314,28 +2400,479 @@
       </rPr>
       <t xml:space="preserve"> 적을 살피기 위해 높이 지은 누각</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>심수(深愁): 깊은 시름</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>香菜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻辣</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼얼하고 매운맛</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>孜然</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쯔란</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>양꼬치에 들어가는 향신료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼얼하고 매운 맛 (마라)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>醋</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>식초</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>마늘</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>파</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒜</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>葱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고추기름</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>辣椒油</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>要</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요하다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>多放点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>多放点+재료 : 많이 넣어주세요</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>少放点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>少放点+재료 : 적게 넣어주세요</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>放</t>
+  </si>
+  <si>
+    <t>넣다, 첨가하다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>종업원</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>일성호가(一聲胡笳):</t>
+      <t>服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>务员</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老板</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>给</t>
+  </si>
+  <si>
+    <t>주다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>请</t>
+  </si>
+  <si>
+    <t>부디, 제발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴판</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>菜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>물</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>차갑다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>숟가락</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>젓가락</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>포크</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>勺子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叉子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>筷</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="2"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 어디선가 들려오는 외마디 피리 소리</t>
+      <t>子</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>汤勺</t>
+  </si>
+  <si>
+    <t>국자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>티슈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>纸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>巾</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>围</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>裙</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞치마</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞접시</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>碟子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>포장용기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>打包盒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>찬물</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰水</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>콜라</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>맥주</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이다(스프라이트)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>可</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>乐</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>啤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>酒</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪碧</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶</t>
+  </si>
+  <si>
+    <t>병</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>잔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>双</t>
+  </si>
+  <si>
+    <t>쌍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好</t>
+  </si>
+  <si>
+    <t>안녕하세요, 저기요</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>罐</t>
+  </si>
+  <si>
+    <t>캔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杯</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷</t>
+  </si>
+  <si>
+    <t>긁다 (카드 등)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>支付</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>宝</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>알리페이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>微信支付</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>위챗페이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금, 약간 (부정적)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>点</t>
+  </si>
+  <si>
+    <t>양 표현</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스캔하다 (QR 등)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2502,6 +3039,20 @@
       <name val="Noto Sans KR"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3415,7 +3966,7 @@
         <v>279</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D2" t="s">
         <v>275</v>
@@ -3440,7 +3991,7 @@
         <v>280</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
         <v>276</v>
@@ -3465,7 +4016,7 @@
         <v>283</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D4" t="s">
         <v>277</v>
@@ -3490,7 +4041,7 @@
         <v>284</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D5" t="s">
         <v>278</v>
@@ -3512,7 +4063,7 @@
         <v>50004</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" si="0"/>
@@ -3528,13 +4079,13 @@
         <v>50005</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E7" s="6" t="str">
         <f>B7</f>
@@ -3545,7 +4096,10 @@
         <v>闲山岛月明夜</v>
       </c>
       <c r="H7" t="s">
-        <v>339</v>
+        <v>338</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -3553,13 +4107,13 @@
         <v>50006</v>
       </c>
       <c r="B8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E8" s="6" t="str">
         <f t="shared" si="0"/>
@@ -3570,10 +4124,10 @@
         <v>上戍楼抚大刀</v>
       </c>
       <c r="H8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -3581,13 +4135,13 @@
         <v>50007</v>
       </c>
       <c r="B9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E9" s="6" t="str">
         <f t="shared" si="0"/>
@@ -3598,7 +4152,10 @@
         <v>深愁时何处</v>
       </c>
       <c r="H9" t="s">
-        <v>341</v>
+        <v>340</v>
+      </c>
+      <c r="I9" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.4">
@@ -3606,13 +4163,13 @@
         <v>50008</v>
       </c>
       <c r="B10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E10" s="6" t="str">
         <f>B10</f>
@@ -3623,10 +4180,10 @@
         <v>一声羌笛更添愁</v>
       </c>
       <c r="H10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -3788,7 +4345,7 @@
         <v>50020</v>
       </c>
       <c r="C22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="2"/>
@@ -7997,13 +8554,13 @@
         <v>100004</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E6" s="6" t="str">
         <f t="shared" si="2"/>
@@ -8019,13 +8576,13 @@
         <v>100005</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E7" s="6" t="str">
         <f t="shared" si="2"/>
@@ -8041,13 +8598,13 @@
         <v>100006</v>
       </c>
       <c r="B8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E8" s="6" t="str">
         <f t="shared" si="2"/>
@@ -8063,13 +8620,13 @@
         <v>100007</v>
       </c>
       <c r="B9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E9" s="6" t="str">
         <f t="shared" si="2"/>
@@ -8084,16 +8641,22 @@
       <c r="A10">
         <v>100008</v>
       </c>
+      <c r="B10" t="s">
+        <v>383</v>
+      </c>
       <c r="C10" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E10" s="6">
+      <c r="D10" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="E10" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
+        <v>冰</v>
+      </c>
+      <c r="F10" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>冰</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -8336,7 +8899,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C1B3F7-54F4-4D6B-B9DF-C355C73B066C}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="22.875" customWidth="1"/>
@@ -8382,7 +8945,7 @@
         <v>307</v>
       </c>
       <c r="D2" t="s">
-        <v>308</v>
+        <v>427</v>
       </c>
       <c r="E2" s="6" t="str">
         <f t="shared" ref="E2:E5" si="0">B2</f>
@@ -8398,13 +8961,13 @@
         <v>300001</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>307</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E3" s="6" t="str">
         <f t="shared" si="0"/>
@@ -8416,56 +8979,143 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="7"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="6">
+      <c r="A4">
+        <v>300002</v>
+      </c>
+      <c r="B4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="E4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
+        <v>请</v>
+      </c>
+      <c r="F4" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>请</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>300003</v>
+      </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="3"/>
       <c r="E5" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E5:E12" si="2">B5</f>
         <v>0</v>
       </c>
       <c r="F5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F5:F12" si="3">B5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>300004</v>
+      </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="E6" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>300005</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="E7" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>300006</v>
+      </c>
       <c r="B8" s="11"/>
       <c r="C8" s="6"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="E8" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>300007</v>
+      </c>
       <c r="C9" s="6"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="E9" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>300008</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>300009</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>300010</v>
+      </c>
+      <c r="E12" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -8595,6 +9245,138 @@
         <v>165</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6" t="s">
+        <v>408</v>
+      </c>
+      <c r="C6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" t="s">
+        <v>409</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="6" t="str">
+        <f>B6</f>
+        <v>瓶</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" t="s">
+        <v>410</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="6" t="str">
+        <f>B7</f>
+        <v>杯</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2027</v>
+      </c>
+      <c r="B8" t="s">
+        <v>411</v>
+      </c>
+      <c r="C8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" t="s">
+        <v>412</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="6" t="str">
+        <f t="shared" ref="F8:F13" si="0">B8</f>
+        <v>双</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2028</v>
+      </c>
+      <c r="B9" t="s">
+        <v>415</v>
+      </c>
+      <c r="C9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>罐</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2029</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2030</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2031</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2032</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D25" s="13"/>
       <c r="E25" s="6"/>
@@ -8720,13 +9502,13 @@
         <v>3003</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C5" t="s">
         <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E5" s="6" t="str">
         <f>B5</f>
@@ -9205,7 +9987,7 @@
         <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -9226,7 +10008,7 @@
         <v>115</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>50</v>
@@ -9624,80 +10406,110 @@
       <c r="A13">
         <v>10011</v>
       </c>
+      <c r="B13" t="s">
+        <v>362</v>
+      </c>
       <c r="C13" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="6">
+      <c r="D13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E13" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
+        <v>要</v>
+      </c>
+      <c r="F13" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>要</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>10012</v>
       </c>
+      <c r="B14" t="s">
+        <v>368</v>
+      </c>
       <c r="C14" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="6">
+      <c r="D14" t="s">
+        <v>369</v>
+      </c>
+      <c r="E14" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="6">
+        <v>放</v>
+      </c>
+      <c r="F14" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>放</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>10013</v>
       </c>
+      <c r="B15" t="s">
+        <v>374</v>
+      </c>
       <c r="C15" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="6">
+      <c r="D15" t="s">
+        <v>375</v>
+      </c>
+      <c r="E15" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
+        <v>给</v>
+      </c>
+      <c r="F15" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>给</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>10014</v>
       </c>
+      <c r="B16" t="s">
+        <v>418</v>
+      </c>
       <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="6">
+      <c r="D16" t="s">
+        <v>419</v>
+      </c>
+      <c r="E16" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
+        <v>刷</v>
+      </c>
+      <c r="F16" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>刷</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>10015</v>
       </c>
+      <c r="B17" s="12" t="s">
+        <v>426</v>
+      </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="6">
+      <c r="D17" t="s">
+        <v>431</v>
+      </c>
+      <c r="E17" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
+        <v>扫</v>
+      </c>
+      <c r="F17" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>扫</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -9865,6 +10677,7 @@
     <col min="4" max="4" width="42.5" customWidth="1"/>
     <col min="5" max="5" width="43.125" customWidth="1"/>
     <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -10301,63 +11114,157 @@
         <v>银行职员</v>
       </c>
     </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>20017</v>
+      </c>
+      <c r="B25" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
+        <v>370</v>
+      </c>
+      <c r="E25" s="6" t="str">
+        <f t="shared" ref="E25:E31" si="3">B25</f>
+        <v>服务员</v>
+      </c>
+      <c r="F25" s="6" t="str">
+        <f t="shared" ref="F25:F31" si="4">B25</f>
+        <v>服务员</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>20018</v>
+      </c>
+      <c r="B26" t="s">
+        <v>373</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
+        <v>372</v>
+      </c>
+      <c r="E26" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>老板</v>
+      </c>
+      <c r="F26" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>老板</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E27" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E28" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E29" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E30" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E31" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E37" s="6">
-        <f t="shared" ref="E37:E58" si="3">B37</f>
+        <f t="shared" ref="E37:E58" si="5">B37</f>
         <v>0</v>
       </c>
       <c r="F37" s="6">
-        <f t="shared" ref="F37:F58" si="4">B37</f>
+        <f t="shared" ref="F37:F58" si="6">B37</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E38" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F38" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E39" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F39" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E40" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F40" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E41" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F41" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E42" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F42" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -10375,11 +11282,11 @@
         <v>122</v>
       </c>
       <c r="E43" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>工作</v>
       </c>
       <c r="F43" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>工作</v>
       </c>
     </row>
@@ -10397,11 +11304,11 @@
         <v>124</v>
       </c>
       <c r="E44" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>银行</v>
       </c>
       <c r="F44" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>银行</v>
       </c>
     </row>
@@ -10419,11 +11326,11 @@
         <v>148</v>
       </c>
       <c r="E45" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>手机</v>
       </c>
       <c r="F45" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>手机</v>
       </c>
     </row>
@@ -10441,11 +11348,11 @@
         <v>149</v>
       </c>
       <c r="E46" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>书</v>
       </c>
       <c r="F46" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>书</v>
       </c>
     </row>
@@ -10463,11 +11370,11 @@
         <v>151</v>
       </c>
       <c r="E47" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>狗</v>
       </c>
       <c r="F47" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>狗</v>
       </c>
     </row>
@@ -10485,11 +11392,11 @@
         <v>156</v>
       </c>
       <c r="E48" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>猫</v>
       </c>
       <c r="F48" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>猫</v>
       </c>
     </row>
@@ -10507,11 +11414,11 @@
         <v>157</v>
       </c>
       <c r="E49" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>鸡</v>
       </c>
       <c r="F49" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>鸡</v>
       </c>
     </row>
@@ -10529,11 +11436,11 @@
         <v>158</v>
       </c>
       <c r="E50" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>猪</v>
       </c>
       <c r="F50" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>猪</v>
       </c>
     </row>
@@ -10551,11 +11458,11 @@
         <v>159</v>
       </c>
       <c r="E51" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>牛</v>
       </c>
       <c r="F51" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>牛</v>
       </c>
     </row>
@@ -10573,11 +11480,11 @@
         <v>160</v>
       </c>
       <c r="E52" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>鸭子</v>
       </c>
       <c r="F52" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>鸭子</v>
       </c>
     </row>
@@ -10595,11 +11502,11 @@
         <v>173</v>
       </c>
       <c r="E53" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>羊</v>
       </c>
       <c r="F53" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>羊</v>
       </c>
     </row>
@@ -10617,11 +11524,11 @@
         <v>174</v>
       </c>
       <c r="E54" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>猪肉</v>
       </c>
       <c r="F54" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>猪肉</v>
       </c>
     </row>
@@ -10639,11 +11546,11 @@
         <v>175</v>
       </c>
       <c r="E55" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>牛肉</v>
       </c>
       <c r="F55" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>牛肉</v>
       </c>
     </row>
@@ -10661,11 +11568,11 @@
         <v>176</v>
       </c>
       <c r="E56" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>鸭肉</v>
       </c>
       <c r="F56" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>鸭肉</v>
       </c>
     </row>
@@ -10683,11 +11590,11 @@
         <v>177</v>
       </c>
       <c r="E57" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>羊肉</v>
       </c>
       <c r="F57" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>羊肉</v>
       </c>
     </row>
@@ -10705,11 +11612,11 @@
         <v>178</v>
       </c>
       <c r="E58" s="6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>鸡肉</v>
       </c>
       <c r="F58" s="6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>鸡肉</v>
       </c>
     </row>
@@ -10727,11 +11634,11 @@
         <v>193</v>
       </c>
       <c r="E59" s="6" t="str">
-        <f t="shared" ref="E59:E65" si="5">B59</f>
+        <f t="shared" ref="E59:E65" si="7">B59</f>
         <v>洗手间</v>
       </c>
       <c r="F59" s="6" t="str">
-        <f t="shared" ref="F59:F65" si="6">B59</f>
+        <f t="shared" ref="F59:F65" si="8">B59</f>
         <v>洗手间</v>
       </c>
     </row>
@@ -10749,11 +11656,11 @@
         <v>194</v>
       </c>
       <c r="E60" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>地铁站</v>
       </c>
       <c r="F60" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>地铁站</v>
       </c>
     </row>
@@ -10775,7 +11682,7 @@
         <v>发型</v>
       </c>
       <c r="F61" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>发型</v>
       </c>
       <c r="G61" s="23" t="s">
@@ -10796,15 +11703,15 @@
         <v>300</v>
       </c>
       <c r="E62" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>短发</v>
       </c>
       <c r="F62" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>短发</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -10825,7 +11732,7 @@
         <v>韩式</v>
       </c>
       <c r="F63" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>韩式</v>
       </c>
     </row>
@@ -10834,7 +11741,7 @@
         <v>20120</v>
       </c>
       <c r="B64" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C64" t="s">
         <v>73</v>
@@ -10847,43 +11754,55 @@
         <v>水温</v>
       </c>
       <c r="F64" s="6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>水温</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>20121</v>
       </c>
+      <c r="B65" t="s">
+        <v>380</v>
+      </c>
       <c r="C65" t="s">
         <v>73</v>
       </c>
-      <c r="E65" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="F65" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D65" t="s">
+        <v>381</v>
+      </c>
+      <c r="E65" s="6" t="str">
+        <f t="shared" si="7"/>
+        <v>水</v>
+      </c>
+      <c r="F65" s="6" t="str">
+        <f t="shared" si="8"/>
+        <v>水</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>20122</v>
       </c>
+      <c r="B66" t="s">
+        <v>401</v>
+      </c>
       <c r="C66" t="s">
         <v>73</v>
       </c>
-      <c r="E66" s="6">
+      <c r="D66" t="s">
+        <v>400</v>
+      </c>
+      <c r="E66" s="6" t="str">
         <f>B66</f>
-        <v>0</v>
-      </c>
-      <c r="F66" s="6">
+        <v>冰水</v>
+      </c>
+      <c r="F66" s="6" t="str">
         <f>B66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+        <v>冰水</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>20123</v>
       </c>
@@ -10900,11 +11819,11 @@
         <v>191</v>
       </c>
       <c r="F67" s="6" t="str">
-        <f t="shared" ref="F67:F72" si="7">B67</f>
+        <f t="shared" ref="F67:F72" si="9">B67</f>
         <v>边</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>20124</v>
       </c>
@@ -10918,15 +11837,15 @@
         <v>220</v>
       </c>
       <c r="E68" s="6" t="str">
-        <f t="shared" ref="E68:E72" si="8">B68</f>
+        <f t="shared" ref="E68:E72" si="10">B68</f>
         <v>方向</v>
       </c>
       <c r="F68" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>方向</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>20125</v>
       </c>
@@ -10940,15 +11859,15 @@
         <v>221</v>
       </c>
       <c r="E69" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>右</v>
       </c>
       <c r="F69" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>右</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>20126</v>
       </c>
@@ -10965,11 +11884,11 @@
         <v>191</v>
       </c>
       <c r="F70" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>反</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>20127</v>
       </c>
@@ -10986,312 +11905,432 @@
         <v>191</v>
       </c>
       <c r="F71" s="6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>楼</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>20128</v>
       </c>
+      <c r="B72" t="s">
+        <v>347</v>
+      </c>
       <c r="C72" t="s">
         <v>73</v>
       </c>
-      <c r="E72" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F72" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D72" t="s">
+        <v>346</v>
+      </c>
+      <c r="E72" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>香菜</v>
+      </c>
+      <c r="F72" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>香菜</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>20129</v>
       </c>
+      <c r="B73" t="s">
+        <v>348</v>
+      </c>
       <c r="C73" t="s">
         <v>73</v>
       </c>
-      <c r="E73" s="6">
-        <f t="shared" ref="E73:E81" si="9">B73</f>
-        <v>0</v>
-      </c>
-      <c r="F73" s="6">
-        <f t="shared" ref="F73:F81" si="10">B73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D73" t="s">
+        <v>349</v>
+      </c>
+      <c r="E73" s="6" t="str">
+        <f t="shared" ref="E73:E81" si="11">B73</f>
+        <v>麻辣</v>
+      </c>
+      <c r="F73" s="6" t="str">
+        <f t="shared" ref="F73:F81" si="12">B73</f>
+        <v>麻辣</v>
+      </c>
+      <c r="H73" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>20130</v>
       </c>
+      <c r="B74" t="s">
+        <v>350</v>
+      </c>
       <c r="C74" t="s">
         <v>73</v>
       </c>
-      <c r="E74" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F74" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D74" t="s">
+        <v>351</v>
+      </c>
+      <c r="E74" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>孜然</v>
+      </c>
+      <c r="F74" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>孜然</v>
+      </c>
+      <c r="H74" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>20131</v>
       </c>
+      <c r="B75" t="s">
+        <v>354</v>
+      </c>
       <c r="C75" t="s">
         <v>73</v>
       </c>
-      <c r="E75" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F75" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D75" t="s">
+        <v>355</v>
+      </c>
+      <c r="E75" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>醋</v>
+      </c>
+      <c r="F75" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>醋</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>20132</v>
       </c>
+      <c r="B76" t="s">
+        <v>358</v>
+      </c>
       <c r="C76" t="s">
         <v>73</v>
       </c>
-      <c r="E76" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F76" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D76" t="s">
+        <v>356</v>
+      </c>
+      <c r="E76" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>蒜</v>
+      </c>
+      <c r="F76" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>蒜</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>20133</v>
       </c>
+      <c r="B77" t="s">
+        <v>359</v>
+      </c>
       <c r="C77" t="s">
         <v>73</v>
       </c>
-      <c r="E77" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F77" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D77" t="s">
+        <v>357</v>
+      </c>
+      <c r="E77" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>葱</v>
+      </c>
+      <c r="F77" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>葱</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>20134</v>
       </c>
+      <c r="B78" t="s">
+        <v>361</v>
+      </c>
       <c r="C78" t="s">
         <v>73</v>
       </c>
-      <c r="E78" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F78" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D78" t="s">
+        <v>360</v>
+      </c>
+      <c r="E78" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>辣椒油</v>
+      </c>
+      <c r="F78" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>辣椒油</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>20135</v>
       </c>
+      <c r="B79" t="s">
+        <v>379</v>
+      </c>
       <c r="C79" t="s">
         <v>73</v>
       </c>
-      <c r="E79" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F79" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D79" t="s">
+        <v>378</v>
+      </c>
+      <c r="E79" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>菜单</v>
+      </c>
+      <c r="F79" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>菜单</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>20136</v>
       </c>
+      <c r="B80" t="s">
+        <v>387</v>
+      </c>
       <c r="C80" t="s">
         <v>73</v>
       </c>
-      <c r="E80" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F80" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
+      <c r="D80" t="s">
+        <v>384</v>
+      </c>
+      <c r="E80" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>勺子</v>
+      </c>
+      <c r="F80" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>勺子</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>20137</v>
       </c>
+      <c r="B81" t="s">
+        <v>388</v>
+      </c>
       <c r="C81" t="s">
         <v>73</v>
       </c>
-      <c r="E81" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F81" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
+      <c r="D81" t="s">
+        <v>386</v>
+      </c>
+      <c r="E81" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>叉子</v>
+      </c>
+      <c r="F81" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>叉子</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>20138</v>
       </c>
+      <c r="B82" s="11" t="s">
+        <v>389</v>
+      </c>
       <c r="C82" t="s">
         <v>73</v>
       </c>
-      <c r="E82" s="6">
-        <f t="shared" ref="E82:E137" si="11">B82</f>
-        <v>0</v>
-      </c>
-      <c r="F82" s="6">
-        <f t="shared" ref="F82:F136" si="12">B82</f>
-        <v>0</v>
+      <c r="D82" t="s">
+        <v>385</v>
+      </c>
+      <c r="E82" s="6" t="str">
+        <f t="shared" ref="E82:E137" si="13">B82</f>
+        <v>筷子</v>
+      </c>
+      <c r="F82" s="6" t="str">
+        <f t="shared" ref="F82:F136" si="14">B82</f>
+        <v>筷子</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>20139</v>
       </c>
+      <c r="B83" t="s">
+        <v>390</v>
+      </c>
       <c r="C83" t="s">
         <v>73</v>
       </c>
-      <c r="E83" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F83" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D83" t="s">
+        <v>391</v>
+      </c>
+      <c r="E83" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>汤勺</v>
+      </c>
+      <c r="F83" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>汤勺</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>20140</v>
       </c>
+      <c r="B84" s="11" t="s">
+        <v>393</v>
+      </c>
       <c r="C84" t="s">
         <v>73</v>
       </c>
-      <c r="E84" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F84" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D84" t="s">
+        <v>392</v>
+      </c>
+      <c r="E84" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>纸巾</v>
+      </c>
+      <c r="F84" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>纸巾</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>20141</v>
       </c>
+      <c r="B85" s="11" t="s">
+        <v>394</v>
+      </c>
       <c r="C85" t="s">
         <v>73</v>
       </c>
-      <c r="E85" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D85" t="s">
+        <v>395</v>
+      </c>
+      <c r="E85" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>围裙</v>
+      </c>
+      <c r="F85" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>围裙</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>20142</v>
       </c>
+      <c r="B86" t="s">
+        <v>397</v>
+      </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
-      <c r="E86" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F86" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D86" t="s">
+        <v>396</v>
+      </c>
+      <c r="E86" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>碟子</v>
+      </c>
+      <c r="F86" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>碟子</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>20143</v>
       </c>
+      <c r="B87" t="s">
+        <v>399</v>
+      </c>
       <c r="C87" t="s">
         <v>73</v>
       </c>
-      <c r="E87" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F87" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D87" t="s">
+        <v>398</v>
+      </c>
+      <c r="E87" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>打包盒</v>
+      </c>
+      <c r="F87" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>打包盒</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>20144</v>
       </c>
+      <c r="B88" t="s">
+        <v>421</v>
+      </c>
       <c r="C88" t="s">
         <v>73</v>
       </c>
-      <c r="E88" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F88" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D88" t="s">
+        <v>420</v>
+      </c>
+      <c r="E88" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>卡</v>
+      </c>
+      <c r="F88" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>卡</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>20145</v>
       </c>
+      <c r="B89" t="s">
+        <v>424</v>
+      </c>
       <c r="C89" t="s">
         <v>73</v>
       </c>
-      <c r="E89" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F89" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D89" t="s">
+        <v>425</v>
+      </c>
+      <c r="E89" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>微信支付</v>
+      </c>
+      <c r="F89" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>微信支付</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>20146</v>
       </c>
+      <c r="B90" t="s">
+        <v>422</v>
+      </c>
       <c r="C90" t="s">
         <v>73</v>
       </c>
-      <c r="E90" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F90" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D90" t="s">
+        <v>423</v>
+      </c>
+      <c r="E90" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>支付宝</v>
+      </c>
+      <c r="F90" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>支付宝</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -11302,11 +12341,11 @@
         <v>73</v>
       </c>
       <c r="E91" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F91" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11318,11 +12357,11 @@
         <v>73</v>
       </c>
       <c r="E92" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F92" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11334,11 +12373,11 @@
         <v>73</v>
       </c>
       <c r="E93" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F93" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11346,48 +12385,66 @@
       <c r="A94">
         <v>20150</v>
       </c>
+      <c r="B94" t="s">
+        <v>405</v>
+      </c>
       <c r="C94" t="s">
         <v>73</v>
       </c>
-      <c r="E94" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F94" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D94" t="s">
+        <v>402</v>
+      </c>
+      <c r="E94" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>可乐</v>
+      </c>
+      <c r="F94" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>可乐</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>20151</v>
       </c>
+      <c r="B95" s="11" t="s">
+        <v>406</v>
+      </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
-      <c r="E95" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F95" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D95" t="s">
+        <v>403</v>
+      </c>
+      <c r="E95" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>啤酒</v>
+      </c>
+      <c r="F95" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>啤酒</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>20152</v>
       </c>
+      <c r="B96" t="s">
+        <v>407</v>
+      </c>
       <c r="C96" t="s">
         <v>73</v>
       </c>
-      <c r="E96" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F96" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="D96" t="s">
+        <v>404</v>
+      </c>
+      <c r="E96" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v>雪碧</v>
+      </c>
+      <c r="F96" s="6" t="str">
+        <f t="shared" si="14"/>
+        <v>雪碧</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -11398,11 +12455,11 @@
         <v>73</v>
       </c>
       <c r="E97" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F97" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11414,11 +12471,11 @@
         <v>73</v>
       </c>
       <c r="E98" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F98" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11430,11 +12487,11 @@
         <v>73</v>
       </c>
       <c r="E99" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F99" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11446,11 +12503,11 @@
         <v>73</v>
       </c>
       <c r="E100" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F100" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11462,11 +12519,11 @@
         <v>73</v>
       </c>
       <c r="E101" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F101" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11478,11 +12535,11 @@
         <v>73</v>
       </c>
       <c r="E102" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F102" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11494,11 +12551,11 @@
         <v>73</v>
       </c>
       <c r="E103" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F103" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11510,11 +12567,11 @@
         <v>73</v>
       </c>
       <c r="E104" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F104" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11526,11 +12583,11 @@
         <v>73</v>
       </c>
       <c r="E105" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F105" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11542,11 +12599,11 @@
         <v>73</v>
       </c>
       <c r="E106" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F106" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11558,11 +12615,11 @@
         <v>73</v>
       </c>
       <c r="E107" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F107" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11574,11 +12631,11 @@
         <v>73</v>
       </c>
       <c r="E108" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F108" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11590,11 +12647,11 @@
         <v>73</v>
       </c>
       <c r="E109" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F109" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11606,11 +12663,11 @@
         <v>73</v>
       </c>
       <c r="E110" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F110" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11622,11 +12679,11 @@
         <v>73</v>
       </c>
       <c r="E111" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F111" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11638,11 +12695,11 @@
         <v>73</v>
       </c>
       <c r="E112" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F112" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11654,11 +12711,11 @@
         <v>73</v>
       </c>
       <c r="E113" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F113" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11670,11 +12727,11 @@
         <v>73</v>
       </c>
       <c r="E114" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F114" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11686,11 +12743,11 @@
         <v>73</v>
       </c>
       <c r="E115" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F115" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11702,11 +12759,11 @@
         <v>73</v>
       </c>
       <c r="E116" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F116" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11718,11 +12775,11 @@
         <v>73</v>
       </c>
       <c r="E117" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F117" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11734,11 +12791,11 @@
         <v>73</v>
       </c>
       <c r="E118" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F118" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11750,11 +12807,11 @@
         <v>73</v>
       </c>
       <c r="E119" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F119" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11766,11 +12823,11 @@
         <v>73</v>
       </c>
       <c r="E120" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F120" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11782,11 +12839,11 @@
         <v>73</v>
       </c>
       <c r="E121" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F121" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11798,11 +12855,11 @@
         <v>73</v>
       </c>
       <c r="E122" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F122" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11814,11 +12871,11 @@
         <v>73</v>
       </c>
       <c r="E123" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F123" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11830,11 +12887,11 @@
         <v>73</v>
       </c>
       <c r="E124" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F124" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11846,11 +12903,11 @@
         <v>73</v>
       </c>
       <c r="E125" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F125" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11862,11 +12919,11 @@
         <v>73</v>
       </c>
       <c r="E126" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F126" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11878,11 +12935,11 @@
         <v>73</v>
       </c>
       <c r="E127" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F127" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11894,11 +12951,11 @@
         <v>73</v>
       </c>
       <c r="E128" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F128" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11910,11 +12967,11 @@
         <v>73</v>
       </c>
       <c r="E129" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F129" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11926,11 +12983,11 @@
         <v>73</v>
       </c>
       <c r="E130" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F130" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11942,11 +12999,11 @@
         <v>73</v>
       </c>
       <c r="E131" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F131" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11958,11 +13015,11 @@
         <v>73</v>
       </c>
       <c r="E132" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F132" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11974,11 +13031,11 @@
         <v>73</v>
       </c>
       <c r="E133" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F133" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -11990,11 +13047,11 @@
         <v>73</v>
       </c>
       <c r="E134" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F134" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -12006,11 +13063,11 @@
         <v>73</v>
       </c>
       <c r="E135" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F135" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -12022,11 +13079,11 @@
         <v>73</v>
       </c>
       <c r="E136" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F136" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -12038,11 +13095,11 @@
         <v>73</v>
       </c>
       <c r="E137" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F137" s="6">
-        <f t="shared" ref="F137:F200" si="13">B137</f>
+        <f t="shared" ref="F137:F200" si="15">B137</f>
         <v>0</v>
       </c>
     </row>
@@ -12054,11 +13111,11 @@
         <v>73</v>
       </c>
       <c r="E138" s="6">
-        <f t="shared" ref="E138:E201" si="14">B138</f>
+        <f t="shared" ref="E138:E201" si="16">B138</f>
         <v>0</v>
       </c>
       <c r="F138" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12070,11 +13127,11 @@
         <v>73</v>
       </c>
       <c r="E139" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F139" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12086,11 +13143,11 @@
         <v>73</v>
       </c>
       <c r="E140" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F140" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12102,11 +13159,11 @@
         <v>73</v>
       </c>
       <c r="E141" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F141" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12118,11 +13175,11 @@
         <v>73</v>
       </c>
       <c r="E142" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F142" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12134,11 +13191,11 @@
         <v>73</v>
       </c>
       <c r="E143" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F143" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12150,11 +13207,11 @@
         <v>73</v>
       </c>
       <c r="E144" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F144" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12166,11 +13223,11 @@
         <v>73</v>
       </c>
       <c r="E145" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F145" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12182,11 +13239,11 @@
         <v>73</v>
       </c>
       <c r="E146" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F146" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12198,11 +13255,11 @@
         <v>73</v>
       </c>
       <c r="E147" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F147" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12214,11 +13271,11 @@
         <v>73</v>
       </c>
       <c r="E148" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F148" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12230,11 +13287,11 @@
         <v>73</v>
       </c>
       <c r="E149" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F149" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12246,11 +13303,11 @@
         <v>73</v>
       </c>
       <c r="E150" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F150" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12262,11 +13319,11 @@
         <v>73</v>
       </c>
       <c r="E151" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F151" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12278,11 +13335,11 @@
         <v>73</v>
       </c>
       <c r="E152" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F152" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12294,11 +13351,11 @@
         <v>73</v>
       </c>
       <c r="E153" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F153" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12310,11 +13367,11 @@
         <v>73</v>
       </c>
       <c r="E154" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F154" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12326,11 +13383,11 @@
         <v>73</v>
       </c>
       <c r="E155" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F155" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12342,11 +13399,11 @@
         <v>73</v>
       </c>
       <c r="E156" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F156" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12358,11 +13415,11 @@
         <v>73</v>
       </c>
       <c r="E157" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F157" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12374,11 +13431,11 @@
         <v>73</v>
       </c>
       <c r="E158" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F158" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12390,11 +13447,11 @@
         <v>73</v>
       </c>
       <c r="E159" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F159" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12406,11 +13463,11 @@
         <v>73</v>
       </c>
       <c r="E160" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F160" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12422,11 +13479,11 @@
         <v>73</v>
       </c>
       <c r="E161" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F161" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12438,11 +13495,11 @@
         <v>73</v>
       </c>
       <c r="E162" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F162" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12454,11 +13511,11 @@
         <v>73</v>
       </c>
       <c r="E163" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F163" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12470,11 +13527,11 @@
         <v>73</v>
       </c>
       <c r="E164" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F164" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12486,11 +13543,11 @@
         <v>73</v>
       </c>
       <c r="E165" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F165" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12502,11 +13559,11 @@
         <v>73</v>
       </c>
       <c r="E166" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F166" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12518,11 +13575,11 @@
         <v>73</v>
       </c>
       <c r="E167" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F167" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12534,11 +13591,11 @@
         <v>73</v>
       </c>
       <c r="E168" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F168" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12550,11 +13607,11 @@
         <v>73</v>
       </c>
       <c r="E169" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F169" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12566,11 +13623,11 @@
         <v>73</v>
       </c>
       <c r="E170" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F170" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12582,11 +13639,11 @@
         <v>73</v>
       </c>
       <c r="E171" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F171" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12598,11 +13655,11 @@
         <v>73</v>
       </c>
       <c r="E172" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F172" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12614,11 +13671,11 @@
         <v>73</v>
       </c>
       <c r="E173" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F173" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12630,11 +13687,11 @@
         <v>73</v>
       </c>
       <c r="E174" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F174" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12646,11 +13703,11 @@
         <v>73</v>
       </c>
       <c r="E175" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F175" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12662,11 +13719,11 @@
         <v>73</v>
       </c>
       <c r="E176" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F176" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12678,11 +13735,11 @@
         <v>73</v>
       </c>
       <c r="E177" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F177" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12694,11 +13751,11 @@
         <v>73</v>
       </c>
       <c r="E178" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F178" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12710,11 +13767,11 @@
         <v>73</v>
       </c>
       <c r="E179" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F179" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12726,11 +13783,11 @@
         <v>73</v>
       </c>
       <c r="E180" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F180" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12742,11 +13799,11 @@
         <v>73</v>
       </c>
       <c r="E181" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F181" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12758,11 +13815,11 @@
         <v>73</v>
       </c>
       <c r="E182" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F182" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12774,11 +13831,11 @@
         <v>73</v>
       </c>
       <c r="E183" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F183" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12790,11 +13847,11 @@
         <v>73</v>
       </c>
       <c r="E184" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F184" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12806,11 +13863,11 @@
         <v>73</v>
       </c>
       <c r="E185" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F185" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12822,11 +13879,11 @@
         <v>73</v>
       </c>
       <c r="E186" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F186" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12838,11 +13895,11 @@
         <v>73</v>
       </c>
       <c r="E187" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F187" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12854,11 +13911,11 @@
         <v>73</v>
       </c>
       <c r="E188" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F188" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12870,11 +13927,11 @@
         <v>73</v>
       </c>
       <c r="E189" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F189" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12886,11 +13943,11 @@
         <v>73</v>
       </c>
       <c r="E190" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F190" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12902,11 +13959,11 @@
         <v>73</v>
       </c>
       <c r="E191" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F191" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12918,11 +13975,11 @@
         <v>73</v>
       </c>
       <c r="E192" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F192" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12934,11 +13991,11 @@
         <v>73</v>
       </c>
       <c r="E193" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F193" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12950,11 +14007,11 @@
         <v>73</v>
       </c>
       <c r="E194" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F194" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12966,11 +14023,11 @@
         <v>73</v>
       </c>
       <c r="E195" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F195" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12982,11 +14039,11 @@
         <v>73</v>
       </c>
       <c r="E196" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F196" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -12998,11 +14055,11 @@
         <v>73</v>
       </c>
       <c r="E197" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F197" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -13014,11 +14071,11 @@
         <v>73</v>
       </c>
       <c r="E198" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F198" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -13030,11 +14087,11 @@
         <v>73</v>
       </c>
       <c r="E199" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F199" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -13046,11 +14103,11 @@
         <v>73</v>
       </c>
       <c r="E200" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F200" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -13062,11 +14119,11 @@
         <v>73</v>
       </c>
       <c r="E201" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F201" s="6">
-        <f t="shared" ref="F201:F264" si="15">B201</f>
+        <f t="shared" ref="F201:F264" si="17">B201</f>
         <v>0</v>
       </c>
     </row>
@@ -13078,11 +14135,11 @@
         <v>73</v>
       </c>
       <c r="E202" s="6">
-        <f t="shared" ref="E202:E265" si="16">B202</f>
+        <f t="shared" ref="E202:E265" si="18">B202</f>
         <v>0</v>
       </c>
       <c r="F202" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13094,11 +14151,11 @@
         <v>73</v>
       </c>
       <c r="E203" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F203" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13110,11 +14167,11 @@
         <v>73</v>
       </c>
       <c r="E204" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F204" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13126,11 +14183,11 @@
         <v>73</v>
       </c>
       <c r="E205" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F205" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13142,11 +14199,11 @@
         <v>73</v>
       </c>
       <c r="E206" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F206" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13158,11 +14215,11 @@
         <v>73</v>
       </c>
       <c r="E207" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F207" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13174,11 +14231,11 @@
         <v>73</v>
       </c>
       <c r="E208" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F208" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13190,11 +14247,11 @@
         <v>73</v>
       </c>
       <c r="E209" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F209" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13206,11 +14263,11 @@
         <v>73</v>
       </c>
       <c r="E210" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F210" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13222,11 +14279,11 @@
         <v>73</v>
       </c>
       <c r="E211" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F211" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13238,11 +14295,11 @@
         <v>73</v>
       </c>
       <c r="E212" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F212" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13254,11 +14311,11 @@
         <v>73</v>
       </c>
       <c r="E213" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F213" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13270,11 +14327,11 @@
         <v>73</v>
       </c>
       <c r="E214" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F214" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13286,11 +14343,11 @@
         <v>73</v>
       </c>
       <c r="E215" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F215" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13302,11 +14359,11 @@
         <v>73</v>
       </c>
       <c r="E216" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F216" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13318,11 +14375,11 @@
         <v>73</v>
       </c>
       <c r="E217" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F217" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13334,11 +14391,11 @@
         <v>73</v>
       </c>
       <c r="E218" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F218" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13350,11 +14407,11 @@
         <v>73</v>
       </c>
       <c r="E219" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F219" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13366,11 +14423,11 @@
         <v>73</v>
       </c>
       <c r="E220" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F220" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13382,11 +14439,11 @@
         <v>73</v>
       </c>
       <c r="E221" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F221" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13398,11 +14455,11 @@
         <v>73</v>
       </c>
       <c r="E222" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F222" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13414,11 +14471,11 @@
         <v>73</v>
       </c>
       <c r="E223" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F223" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13430,11 +14487,11 @@
         <v>73</v>
       </c>
       <c r="E224" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F224" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13446,11 +14503,11 @@
         <v>73</v>
       </c>
       <c r="E225" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F225" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13462,11 +14519,11 @@
         <v>73</v>
       </c>
       <c r="E226" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F226" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13478,11 +14535,11 @@
         <v>73</v>
       </c>
       <c r="E227" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F227" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13494,11 +14551,11 @@
         <v>73</v>
       </c>
       <c r="E228" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F228" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13510,11 +14567,11 @@
         <v>73</v>
       </c>
       <c r="E229" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F229" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13526,11 +14583,11 @@
         <v>73</v>
       </c>
       <c r="E230" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F230" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13542,11 +14599,11 @@
         <v>73</v>
       </c>
       <c r="E231" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F231" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13558,11 +14615,11 @@
         <v>73</v>
       </c>
       <c r="E232" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F232" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13574,11 +14631,11 @@
         <v>73</v>
       </c>
       <c r="E233" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F233" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13590,11 +14647,11 @@
         <v>73</v>
       </c>
       <c r="E234" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F234" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13606,11 +14663,11 @@
         <v>73</v>
       </c>
       <c r="E235" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F235" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13622,11 +14679,11 @@
         <v>73</v>
       </c>
       <c r="E236" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F236" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13638,11 +14695,11 @@
         <v>73</v>
       </c>
       <c r="E237" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F237" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13654,11 +14711,11 @@
         <v>73</v>
       </c>
       <c r="E238" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F238" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13670,11 +14727,11 @@
         <v>73</v>
       </c>
       <c r="E239" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F239" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13686,11 +14743,11 @@
         <v>73</v>
       </c>
       <c r="E240" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F240" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13702,11 +14759,11 @@
         <v>73</v>
       </c>
       <c r="E241" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F241" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13718,11 +14775,11 @@
         <v>73</v>
       </c>
       <c r="E242" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F242" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13734,11 +14791,11 @@
         <v>73</v>
       </c>
       <c r="E243" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F243" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13750,11 +14807,11 @@
         <v>73</v>
       </c>
       <c r="E244" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F244" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13766,11 +14823,11 @@
         <v>73</v>
       </c>
       <c r="E245" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F245" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13782,11 +14839,11 @@
         <v>73</v>
       </c>
       <c r="E246" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F246" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13798,11 +14855,11 @@
         <v>73</v>
       </c>
       <c r="E247" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F247" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13814,11 +14871,11 @@
         <v>73</v>
       </c>
       <c r="E248" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F248" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13830,11 +14887,11 @@
         <v>73</v>
       </c>
       <c r="E249" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F249" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13846,11 +14903,11 @@
         <v>73</v>
       </c>
       <c r="E250" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F250" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13862,11 +14919,11 @@
         <v>73</v>
       </c>
       <c r="E251" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F251" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13878,11 +14935,11 @@
         <v>73</v>
       </c>
       <c r="E252" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F252" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13894,11 +14951,11 @@
         <v>73</v>
       </c>
       <c r="E253" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F253" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13910,11 +14967,11 @@
         <v>73</v>
       </c>
       <c r="E254" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F254" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13926,11 +14983,11 @@
         <v>73</v>
       </c>
       <c r="E255" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F255" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13942,11 +14999,11 @@
         <v>73</v>
       </c>
       <c r="E256" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F256" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13958,11 +15015,11 @@
         <v>73</v>
       </c>
       <c r="E257" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F257" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13974,11 +15031,11 @@
         <v>73</v>
       </c>
       <c r="E258" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F258" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -13990,11 +15047,11 @@
         <v>73</v>
       </c>
       <c r="E259" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F259" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14006,11 +15063,11 @@
         <v>73</v>
       </c>
       <c r="E260" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F260" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14022,11 +15079,11 @@
         <v>73</v>
       </c>
       <c r="E261" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F261" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14038,11 +15095,11 @@
         <v>73</v>
       </c>
       <c r="E262" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F262" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14054,11 +15111,11 @@
         <v>73</v>
       </c>
       <c r="E263" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F263" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14070,11 +15127,11 @@
         <v>73</v>
       </c>
       <c r="E264" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F264" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -14086,11 +15143,11 @@
         <v>73</v>
       </c>
       <c r="E265" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F265" s="6">
-        <f t="shared" ref="F265:F328" si="17">B265</f>
+        <f t="shared" ref="F265:F328" si="19">B265</f>
         <v>0</v>
       </c>
     </row>
@@ -14102,11 +15159,11 @@
         <v>73</v>
       </c>
       <c r="E266" s="6">
-        <f t="shared" ref="E266:E329" si="18">B266</f>
+        <f t="shared" ref="E266:E329" si="20">B266</f>
         <v>0</v>
       </c>
       <c r="F266" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14118,11 +15175,11 @@
         <v>73</v>
       </c>
       <c r="E267" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F267" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14134,11 +15191,11 @@
         <v>73</v>
       </c>
       <c r="E268" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F268" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14150,11 +15207,11 @@
         <v>73</v>
       </c>
       <c r="E269" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F269" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14166,11 +15223,11 @@
         <v>73</v>
       </c>
       <c r="E270" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F270" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14182,11 +15239,11 @@
         <v>73</v>
       </c>
       <c r="E271" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F271" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14198,11 +15255,11 @@
         <v>73</v>
       </c>
       <c r="E272" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F272" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14214,11 +15271,11 @@
         <v>73</v>
       </c>
       <c r="E273" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F273" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14230,11 +15287,11 @@
         <v>73</v>
       </c>
       <c r="E274" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F274" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14246,11 +15303,11 @@
         <v>73</v>
       </c>
       <c r="E275" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F275" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14262,11 +15319,11 @@
         <v>73</v>
       </c>
       <c r="E276" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F276" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14278,11 +15335,11 @@
         <v>73</v>
       </c>
       <c r="E277" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F277" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14294,11 +15351,11 @@
         <v>73</v>
       </c>
       <c r="E278" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F278" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14310,11 +15367,11 @@
         <v>73</v>
       </c>
       <c r="E279" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F279" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14326,11 +15383,11 @@
         <v>73</v>
       </c>
       <c r="E280" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F280" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14342,11 +15399,11 @@
         <v>73</v>
       </c>
       <c r="E281" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F281" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14358,11 +15415,11 @@
         <v>73</v>
       </c>
       <c r="E282" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F282" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14374,11 +15431,11 @@
         <v>73</v>
       </c>
       <c r="E283" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F283" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14390,11 +15447,11 @@
         <v>73</v>
       </c>
       <c r="E284" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F284" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14406,11 +15463,11 @@
         <v>73</v>
       </c>
       <c r="E285" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F285" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14422,11 +15479,11 @@
         <v>73</v>
       </c>
       <c r="E286" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F286" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14438,11 +15495,11 @@
         <v>73</v>
       </c>
       <c r="E287" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F287" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14454,11 +15511,11 @@
         <v>73</v>
       </c>
       <c r="E288" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F288" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14470,11 +15527,11 @@
         <v>73</v>
       </c>
       <c r="E289" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F289" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14486,11 +15543,11 @@
         <v>73</v>
       </c>
       <c r="E290" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F290" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14502,11 +15559,11 @@
         <v>73</v>
       </c>
       <c r="E291" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F291" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14518,11 +15575,11 @@
         <v>73</v>
       </c>
       <c r="E292" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F292" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14534,11 +15591,11 @@
         <v>73</v>
       </c>
       <c r="E293" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F293" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14550,11 +15607,11 @@
         <v>73</v>
       </c>
       <c r="E294" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F294" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14566,11 +15623,11 @@
         <v>73</v>
       </c>
       <c r="E295" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F295" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14582,11 +15639,11 @@
         <v>73</v>
       </c>
       <c r="E296" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F296" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14598,11 +15655,11 @@
         <v>73</v>
       </c>
       <c r="E297" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F297" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14614,11 +15671,11 @@
         <v>73</v>
       </c>
       <c r="E298" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F298" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14630,11 +15687,11 @@
         <v>73</v>
       </c>
       <c r="E299" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F299" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14646,11 +15703,11 @@
         <v>73</v>
       </c>
       <c r="E300" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F300" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14662,11 +15719,11 @@
         <v>73</v>
       </c>
       <c r="E301" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F301" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14678,11 +15735,11 @@
         <v>73</v>
       </c>
       <c r="E302" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F302" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14694,11 +15751,11 @@
         <v>73</v>
       </c>
       <c r="E303" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F303" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14710,11 +15767,11 @@
         <v>73</v>
       </c>
       <c r="E304" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F304" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14726,11 +15783,11 @@
         <v>73</v>
       </c>
       <c r="E305" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F305" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14742,11 +15799,11 @@
         <v>73</v>
       </c>
       <c r="E306" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F306" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14758,11 +15815,11 @@
         <v>73</v>
       </c>
       <c r="E307" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F307" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14774,11 +15831,11 @@
         <v>73</v>
       </c>
       <c r="E308" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F308" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14790,11 +15847,11 @@
         <v>73</v>
       </c>
       <c r="E309" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F309" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14806,11 +15863,11 @@
         <v>73</v>
       </c>
       <c r="E310" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F310" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14822,11 +15879,11 @@
         <v>73</v>
       </c>
       <c r="E311" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F311" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14838,11 +15895,11 @@
         <v>73</v>
       </c>
       <c r="E312" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F312" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14854,11 +15911,11 @@
         <v>73</v>
       </c>
       <c r="E313" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F313" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14870,11 +15927,11 @@
         <v>73</v>
       </c>
       <c r="E314" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F314" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14886,11 +15943,11 @@
         <v>73</v>
       </c>
       <c r="E315" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F315" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14902,11 +15959,11 @@
         <v>73</v>
       </c>
       <c r="E316" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F316" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14918,11 +15975,11 @@
         <v>73</v>
       </c>
       <c r="E317" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F317" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14934,11 +15991,11 @@
         <v>73</v>
       </c>
       <c r="E318" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F318" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14950,11 +16007,11 @@
         <v>73</v>
       </c>
       <c r="E319" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F319" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14966,11 +16023,11 @@
         <v>73</v>
       </c>
       <c r="E320" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F320" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14982,11 +16039,11 @@
         <v>73</v>
       </c>
       <c r="E321" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F321" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -14998,11 +16055,11 @@
         <v>73</v>
       </c>
       <c r="E322" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F322" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -15014,11 +16071,11 @@
         <v>73</v>
       </c>
       <c r="E323" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F323" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -15030,11 +16087,11 @@
         <v>73</v>
       </c>
       <c r="E324" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F324" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -15046,11 +16103,11 @@
         <v>73</v>
       </c>
       <c r="E325" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F325" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -15062,11 +16119,11 @@
         <v>73</v>
       </c>
       <c r="E326" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F326" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -15078,11 +16135,11 @@
         <v>73</v>
       </c>
       <c r="E327" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F327" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -15094,11 +16151,11 @@
         <v>73</v>
       </c>
       <c r="E328" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F328" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -15110,11 +16167,11 @@
         <v>73</v>
       </c>
       <c r="E329" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F329" s="6">
-        <f t="shared" ref="F329:F392" si="19">B329</f>
+        <f t="shared" ref="F329:F392" si="21">B329</f>
         <v>0</v>
       </c>
     </row>
@@ -15126,11 +16183,11 @@
         <v>73</v>
       </c>
       <c r="E330" s="6">
-        <f t="shared" ref="E330:E393" si="20">B330</f>
+        <f t="shared" ref="E330:E393" si="22">B330</f>
         <v>0</v>
       </c>
       <c r="F330" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15142,11 +16199,11 @@
         <v>73</v>
       </c>
       <c r="E331" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F331" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15158,11 +16215,11 @@
         <v>73</v>
       </c>
       <c r="E332" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F332" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15174,11 +16231,11 @@
         <v>73</v>
       </c>
       <c r="E333" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F333" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15190,11 +16247,11 @@
         <v>73</v>
       </c>
       <c r="E334" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F334" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15206,11 +16263,11 @@
         <v>73</v>
       </c>
       <c r="E335" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F335" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15222,11 +16279,11 @@
         <v>73</v>
       </c>
       <c r="E336" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F336" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15238,11 +16295,11 @@
         <v>73</v>
       </c>
       <c r="E337" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F337" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15254,11 +16311,11 @@
         <v>73</v>
       </c>
       <c r="E338" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F338" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15270,11 +16327,11 @@
         <v>73</v>
       </c>
       <c r="E339" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F339" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15286,11 +16343,11 @@
         <v>73</v>
       </c>
       <c r="E340" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F340" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15302,11 +16359,11 @@
         <v>73</v>
       </c>
       <c r="E341" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F341" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15318,11 +16375,11 @@
         <v>73</v>
       </c>
       <c r="E342" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F342" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15334,11 +16391,11 @@
         <v>73</v>
       </c>
       <c r="E343" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F343" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15350,11 +16407,11 @@
         <v>73</v>
       </c>
       <c r="E344" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F344" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15366,11 +16423,11 @@
         <v>73</v>
       </c>
       <c r="E345" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F345" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15382,11 +16439,11 @@
         <v>73</v>
       </c>
       <c r="E346" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F346" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15398,11 +16455,11 @@
         <v>73</v>
       </c>
       <c r="E347" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F347" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15414,11 +16471,11 @@
         <v>73</v>
       </c>
       <c r="E348" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F348" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15430,11 +16487,11 @@
         <v>73</v>
       </c>
       <c r="E349" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F349" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15446,11 +16503,11 @@
         <v>73</v>
       </c>
       <c r="E350" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F350" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15462,11 +16519,11 @@
         <v>73</v>
       </c>
       <c r="E351" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F351" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15478,11 +16535,11 @@
         <v>73</v>
       </c>
       <c r="E352" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F352" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15494,11 +16551,11 @@
         <v>73</v>
       </c>
       <c r="E353" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F353" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15510,11 +16567,11 @@
         <v>73</v>
       </c>
       <c r="E354" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F354" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15526,11 +16583,11 @@
         <v>73</v>
       </c>
       <c r="E355" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F355" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15542,11 +16599,11 @@
         <v>73</v>
       </c>
       <c r="E356" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F356" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15558,11 +16615,11 @@
         <v>73</v>
       </c>
       <c r="E357" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F357" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15574,11 +16631,11 @@
         <v>73</v>
       </c>
       <c r="E358" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F358" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15590,11 +16647,11 @@
         <v>73</v>
       </c>
       <c r="E359" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F359" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15606,11 +16663,11 @@
         <v>73</v>
       </c>
       <c r="E360" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F360" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15622,11 +16679,11 @@
         <v>73</v>
       </c>
       <c r="E361" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F361" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15638,11 +16695,11 @@
         <v>73</v>
       </c>
       <c r="E362" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F362" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15654,11 +16711,11 @@
         <v>73</v>
       </c>
       <c r="E363" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F363" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15670,11 +16727,11 @@
         <v>73</v>
       </c>
       <c r="E364" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F364" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15686,11 +16743,11 @@
         <v>73</v>
       </c>
       <c r="E365" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F365" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15702,11 +16759,11 @@
         <v>73</v>
       </c>
       <c r="E366" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F366" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15718,11 +16775,11 @@
         <v>73</v>
       </c>
       <c r="E367" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F367" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15734,11 +16791,11 @@
         <v>73</v>
       </c>
       <c r="E368" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F368" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15750,11 +16807,11 @@
         <v>73</v>
       </c>
       <c r="E369" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F369" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15766,11 +16823,11 @@
         <v>73</v>
       </c>
       <c r="E370" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F370" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15782,11 +16839,11 @@
         <v>73</v>
       </c>
       <c r="E371" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F371" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15798,11 +16855,11 @@
         <v>73</v>
       </c>
       <c r="E372" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F372" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15814,11 +16871,11 @@
         <v>73</v>
       </c>
       <c r="E373" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F373" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15830,11 +16887,11 @@
         <v>73</v>
       </c>
       <c r="E374" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F374" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15846,11 +16903,11 @@
         <v>73</v>
       </c>
       <c r="E375" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F375" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15862,11 +16919,11 @@
         <v>73</v>
       </c>
       <c r="E376" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F376" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15878,11 +16935,11 @@
         <v>73</v>
       </c>
       <c r="E377" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F377" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15894,11 +16951,11 @@
         <v>73</v>
       </c>
       <c r="E378" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F378" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15910,11 +16967,11 @@
         <v>73</v>
       </c>
       <c r="E379" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F379" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15926,11 +16983,11 @@
         <v>73</v>
       </c>
       <c r="E380" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F380" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15942,11 +16999,11 @@
         <v>73</v>
       </c>
       <c r="E381" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F381" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15958,11 +17015,11 @@
         <v>73</v>
       </c>
       <c r="E382" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F382" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15974,11 +17031,11 @@
         <v>73</v>
       </c>
       <c r="E383" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F383" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -15990,11 +17047,11 @@
         <v>73</v>
       </c>
       <c r="E384" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F384" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -16006,11 +17063,11 @@
         <v>73</v>
       </c>
       <c r="E385" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F385" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -16022,11 +17079,11 @@
         <v>73</v>
       </c>
       <c r="E386" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F386" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -16038,11 +17095,11 @@
         <v>73</v>
       </c>
       <c r="E387" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F387" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -16054,11 +17111,11 @@
         <v>73</v>
       </c>
       <c r="E388" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F388" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -16070,11 +17127,11 @@
         <v>73</v>
       </c>
       <c r="E389" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F389" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -16086,11 +17143,11 @@
         <v>73</v>
       </c>
       <c r="E390" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F390" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -16102,11 +17159,11 @@
         <v>73</v>
       </c>
       <c r="E391" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F391" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -16118,11 +17175,11 @@
         <v>73</v>
       </c>
       <c r="E392" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F392" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -16134,11 +17191,11 @@
         <v>73</v>
       </c>
       <c r="E393" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F393" s="6">
-        <f t="shared" ref="F393:F456" si="21">B393</f>
+        <f t="shared" ref="F393:F456" si="23">B393</f>
         <v>0</v>
       </c>
     </row>
@@ -16150,11 +17207,11 @@
         <v>73</v>
       </c>
       <c r="E394" s="6">
-        <f t="shared" ref="E394:E457" si="22">B394</f>
+        <f t="shared" ref="E394:E457" si="24">B394</f>
         <v>0</v>
       </c>
       <c r="F394" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16166,11 +17223,11 @@
         <v>73</v>
       </c>
       <c r="E395" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F395" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16182,11 +17239,11 @@
         <v>73</v>
       </c>
       <c r="E396" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F396" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16198,11 +17255,11 @@
         <v>73</v>
       </c>
       <c r="E397" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F397" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16214,11 +17271,11 @@
         <v>73</v>
       </c>
       <c r="E398" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F398" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16230,11 +17287,11 @@
         <v>73</v>
       </c>
       <c r="E399" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F399" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16246,11 +17303,11 @@
         <v>73</v>
       </c>
       <c r="E400" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F400" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16262,11 +17319,11 @@
         <v>73</v>
       </c>
       <c r="E401" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F401" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16278,11 +17335,11 @@
         <v>73</v>
       </c>
       <c r="E402" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F402" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16294,11 +17351,11 @@
         <v>73</v>
       </c>
       <c r="E403" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F403" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16310,11 +17367,11 @@
         <v>73</v>
       </c>
       <c r="E404" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F404" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16326,11 +17383,11 @@
         <v>73</v>
       </c>
       <c r="E405" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F405" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16342,11 +17399,11 @@
         <v>73</v>
       </c>
       <c r="E406" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F406" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16358,11 +17415,11 @@
         <v>73</v>
       </c>
       <c r="E407" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F407" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16374,11 +17431,11 @@
         <v>73</v>
       </c>
       <c r="E408" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F408" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16390,11 +17447,11 @@
         <v>73</v>
       </c>
       <c r="E409" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F409" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16406,11 +17463,11 @@
         <v>73</v>
       </c>
       <c r="E410" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F410" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16422,11 +17479,11 @@
         <v>73</v>
       </c>
       <c r="E411" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F411" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16438,11 +17495,11 @@
         <v>73</v>
       </c>
       <c r="E412" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F412" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16454,11 +17511,11 @@
         <v>73</v>
       </c>
       <c r="E413" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F413" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16470,11 +17527,11 @@
         <v>73</v>
       </c>
       <c r="E414" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F414" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16486,11 +17543,11 @@
         <v>73</v>
       </c>
       <c r="E415" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F415" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16502,11 +17559,11 @@
         <v>73</v>
       </c>
       <c r="E416" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F416" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16518,11 +17575,11 @@
         <v>73</v>
       </c>
       <c r="E417" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F417" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16534,11 +17591,11 @@
         <v>73</v>
       </c>
       <c r="E418" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F418" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16550,11 +17607,11 @@
         <v>73</v>
       </c>
       <c r="E419" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F419" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16566,11 +17623,11 @@
         <v>73</v>
       </c>
       <c r="E420" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F420" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16582,11 +17639,11 @@
         <v>73</v>
       </c>
       <c r="E421" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F421" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16598,11 +17655,11 @@
         <v>73</v>
       </c>
       <c r="E422" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F422" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16614,11 +17671,11 @@
         <v>73</v>
       </c>
       <c r="E423" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F423" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16630,11 +17687,11 @@
         <v>73</v>
       </c>
       <c r="E424" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F424" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16646,11 +17703,11 @@
         <v>73</v>
       </c>
       <c r="E425" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F425" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16662,11 +17719,11 @@
         <v>73</v>
       </c>
       <c r="E426" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F426" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16678,11 +17735,11 @@
         <v>73</v>
       </c>
       <c r="E427" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F427" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16694,11 +17751,11 @@
         <v>73</v>
       </c>
       <c r="E428" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F428" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16710,11 +17767,11 @@
         <v>73</v>
       </c>
       <c r="E429" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F429" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16726,11 +17783,11 @@
         <v>73</v>
       </c>
       <c r="E430" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F430" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16742,11 +17799,11 @@
         <v>73</v>
       </c>
       <c r="E431" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F431" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16758,11 +17815,11 @@
         <v>73</v>
       </c>
       <c r="E432" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F432" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16774,11 +17831,11 @@
         <v>73</v>
       </c>
       <c r="E433" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F433" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16790,11 +17847,11 @@
         <v>73</v>
       </c>
       <c r="E434" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F434" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16806,11 +17863,11 @@
         <v>73</v>
       </c>
       <c r="E435" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F435" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16822,11 +17879,11 @@
         <v>73</v>
       </c>
       <c r="E436" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F436" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16838,11 +17895,11 @@
         <v>73</v>
       </c>
       <c r="E437" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F437" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16854,11 +17911,11 @@
         <v>73</v>
       </c>
       <c r="E438" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F438" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16870,11 +17927,11 @@
         <v>73</v>
       </c>
       <c r="E439" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F439" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16886,11 +17943,11 @@
         <v>73</v>
       </c>
       <c r="E440" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F440" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16902,11 +17959,11 @@
         <v>73</v>
       </c>
       <c r="E441" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F441" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16918,11 +17975,11 @@
         <v>73</v>
       </c>
       <c r="E442" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F442" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16934,11 +17991,11 @@
         <v>73</v>
       </c>
       <c r="E443" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F443" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16950,11 +18007,11 @@
         <v>73</v>
       </c>
       <c r="E444" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F444" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -16972,11 +18029,11 @@
         <v>0</v>
       </c>
       <c r="E445" s="6" t="str">
-        <f t="shared" ref="E445:E452" si="23">B445</f>
+        <f t="shared" ref="E445:E452" si="25">B445</f>
         <v>苹果</v>
       </c>
       <c r="F445" s="6" t="str">
-        <f t="shared" ref="F445:F452" si="24">B445</f>
+        <f t="shared" ref="F445:F452" si="26">B445</f>
         <v>苹果</v>
       </c>
     </row>
@@ -16994,11 +18051,11 @@
         <v>10</v>
       </c>
       <c r="E446" s="6" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>芒果</v>
       </c>
       <c r="F446" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>芒果</v>
       </c>
     </row>
@@ -17016,11 +18073,11 @@
         <v>4</v>
       </c>
       <c r="E447" s="6" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>西瓜</v>
       </c>
       <c r="F447" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>西瓜</v>
       </c>
     </row>
@@ -17038,11 +18095,11 @@
         <v>11</v>
       </c>
       <c r="E448" s="6" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>菠萝</v>
       </c>
       <c r="F448" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>菠萝</v>
       </c>
     </row>
@@ -17060,11 +18117,11 @@
         <v>12</v>
       </c>
       <c r="E449" s="6" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>草莓</v>
       </c>
       <c r="F449" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>草莓</v>
       </c>
     </row>
@@ -17082,11 +18139,11 @@
         <v>13</v>
       </c>
       <c r="E450" s="6" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>山竹</v>
       </c>
       <c r="F450" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>山竹</v>
       </c>
     </row>
@@ -17104,11 +18161,11 @@
         <v>28</v>
       </c>
       <c r="E451" s="6" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>樱桃</v>
       </c>
       <c r="F451" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>樱桃</v>
       </c>
     </row>
@@ -17126,11 +18183,11 @@
         <v>45</v>
       </c>
       <c r="E452" s="6" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>香蕉</v>
       </c>
       <c r="F452" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>香蕉</v>
       </c>
     </row>
@@ -17142,11 +18199,11 @@
         <v>73</v>
       </c>
       <c r="E453" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F453" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -17158,11 +18215,11 @@
         <v>73</v>
       </c>
       <c r="E454" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F454" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -17174,11 +18231,11 @@
         <v>73</v>
       </c>
       <c r="E455" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F455" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -17190,11 +18247,11 @@
         <v>73</v>
       </c>
       <c r="E456" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F456" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -17206,11 +18263,11 @@
         <v>73</v>
       </c>
       <c r="E457" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F457" s="6">
-        <f t="shared" ref="F457:F467" si="25">B457</f>
+        <f t="shared" ref="F457:F467" si="27">B457</f>
         <v>0</v>
       </c>
     </row>
@@ -17222,11 +18279,11 @@
         <v>73</v>
       </c>
       <c r="E458" s="6">
-        <f t="shared" ref="E458:E467" si="26">B458</f>
+        <f t="shared" ref="E458:E467" si="28">B458</f>
         <v>0</v>
       </c>
       <c r="F458" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -17238,11 +18295,11 @@
         <v>73</v>
       </c>
       <c r="E459" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F459" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -17254,11 +18311,11 @@
         <v>73</v>
       </c>
       <c r="E460" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F460" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -17270,11 +18327,11 @@
         <v>73</v>
       </c>
       <c r="E461" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F461" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -17286,11 +18343,11 @@
         <v>73</v>
       </c>
       <c r="E462" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F462" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -17302,11 +18359,11 @@
         <v>73</v>
       </c>
       <c r="E463" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F463" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -17318,11 +18375,11 @@
         <v>73</v>
       </c>
       <c r="E464" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F464" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -17334,11 +18391,11 @@
         <v>73</v>
       </c>
       <c r="E465" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F465" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -17350,11 +18407,11 @@
         <v>73</v>
       </c>
       <c r="E466" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F466" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -17366,11 +18423,11 @@
         <v>73</v>
       </c>
       <c r="E467" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F467" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -22041,13 +23098,13 @@
         <v>40000</v>
       </c>
       <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" t="s">
         <v>323</v>
-      </c>
-      <c r="C2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D2" t="s">
-        <v>324</v>
       </c>
       <c r="E2" s="6" t="str">
         <f t="shared" ref="E2:E4" si="0">B2</f>
@@ -22063,13 +23120,13 @@
         <v>40001</v>
       </c>
       <c r="B3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E3" s="6" t="str">
         <f t="shared" si="0"/>
@@ -22084,31 +23141,89 @@
       <c r="A4">
         <v>40002</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="6"/>
-      <c r="E4" s="6">
+      <c r="B4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
+        <v>多放点</v>
+      </c>
+      <c r="F4" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>多放点</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="A5">
+        <v>40003</v>
+      </c>
+      <c r="B5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f t="shared" ref="E5:E6" si="2">B5</f>
+        <v>少放点</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <f t="shared" ref="F5:F6" si="3">B5</f>
+        <v>少放点</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="A6">
+        <v>40004</v>
+      </c>
+      <c r="B6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D6" t="s">
+        <v>414</v>
+      </c>
+      <c r="E6" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>你好</v>
+      </c>
+      <c r="F6" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>你好</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="A7">
+        <v>40005</v>
+      </c>
+      <c r="B7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="D7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f t="shared" ref="E7" si="4">B7</f>
+        <v>点</v>
+      </c>
+      <c r="F7" s="6" t="str">
+        <f t="shared" ref="F7" si="5">B7</f>
+        <v>点</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C8" s="6"/>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF2C546-34C3-4310-91B2-885B645EFBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56A8453-17A7-4C7E-A9A9-87F55E00E8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32865" yWindow="2325" windowWidth="32745" windowHeight="17535" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -2483,15 +2483,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>多放点+재료 : 많이 넣어주세요</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>少放点</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>少放点+재료 : 적게 넣어주세요</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2802,9 +2794,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>刷</t>
-  </si>
-  <si>
     <t>긁다 (카드 등)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2865,6 +2854,18 @@
   </si>
   <si>
     <t>스캔하다 (QR 등)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>多 + 동사 + 点 : 조금 더 많이 동사해라</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>少 + 동사 + 点 : 조금 더 적게 동사해라</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -8642,13 +8643,13 @@
         <v>100008</v>
       </c>
       <c r="B10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E10" s="6" t="str">
         <f t="shared" si="2"/>
@@ -8945,14 +8946,14 @@
         <v>307</v>
       </c>
       <c r="D2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E2" s="6" t="str">
-        <f t="shared" ref="E2:E5" si="0">B2</f>
+        <f t="shared" ref="E2:E4" si="0">B2</f>
         <v>有点</v>
       </c>
       <c r="F2" s="6" t="str">
-        <f t="shared" ref="F2:F5" si="1">B2</f>
+        <f t="shared" ref="F2:F4" si="1">B2</f>
         <v>有点</v>
       </c>
     </row>
@@ -8983,13 +8984,13 @@
         <v>300002</v>
       </c>
       <c r="B4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>307</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E4" s="6" t="str">
         <f t="shared" si="0"/>
@@ -9175,7 +9176,7 @@
         <v>50</v>
       </c>
       <c r="F2" s="6" t="str">
-        <f>B2</f>
+        <f t="shared" ref="F2:F7" si="0">B2</f>
         <v>斤</v>
       </c>
     </row>
@@ -9196,7 +9197,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="6" t="str">
-        <f>B3</f>
+        <f t="shared" si="0"/>
         <v>个</v>
       </c>
     </row>
@@ -9217,7 +9218,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="6" t="str">
-        <f>B4</f>
+        <f t="shared" si="0"/>
         <v>本</v>
       </c>
     </row>
@@ -9238,7 +9239,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="6" t="str">
-        <f>B5</f>
+        <f t="shared" si="0"/>
         <v>只</v>
       </c>
       <c r="G5" s="16" t="s">
@@ -9250,19 +9251,19 @@
         <v>2025</v>
       </c>
       <c r="B6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C6" t="s">
         <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F6" s="6" t="str">
-        <f>B6</f>
+        <f t="shared" si="0"/>
         <v>瓶</v>
       </c>
     </row>
@@ -9271,19 +9272,19 @@
         <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C7" t="s">
         <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F7" s="6" t="str">
-        <f>B7</f>
+        <f t="shared" si="0"/>
         <v>杯</v>
       </c>
     </row>
@@ -9292,19 +9293,19 @@
         <v>2027</v>
       </c>
       <c r="B8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C8" t="s">
         <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F8" s="6" t="str">
-        <f t="shared" ref="F8:F13" si="0">B8</f>
+        <f t="shared" ref="F8:F13" si="1">B8</f>
         <v>双</v>
       </c>
     </row>
@@ -9313,19 +9314,19 @@
         <v>2028</v>
       </c>
       <c r="B9" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C9" t="s">
         <v>142</v>
       </c>
       <c r="D9" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F9" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>罐</v>
       </c>
     </row>
@@ -9337,7 +9338,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9349,7 +9350,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9361,7 +9362,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9373,7 +9374,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10429,13 +10430,13 @@
         <v>10012</v>
       </c>
       <c r="B14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C14" t="s">
         <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E14" s="6" t="str">
         <f t="shared" si="2"/>
@@ -10451,13 +10452,13 @@
         <v>10013</v>
       </c>
       <c r="B15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C15" t="s">
         <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E15" s="6" t="str">
         <f t="shared" si="2"/>
@@ -10473,13 +10474,13 @@
         <v>10014</v>
       </c>
       <c r="B16" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="C16" t="s">
         <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E16" s="6" t="str">
         <f t="shared" si="2"/>
@@ -10495,13 +10496,13 @@
         <v>10015</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E17" s="6" t="str">
         <f t="shared" si="2"/>
@@ -11119,13 +11120,13 @@
         <v>20017</v>
       </c>
       <c r="B25" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C25" t="s">
         <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E25" s="6" t="str">
         <f t="shared" ref="E25:E31" si="3">B25</f>
@@ -11141,13 +11142,13 @@
         <v>20018</v>
       </c>
       <c r="B26" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C26" t="s">
         <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E26" s="6" t="str">
         <f t="shared" si="3"/>
@@ -11763,13 +11764,13 @@
         <v>20121</v>
       </c>
       <c r="B65" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C65" t="s">
         <v>73</v>
       </c>
       <c r="D65" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E65" s="6" t="str">
         <f t="shared" si="7"/>
@@ -11785,13 +11786,13 @@
         <v>20122</v>
       </c>
       <c r="B66" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C66" t="s">
         <v>73</v>
       </c>
       <c r="D66" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E66" s="6" t="str">
         <f>B66</f>
@@ -12074,13 +12075,13 @@
         <v>20135</v>
       </c>
       <c r="B79" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C79" t="s">
         <v>73</v>
       </c>
       <c r="D79" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E79" s="6" t="str">
         <f t="shared" si="11"/>
@@ -12096,13 +12097,13 @@
         <v>20136</v>
       </c>
       <c r="B80" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C80" t="s">
         <v>73</v>
       </c>
       <c r="D80" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E80" s="6" t="str">
         <f t="shared" si="11"/>
@@ -12118,13 +12119,13 @@
         <v>20137</v>
       </c>
       <c r="B81" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C81" t="s">
         <v>73</v>
       </c>
       <c r="D81" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E81" s="6" t="str">
         <f t="shared" si="11"/>
@@ -12140,13 +12141,13 @@
         <v>20138</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C82" t="s">
         <v>73</v>
       </c>
       <c r="D82" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E82" s="6" t="str">
         <f t="shared" ref="E82:E137" si="13">B82</f>
@@ -12162,13 +12163,13 @@
         <v>20139</v>
       </c>
       <c r="B83" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C83" t="s">
         <v>73</v>
       </c>
       <c r="D83" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E83" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12184,13 +12185,13 @@
         <v>20140</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C84" t="s">
         <v>73</v>
       </c>
       <c r="D84" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E84" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12206,13 +12207,13 @@
         <v>20141</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C85" t="s">
         <v>73</v>
       </c>
       <c r="D85" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E85" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12228,13 +12229,13 @@
         <v>20142</v>
       </c>
       <c r="B86" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C86" t="s">
         <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E86" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12250,13 +12251,13 @@
         <v>20143</v>
       </c>
       <c r="B87" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C87" t="s">
         <v>73</v>
       </c>
       <c r="D87" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E87" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12272,13 +12273,13 @@
         <v>20144</v>
       </c>
       <c r="B88" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C88" t="s">
         <v>73</v>
       </c>
       <c r="D88" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E88" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12294,13 +12295,13 @@
         <v>20145</v>
       </c>
       <c r="B89" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C89" t="s">
         <v>73</v>
       </c>
       <c r="D89" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E89" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12316,13 +12317,13 @@
         <v>20146</v>
       </c>
       <c r="B90" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C90" t="s">
         <v>73</v>
       </c>
       <c r="D90" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E90" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12386,13 +12387,13 @@
         <v>20150</v>
       </c>
       <c r="B94" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C94" t="s">
         <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E94" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12408,13 +12409,13 @@
         <v>20151</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C95" t="s">
         <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E95" s="6" t="str">
         <f t="shared" si="13"/>
@@ -12430,13 +12431,13 @@
         <v>20152</v>
       </c>
       <c r="B96" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C96" t="s">
         <v>73</v>
       </c>
       <c r="D96" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E96" s="6" t="str">
         <f t="shared" si="13"/>
@@ -23148,7 +23149,7 @@
         <v>321</v>
       </c>
       <c r="D4" t="s">
-        <v>365</v>
+        <v>429</v>
       </c>
       <c r="E4" s="6" t="str">
         <f t="shared" si="0"/>
@@ -23164,13 +23165,13 @@
         <v>40003</v>
       </c>
       <c r="B5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C5" t="s">
         <v>321</v>
       </c>
       <c r="D5" t="s">
-        <v>367</v>
+        <v>430</v>
       </c>
       <c r="E5" s="6" t="str">
         <f t="shared" ref="E5:E6" si="2">B5</f>
@@ -23186,13 +23187,13 @@
         <v>40004</v>
       </c>
       <c r="B6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C6" t="s">
         <v>321</v>
       </c>
       <c r="D6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E6" s="6" t="str">
         <f t="shared" si="2"/>
@@ -23208,13 +23209,13 @@
         <v>40005</v>
       </c>
       <c r="B7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D7" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E7" s="6" t="str">
         <f t="shared" ref="E7" si="4">B7</f>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56A8453-17A7-4C7E-A9A9-87F55E00E8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA394C77-0DA8-47E5-AB82-EFFDEA2240F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32865" yWindow="2325" windowWidth="32745" windowHeight="17535" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11025" yWindow="2310" windowWidth="32745" windowHeight="17535" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수사" sheetId="4" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="434">
   <si>
     <t>사과</t>
   </si>
@@ -2868,12 +2868,41 @@
     <t>刷</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>pinyin</t>
+  </si>
+  <si>
+    <r>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ě</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lè</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3054,6 +3083,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="3">
@@ -10669,7 +10705,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H467"/>
+  <dimension ref="A1:I467"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.875" customWidth="1"/>
@@ -10681,7 +10717,7 @@
     <col min="8" max="8" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -10706,42 +10742,45 @@
       <c r="H1" s="8" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>20000</v>
       </c>
@@ -10763,7 +10802,7 @@
         <v>上班族</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>20001</v>
       </c>
@@ -10785,7 +10824,7 @@
         <v>公司职员</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>20002</v>
       </c>
@@ -10807,7 +10846,7 @@
         <v>毕业生</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>20003</v>
       </c>
@@ -10829,7 +10868,7 @@
         <v>厨师</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>20004</v>
       </c>
@@ -10851,7 +10890,7 @@
         <v>歌手</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>20005</v>
       </c>
@@ -10873,7 +10912,7 @@
         <v>韩国人</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>20006</v>
       </c>
@@ -10895,7 +10934,7 @@
         <v>中国人</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>20007</v>
       </c>
@@ -10917,7 +10956,7 @@
         <v>程序员</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>20008</v>
       </c>
@@ -12114,7 +12153,7 @@
         <v>勺子</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>20137</v>
       </c>
@@ -12136,7 +12175,7 @@
         <v>叉子</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>20138</v>
       </c>
@@ -12158,7 +12197,7 @@
         <v>筷子</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>20139</v>
       </c>
@@ -12180,7 +12219,7 @@
         <v>汤勺</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>20140</v>
       </c>
@@ -12202,7 +12241,7 @@
         <v>纸巾</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>20141</v>
       </c>
@@ -12224,7 +12263,7 @@
         <v>围裙</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>20142</v>
       </c>
@@ -12246,7 +12285,7 @@
         <v>碟子</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>20143</v>
       </c>
@@ -12268,7 +12307,7 @@
         <v>打包盒</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>20144</v>
       </c>
@@ -12290,7 +12329,7 @@
         <v>卡</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>20145</v>
       </c>
@@ -12312,7 +12351,7 @@
         <v>微信支付</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>20146</v>
       </c>
@@ -12334,7 +12373,7 @@
         <v>支付宝</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>20147</v>
       </c>
@@ -12350,7 +12389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>20148</v>
       </c>
@@ -12366,7 +12405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>20149</v>
       </c>
@@ -12382,7 +12421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>20150</v>
       </c>
@@ -12403,8 +12442,11 @@
         <f t="shared" si="14"/>
         <v>可乐</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I94" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>20151</v>
       </c>
@@ -12426,7 +12468,7 @@
         <v>啤酒</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>20152</v>
       </c>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -12967,7 +12967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13033,8 +13033,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>30000</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
@@ -13049,8 +13051,10 @@
       <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>30116</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30116</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -13085,8 +13089,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>30117</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30117</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -13121,8 +13127,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>30118</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30118</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -13138,7 +13146,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">헤이티 ( 중국 밀크티 프렌차이즈 ) </t>
+          <t>헤이티 ( 중국 밀크티 프렌차이즈 )</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -13157,8 +13165,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>30119</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30119</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -13193,8 +13203,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>30120</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30120</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -13229,8 +13241,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>30121</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30121</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -13265,8 +13279,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>30122</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30122</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -13301,8 +13317,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>30123</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30123</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -13341,8 +13359,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>30124</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30124</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -13381,8 +13401,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>30125</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30125</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -13421,8 +13443,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>30126</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30126</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -13461,8 +13485,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>30127</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30127</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -13501,8 +13527,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>30128</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>30128</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -13545,8 +13573,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>30129</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>30129</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -13585,8 +13615,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>30130</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30130</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -13625,8 +13657,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>30131</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>30131</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -13665,8 +13699,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>30132</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>30132</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -13705,8 +13741,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>30133</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>30133</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -13745,8 +13783,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>30134</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>30134</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -13781,8 +13821,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>30135</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>30135</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -13813,6 +13855,52 @@
       <c r="L22" t="inlineStr">
         <is>
           <t>高胤祯</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>30136</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>李舜臣</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>이순신 - 한산도가</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>30136</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>李舜臣</t>
         </is>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -4793,7 +4793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L453"/>
+  <dimension ref="A1:L455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12953,6 +12953,98 @@
       <c r="L453" t="inlineStr">
         <is>
           <t>现金</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>20510</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>机场</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>공항</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>gtts</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>20510</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>机场</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>20511</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>酒店</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>호텔</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>酒店</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>酒店</t>
         </is>
       </c>
     </row>
@@ -13033,10 +13125,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="A2" t="n">
+        <v>30000</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
@@ -13051,10 +13141,8 @@
       <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>30116</t>
-        </is>
+      <c r="A3" t="n">
+        <v>30116</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -13089,10 +13177,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>30117</t>
-        </is>
+      <c r="A4" t="n">
+        <v>30117</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -13127,10 +13213,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30118</t>
-        </is>
+      <c r="A5" t="n">
+        <v>30118</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -13165,10 +13249,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30119</t>
-        </is>
+      <c r="A6" t="n">
+        <v>30119</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -13203,10 +13285,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>30120</t>
-        </is>
+      <c r="A7" t="n">
+        <v>30120</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -13241,10 +13321,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>30121</t>
-        </is>
+      <c r="A8" t="n">
+        <v>30121</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -13279,10 +13357,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>30122</t>
-        </is>
+      <c r="A9" t="n">
+        <v>30122</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -13317,10 +13393,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>30123</t>
-        </is>
+      <c r="A10" t="n">
+        <v>30123</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -13359,10 +13433,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>30124</t>
-        </is>
+      <c r="A11" t="n">
+        <v>30124</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -13401,10 +13473,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>30125</t>
-        </is>
+      <c r="A12" t="n">
+        <v>30125</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -13443,10 +13513,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>30126</t>
-        </is>
+      <c r="A13" t="n">
+        <v>30126</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -13485,10 +13553,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>30127</t>
-        </is>
+      <c r="A14" t="n">
+        <v>30127</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -13527,10 +13593,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>30128</t>
-        </is>
+      <c r="A15" t="n">
+        <v>30128</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -13573,10 +13637,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>30129</t>
-        </is>
+      <c r="A16" t="n">
+        <v>30129</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -13615,10 +13677,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>30130</t>
-        </is>
+      <c r="A17" t="n">
+        <v>30130</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -13657,10 +13717,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>30131</t>
-        </is>
+      <c r="A18" t="n">
+        <v>30131</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -13699,10 +13757,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>30132</t>
-        </is>
+      <c r="A19" t="n">
+        <v>30132</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -13741,10 +13797,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>30133</t>
-        </is>
+      <c r="A20" t="n">
+        <v>30133</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -13783,10 +13837,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>30134</t>
-        </is>
+      <c r="A21" t="n">
+        <v>30134</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -13821,10 +13873,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>30135</t>
-        </is>
+      <c r="A22" t="n">
+        <v>30135</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -13859,10 +13909,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>30136</t>
-        </is>
+      <c r="A23" t="n">
+        <v>30136</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,30 +461,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -514,13 +519,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>一</t>
         </is>
@@ -550,13 +556,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>两</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>两</t>
         </is>
@@ -586,13 +593,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>二</t>
         </is>
@@ -622,13 +630,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>三</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>三</t>
         </is>
@@ -658,13 +667,14 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>四</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>四</t>
         </is>
@@ -694,13 +704,14 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>五</t>
         </is>
@@ -730,13 +741,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>六</t>
         </is>
@@ -766,13 +778,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>七</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>七</t>
         </is>
@@ -802,13 +815,14 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>八</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>八</t>
         </is>
@@ -838,13 +852,14 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>九</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>九</t>
         </is>
@@ -874,13 +889,14 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>十</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>十</t>
         </is>
@@ -910,13 +926,14 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>十一</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>十一</t>
         </is>
@@ -946,13 +963,14 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>十二</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>十二</t>
         </is>
@@ -982,13 +1000,14 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>十三</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>十三</t>
         </is>
@@ -1018,13 +1037,14 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>十四</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>十四</t>
         </is>
@@ -1054,13 +1074,14 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>十五</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>十五</t>
         </is>
@@ -1090,13 +1111,14 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
         <is>
           <t>十六</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>十六</t>
         </is>
@@ -1126,13 +1148,14 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>十七</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>十七</t>
         </is>
@@ -1162,13 +1185,14 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>十八</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>十八</t>
         </is>
@@ -1198,13 +1222,14 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
         <is>
           <t>十九</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>十九</t>
         </is>
@@ -1234,13 +1259,14 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>二十</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>二十</t>
         </is>
@@ -1257,7 +1283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,30 +1319,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -1342,17 +1373,18 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>床前明月光</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>resource/video/床前明月光.mp4</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>床前明月光</t>
         </is>
@@ -1378,17 +1410,18 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>疑是地上霜</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>resource/video/疑是地上霜.mp4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>疑是地上霜</t>
         </is>
@@ -1414,17 +1447,18 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>举头望明月</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>resource/video/举头望明月.mp4</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>举头望明月</t>
         </is>
@@ -1450,17 +1484,18 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>低头思故乡</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>resource/video/低头思故乡.mp4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>低头思故乡</t>
         </is>
@@ -1478,11 +1513,12 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1503,24 +1539,25 @@
           <t>한산섬 달 밝은 밤에</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>한산도(闲山岛 ): 통영의 섬 ( 삼도수군통제영 )</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>闲山岛月明夜</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>resource/video/闲山岛月明夜.mp4</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>闲山岛月明夜</t>
         </is>
@@ -1543,24 +1580,25 @@
           <t>수루에 올라 큰 칼을 어루만지니</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>수루(戍樓): 적을 살피기 위해 높이 지은 누각</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>上戍楼抚大刀</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>resource/video/上戍楼抚大刀.mp4</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>上戍楼抚大刀</t>
         </is>
@@ -1583,24 +1621,25 @@
           <t>깊은 시름에 잠긴 이때</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>심수(深愁): 깊은 시름</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>深愁时何处</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>resource/video/深愁时何处.mp4</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>深愁时何处</t>
         </is>
@@ -1623,24 +1662,25 @@
           <t>어디선가 들려오는 피리 소리가 시름을 더하는구나</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>일성(一声): 한 가닥 소리\n羌笛 (강독): 강족의 피리 -&gt; 변방의 쓸쓸함</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>一声羌笛更添愁</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>resource/video/一声羌笛更添愁.mp4</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>一声羌笛更添愁</t>
         </is>
@@ -1658,11 +1698,12 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1678,11 +1719,12 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1698,11 +1740,12 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1718,11 +1761,12 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1738,11 +1782,12 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1758,11 +1803,12 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1778,11 +1824,12 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1798,11 +1845,12 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1818,11 +1866,12 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1838,11 +1887,12 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1858,11 +1908,12 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1882,11 +1933,12 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1901,7 +1953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,30 +1989,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -1990,13 +2047,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>贵</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>贵</t>
         </is>
@@ -2026,13 +2084,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>好吃</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>好吃</t>
         </is>
@@ -2062,13 +2121,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>对</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>对</t>
         </is>
@@ -2098,13 +2158,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>错</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>错</t>
         </is>
@@ -2134,13 +2195,14 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>烫</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>烫</t>
         </is>
@@ -2170,13 +2232,14 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>热</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>热</t>
         </is>
@@ -2206,13 +2269,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>凉</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>凉</t>
         </is>
@@ -2242,13 +2306,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>冷</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>冷</t>
         </is>
@@ -2278,13 +2343,14 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>冰</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>冰</t>
         </is>
@@ -2301,7 +2367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2337,30 +2403,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2390,13 +2461,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>往</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>往</t>
         </is>
@@ -2413,7 +2485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2449,30 +2521,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2502,13 +2579,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>有点</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>有点</t>
         </is>
@@ -2538,13 +2616,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>太</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>太</t>
         </is>
@@ -2574,13 +2653,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>请</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>请</t>
         </is>
@@ -2597,7 +2677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2633,30 +2713,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2686,13 +2771,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>斤</t>
         </is>
@@ -2722,13 +2808,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>个</t>
         </is>
@@ -2758,13 +2845,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>本</t>
         </is>
@@ -2798,13 +2886,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>只</t>
         </is>
@@ -2834,13 +2923,14 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>瓶</t>
         </is>
@@ -2870,13 +2960,14 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>杯</t>
         </is>
@@ -2906,13 +2997,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>双</t>
         </is>
@@ -2942,13 +3034,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>罐</t>
         </is>
@@ -2965,7 +3058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,30 +3094,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -3054,13 +3152,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>吗</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>吗</t>
         </is>
@@ -3090,13 +3189,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>不</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>不</t>
         </is>
@@ -3126,13 +3226,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>的</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>的</t>
         </is>
@@ -3162,13 +3263,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>了</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>了</t>
         </is>
@@ -3185,7 +3287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3221,30 +3323,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -3274,13 +3381,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>我</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>我</t>
         </is>
@@ -3310,13 +3418,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>你</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>你</t>
         </is>
@@ -3346,13 +3455,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>您</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>您</t>
         </is>
@@ -3382,13 +3492,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>他</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>他</t>
         </is>
@@ -3418,13 +3529,14 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>她</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>她</t>
         </is>
@@ -3454,13 +3566,14 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>我们</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>我们</t>
         </is>
@@ -3490,13 +3603,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>你们</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>你们</t>
         </is>
@@ -3526,13 +3640,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>他们</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>他们</t>
         </is>
@@ -3562,13 +3677,14 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>她们</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>她们</t>
         </is>
@@ -3585,7 +3701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3621,30 +3737,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -3674,13 +3795,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>这</t>
         </is>
@@ -3710,13 +3832,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>那</t>
         </is>
@@ -3746,13 +3869,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>这个</t>
         </is>
@@ -3782,13 +3906,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>那个</t>
         </is>
@@ -3818,13 +3943,14 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>这儿</t>
         </is>
@@ -3854,13 +3980,14 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>那儿</t>
         </is>
@@ -3890,13 +4017,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>哪儿</t>
         </is>
@@ -3926,13 +4054,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>几</t>
         </is>
@@ -3962,13 +4091,14 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>这样</t>
         </is>
@@ -3998,13 +4128,14 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>那样</t>
         </is>
@@ -4034,13 +4165,14 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>哪样</t>
         </is>
@@ -4070,13 +4202,14 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>这种</t>
         </is>
@@ -4093,7 +4226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4129,30 +4262,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -4182,13 +4320,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -4218,13 +4357,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>在</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>在</t>
         </is>
@@ -4254,13 +4394,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>去</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>去</t>
         </is>
@@ -4290,13 +4431,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>有</t>
         </is>
@@ -4326,13 +4468,14 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>等</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>等</t>
         </is>
@@ -4362,13 +4505,14 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>工作</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>工作</t>
         </is>
@@ -4398,13 +4542,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>好</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>好</t>
         </is>
@@ -4434,13 +4579,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>吃</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>吃</t>
         </is>
@@ -4470,13 +4616,14 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>坐</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>坐</t>
         </is>
@@ -4506,13 +4653,14 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>骑</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>骑</t>
         </is>
@@ -4542,13 +4690,14 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>走</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>走</t>
         </is>
@@ -4578,13 +4727,14 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>要</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>要</t>
         </is>
@@ -4614,13 +4764,14 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>放</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>放</t>
         </is>
@@ -4650,13 +4801,14 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>给</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>给</t>
         </is>
@@ -4686,13 +4838,14 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>刷</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>刷</t>
         </is>
@@ -4722,13 +4875,14 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>扫</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>扫</t>
         </is>
@@ -4760,23 +4914,24 @@
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>edge</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>ko-KR-SunHiNeural</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>付</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>付</t>
         </is>
@@ -4793,7 +4948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L455"/>
+  <dimension ref="A1:M477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4829,30 +4984,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -4871,6 +5031,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -4885,6 +5046,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -4899,6 +5061,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -4913,6 +5076,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -4927,6 +5091,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -4941,6 +5106,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4966,13 +5132,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>上班族</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>上班族</t>
         </is>
@@ -5002,13 +5169,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>公司职员</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>公司职员</t>
         </is>
@@ -5038,13 +5206,14 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>毕业生</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>毕业生</t>
         </is>
@@ -5074,13 +5243,14 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>厨师</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>厨师</t>
         </is>
@@ -5110,13 +5280,14 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>歌手</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>歌手</t>
         </is>
@@ -5146,13 +5317,14 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>韩国人</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>韩国人</t>
         </is>
@@ -5182,13 +5354,14 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>中国人</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>中国人</t>
         </is>
@@ -5218,13 +5391,14 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>程序员</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>程序员</t>
         </is>
@@ -5254,13 +5428,14 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>学生</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>学生</t>
         </is>
@@ -5290,13 +5465,14 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>工程师</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>程序员</t>
         </is>
@@ -5326,13 +5502,14 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
         <is>
           <t>老师</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>老师</t>
         </is>
@@ -5362,13 +5539,14 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>医生</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>医生</t>
         </is>
@@ -5398,13 +5576,14 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>公务员</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>公务员</t>
         </is>
@@ -5434,13 +5613,14 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
         <is>
           <t>设计师</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>设计师</t>
         </is>
@@ -5470,13 +5650,14 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>律师</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>律师</t>
         </is>
@@ -5506,13 +5687,14 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
         <is>
           <t>会计</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>会计</t>
         </is>
@@ -5542,13 +5724,14 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
         <is>
           <t>银行职员</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>银行职员</t>
         </is>
@@ -5578,13 +5761,14 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
         <is>
           <t>服务员</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
         <is>
           <t>服务员</t>
         </is>
@@ -5614,13 +5798,14 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
         <is>
           <t>老板</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>老板</t>
         </is>
@@ -5639,6 +5824,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -5653,6 +5839,7 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -5667,6 +5854,7 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -5681,6 +5869,7 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -5695,6 +5884,7 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -5709,6 +5899,7 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -5723,6 +5914,7 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -5737,6 +5929,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -5751,6 +5944,7 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -5765,6 +5959,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -5779,6 +5974,7 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -5793,6 +5989,7 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -5807,6 +6004,7 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -5821,6 +6019,7 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -5835,6 +6034,7 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5860,13 +6060,14 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
         <is>
           <t>手机</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
         <is>
           <t>手机</t>
         </is>
@@ -5896,13 +6097,14 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
         <is>
           <t>工作</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
         <is>
           <t>工作</t>
         </is>
@@ -5932,13 +6134,14 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
         <is>
           <t>银行</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
         <is>
           <t>银行</t>
         </is>
@@ -5957,6 +6160,7 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5982,13 +6186,14 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
         <is>
           <t>书</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
         <is>
           <t>书</t>
         </is>
@@ -6018,13 +6223,14 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
         <is>
           <t>狗</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
         <is>
           <t>狗</t>
         </is>
@@ -6054,13 +6260,14 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
         <is>
           <t>猫</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
         <is>
           <t>猫</t>
         </is>
@@ -6090,13 +6297,14 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
         <is>
           <t>鸡</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
         <is>
           <t>鸡</t>
         </is>
@@ -6126,13 +6334,14 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
         <is>
           <t>猪</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
         <is>
           <t>猪</t>
         </is>
@@ -6162,13 +6371,14 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
         <is>
           <t>牛</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
         <is>
           <t>牛</t>
         </is>
@@ -6198,13 +6408,14 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
         <is>
           <t>鸭子</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
         <is>
           <t>鸭子</t>
         </is>
@@ -6234,13 +6445,14 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
         <is>
           <t>羊</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
         <is>
           <t>羊</t>
         </is>
@@ -6270,13 +6482,14 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
         <is>
           <t>猪肉</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
         <is>
           <t>猪肉</t>
         </is>
@@ -6306,13 +6519,14 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
         <is>
           <t>牛肉</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
         <is>
           <t>牛肉</t>
         </is>
@@ -6342,13 +6556,14 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
         <is>
           <t>鸭肉</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
         <is>
           <t>鸭肉</t>
         </is>
@@ -6378,13 +6593,14 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
         <is>
           <t>羊肉</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
         <is>
           <t>羊肉</t>
         </is>
@@ -6414,13 +6630,14 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
         <is>
           <t>鸡肉</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
         <is>
           <t>鸡肉</t>
         </is>
@@ -6450,13 +6667,14 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
         <is>
           <t>洗手间</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
         <is>
           <t>洗手间</t>
         </is>
@@ -6486,13 +6704,14 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
         <is>
           <t>地铁站</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
         <is>
           <t>地铁站</t>
         </is>
@@ -6526,13 +6745,14 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
         <is>
           <t>发型</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
         <is>
           <t>发型</t>
         </is>
@@ -6566,13 +6786,14 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
         <is>
           <t>短发</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
         <is>
           <t>短发</t>
         </is>
@@ -6602,13 +6823,14 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
         <is>
           <t>韩式</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
         <is>
           <t>韩式</t>
         </is>
@@ -6638,13 +6860,14 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
         <is>
           <t>水温</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
         <is>
           <t>水温</t>
         </is>
@@ -6674,13 +6897,14 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
         <is>
           <t>水</t>
         </is>
@@ -6710,13 +6934,14 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
         <is>
           <t>冰水</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
         <is>
           <t>冰水</t>
         </is>
@@ -6746,13 +6971,14 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
         <is>
           <t>边</t>
         </is>
@@ -6782,13 +7008,14 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
@@ -6818,13 +7045,14 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
         <is>
           <t>右</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
         <is>
           <t>右</t>
         </is>
@@ -6854,13 +7082,14 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
         <is>
           <t>反</t>
         </is>
@@ -6890,13 +7119,14 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
         <is>
           <t>楼</t>
         </is>
@@ -6926,13 +7156,14 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
         <is>
           <t>香菜</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
         <is>
           <t>香菜</t>
         </is>
@@ -6959,20 +7190,21 @@
           <t>얼얼하고 매운맛</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
         <is>
           <t>얼얼하고 매운 맛 (마라)</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
         <is>
           <t>麻辣</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
         <is>
           <t>麻辣</t>
         </is>
@@ -6999,20 +7231,21 @@
           <t>쯔란</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
         <is>
           <t>양꼬치에 들어가는 향신료</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
         <is>
           <t>孜然</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
         <is>
           <t>孜然</t>
         </is>
@@ -7042,13 +7275,14 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
         <is>
           <t>醋</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
         <is>
           <t>醋</t>
         </is>
@@ -7078,13 +7312,14 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
         <is>
           <t>蒜</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
         <is>
           <t>蒜</t>
         </is>
@@ -7114,13 +7349,14 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
         <is>
           <t>葱</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
         <is>
           <t>葱</t>
         </is>
@@ -7150,13 +7386,14 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
         <is>
           <t>辣椒油</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
         <is>
           <t>辣椒油</t>
         </is>
@@ -7186,13 +7423,14 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
         <is>
           <t>菜单</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
         <is>
           <t>菜单</t>
         </is>
@@ -7222,13 +7460,14 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
         <is>
           <t>勺子</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
         <is>
           <t>勺子</t>
         </is>
@@ -7258,13 +7497,14 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
         <is>
           <t>叉子</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
         <is>
           <t>叉子</t>
         </is>
@@ -7294,13 +7534,14 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
         <is>
           <t>筷子</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
         <is>
           <t>筷子</t>
         </is>
@@ -7330,13 +7571,14 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
         <is>
           <t>汤勺</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr">
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
         <is>
           <t>汤勺</t>
         </is>
@@ -7366,13 +7608,14 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
         <is>
           <t>纸巾</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
         <is>
           <t>纸巾</t>
         </is>
@@ -7402,13 +7645,14 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
         <is>
           <t>围裙</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
         <is>
           <t>围裙</t>
         </is>
@@ -7438,13 +7682,14 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
         <is>
           <t>碟子</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
         <is>
           <t>碟子</t>
         </is>
@@ -7474,13 +7719,14 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
         <is>
           <t>打包盒</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
         <is>
           <t>打包盒</t>
         </is>
@@ -7510,13 +7756,14 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
         <is>
           <t>卡</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
         <is>
           <t>卡</t>
         </is>
@@ -7546,13 +7793,14 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
         <is>
           <t>微信支付</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
         <is>
           <t>微信支付</t>
         </is>
@@ -7582,13 +7830,14 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr">
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
         <is>
           <t>支付宝</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr">
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
         <is>
           <t>支付宝</t>
         </is>
@@ -7607,6 +7856,7 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -7621,6 +7871,7 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -7635,6 +7886,7 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7664,13 +7916,14 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
         <is>
           <t>可乐</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
         <is>
           <t>可乐</t>
         </is>
@@ -7700,13 +7953,14 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
         <is>
           <t>啤酒</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
         <is>
           <t>啤酒</t>
         </is>
@@ -7736,13 +7990,14 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
         <is>
           <t>雪碧</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr">
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
         <is>
           <t>雪碧</t>
         </is>
@@ -7761,6 +8016,7 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
@@ -7775,6 +8031,7 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
@@ -7789,6 +8046,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -7803,6 +8061,7 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
@@ -7817,6 +8076,7 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -7831,6 +8091,7 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
@@ -7845,6 +8106,7 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
@@ -7859,6 +8121,7 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
@@ -7873,6 +8136,7 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -7887,6 +8151,7 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
@@ -7901,6 +8166,7 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -7915,6 +8181,7 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
@@ -7929,6 +8196,7 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
@@ -7943,6 +8211,7 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -7957,6 +8226,7 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
@@ -7971,6 +8241,7 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
@@ -7985,6 +8256,7 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
@@ -7999,6 +8271,7 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
@@ -8013,6 +8286,7 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
@@ -8027,6 +8301,7 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -8041,6 +8316,7 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
@@ -8055,6 +8331,7 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
@@ -8069,6 +8346,7 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -8083,6 +8361,7 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
@@ -8097,6 +8376,7 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
@@ -8111,6 +8391,7 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
@@ -8125,6 +8406,7 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
@@ -8139,6 +8421,7 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
@@ -8153,6 +8436,7 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
@@ -8167,6 +8451,7 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
@@ -8181,6 +8466,7 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
@@ -8195,6 +8481,7 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
@@ -8209,6 +8496,7 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
@@ -8223,6 +8511,7 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
@@ -8237,6 +8526,7 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -8251,6 +8541,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
@@ -8265,6 +8556,7 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
@@ -8279,6 +8571,7 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
@@ -8293,6 +8586,7 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
@@ -8307,6 +8601,7 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
@@ -8321,6 +8616,7 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
@@ -8335,6 +8631,7 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
@@ -8349,6 +8646,7 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
@@ -8363,6 +8661,7 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -8377,6 +8676,7 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
@@ -8391,6 +8691,7 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
@@ -8405,6 +8706,7 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
@@ -8419,6 +8721,7 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -8433,6 +8736,7 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
@@ -8447,6 +8751,7 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
@@ -8461,6 +8766,7 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
@@ -8475,6 +8781,7 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
@@ -8489,6 +8796,7 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
@@ -8503,6 +8811,7 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
@@ -8517,6 +8826,7 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -8531,6 +8841,7 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
@@ -8545,6 +8856,7 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
@@ -8559,6 +8871,7 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
@@ -8573,6 +8886,7 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
@@ -8587,6 +8901,7 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
@@ -8601,6 +8916,7 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
@@ -8615,6 +8931,7 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
@@ -8629,6 +8946,7 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
@@ -8643,6 +8961,7 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
@@ -8657,6 +8976,7 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -8671,6 +8991,7 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
@@ -8685,6 +9006,7 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
@@ -8699,6 +9021,7 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -8713,6 +9036,7 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
@@ -8727,6 +9051,7 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -8741,6 +9066,7 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -8755,6 +9081,7 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -8769,6 +9096,7 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
@@ -8783,6 +9111,7 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -8797,6 +9126,7 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
@@ -8811,6 +9141,7 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
@@ -8825,6 +9156,7 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
@@ -8839,6 +9171,7 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
@@ -8853,6 +9186,7 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
@@ -8867,6 +9201,7 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
@@ -8881,6 +9216,7 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
@@ -8895,6 +9231,7 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
@@ -8909,6 +9246,7 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
@@ -8923,6 +9261,7 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
@@ -8937,6 +9276,7 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
@@ -8951,6 +9291,7 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
@@ -8965,6 +9306,7 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
@@ -8979,6 +9321,7 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
@@ -8993,6 +9336,7 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>
@@ -9007,6 +9351,7 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
@@ -9021,6 +9366,7 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
@@ -9035,6 +9381,7 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
@@ -9049,6 +9396,7 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
@@ -9063,6 +9411,7 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
@@ -9077,6 +9426,7 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
@@ -9091,6 +9441,7 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
@@ -9105,6 +9456,7 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
@@ -9119,6 +9471,7 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
@@ -9133,6 +9486,7 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>
@@ -9147,6 +9501,7 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
@@ -9161,6 +9516,7 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
@@ -9175,6 +9531,7 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
@@ -9189,6 +9546,7 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
@@ -9203,6 +9561,7 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
@@ -9217,6 +9576,7 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
@@ -9231,6 +9591,7 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
@@ -9245,6 +9606,7 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
@@ -9259,6 +9621,7 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
@@ -9273,6 +9636,7 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
@@ -9287,6 +9651,7 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
@@ -9301,6 +9666,7 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
@@ -9315,6 +9681,7 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
@@ -9329,6 +9696,7 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
@@ -9343,6 +9711,7 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
@@ -9357,6 +9726,7 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
@@ -9371,6 +9741,7 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr"/>
@@ -9385,6 +9756,7 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
@@ -9399,6 +9771,7 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr"/>
@@ -9413,6 +9786,7 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr"/>
@@ -9427,6 +9801,7 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr"/>
@@ -9441,6 +9816,7 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr"/>
@@ -9455,6 +9831,7 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
@@ -9469,6 +9846,7 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
@@ -9483,6 +9861,7 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr"/>
@@ -9497,6 +9876,7 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr"/>
@@ -9511,6 +9891,7 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr"/>
@@ -9525,6 +9906,7 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr"/>
@@ -9539,6 +9921,7 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr"/>
@@ -9553,6 +9936,7 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr"/>
@@ -9567,6 +9951,7 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr"/>
@@ -9581,6 +9966,7 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr"/>
@@ -9595,6 +9981,7 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr"/>
@@ -9609,6 +9996,7 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr"/>
@@ -9623,6 +10011,7 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
@@ -9637,6 +10026,7 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
@@ -9651,6 +10041,7 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr"/>
@@ -9665,6 +10056,7 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr"/>
@@ -9679,6 +10071,7 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr"/>
@@ -9693,6 +10086,7 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr"/>
@@ -9707,6 +10101,7 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr"/>
@@ -9721,6 +10116,7 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr"/>
@@ -9735,6 +10131,7 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr"/>
@@ -9749,6 +10146,7 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr"/>
@@ -9763,6 +10161,7 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr"/>
@@ -9777,6 +10176,7 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr"/>
@@ -9791,6 +10191,7 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr"/>
@@ -9805,6 +10206,7 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr"/>
@@ -9819,6 +10221,7 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr"/>
@@ -9833,6 +10236,7 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr"/>
@@ -9847,6 +10251,7 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr"/>
@@ -9861,6 +10266,7 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr"/>
@@ -9875,6 +10281,7 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr"/>
@@ -9889,6 +10296,7 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr"/>
@@ -9903,6 +10311,7 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr"/>
@@ -9917,6 +10326,7 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr"/>
@@ -9931,6 +10341,7 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr"/>
@@ -9945,6 +10356,7 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr"/>
@@ -9959,6 +10371,7 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr"/>
@@ -9973,6 +10386,7 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr"/>
@@ -9987,6 +10401,7 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr"/>
@@ -10001,6 +10416,7 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr"/>
@@ -10015,6 +10431,7 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
@@ -10029,6 +10446,7 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr"/>
@@ -10043,6 +10461,7 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr"/>
@@ -10057,6 +10476,7 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr"/>
@@ -10071,6 +10491,7 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr"/>
@@ -10085,6 +10506,7 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr"/>
@@ -10099,6 +10521,7 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr"/>
@@ -10113,6 +10536,7 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr"/>
@@ -10127,6 +10551,7 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr"/>
@@ -10141,6 +10566,7 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr"/>
@@ -10155,6 +10581,7 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr"/>
@@ -10169,6 +10596,7 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr"/>
@@ -10183,6 +10611,7 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr"/>
@@ -10197,6 +10626,7 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr"/>
@@ -10211,6 +10641,7 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr"/>
@@ -10225,6 +10656,7 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr"/>
@@ -10239,6 +10671,7 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
@@ -10253,6 +10686,7 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr"/>
@@ -10267,6 +10701,7 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr"/>
@@ -10281,6 +10716,7 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr"/>
@@ -10295,6 +10731,7 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr"/>
@@ -10309,6 +10746,7 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
@@ -10323,6 +10761,7 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr"/>
@@ -10337,6 +10776,7 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr"/>
@@ -10351,6 +10791,7 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr"/>
@@ -10365,6 +10806,7 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr"/>
@@ -10379,6 +10821,7 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr"/>
@@ -10393,6 +10836,7 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr"/>
@@ -10407,6 +10851,7 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr"/>
@@ -10421,6 +10866,7 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr"/>
@@ -10435,6 +10881,7 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr"/>
@@ -10449,6 +10896,7 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr"/>
@@ -10463,6 +10911,7 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr"/>
@@ -10477,6 +10926,7 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr"/>
@@ -10491,6 +10941,7 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr"/>
@@ -10505,6 +10956,7 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr"/>
@@ -10519,6 +10971,7 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr"/>
@@ -10533,6 +10986,7 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr"/>
@@ -10547,6 +11001,7 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr"/>
@@ -10561,6 +11016,7 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr"/>
@@ -10575,6 +11031,7 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
@@ -10589,6 +11046,7 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr"/>
@@ -10603,6 +11061,7 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr"/>
@@ -10617,6 +11076,7 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr"/>
@@ -10631,6 +11091,7 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr"/>
@@ -10645,6 +11106,7 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr"/>
@@ -10659,6 +11121,7 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr"/>
@@ -10673,6 +11136,7 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr"/>
@@ -10687,6 +11151,7 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr"/>
@@ -10701,6 +11166,7 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr"/>
@@ -10715,6 +11181,7 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr"/>
@@ -10729,6 +11196,7 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr"/>
@@ -10743,6 +11211,7 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr"/>
@@ -10757,6 +11226,7 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr"/>
@@ -10771,6 +11241,7 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr"/>
@@ -10785,6 +11256,7 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr"/>
@@ -10799,6 +11271,7 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr"/>
@@ -10813,6 +11286,7 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr"/>
@@ -10827,6 +11301,7 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr"/>
@@ -10841,6 +11316,7 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr"/>
@@ -10855,6 +11331,7 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr"/>
@@ -10869,6 +11346,7 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr"/>
@@ -10883,6 +11361,7 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr"/>
@@ -10897,6 +11376,7 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr"/>
@@ -10911,6 +11391,7 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr"/>
@@ -10925,6 +11406,7 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr"/>
@@ -10939,6 +11421,7 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr"/>
@@ -10953,6 +11436,7 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr"/>
@@ -10967,6 +11451,7 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr"/>
@@ -10981,6 +11466,7 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr"/>
@@ -10995,6 +11481,7 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr"/>
@@ -11009,6 +11496,7 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr"/>
@@ -11023,6 +11511,7 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr"/>
@@ -11037,6 +11526,7 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr"/>
@@ -11051,6 +11541,7 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr"/>
@@ -11065,6 +11556,7 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr"/>
@@ -11079,6 +11571,7 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr"/>
@@ -11093,6 +11586,7 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr"/>
@@ -11107,6 +11601,7 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr"/>
@@ -11121,6 +11616,7 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr"/>
@@ -11135,6 +11631,7 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr"/>
@@ -11149,6 +11646,7 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr"/>
@@ -11163,6 +11661,7 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr"/>
@@ -11177,6 +11676,7 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr"/>
@@ -11191,6 +11691,7 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr"/>
@@ -11205,6 +11706,7 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr"/>
@@ -11219,6 +11721,7 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr"/>
@@ -11233,6 +11736,7 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr"/>
@@ -11247,6 +11751,7 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr"/>
@@ -11261,6 +11766,7 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr"/>
@@ -11275,6 +11781,7 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr"/>
@@ -11289,6 +11796,7 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr"/>
@@ -11303,6 +11811,7 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr"/>
@@ -11317,6 +11826,7 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr"/>
@@ -11331,6 +11841,7 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr"/>
@@ -11345,6 +11856,7 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr"/>
@@ -11359,6 +11871,7 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr"/>
@@ -11373,6 +11886,7 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr"/>
@@ -11387,6 +11901,7 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr"/>
@@ -11401,6 +11916,7 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr"/>
@@ -11415,6 +11931,7 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr"/>
@@ -11429,6 +11946,7 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr"/>
@@ -11443,6 +11961,7 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr"/>
@@ -11457,6 +11976,7 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr"/>
@@ -11471,6 +11991,7 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr"/>
@@ -11485,6 +12006,7 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr"/>
@@ -11499,6 +12021,7 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr"/>
@@ -11513,6 +12036,7 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr"/>
@@ -11527,6 +12051,7 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr"/>
@@ -11541,6 +12066,7 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr"/>
@@ -11555,6 +12081,7 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr"/>
@@ -11569,6 +12096,7 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr"/>
@@ -11583,6 +12111,7 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr"/>
@@ -11597,6 +12126,7 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr"/>
@@ -11611,6 +12141,7 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr"/>
@@ -11625,6 +12156,7 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr"/>
@@ -11639,6 +12171,7 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr"/>
@@ -11653,6 +12186,7 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr"/>
@@ -11667,6 +12201,7 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr"/>
@@ -11681,6 +12216,7 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr"/>
@@ -11695,6 +12231,7 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr"/>
@@ -11709,6 +12246,7 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr"/>
@@ -11723,6 +12261,7 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr"/>
@@ -11737,6 +12276,7 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr"/>
@@ -11751,6 +12291,7 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr"/>
@@ -11765,6 +12306,7 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr"/>
@@ -11779,6 +12321,7 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr"/>
@@ -11793,6 +12336,7 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr"/>
@@ -11807,6 +12351,7 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr"/>
@@ -11821,6 +12366,7 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr"/>
@@ -11835,6 +12381,7 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr"/>
@@ -11849,6 +12396,7 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr"/>
@@ -11863,6 +12411,7 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr"/>
@@ -11877,6 +12426,7 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr"/>
@@ -11891,6 +12441,7 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr"/>
@@ -11905,6 +12456,7 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr"/>
@@ -11919,6 +12471,7 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr"/>
@@ -11933,6 +12486,7 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr"/>
@@ -11947,6 +12501,7 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr"/>
@@ -11961,6 +12516,7 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr"/>
@@ -11975,6 +12531,7 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr"/>
@@ -11989,6 +12546,7 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr"/>
@@ -12003,6 +12561,7 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr"/>
@@ -12017,6 +12576,7 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr"/>
@@ -12031,6 +12591,7 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr"/>
@@ -12045,6 +12606,7 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr"/>
@@ -12059,6 +12621,7 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr"/>
@@ -12073,6 +12636,7 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr"/>
@@ -12087,6 +12651,7 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr"/>
@@ -12101,6 +12666,7 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr"/>
@@ -12115,6 +12681,7 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr"/>
@@ -12129,6 +12696,7 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr"/>
@@ -12143,6 +12711,7 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr"/>
@@ -12157,6 +12726,7 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr"/>
@@ -12171,6 +12741,7 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr"/>
@@ -12185,6 +12756,7 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr"/>
@@ -12199,6 +12771,7 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr"/>
@@ -12213,6 +12786,7 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr"/>
@@ -12227,6 +12801,7 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr"/>
@@ -12241,6 +12816,7 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr"/>
@@ -12255,6 +12831,7 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr"/>
@@ -12269,6 +12846,7 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr"/>
@@ -12283,6 +12861,7 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr"/>
@@ -12297,6 +12876,7 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr"/>
@@ -12311,6 +12891,7 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr"/>
@@ -12325,6 +12906,7 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr"/>
@@ -12339,6 +12921,7 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr"/>
@@ -12353,6 +12936,7 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr"/>
@@ -12367,6 +12951,7 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr"/>
@@ -12381,6 +12966,7 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr"/>
@@ -12395,6 +12981,7 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr"/>
@@ -12409,6 +12996,7 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr"/>
@@ -12423,6 +13011,7 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr"/>
@@ -12437,6 +13026,7 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr"/>
       <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr"/>
@@ -12451,6 +13041,7 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr"/>
       <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr"/>
@@ -12465,6 +13056,7 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr"/>
       <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr"/>
@@ -12479,6 +13071,7 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr"/>
       <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr"/>
@@ -12493,6 +13086,7 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr"/>
@@ -12507,6 +13101,7 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr"/>
       <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr"/>
@@ -12521,6 +13116,7 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr"/>
       <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr"/>
@@ -12535,6 +13131,7 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr"/>
       <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr"/>
@@ -12549,6 +13146,7 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr"/>
@@ -12563,6 +13161,7 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr"/>
@@ -12577,6 +13176,7 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr"/>
@@ -12591,6 +13191,7 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr"/>
@@ -12605,6 +13206,7 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr"/>
@@ -12619,6 +13221,7 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr"/>
       <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -12644,13 +13247,14 @@
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr">
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
         <is>
           <t>苹果</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr">
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
         <is>
           <t>苹果</t>
         </is>
@@ -12680,13 +13284,14 @@
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr"/>
       <c r="I446" t="inlineStr"/>
-      <c r="J446" t="inlineStr">
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
         <is>
           <t>芒果</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
-      <c r="L446" t="inlineStr">
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr">
         <is>
           <t>芒果</t>
         </is>
@@ -12716,13 +13321,14 @@
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr">
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
         <is>
           <t>西瓜</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
-      <c r="L447" t="inlineStr">
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr">
         <is>
           <t>西瓜</t>
         </is>
@@ -12752,13 +13358,14 @@
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr"/>
-      <c r="J448" t="inlineStr">
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
         <is>
           <t>菠萝</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
-      <c r="L448" t="inlineStr">
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
         <is>
           <t>菠萝</t>
         </is>
@@ -12788,13 +13395,14 @@
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
-      <c r="J449" t="inlineStr">
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
         <is>
           <t>草莓</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
-      <c r="L449" t="inlineStr">
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr">
         <is>
           <t>草莓</t>
         </is>
@@ -12824,13 +13432,14 @@
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr">
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
         <is>
           <t>山竹</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr">
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
         <is>
           <t>山竹</t>
         </is>
@@ -12860,13 +13469,14 @@
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr"/>
-      <c r="J451" t="inlineStr">
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
         <is>
           <t>樱桃</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
-      <c r="L451" t="inlineStr">
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr">
         <is>
           <t>樱桃</t>
         </is>
@@ -12896,13 +13506,14 @@
       <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr"/>
-      <c r="J452" t="inlineStr">
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
         <is>
           <t>香蕉</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
-      <c r="L452" t="inlineStr">
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr">
         <is>
           <t>香蕉</t>
         </is>
@@ -12934,23 +13545,24 @@
         </is>
       </c>
       <c r="G453" t="inlineStr"/>
-      <c r="H453" t="inlineStr">
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr">
         <is>
           <t>edge</t>
         </is>
       </c>
-      <c r="I453" t="inlineStr">
+      <c r="J453" t="inlineStr">
         <is>
           <t>ko-KR-SunHiNeural</t>
         </is>
       </c>
-      <c r="J453" t="inlineStr">
+      <c r="K453" t="inlineStr">
         <is>
           <t>现金</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
-      <c r="L453" t="inlineStr">
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr">
         <is>
           <t>现金</t>
         </is>
@@ -12982,19 +13594,20 @@
         </is>
       </c>
       <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr">
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr">
         <is>
           <t>gtts</t>
         </is>
       </c>
-      <c r="I454" t="inlineStr"/>
-      <c r="J454" t="inlineStr">
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
         <is>
           <t>20510</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
-      <c r="L454" t="inlineStr">
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr">
         <is>
           <t>机场</t>
         </is>
@@ -13026,25 +13639,1276 @@
         </is>
       </c>
       <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr">
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr">
         <is>
           <t>edge</t>
         </is>
       </c>
-      <c r="I455" t="inlineStr">
+      <c r="J455" t="inlineStr">
         <is>
           <t>ko-KR-SunHiNeural</t>
         </is>
       </c>
-      <c r="J455" t="inlineStr">
+      <c r="K455" t="inlineStr">
         <is>
           <t>酒店</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
-      <c r="L455" t="inlineStr">
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr">
         <is>
           <t>酒店</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>20019</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>xīngqīyī</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>월요일</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>ko-KR-InJoonNeural</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>星期一</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>20020</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>xīngqī'èr</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>화요일</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>星期二</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>20021</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>xīngqīsān</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>수요일</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>星期三</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>20022</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>xīngqīsì</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>목요일</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>星期四</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>20023</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>xīngqīwǔ</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>금요일</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>星期五</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>20024</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>xīngqīliù</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>토요일</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>星期六</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>20025</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>星期天</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>xīngqītiān</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>일요일</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>星期天</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>星期天</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>20026</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>今天</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>jīntiān</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>오늘</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>今天</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>今天</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>20027</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>明天</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>míngtiān</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>내일</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>明天</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>明天</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>20028</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>昨天</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>zuótiān</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>어제</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Yesterday</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>昨天</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>昨天</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>20029</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>上周</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>shàngzhōu</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>지난주</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Last week</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>上周</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>上周</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>20030</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>这周</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>zhèzhōu</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>이번 주</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>This week</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>这周</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>这周</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>20031</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>xiàzhōu</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>다음 주</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Next week</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>下周</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>20032</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>去年</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>qùnián</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>작년</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Last year</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>去年</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>去年</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>20033</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>今年</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>jīnnián</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>올해</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>This year</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>今年</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>今年</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>20034</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>明年</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>míngnián</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>내년</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Next year</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>明年</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>明年</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>20035</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>前天</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>qiántiān</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>그저께</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>The day before yesterday</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>前天</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>前天</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>20036</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>后天</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>hòutiān</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>모레</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>The day after tomorrow</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>后天</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>后天</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>20037</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>上个月</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>shànggeyuè</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>지난달</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Last month</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>上个月</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>上个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>20038</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>这个月</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>zhègeyuè</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>이번 달</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>This month</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>这个月</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>这个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>20039</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>下个月</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>xiàgeyuè</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>다음 달</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Next month</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>下个月</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>下个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>20040</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>每天</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>měitiān</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>매일</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Every day</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>每天</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>每天</t>
         </is>
       </c>
     </row>
@@ -13059,7 +14923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13095,30 +14959,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -13139,6 +15008,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -13164,13 +15034,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>地铁站</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>地铁站</t>
         </is>
@@ -13200,13 +15071,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>外滩</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>外滩</t>
         </is>
@@ -13236,13 +15108,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>喜茶</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>喜茶</t>
         </is>
@@ -13272,13 +15145,14 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>海底捞</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>海底捞</t>
         </is>
@@ -13308,13 +15182,14 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>瑞幸咖啡</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>瑞幸咖啡</t>
         </is>
@@ -13344,13 +15219,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>东方明珠</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>东方明珠</t>
         </is>
@@ -13380,13 +15256,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>迪士尼乐园</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>迪士尼乐园</t>
         </is>
@@ -13413,20 +15290,21 @@
           <t>푸바오</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>福(복)+宝(보배) = "복을 가져다주는 보물"</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>福宝</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>福宝</t>
         </is>
@@ -13453,20 +15331,21 @@
           <t>아이바오</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>爱(사랑)+宝(보배) = “사랑스러운 보물”</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>爱宝</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>爱宝</t>
         </is>
@@ -13493,20 +15372,21 @@
           <t>러바오</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>乐(즐거울)+宝(보배) = “즐거움을 주는 보물”</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>乐宝</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>乐宝</t>
         </is>
@@ -13533,20 +15413,21 @@
           <t>루이바오</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>睿(슬기로울)+宝(보배) = “슬기로운 보물”</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>睿宝</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>睿宝</t>
         </is>
@@ -13573,20 +15454,21 @@
           <t>후이바오</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>辉(빛날)+宝(보배) = “빛나는 보물”</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>辉宝</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>辉宝</t>
         </is>
@@ -13613,24 +15495,25 @@
           <t>바오 패밀리</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>宝(보배)+家(가족) = “바오 가족”</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>ko-KR-SunHiNeural</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>宝家</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>宝家</t>
         </is>
@@ -13657,20 +15540,21 @@
           <t>마오쩌둥 (모택동)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>중화인민공화국의 창건자</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>毛泽东</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>毛泽东</t>
         </is>
@@ -13697,20 +15581,21 @@
           <t>저우언라이 (주은래)</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>건국 초기부터 1976년 사망할 때까지 무려 27년간 총리직을 지키며 중국의 행정과 외교를 도맡은 2인자</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>邓小平</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>邓小平</t>
         </is>
@@ -13737,20 +15622,21 @@
           <t>덩샤오핑 (등소평)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>현대 중국을 부유하게 만든 '개혁개방의 총설계자'</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
         <is>
           <t>周恩来</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>周恩来</t>
         </is>
@@ -13777,20 +15663,21 @@
           <t>장쩌민 (강택민)</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>중국의 고속 경제 성장기를 이끈 실용주의 정치가</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>邓小平</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>邓小平</t>
         </is>
@@ -13817,20 +15704,21 @@
           <t>시진핑 (습근평)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>마오쩌둥 이후 가장 강력한 1인 지배 체제를 구축한 현직 주석</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>习近平</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>习近平</t>
         </is>
@@ -13860,13 +15748,14 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
         <is>
           <t>张元英</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>张元英</t>
         </is>
@@ -13896,13 +15785,14 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>高胤祯</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>高胤祯</t>
         </is>
@@ -13930,23 +15820,24 @@
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>edge</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>ko-KR-SunHiNeural</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>30136</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>李舜臣</t>
         </is>
@@ -13963,7 +15854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13999,30 +15890,35 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>en_meaning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -14052,13 +15948,14 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>太烫了</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>太烫了</t>
         </is>
@@ -14088,13 +15985,14 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>太凉了</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>太凉了</t>
         </is>
@@ -14124,13 +16022,14 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>多放点</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>多放点</t>
         </is>
@@ -14160,13 +16059,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>少放点</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>少放点</t>
         </is>
@@ -14196,13 +16096,14 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>你好</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>你好</t>
         </is>
@@ -14232,13 +16133,14 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>点</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>点</t>
         </is>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -29,13 +29,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +49,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,12 +57,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +441,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -1287,67 +1299,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -1957,67 +1969,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2371,67 +2383,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2489,67 +2501,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2681,67 +2693,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -3062,67 +3074,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -3291,67 +3303,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -3705,67 +3717,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -4230,67 +4242,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -4948,71 +4960,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M477"/>
+  <dimension ref="A1:M486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -5109,8 +5121,10 @@
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>20000</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -5146,8 +5160,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>20001</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -5183,8 +5199,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>20002</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20002</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -5220,8 +5238,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>20003</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20003</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -5257,8 +5277,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>20004</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20004</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -5294,8 +5316,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>20005</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20005</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -5331,8 +5355,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>20006</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20006</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -5368,8 +5394,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>20007</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20007</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5405,8 +5433,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>20008</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20008</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -5442,8 +5472,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>20009</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20009</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5479,8 +5511,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>20010</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20010</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -5516,8 +5550,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>20011</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20011</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -5553,8 +5589,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>20012</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20012</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -5590,8 +5628,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20013</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -5627,8 +5667,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>20014</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20014</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -5664,8 +5706,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>20015</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20015</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -5701,8 +5745,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>20016</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20016</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -5738,8 +5784,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>20017</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20017</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5775,8 +5823,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>20018</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20018</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -6037,8 +6087,10 @@
       <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>20099</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20099</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -6074,8 +6126,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>20100</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20100</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -6111,8 +6165,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>20101</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20101</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -6163,8 +6219,10 @@
       <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>20102</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20102</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -6200,8 +6258,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>20103</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20103</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -6237,8 +6297,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>20104</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20104</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -6274,8 +6336,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>20105</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20105</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6311,8 +6375,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>20106</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20106</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6348,8 +6414,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>20107</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20107</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6385,8 +6453,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>20108</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20108</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6422,8 +6492,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>20109</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20109</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6459,8 +6531,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>20110</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20110</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6496,8 +6570,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>20111</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20111</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6533,8 +6609,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>20112</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20112</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6570,8 +6648,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>20113</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20113</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -6607,8 +6687,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>20114</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20114</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6644,8 +6726,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>20115</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20115</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6681,8 +6765,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>20116</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20116</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6718,8 +6804,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>20117</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20117</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6759,8 +6847,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>20118</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20118</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6800,8 +6890,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>20119</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20119</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6837,8 +6929,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>20120</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20120</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6874,8 +6968,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>20121</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -6911,8 +7007,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>20122</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20122</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -6948,8 +7046,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>20123</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20123</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -6985,8 +7085,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>20124</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20124</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -7022,8 +7124,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>20125</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20125</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -7059,8 +7163,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>20126</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20126</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -7096,8 +7202,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>20127</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20127</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -7133,8 +7241,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>20128</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20128</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -7170,8 +7280,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>20129</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20129</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -7211,8 +7323,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>20130</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20130</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -7252,8 +7366,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>20131</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20131</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -7289,8 +7405,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>20132</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20132</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -7326,8 +7444,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>20133</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20133</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -7363,8 +7483,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>20134</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20134</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -7400,8 +7522,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>20135</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20135</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -7437,8 +7561,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>20136</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20136</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -7474,8 +7600,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
-        <v>20137</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20137</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -7511,8 +7639,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>20138</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20138</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -7548,8 +7678,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>20139</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20139</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -7585,8 +7717,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>20140</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20140</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -7622,8 +7756,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>20141</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20141</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -7659,8 +7795,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>20142</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20142</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -7696,8 +7834,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>20143</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20143</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -7733,8 +7873,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>20144</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20144</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -7770,8 +7912,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>20145</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20145</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -7807,8 +7951,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v>20146</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20146</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -7889,8 +8035,10 @@
       <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v>20150</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20150</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -7930,8 +8078,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>20151</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20151</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -7967,8 +8117,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>20152</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20152</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -13224,8 +13376,10 @@
       <c r="M444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" t="n">
-        <v>20501</v>
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>20501</t>
+        </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -13261,8 +13415,10 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="n">
-        <v>20502</v>
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>20502</t>
+        </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -13298,8 +13454,10 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="n">
-        <v>20503</v>
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>20503</t>
+        </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -13335,8 +13493,10 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="n">
-        <v>20504</v>
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>20504</t>
+        </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -13372,8 +13532,10 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="n">
-        <v>20505</v>
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>20505</t>
+        </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -13409,8 +13571,10 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="n">
-        <v>20506</v>
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>20506</t>
+        </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -13446,8 +13610,10 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="n">
-        <v>20507</v>
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>20507</t>
+        </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -13483,8 +13649,10 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="n">
-        <v>20508</v>
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>20508</t>
+        </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -13520,8 +13688,10 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="n">
-        <v>20509</v>
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>20509</t>
+        </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -13569,8 +13739,10 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="n">
-        <v>20510</v>
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>20510</t>
+        </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -13614,8 +13786,10 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="n">
-        <v>20511</v>
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>20511</t>
+        </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -13663,8 +13837,10 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="n">
-        <v>20019</v>
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>20019</t>
+        </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -13716,8 +13892,10 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="n">
-        <v>20020</v>
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>20020</t>
+        </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -13773,8 +13951,10 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="n">
-        <v>20021</v>
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>20021</t>
+        </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -13830,8 +14010,10 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="n">
-        <v>20022</v>
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>20022</t>
+        </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -13887,8 +14069,10 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="n">
-        <v>20023</v>
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>20023</t>
+        </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -13944,8 +14128,10 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="n">
-        <v>20024</v>
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>20024</t>
+        </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -14001,8 +14187,10 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="n">
-        <v>20025</v>
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>20025</t>
+        </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -14058,8 +14246,10 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="n">
-        <v>20026</v>
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>20026</t>
+        </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -14115,8 +14305,10 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="n">
-        <v>20027</v>
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>20027</t>
+        </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -14172,8 +14364,10 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="n">
-        <v>20028</v>
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>20028</t>
+        </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -14229,8 +14423,10 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="n">
-        <v>20029</v>
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>20029</t>
+        </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -14286,8 +14482,10 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="n">
-        <v>20030</v>
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>20030</t>
+        </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -14343,8 +14541,10 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="n">
-        <v>20031</v>
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>20031</t>
+        </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -14400,8 +14600,10 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="n">
-        <v>20032</v>
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>20032</t>
+        </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -14457,8 +14659,10 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="n">
-        <v>20033</v>
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>20033</t>
+        </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -14514,8 +14718,10 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="n">
-        <v>20034</v>
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>20034</t>
+        </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -14571,8 +14777,10 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="n">
-        <v>20035</v>
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>20035</t>
+        </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -14628,8 +14836,10 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="n">
-        <v>20036</v>
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>20036</t>
+        </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -14685,8 +14895,10 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="n">
-        <v>20037</v>
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>20037</t>
+        </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -14742,8 +14954,10 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="n">
-        <v>20038</v>
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>20038</t>
+        </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -14799,8 +15013,10 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="n">
-        <v>20039</v>
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>20039</t>
+        </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -14856,8 +15072,10 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="n">
-        <v>20040</v>
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>20040</t>
+        </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -14909,6 +15127,537 @@
       <c r="M477" t="inlineStr">
         <is>
           <t>每天</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>妈妈</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>māma</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>엄마</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>妈妈</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>妈妈</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>20042</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>爸爸</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>bàba</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>아빠</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>爸爸</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>爸爸</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>哥哥</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>gēge</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>오빠/형</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Older Brother</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>哥哥</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>哥哥</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>姐姐</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>jiějie</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>언니/누나</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Older Sister</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>姐姐</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>姐姐</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>20045</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>弟弟</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>dìdi</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>남동생</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Younger Brother</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr"/>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>弟弟</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>弟弟</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>20046</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>妹妹</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>mèimei</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>여동생</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Younger Sister</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>妹妹</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>妹妹</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>20047</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>爷爷</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>yéye</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>할아버지</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Grandfather</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr"/>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>爷爷</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>爷爷</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>20048</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>奶奶</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>nǎinai</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>할머니</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Grandmother</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>奶奶</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>奶奶</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>20049</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>孩子</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>háizi</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>아이, 자녀</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>孩子</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>孩子</t>
         </is>
       </c>
     </row>
@@ -14927,67 +15676,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -15858,67 +16607,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -29,13 +29,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +49,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,12 +57,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,72 +441,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -1313,72 +1325,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2009,72 +2021,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2437,72 +2449,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2561,72 +2573,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -2761,72 +2773,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -3155,72 +3167,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -3393,72 +3405,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -3821,72 +3833,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -4359,84 +4371,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>10000</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -4473,8 +4487,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>10001</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -4511,31 +4527,57 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>10002</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>去</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>qù</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>동사</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>~에 가다</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>go</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>去</t>
@@ -4549,8 +4591,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>10003</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -4587,8 +4631,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>10004</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10004</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -4625,31 +4671,57 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>10005</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>工作</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>gōngzuò</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>동사</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>일하다</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>work</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>工作</t>
@@ -4663,8 +4735,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>10006</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10006</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -4701,31 +4775,57 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>10007</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10007</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>吃</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>chī</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>동사</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>먹다</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>eat</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>吃</t>
@@ -4739,31 +4839,57 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>10008</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10008</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>坐</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>zuò</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>동사</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>타다 (자동차, 지하철 등)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>坐</t>
@@ -4777,8 +4903,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10009</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10009</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -4815,31 +4943,57 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>10010</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10010</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>走</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>zǒu</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>동사</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>걷다</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>walk / leave</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>走</t>
@@ -4853,8 +5007,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>10011</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -4891,8 +5047,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>10012</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -4929,31 +5087,57 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>10013</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10013</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>给</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gěi</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>동사</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>주다</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>give</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>给</t>
@@ -4967,8 +5151,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>10014</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10014</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -5005,8 +5191,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>10015</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10015</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5043,8 +5231,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>10016</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>10016</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -5089,6 +5279,2950 @@
       <c r="N18" t="inlineStr">
         <is>
           <t>付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10017</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>来</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lái</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>오다</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>come</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>来</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>来</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10018</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>买</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mǎi</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>사다</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>买</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>买</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>10019</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>卖</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mài</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>팔다</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>卖</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>卖</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>10020</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>收</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>shōu</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>받다</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>receive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>收</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>收</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>10021</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>问</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wèn</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>묻다</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>问</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>问</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>huídá</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>대답하다</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>看</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>kàn</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>보다</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>see / watch</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>看</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>看</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>听</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>tīng</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>듣다</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>listen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>听</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>听</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>10025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>说</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>shuō</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>말하다</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>speak / say</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>说</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>说</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>10026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>学</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>xué</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>배우다</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>learn</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>学</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>学</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>10027</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>教</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jiāo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>가르치다</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>teach</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>教</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>教</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10028</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>赢</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>yíng</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>이기다</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>赢</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>赢</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>10029</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>输</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>shū</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>지다</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>lose</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>输</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>输</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10030</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>kāi</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>열다</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10031</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>关</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>guān</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>닫다</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>关</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>关</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>10032</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>shàng</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>올라가다</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>go up</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10033</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>xià</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>내려가다</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>go down</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10034</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>进</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jìn</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>들어가다</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>进</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>进</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10035</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>chū</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>나가다</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10036</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>起</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>qǐ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>일어나다</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>get up</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>起</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>起</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10037</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>穿</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>chuān</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>입다</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>put on</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>穿</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>穿</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10038</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>脱</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>tuō</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>벗다</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>take off</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>脱</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>脱</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10039</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>开始</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>kāishǐ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>시작하다</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>开始</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>开始</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10040</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>结束</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>jiéshù</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>끝내다</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>finish</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>结束</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>结束</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10041</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>记得</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jìde</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>기억하다</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>remember</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>记得</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>记得</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10042</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>忘记</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>wàngjì</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>잊다</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>forget</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>忘记</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>忘记</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10043</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>喜欢</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>xǐhuan</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>좋아하다</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>like</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>喜欢</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>喜欢</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10044</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>讨厌</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>tǎoyàn</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>싫어하다</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>dislike</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>讨厌</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>讨厌</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10045</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>爱</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ài</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>사랑하다</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>爱</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>爱</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10046</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>恨</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>hèn</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>미워하다</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>hate</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>恨</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>恨</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10047</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>休息</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>xiūxi</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>쉬다</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>休息</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>休息</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10048</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>jiè</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>빌리다</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>borrow</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>huán</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>돌려주다</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>return</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10050</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sòng</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>보내다</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>send</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>送</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10051</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>收到</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>shōudào</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>받다</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>receive</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>收到</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>收到</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10052</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>找</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>zhǎo</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>찾다</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>find / look for</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>找</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>找</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10053</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>丢</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>diū</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>잃어버리다</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>lose</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>丢</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>丢</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10054</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>停</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>tíng</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>멈추다</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>停</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>停</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10055</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>喝</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>hē</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>마시다</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>drink</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>喝</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>喝</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>10056</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>做</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>zuò</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>만들다, 하다</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>do / make</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>做</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>做</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>10057</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>用</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>yòng</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>사용하다</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>用</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>用</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>10058</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>住</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>zhù</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>살다, 머무르다</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>live / stay</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>住</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>住</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>10059</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>离开</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>líkāi</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>떠나다</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>leave</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>离开</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>离开</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>10060</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>进去</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>jìnqù</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>들어가다</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>go in</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>进去</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>进去</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>10061</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>出来</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>chūlái</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>나오다</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>come out</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>出来</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>出来</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>10062</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>跑</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>pǎo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>반대</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>뛰다</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ko-KR-SunHiNeural</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>跑</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>跑</t>
         </is>
       </c>
     </row>
@@ -5107,72 +8241,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -18025,72 +21159,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>
@@ -18983,72 +22117,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>word</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pinyin</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pos</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>en_meaning</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>tip</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>tts_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tts_voice</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>img_path</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>video_path</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>sound_path</t>
         </is>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -1901,7 +1901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,8 +1967,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>100000</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2003,28 +2005,46 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>100001</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>100001</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>好吃</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>hǎochī</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>형용사</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>맛있는</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>맛있다</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Delicious</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
@@ -2039,8 +2059,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>100002</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>100002</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2075,8 +2097,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>100003</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>100003</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2111,8 +2135,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>100004</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>100004</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2147,8 +2173,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>100005</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>100005</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2183,8 +2211,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>100006</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>100006</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2219,8 +2249,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>100007</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>100007</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2255,8 +2287,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>100008</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>100008</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2287,6 +2321,654 @@
       <c r="L10" t="inlineStr">
         <is>
           <t>冰</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>100009</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hǎo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>좋다</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>100010</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>好喝</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hǎohē</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>음료가 맛있다</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Tasty</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>好喝</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>好喝</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>100011</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>好看</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hǎokàn</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>보기 좋다</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Beautiful</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>好看</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>好看</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>100012</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>好听</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hǎotīng</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>듣기 좋다</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Melodious</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>好听</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>好听</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>100013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>好玩</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hǎowán</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>재미있다</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>好玩</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>好玩</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>100014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>好用</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>hǎoyòng</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>유용하다</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Useful</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>好用</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>好用</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>100015</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>好笑</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hǎoxiào</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>웃기다</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Funny</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>好笑</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>好笑</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>100016</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>好做</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>hǎozuò</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>만들기 쉽다</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Easy to make</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>好做</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>好做</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>100017</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>好受</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>hǎoshòu</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>편안하다, 기분 좋다</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Comfortable</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>好受</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>好受</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>100018</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>好走</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>hǎozǒu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>걷기 좋다</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Easy to walk</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>好走</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>好走</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>100019</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>好学</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>hǎoxué</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>배우기 쉽다</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Easy to learn</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>好学</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>好学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>100020</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>好闻</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hǎowén</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>好</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>냄새 좋다</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Good-smelling</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>好闻</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>好闻</t>
         </is>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -1967,10 +1967,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="A2" t="n">
+        <v>100000</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2005,10 +2003,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>100001</t>
-        </is>
+      <c r="A3" t="n">
+        <v>100001</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2059,10 +2055,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>100002</t>
-        </is>
+      <c r="A4" t="n">
+        <v>100002</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2097,10 +2091,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>100003</t>
-        </is>
+      <c r="A5" t="n">
+        <v>100003</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2135,10 +2127,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>100004</t>
-        </is>
+      <c r="A6" t="n">
+        <v>100004</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2173,10 +2163,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>100005</t>
-        </is>
+      <c r="A7" t="n">
+        <v>100005</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2211,10 +2199,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>100006</t>
-        </is>
+      <c r="A8" t="n">
+        <v>100006</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2249,10 +2235,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>100007</t>
-        </is>
+      <c r="A9" t="n">
+        <v>100007</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2287,10 +2271,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>100008</t>
-        </is>
+      <c r="A10" t="n">
+        <v>100008</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2325,10 +2307,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>100009</t>
-        </is>
+      <c r="A11" t="n">
+        <v>100009</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2379,10 +2359,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>100010</t>
-        </is>
+      <c r="A12" t="n">
+        <v>100010</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2433,10 +2411,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>100011</t>
-        </is>
+      <c r="A13" t="n">
+        <v>100011</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2487,10 +2463,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>100012</t>
-        </is>
+      <c r="A14" t="n">
+        <v>100012</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2541,10 +2515,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>100013</t>
-        </is>
+      <c r="A15" t="n">
+        <v>100013</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2595,10 +2567,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>100014</t>
-        </is>
+      <c r="A16" t="n">
+        <v>100014</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2649,10 +2619,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>100015</t>
-        </is>
+      <c r="A17" t="n">
+        <v>100015</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2703,10 +2671,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>100016</t>
-        </is>
+      <c r="A18" t="n">
+        <v>100016</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2757,10 +2723,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>100017</t>
-        </is>
+      <c r="A19" t="n">
+        <v>100017</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2811,10 +2775,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>100018</t>
-        </is>
+      <c r="A20" t="n">
+        <v>100018</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2865,10 +2827,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>100019</t>
-        </is>
+      <c r="A21" t="n">
+        <v>100019</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2919,10 +2879,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>100020</t>
-        </is>
+      <c r="A22" t="n">
+        <v>100020</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -7955,7 +7913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L514"/>
+  <dimension ref="A1:L523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8473,20 +8431,36 @@
           <t>老师</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lǎoshī</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>명사</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>선생님</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
@@ -8761,20 +8735,36 @@
           <t>老板</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lǎobǎn</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>명사</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>사장님</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
@@ -19269,6 +19259,466 @@
           <t>椰子</t>
         </is>
       </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>20078</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>老公</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>lǎogōng</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>남편</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>husband</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr"/>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>老公</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>老公</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>20079</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>老婆</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>lǎopó</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>아내</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>wife</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr"/>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>老婆</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>老婆</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>20080</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>老人</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>lǎorén</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>노인</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>elderly</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr"/>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>老人</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>老人</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>20081</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>老外</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>lǎowài</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>외국인</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>foreigner</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>老外</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>老外</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>20082</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>老样子</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>lǎoyàngzi</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>여전한 모습</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>same as before</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr"/>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>老样子</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>老样子</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>20083</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>老朋友</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>lǎopéngyou</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>오랜 친구</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>old friend</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>老朋友</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>老朋友</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>20084</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>老家</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>lǎojiā</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>고향</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>hometown</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>老家</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>老家</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>20085</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>老百姓</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>lǎobǎixìng</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>서민, 국민</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>ordinary people</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>老百姓</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>老百姓</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>20086</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>老</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>lǎo</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr"/>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>lao</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>오래된, 늙다</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>old, aged</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -7913,7 +7913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L523"/>
+  <dimension ref="A1:L544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8063,8 +8063,10 @@
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>20000</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -8099,8 +8101,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>20001</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -8135,8 +8139,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>20002</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20002</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -8171,8 +8177,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>20003</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20003</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -8207,8 +8215,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>20004</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20004</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -8243,8 +8253,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>20005</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20005</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -8279,8 +8291,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>20006</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20006</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -8315,8 +8329,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>20007</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20007</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -8351,8 +8367,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>20008</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20008</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -8387,8 +8405,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>20009</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20009</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -8423,8 +8443,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>20010</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20010</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -8475,8 +8497,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>20011</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20011</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -8511,8 +8535,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>20012</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20012</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -8547,8 +8573,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20013</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -8583,8 +8611,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>20014</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20014</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -8619,8 +8649,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>20015</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20015</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -8655,8 +8687,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>20016</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20016</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -8691,8 +8725,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>20017</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20017</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -8727,8 +8763,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>20018</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20018</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -8989,8 +9027,10 @@
       <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>20099</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20099</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -9025,8 +9065,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>20100</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20100</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -9061,8 +9103,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>20101</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20101</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -9111,8 +9155,10 @@
       <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>20102</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20102</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -9147,8 +9193,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>20103</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20103</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -9166,7 +9214,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>개</t>
@@ -9191,8 +9243,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>20104</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20104</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -9210,7 +9264,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>고양이</t>
@@ -9235,8 +9293,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>20105</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20105</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -9254,7 +9314,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>닭</t>
@@ -9279,8 +9343,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>20106</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20106</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -9294,7 +9360,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>돼지</t>
@@ -9319,8 +9389,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>20107</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20107</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -9334,7 +9406,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>소</t>
@@ -9359,8 +9435,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>20108</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20108</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -9374,7 +9452,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>오리</t>
@@ -9399,8 +9481,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>20109</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20109</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -9414,7 +9498,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>양</t>
@@ -9439,8 +9527,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>20110</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20110</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -9475,8 +9565,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>20111</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20111</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -9511,8 +9603,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>20112</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20112</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -9547,8 +9641,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>20113</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20113</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -9583,8 +9679,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>20114</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20114</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -9619,8 +9717,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>20115</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20115</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -9655,8 +9755,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>20116</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20116</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -9691,8 +9793,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>20117</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20117</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -9731,8 +9835,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>20118</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20118</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -9771,8 +9877,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>20119</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20119</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -9807,8 +9915,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>20120</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20120</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -9843,8 +9953,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>20121</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -9879,8 +9991,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>20122</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20122</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -9915,8 +10029,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>20123</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20123</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -9951,8 +10067,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>20124</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20124</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -9987,8 +10105,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>20125</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20125</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -10023,8 +10143,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>20126</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20126</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -10059,8 +10181,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>20127</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20127</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -10095,8 +10219,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>20128</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20128</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -10131,8 +10257,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>20129</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20129</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -10171,8 +10299,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>20130</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20130</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -10211,8 +10341,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>20131</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20131</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -10247,8 +10379,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>20132</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20132</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -10283,8 +10417,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>20133</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20133</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -10319,8 +10455,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>20134</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20134</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -10355,8 +10493,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>20135</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20135</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -10391,8 +10531,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>20136</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20136</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -10427,8 +10569,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
-        <v>20137</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20137</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -10463,8 +10607,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>20138</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20138</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -10499,8 +10645,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>20139</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20139</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -10535,8 +10683,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>20140</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20140</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -10571,8 +10721,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>20141</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20141</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -10607,8 +10759,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>20142</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20142</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -10643,8 +10797,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>20143</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20143</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -10679,8 +10835,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>20144</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20144</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -10715,8 +10873,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>20145</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20145</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -10751,8 +10911,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v>20146</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20146</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -10829,8 +10991,10 @@
       <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v>20150</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20150</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -10869,8 +11033,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>20151</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20151</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -10905,8 +11071,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>20152</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20152</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -15813,8 +15981,10 @@
       <c r="L444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" t="n">
-        <v>20501</v>
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>20501</t>
+        </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -15865,8 +16035,10 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="n">
-        <v>20502</v>
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>20502</t>
+        </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -15917,8 +16089,10 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="n">
-        <v>20503</v>
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>20503</t>
+        </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -15969,8 +16143,10 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="n">
-        <v>20504</v>
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>20504</t>
+        </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -16021,8 +16197,10 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="n">
-        <v>20505</v>
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>20505</t>
+        </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -16073,8 +16251,10 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="n">
-        <v>20506</v>
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>20506</t>
+        </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -16125,8 +16305,10 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="n">
-        <v>20507</v>
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>20507</t>
+        </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -16177,8 +16359,10 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="n">
-        <v>20508</v>
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>20508</t>
+        </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -16229,8 +16413,10 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="n">
-        <v>20509</v>
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>20509</t>
+        </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -16269,8 +16455,10 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="n">
-        <v>20510</v>
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>20510</t>
+        </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -16309,8 +16497,10 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="n">
-        <v>20511</v>
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>20511</t>
+        </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -16349,8 +16539,10 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="n">
-        <v>20019</v>
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>20019</t>
+        </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -16372,7 +16564,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G456" t="inlineStr">
         <is>
           <t>월요일</t>
@@ -16397,8 +16593,10 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="n">
-        <v>20020</v>
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>20020</t>
+        </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -16420,7 +16618,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F457" t="inlineStr"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G457" t="inlineStr">
         <is>
           <t>화요일</t>
@@ -16445,8 +16647,10 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="n">
-        <v>20021</v>
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>20021</t>
+        </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -16468,7 +16672,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G458" t="inlineStr">
         <is>
           <t>수요일</t>
@@ -16493,8 +16701,10 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="n">
-        <v>20022</v>
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>20022</t>
+        </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -16516,7 +16726,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G459" t="inlineStr">
         <is>
           <t>목요일</t>
@@ -16541,8 +16755,10 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="n">
-        <v>20023</v>
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>20023</t>
+        </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -16564,7 +16780,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G460" t="inlineStr">
         <is>
           <t>금요일</t>
@@ -16589,8 +16809,10 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="n">
-        <v>20024</v>
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>20024</t>
+        </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -16612,7 +16834,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G461" t="inlineStr">
         <is>
           <t>토요일</t>
@@ -16637,8 +16863,10 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="n">
-        <v>20025</v>
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>20025</t>
+        </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -16660,7 +16888,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G462" t="inlineStr">
         <is>
           <t>일요일</t>
@@ -16685,8 +16917,10 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="n">
-        <v>20026</v>
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>20026</t>
+        </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -16708,7 +16942,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G463" t="inlineStr">
         <is>
           <t>오늘</t>
@@ -16733,8 +16971,10 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="n">
-        <v>20027</v>
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>20027</t>
+        </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -16756,7 +16996,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G464" t="inlineStr">
         <is>
           <t>내일</t>
@@ -16781,8 +17025,10 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="n">
-        <v>20028</v>
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>20028</t>
+        </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -16804,7 +17050,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F465" t="inlineStr"/>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G465" t="inlineStr">
         <is>
           <t>어제</t>
@@ -16829,8 +17079,10 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="n">
-        <v>20029</v>
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>20029</t>
+        </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -16852,7 +17104,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G466" t="inlineStr">
         <is>
           <t>지난주</t>
@@ -16877,8 +17133,10 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="n">
-        <v>20030</v>
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>20030</t>
+        </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -16900,7 +17158,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G467" t="inlineStr">
         <is>
           <t>이번 주</t>
@@ -16925,8 +17187,10 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="n">
-        <v>20031</v>
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>20031</t>
+        </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -16948,7 +17212,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F468" t="inlineStr"/>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G468" t="inlineStr">
         <is>
           <t>다음 주</t>
@@ -16973,8 +17241,10 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="n">
-        <v>20032</v>
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>20032</t>
+        </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -16996,7 +17266,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F469" t="inlineStr"/>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G469" t="inlineStr">
         <is>
           <t>작년</t>
@@ -17021,8 +17295,10 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="n">
-        <v>20033</v>
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>20033</t>
+        </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -17044,7 +17320,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F470" t="inlineStr"/>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G470" t="inlineStr">
         <is>
           <t>올해</t>
@@ -17069,8 +17349,10 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="n">
-        <v>20034</v>
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>20034</t>
+        </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -17092,7 +17374,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F471" t="inlineStr"/>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G471" t="inlineStr">
         <is>
           <t>내년</t>
@@ -17117,8 +17403,10 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="n">
-        <v>20035</v>
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>20035</t>
+        </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -17140,7 +17428,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F472" t="inlineStr"/>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G472" t="inlineStr">
         <is>
           <t>그저께</t>
@@ -17165,8 +17457,10 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="n">
-        <v>20036</v>
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>20036</t>
+        </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -17188,7 +17482,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F473" t="inlineStr"/>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G473" t="inlineStr">
         <is>
           <t>모레</t>
@@ -17213,8 +17511,10 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="n">
-        <v>20037</v>
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>20037</t>
+        </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -17236,7 +17536,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F474" t="inlineStr"/>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G474" t="inlineStr">
         <is>
           <t>지난달</t>
@@ -17261,8 +17565,10 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="n">
-        <v>20038</v>
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>20038</t>
+        </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -17284,7 +17590,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr"/>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G475" t="inlineStr">
         <is>
           <t>이번 달</t>
@@ -17309,8 +17619,10 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="n">
-        <v>20039</v>
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>20039</t>
+        </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -17332,7 +17644,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F476" t="inlineStr"/>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G476" t="inlineStr">
         <is>
           <t>다음 달</t>
@@ -17357,8 +17673,10 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="n">
-        <v>20040</v>
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>20040</t>
+        </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -17380,7 +17698,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F477" t="inlineStr"/>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="G477" t="inlineStr">
         <is>
           <t>매일</t>
@@ -17405,8 +17727,10 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="n">
-        <v>20041</v>
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -17428,7 +17752,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F478" t="inlineStr"/>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>jia</t>
+        </is>
+      </c>
       <c r="G478" t="inlineStr">
         <is>
           <t>엄마</t>
@@ -17453,8 +17781,10 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="n">
-        <v>20042</v>
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>20042</t>
+        </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -17476,7 +17806,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr"/>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>jia</t>
+        </is>
+      </c>
       <c r="G479" t="inlineStr">
         <is>
           <t>아빠</t>
@@ -17501,8 +17835,10 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="n">
-        <v>20043</v>
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -17524,7 +17860,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F480" t="inlineStr"/>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>jia</t>
+        </is>
+      </c>
       <c r="G480" t="inlineStr">
         <is>
           <t>오빠/형</t>
@@ -17549,8 +17889,10 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="n">
-        <v>20044</v>
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -17572,7 +17914,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F481" t="inlineStr"/>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>jia</t>
+        </is>
+      </c>
       <c r="G481" t="inlineStr">
         <is>
           <t>언니/누나</t>
@@ -17597,8 +17943,10 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="n">
-        <v>20045</v>
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>20045</t>
+        </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -17620,7 +17968,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F482" t="inlineStr"/>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>jia</t>
+        </is>
+      </c>
       <c r="G482" t="inlineStr">
         <is>
           <t>남동생</t>
@@ -17645,8 +17997,10 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="n">
-        <v>20046</v>
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>20046</t>
+        </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -17668,7 +18022,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr"/>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>jia</t>
+        </is>
+      </c>
       <c r="G483" t="inlineStr">
         <is>
           <t>여동생</t>
@@ -17693,8 +18051,10 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="n">
-        <v>20047</v>
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>20047</t>
+        </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -17716,7 +18076,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F484" t="inlineStr"/>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>jia</t>
+        </is>
+      </c>
       <c r="G484" t="inlineStr">
         <is>
           <t>할아버지</t>
@@ -17741,8 +18105,10 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="n">
-        <v>20048</v>
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>20048</t>
+        </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -17764,7 +18130,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F485" t="inlineStr"/>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>jia</t>
+        </is>
+      </c>
       <c r="G485" t="inlineStr">
         <is>
           <t>할머니</t>
@@ -17789,8 +18159,10 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="n">
-        <v>20049</v>
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>20049</t>
+        </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -17812,7 +18184,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr"/>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>jia</t>
+        </is>
+      </c>
       <c r="G486" t="inlineStr">
         <is>
           <t>아이, 자녀</t>
@@ -17837,8 +18213,10 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="n">
-        <v>20050</v>
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>20050</t>
+        </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -17860,7 +18238,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F487" t="inlineStr"/>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G487" t="inlineStr">
         <is>
           <t>새</t>
@@ -17885,8 +18267,10 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="n">
-        <v>20051</v>
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>20051</t>
+        </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -17908,7 +18292,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F488" t="inlineStr"/>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G488" t="inlineStr">
         <is>
           <t>물고기</t>
@@ -17933,8 +18321,10 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="n">
-        <v>20052</v>
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>20052</t>
+        </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -17956,7 +18346,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr"/>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G489" t="inlineStr">
         <is>
           <t>말</t>
@@ -17981,8 +18375,10 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="n">
-        <v>20054</v>
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>20054</t>
+        </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -18004,7 +18400,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F490" t="inlineStr"/>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G490" t="inlineStr">
         <is>
           <t>토끼</t>
@@ -18029,8 +18429,10 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="n">
-        <v>20055</v>
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>20055</t>
+        </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -18052,7 +18454,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F491" t="inlineStr"/>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G491" t="inlineStr">
         <is>
           <t>호랑이</t>
@@ -18077,8 +18483,10 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="n">
-        <v>20056</v>
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>20056</t>
+        </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -18100,7 +18508,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F492" t="inlineStr"/>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G492" t="inlineStr">
         <is>
           <t>판다</t>
@@ -18125,8 +18537,10 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="n">
-        <v>20057</v>
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>20057</t>
+        </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -18148,7 +18562,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F493" t="inlineStr"/>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G493" t="inlineStr">
         <is>
           <t>사자</t>
@@ -18173,8 +18591,10 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="n">
-        <v>20058</v>
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>20058</t>
+        </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -18196,7 +18616,11 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F494" t="inlineStr"/>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
       <c r="G494" t="inlineStr">
         <is>
           <t>쥐</t>
@@ -18221,8 +18645,10 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="n">
-        <v>20053</v>
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>20053</t>
+        </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -18273,8 +18699,10 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="n">
-        <v>20059</v>
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>20059</t>
+        </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -18325,8 +18753,10 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="n">
-        <v>20060</v>
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>20060</t>
+        </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -18377,8 +18807,10 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="n">
-        <v>20061</v>
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>20061</t>
+        </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -18429,8 +18861,10 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="n">
-        <v>20062</v>
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>20062</t>
+        </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -18481,8 +18915,10 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="n">
-        <v>20063</v>
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>20063</t>
+        </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -18533,8 +18969,10 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="n">
-        <v>20064</v>
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>20064</t>
+        </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -18585,8 +19023,10 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="n">
-        <v>20065</v>
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>20065</t>
+        </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -18637,8 +19077,10 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="n">
-        <v>20066</v>
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>20066</t>
+        </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -18689,8 +19131,10 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="n">
-        <v>20067</v>
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>20067</t>
+        </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -18741,8 +19185,10 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="n">
-        <v>20068</v>
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>20068</t>
+        </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -18793,8 +19239,10 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="n">
-        <v>20069</v>
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>20069</t>
+        </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -18845,8 +19293,10 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="n">
-        <v>20070</v>
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>20070</t>
+        </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -18897,8 +19347,10 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="n">
-        <v>20071</v>
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>20071</t>
+        </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -18949,8 +19401,10 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="n">
-        <v>20072</v>
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>20072</t>
+        </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -19001,8 +19455,10 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="n">
-        <v>20073</v>
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>20073</t>
+        </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -19053,8 +19509,10 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="n">
-        <v>20074</v>
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>20074</t>
+        </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -19105,8 +19563,10 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="n">
-        <v>20075</v>
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>20075</t>
+        </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -19157,8 +19617,10 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="n">
-        <v>20076</v>
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>20076</t>
+        </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -19209,8 +19671,10 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="n">
-        <v>20077</v>
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>20077</t>
+        </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -19261,8 +19725,10 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="n">
-        <v>20078</v>
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>20078</t>
+        </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -19313,8 +19779,10 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="n">
-        <v>20079</v>
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>20079</t>
+        </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -19365,8 +19833,10 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="n">
-        <v>20080</v>
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>20080</t>
+        </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -19417,8 +19887,10 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="n">
-        <v>20081</v>
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>20081</t>
+        </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -19469,8 +19941,10 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="n">
-        <v>20082</v>
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>20082</t>
+        </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -19521,8 +19995,10 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="n">
-        <v>20083</v>
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>20083</t>
+        </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -19573,8 +20049,10 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="n">
-        <v>20084</v>
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>20084</t>
+        </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -19625,8 +20103,10 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="n">
-        <v>20085</v>
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>20085</t>
+        </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -19677,8 +20157,10 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="n">
-        <v>20086</v>
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>20086</t>
+        </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -19719,6 +20201,1140 @@
       </c>
       <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>20087</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>博物馆</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>bówùguǎn</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>guan</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>박물관</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>museum</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>博物馆</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>博物馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>20088</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>美术馆</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>měishùguǎn</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>guan</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>미술관</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>art museum</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>美术馆</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>美术馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>20089</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>科学馆</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>kēxuéguǎn</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>guan</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>과학관</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>science museum</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>科学馆</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>科学馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>20091</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>宾馆</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>bīnguǎn</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>guan</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>모텔</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>motel</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr"/>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>宾馆</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>宾馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>20092</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>大使馆</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>dàshǐguǎn</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>guan</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>대사관</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>embassy</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr"/>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>大使馆</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>大使馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>20095</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>图书馆</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>túshūguǎn</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>guan</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>도서관</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>library</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr"/>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>图书馆</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>图书馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>20096</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>体育馆</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>tǐyùguǎn</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>guan</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>체육관</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>gymnasium</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr"/>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>体育馆</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>体育馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>20097</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>电视</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>diànshì</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>television</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>电视</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>电视</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>20098</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>电冰箱</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>diànbīngxiāng</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>냉장고</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>电冰箱</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>电冰箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>20147</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>电风扇</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>diànfēngshàn</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>선풍기</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>electric fan</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>电风扇</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>电风扇</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>20149</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>diànchí</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>배터리</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr"/>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>20153</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>电饭煲</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>diànfànbāo</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>밥솥</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>rice cooker</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr"/>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>电饭煲</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>电饭煲</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>20154</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>电热水壶</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>diànrèshuǐhú</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>"0000"</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>전기포트</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>electric kettle</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr"/>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>电热水壶</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>电热水壶</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>20155</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>电动车</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>diàndòngchē</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>전동차</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>electric vehicle</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr"/>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>电动车</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>电动车</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>20156</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>饭馆</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>fànguǎn</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>guan</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr"/>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>饭馆</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>饭馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>20157</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>diànnǎo</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>컴퓨터</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>computer</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr"/>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>电脑</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>20158</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>diànhuà</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>전화기</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>telephone</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr"/>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>20090</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>电</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>diàn</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>전기, 전기의</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>electricity, electric</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr"/>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>电</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>电</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>20093</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>馆</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>guǎn</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>guan</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>건물, 시설</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>building, hall</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr"/>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>馆</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>20094</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>电灯</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>diàndēng</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>전등</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr"/>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>电灯</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>电灯</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>20148</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>电梯</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>diàntī</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>엘리베이터</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>elevator</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>电梯</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>电梯</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -1901,7 +1901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2927,6 +2927,838 @@
       <c r="L22" t="inlineStr">
         <is>
           <t>好闻</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100021</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>高兴</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>gāoxìng</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>기쁘다</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Happy</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>高兴</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>高兴</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100022</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>快乐</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>kuàilè</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>즐겁다</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Joyful</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>快乐</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>快乐</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>100023</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>兴奋</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>xīngfèn</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>신나다</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Excited</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>兴奋</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>兴奋</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>100024</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>感动</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>gǎndòng</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>감동하다</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Moved</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>感动</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>感动</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>100025</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>放心</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>fàngxīn</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>안심하다</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Relieved</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>放心</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>放心</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>100026</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>满意</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mǎnyì</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>만족하다</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Satisfied</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>满意</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>满意</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>100027</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>舒服</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>shūfu</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>편안하다</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Comfortable</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>舒服</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>舒服</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>100028</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>qīngsōng</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>홀가분하다</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Relaxed</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>轻松</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>100029</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>生气</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>shēngqì</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>화나다</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Angry</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>生气</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>生气</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>100030</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>难过</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nánguò</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>슬프다</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sad</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>难过</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>难过</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>100031</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>伤心</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>shāngxīn</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>상심하다</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Heartbroken</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>伤心</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>伤心</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>100032</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>担心</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>dānxīn</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>걱정하다</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Worried</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>担心</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>担心</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>100033</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>紧张</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jǐnzhāng</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>긴장하다</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Nervous</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>紧张</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>紧张</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>100034</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>累</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>lèi</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>피곤하다</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tired</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>累</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>累</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>100035</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>害怕</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>hàipà</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>무섭다</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Afraid</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>害怕</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>害怕</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>100036</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>害羞</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>hàixiū</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>형용사</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>감정</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>부끄럽다</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Shy</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>害羞</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>害羞</t>
         </is>
       </c>
     </row>
@@ -7913,7 +8745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L544"/>
+  <dimension ref="A1:L553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8063,10 +8895,8 @@
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="A8" t="n">
+        <v>20000</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -8101,10 +8931,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20001</t>
-        </is>
+      <c r="A9" t="n">
+        <v>20001</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -8139,10 +8967,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>20002</t>
-        </is>
+      <c r="A10" t="n">
+        <v>20002</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -8177,10 +9003,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>20003</t>
-        </is>
+      <c r="A11" t="n">
+        <v>20003</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -8215,10 +9039,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20004</t>
-        </is>
+      <c r="A12" t="n">
+        <v>20004</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -8253,10 +9075,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20005</t>
-        </is>
+      <c r="A13" t="n">
+        <v>20005</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -8291,10 +9111,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20006</t>
-        </is>
+      <c r="A14" t="n">
+        <v>20006</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -8329,10 +9147,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>20007</t>
-        </is>
+      <c r="A15" t="n">
+        <v>20007</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -8367,10 +9183,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>20008</t>
-        </is>
+      <c r="A16" t="n">
+        <v>20008</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -8405,10 +9219,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20009</t>
-        </is>
+      <c r="A17" t="n">
+        <v>20009</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -8443,10 +9255,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20010</t>
-        </is>
+      <c r="A18" t="n">
+        <v>20010</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -8497,10 +9307,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>20011</t>
-        </is>
+      <c r="A19" t="n">
+        <v>20011</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -8535,10 +9343,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20012</t>
-        </is>
+      <c r="A20" t="n">
+        <v>20012</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -8573,10 +9379,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20013</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -8611,10 +9415,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20014</t>
-        </is>
+      <c r="A22" t="n">
+        <v>20014</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -8649,10 +9451,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20015</t>
-        </is>
+      <c r="A23" t="n">
+        <v>20015</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -8687,10 +9487,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20016</t>
-        </is>
+      <c r="A24" t="n">
+        <v>20016</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -8725,10 +9523,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20017</t>
-        </is>
+      <c r="A25" t="n">
+        <v>20017</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -8763,10 +9559,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20018</t>
-        </is>
+      <c r="A26" t="n">
+        <v>20018</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -9027,10 +9821,8 @@
       <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>20099</t>
-        </is>
+      <c r="A42" t="n">
+        <v>20099</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -9065,10 +9857,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>20100</t>
-        </is>
+      <c r="A43" t="n">
+        <v>20100</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -9103,10 +9893,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>20101</t>
-        </is>
+      <c r="A44" t="n">
+        <v>20101</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -9155,10 +9943,8 @@
       <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>20102</t>
-        </is>
+      <c r="A46" t="n">
+        <v>20102</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -9193,10 +9979,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>20103</t>
-        </is>
+      <c r="A47" t="n">
+        <v>20103</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -9243,10 +10027,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>20104</t>
-        </is>
+      <c r="A48" t="n">
+        <v>20104</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -9293,10 +10075,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>20105</t>
-        </is>
+      <c r="A49" t="n">
+        <v>20105</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -9343,10 +10123,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>20106</t>
-        </is>
+      <c r="A50" t="n">
+        <v>20106</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -9389,10 +10167,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>20107</t>
-        </is>
+      <c r="A51" t="n">
+        <v>20107</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -9435,10 +10211,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>20108</t>
-        </is>
+      <c r="A52" t="n">
+        <v>20108</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -9481,10 +10255,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>20109</t>
-        </is>
+      <c r="A53" t="n">
+        <v>20109</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -9527,10 +10299,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>20110</t>
-        </is>
+      <c r="A54" t="n">
+        <v>20110</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -9565,10 +10335,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>20111</t>
-        </is>
+      <c r="A55" t="n">
+        <v>20111</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -9603,10 +10371,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>20112</t>
-        </is>
+      <c r="A56" t="n">
+        <v>20112</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -9641,10 +10407,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>20113</t>
-        </is>
+      <c r="A57" t="n">
+        <v>20113</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -9679,10 +10443,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>20114</t>
-        </is>
+      <c r="A58" t="n">
+        <v>20114</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -9717,10 +10479,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>20115</t>
-        </is>
+      <c r="A59" t="n">
+        <v>20115</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -9755,10 +10515,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>20116</t>
-        </is>
+      <c r="A60" t="n">
+        <v>20116</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -9793,10 +10551,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>20117</t>
-        </is>
+      <c r="A61" t="n">
+        <v>20117</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -9835,10 +10591,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>20118</t>
-        </is>
+      <c r="A62" t="n">
+        <v>20118</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -9877,10 +10631,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20119</t>
-        </is>
+      <c r="A63" t="n">
+        <v>20119</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -9915,10 +10667,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>20120</t>
-        </is>
+      <c r="A64" t="n">
+        <v>20120</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -9953,10 +10703,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20121</t>
-        </is>
+      <c r="A65" t="n">
+        <v>20121</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -9991,10 +10739,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20122</t>
-        </is>
+      <c r="A66" t="n">
+        <v>20122</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -10029,10 +10775,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>20123</t>
-        </is>
+      <c r="A67" t="n">
+        <v>20123</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -10067,10 +10811,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>20124</t>
-        </is>
+      <c r="A68" t="n">
+        <v>20124</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -10105,10 +10847,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>20125</t>
-        </is>
+      <c r="A69" t="n">
+        <v>20125</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -10143,10 +10883,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>20126</t>
-        </is>
+      <c r="A70" t="n">
+        <v>20126</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -10181,10 +10919,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>20127</t>
-        </is>
+      <c r="A71" t="n">
+        <v>20127</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -10219,10 +10955,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>20128</t>
-        </is>
+      <c r="A72" t="n">
+        <v>20128</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -10257,10 +10991,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>20129</t>
-        </is>
+      <c r="A73" t="n">
+        <v>20129</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -10299,10 +11031,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>20130</t>
-        </is>
+      <c r="A74" t="n">
+        <v>20130</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -10341,10 +11071,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>20131</t>
-        </is>
+      <c r="A75" t="n">
+        <v>20131</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -10379,10 +11107,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>20132</t>
-        </is>
+      <c r="A76" t="n">
+        <v>20132</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -10417,10 +11143,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>20133</t>
-        </is>
+      <c r="A77" t="n">
+        <v>20133</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -10455,10 +11179,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>20134</t>
-        </is>
+      <c r="A78" t="n">
+        <v>20134</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -10493,10 +11215,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>20135</t>
-        </is>
+      <c r="A79" t="n">
+        <v>20135</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -10531,10 +11251,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>20136</t>
-        </is>
+      <c r="A80" t="n">
+        <v>20136</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -10569,10 +11287,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>20137</t>
-        </is>
+      <c r="A81" t="n">
+        <v>20137</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -10607,10 +11323,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>20138</t>
-        </is>
+      <c r="A82" t="n">
+        <v>20138</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -10645,10 +11359,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>20139</t>
-        </is>
+      <c r="A83" t="n">
+        <v>20139</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -10683,10 +11395,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>20140</t>
-        </is>
+      <c r="A84" t="n">
+        <v>20140</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -10721,10 +11431,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>20141</t>
-        </is>
+      <c r="A85" t="n">
+        <v>20141</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -10759,10 +11467,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>20142</t>
-        </is>
+      <c r="A86" t="n">
+        <v>20142</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -10797,10 +11503,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>20143</t>
-        </is>
+      <c r="A87" t="n">
+        <v>20143</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -10835,10 +11539,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>20144</t>
-        </is>
+      <c r="A88" t="n">
+        <v>20144</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -10873,10 +11575,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>20145</t>
-        </is>
+      <c r="A89" t="n">
+        <v>20145</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -10911,10 +11611,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>20146</t>
-        </is>
+      <c r="A90" t="n">
+        <v>20146</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -10991,10 +11689,8 @@
       <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>20150</t>
-        </is>
+      <c r="A94" t="n">
+        <v>20150</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -11033,10 +11729,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>20151</t>
-        </is>
+      <c r="A95" t="n">
+        <v>20151</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -11071,10 +11765,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>20152</t>
-        </is>
+      <c r="A96" t="n">
+        <v>20152</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -15981,10 +16673,8 @@
       <c r="L444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>20501</t>
-        </is>
+      <c r="A445" t="n">
+        <v>20501</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -16035,10 +16725,8 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>20502</t>
-        </is>
+      <c r="A446" t="n">
+        <v>20502</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -16089,10 +16777,8 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>20503</t>
-        </is>
+      <c r="A447" t="n">
+        <v>20503</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -16143,10 +16829,8 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>20504</t>
-        </is>
+      <c r="A448" t="n">
+        <v>20504</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -16197,10 +16881,8 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>20505</t>
-        </is>
+      <c r="A449" t="n">
+        <v>20505</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -16251,10 +16933,8 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>20506</t>
-        </is>
+      <c r="A450" t="n">
+        <v>20506</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -16305,10 +16985,8 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>20507</t>
-        </is>
+      <c r="A451" t="n">
+        <v>20507</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -16359,10 +17037,8 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>20508</t>
-        </is>
+      <c r="A452" t="n">
+        <v>20508</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -16413,10 +17089,8 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>20509</t>
-        </is>
+      <c r="A453" t="n">
+        <v>20509</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -16455,10 +17129,8 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>20510</t>
-        </is>
+      <c r="A454" t="n">
+        <v>20510</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -16497,17 +17169,19 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>20511</t>
-        </is>
+      <c r="A455" t="n">
+        <v>20511</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
           <t>酒店</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr"/>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>jiǔdiàn</t>
+        </is>
+      </c>
       <c r="D455" t="inlineStr">
         <is>
           <t>"00"</t>
@@ -16518,13 +17192,21 @@
           <t>명사</t>
         </is>
       </c>
-      <c r="F455" t="inlineStr"/>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
       <c r="G455" t="inlineStr">
         <is>
           <t>호텔</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
       <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr">
         <is>
@@ -16539,10 +17221,8 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>20019</t>
-        </is>
+      <c r="A456" t="n">
+        <v>20019</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -16593,10 +17273,8 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>20020</t>
-        </is>
+      <c r="A457" t="n">
+        <v>20020</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -16647,10 +17325,8 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>20021</t>
-        </is>
+      <c r="A458" t="n">
+        <v>20021</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -16701,10 +17377,8 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>20022</t>
-        </is>
+      <c r="A459" t="n">
+        <v>20022</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -16755,10 +17429,8 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>20023</t>
-        </is>
+      <c r="A460" t="n">
+        <v>20023</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -16809,10 +17481,8 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>20024</t>
-        </is>
+      <c r="A461" t="n">
+        <v>20024</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -16863,10 +17533,8 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>20025</t>
-        </is>
+      <c r="A462" t="n">
+        <v>20025</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -16917,10 +17585,8 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>20026</t>
-        </is>
+      <c r="A463" t="n">
+        <v>20026</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -16971,10 +17637,8 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>20027</t>
-        </is>
+      <c r="A464" t="n">
+        <v>20027</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -17025,10 +17689,8 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>20028</t>
-        </is>
+      <c r="A465" t="n">
+        <v>20028</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -17079,10 +17741,8 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>20029</t>
-        </is>
+      <c r="A466" t="n">
+        <v>20029</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -17133,10 +17793,8 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>20030</t>
-        </is>
+      <c r="A467" t="n">
+        <v>20030</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -17187,10 +17845,8 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>20031</t>
-        </is>
+      <c r="A468" t="n">
+        <v>20031</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -17241,10 +17897,8 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>20032</t>
-        </is>
+      <c r="A469" t="n">
+        <v>20032</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -17295,10 +17949,8 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>20033</t>
-        </is>
+      <c r="A470" t="n">
+        <v>20033</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -17349,10 +18001,8 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>20034</t>
-        </is>
+      <c r="A471" t="n">
+        <v>20034</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -17403,10 +18053,8 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>20035</t>
-        </is>
+      <c r="A472" t="n">
+        <v>20035</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -17457,10 +18105,8 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>20036</t>
-        </is>
+      <c r="A473" t="n">
+        <v>20036</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -17511,10 +18157,8 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>20037</t>
-        </is>
+      <c r="A474" t="n">
+        <v>20037</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -17565,10 +18209,8 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>20038</t>
-        </is>
+      <c r="A475" t="n">
+        <v>20038</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -17619,10 +18261,8 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>20039</t>
-        </is>
+      <c r="A476" t="n">
+        <v>20039</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -17673,10 +18313,8 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>20040</t>
-        </is>
+      <c r="A477" t="n">
+        <v>20040</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -17727,10 +18365,8 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
+      <c r="A478" t="n">
+        <v>20041</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -17781,10 +18417,8 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>20042</t>
-        </is>
+      <c r="A479" t="n">
+        <v>20042</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -17835,10 +18469,8 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>20043</t>
-        </is>
+      <c r="A480" t="n">
+        <v>20043</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -17889,10 +18521,8 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
+      <c r="A481" t="n">
+        <v>20044</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -17943,10 +18573,8 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>20045</t>
-        </is>
+      <c r="A482" t="n">
+        <v>20045</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -17997,10 +18625,8 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>20046</t>
-        </is>
+      <c r="A483" t="n">
+        <v>20046</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -18051,10 +18677,8 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>20047</t>
-        </is>
+      <c r="A484" t="n">
+        <v>20047</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -18105,10 +18729,8 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>20048</t>
-        </is>
+      <c r="A485" t="n">
+        <v>20048</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -18159,10 +18781,8 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>20049</t>
-        </is>
+      <c r="A486" t="n">
+        <v>20049</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -18213,10 +18833,8 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>20050</t>
-        </is>
+      <c r="A487" t="n">
+        <v>20050</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -18267,10 +18885,8 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>20051</t>
-        </is>
+      <c r="A488" t="n">
+        <v>20051</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -18321,10 +18937,8 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>20052</t>
-        </is>
+      <c r="A489" t="n">
+        <v>20052</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -18375,10 +18989,8 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>20054</t>
-        </is>
+      <c r="A490" t="n">
+        <v>20054</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -18429,10 +19041,8 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>20055</t>
-        </is>
+      <c r="A491" t="n">
+        <v>20055</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -18483,10 +19093,8 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>20056</t>
-        </is>
+      <c r="A492" t="n">
+        <v>20056</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -18537,10 +19145,8 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>20057</t>
-        </is>
+      <c r="A493" t="n">
+        <v>20057</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -18591,10 +19197,8 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>20058</t>
-        </is>
+      <c r="A494" t="n">
+        <v>20058</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -18645,10 +19249,8 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>20053</t>
-        </is>
+      <c r="A495" t="n">
+        <v>20053</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -18699,10 +19301,8 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>20059</t>
-        </is>
+      <c r="A496" t="n">
+        <v>20059</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -18753,10 +19353,8 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>20060</t>
-        </is>
+      <c r="A497" t="n">
+        <v>20060</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -18807,10 +19405,8 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>20061</t>
-        </is>
+      <c r="A498" t="n">
+        <v>20061</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -18861,10 +19457,8 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>20062</t>
-        </is>
+      <c r="A499" t="n">
+        <v>20062</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -18915,10 +19509,8 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>20063</t>
-        </is>
+      <c r="A500" t="n">
+        <v>20063</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -18969,10 +19561,8 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>20064</t>
-        </is>
+      <c r="A501" t="n">
+        <v>20064</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -19023,10 +19613,8 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>20065</t>
-        </is>
+      <c r="A502" t="n">
+        <v>20065</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -19077,10 +19665,8 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>20066</t>
-        </is>
+      <c r="A503" t="n">
+        <v>20066</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -19131,10 +19717,8 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>20067</t>
-        </is>
+      <c r="A504" t="n">
+        <v>20067</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -19185,10 +19769,8 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>20068</t>
-        </is>
+      <c r="A505" t="n">
+        <v>20068</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -19239,10 +19821,8 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>20069</t>
-        </is>
+      <c r="A506" t="n">
+        <v>20069</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -19293,10 +19873,8 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>20070</t>
-        </is>
+      <c r="A507" t="n">
+        <v>20070</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -19347,10 +19925,8 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>20071</t>
-        </is>
+      <c r="A508" t="n">
+        <v>20071</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -19401,10 +19977,8 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>20072</t>
-        </is>
+      <c r="A509" t="n">
+        <v>20072</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -19455,10 +20029,8 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>20073</t>
-        </is>
+      <c r="A510" t="n">
+        <v>20073</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -19509,10 +20081,8 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>20074</t>
-        </is>
+      <c r="A511" t="n">
+        <v>20074</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -19563,10 +20133,8 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>20075</t>
-        </is>
+      <c r="A512" t="n">
+        <v>20075</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -19617,10 +20185,8 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>20076</t>
-        </is>
+      <c r="A513" t="n">
+        <v>20076</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -19671,10 +20237,8 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>20077</t>
-        </is>
+      <c r="A514" t="n">
+        <v>20077</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -19725,10 +20289,8 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>20078</t>
-        </is>
+      <c r="A515" t="n">
+        <v>20078</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -19779,10 +20341,8 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>20079</t>
-        </is>
+      <c r="A516" t="n">
+        <v>20079</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -19833,10 +20393,8 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>20080</t>
-        </is>
+      <c r="A517" t="n">
+        <v>20080</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -19887,10 +20445,8 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>20081</t>
-        </is>
+      <c r="A518" t="n">
+        <v>20081</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -19941,10 +20497,8 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>20082</t>
-        </is>
+      <c r="A519" t="n">
+        <v>20082</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -19995,10 +20549,8 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>20083</t>
-        </is>
+      <c r="A520" t="n">
+        <v>20083</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -20049,10 +20601,8 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>20084</t>
-        </is>
+      <c r="A521" t="n">
+        <v>20084</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -20103,10 +20653,8 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>20085</t>
-        </is>
+      <c r="A522" t="n">
+        <v>20085</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -20157,10 +20705,8 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>20086</t>
-        </is>
+      <c r="A523" t="n">
+        <v>20086</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -20203,10 +20749,8 @@
       <c r="L523" t="inlineStr"/>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>20087</t>
-        </is>
+      <c r="A524" t="n">
+        <v>20087</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -20257,10 +20801,8 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>20088</t>
-        </is>
+      <c r="A525" t="n">
+        <v>20088</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -20311,10 +20853,8 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>20089</t>
-        </is>
+      <c r="A526" t="n">
+        <v>20089</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -20365,10 +20905,8 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>20091</t>
-        </is>
+      <c r="A527" t="n">
+        <v>20091</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -20419,10 +20957,8 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>20092</t>
-        </is>
+      <c r="A528" t="n">
+        <v>20092</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -20473,10 +21009,8 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>20095</t>
-        </is>
+      <c r="A529" t="n">
+        <v>20095</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -20527,10 +21061,8 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>20096</t>
-        </is>
+      <c r="A530" t="n">
+        <v>20096</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -20581,10 +21113,8 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>20097</t>
-        </is>
+      <c r="A531" t="n">
+        <v>20097</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -20635,10 +21165,8 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>20098</t>
-        </is>
+      <c r="A532" t="n">
+        <v>20098</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -20689,10 +21217,8 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>20147</t>
-        </is>
+      <c r="A533" t="n">
+        <v>20147</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -20743,10 +21269,8 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>20149</t>
-        </is>
+      <c r="A534" t="n">
+        <v>20149</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -20797,10 +21321,8 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>20153</t>
-        </is>
+      <c r="A535" t="n">
+        <v>20153</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -20851,10 +21373,8 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>20154</t>
-        </is>
+      <c r="A536" t="n">
+        <v>20154</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -20905,10 +21425,8 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>20155</t>
-        </is>
+      <c r="A537" t="n">
+        <v>20155</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -20959,10 +21477,8 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>20156</t>
-        </is>
+      <c r="A538" t="n">
+        <v>20156</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -21013,10 +21529,8 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>20157</t>
-        </is>
+      <c r="A539" t="n">
+        <v>20157</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -21067,10 +21581,8 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>20158</t>
-        </is>
+      <c r="A540" t="n">
+        <v>20158</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -21121,10 +21633,8 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>20090</t>
-        </is>
+      <c r="A541" t="n">
+        <v>20090</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -21175,10 +21685,8 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>20093</t>
-        </is>
+      <c r="A542" t="n">
+        <v>20093</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -21229,10 +21737,8 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>20094</t>
-        </is>
+      <c r="A543" t="n">
+        <v>20094</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -21283,10 +21789,8 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>20148</t>
-        </is>
+      <c r="A544" t="n">
+        <v>20148</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -21333,6 +21837,470 @@
       <c r="L544" t="inlineStr">
         <is>
           <t>电梯</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>20159</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>商店</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>shāngdiàn</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>상점</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr"/>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>商店</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>商店</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>20160</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>饭店</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>fàndiàn</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr"/>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>饭店</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>饭店</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>20161</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>书店</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>shūdiàn</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>서점</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>bookstore</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr"/>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>书店</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>书店</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>20162</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>花店</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>huādiàn</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>꽃집</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>flower shop</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr"/>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>花店</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>花店</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>20163</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>便利店</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>biànlìdiàn</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>편의점</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>convenience store</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr"/>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>便利店</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>便利店</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>20164</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>药店</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>yàodiàn</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>약국</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr"/>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>药店</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>药店</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>20165</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>服装店</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>fúzhuāngdiàn</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>의류점</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>clothing store</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr"/>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>服装店</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>服装店</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>20166</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>眼镜店</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>yǎnjìngdiàn</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>안경점</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>optical shop</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr"/>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>眼镜店</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>眼镜店</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>20167</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>店</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>diàn</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr"/>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>dian</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>가게</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr"/>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>店</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>店</t>
         </is>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8745,7 +8745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L553"/>
+  <dimension ref="A1:L580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>dian</t>
+          <t>탈것</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -22301,6 +22301,1410 @@
       <c r="L553" t="inlineStr">
         <is>
           <t>店</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>20168</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>飞机</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>fēijī</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>비행기</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Airplane</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr"/>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>飞机</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>飞机</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>20169</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>出租车</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>chūzūchē</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>택시</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Taxi</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr"/>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>出租车</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>出租车</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>20170</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>公交车</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>gōngjiāochē</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>버스</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr"/>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>公交车</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>公交车</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>20171</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>自行车</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>zìxíngchē</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>자전거</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Bicycle</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr"/>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>自行车</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>自行车</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>20172</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>火车</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>huǒchē</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>기차</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr"/>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>火车</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>火车</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>20173</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>地铁</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>dìtiě</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>지하철</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Subway / Metro</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr"/>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>地铁</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>20174</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>船</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>chuán</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>선박</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Boat / Ship</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr"/>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>船</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr"/>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>船</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>20175</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>摩托车</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>mótuōchē</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>오토바이</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr"/>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>摩托车</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr"/>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>摩托车</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>20176</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>高铁</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>gāotiě</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>고속철도</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>High-speed rail</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr"/>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>高铁</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr"/>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>高铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>20177</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>共享单车</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>gòngxiǎng dānchē</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>"0000"</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>공유 자전거</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Shared bicycle</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr"/>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>共享单车</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>共享单车</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>20178</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>bùxíng</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>탈것</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>도보</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Walking</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr"/>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>20179</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>足球</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>zúqiú</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>축구</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Football / Soccer</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr"/>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>足球</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>足球</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>20180</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>篮球</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>lánqiú</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>농구</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Basketball</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr"/>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>篮球</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>篮球</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>20181</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>棒球</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>bàngqiú</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>야구</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Baseball</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr"/>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>棒球</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>棒球</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>20182</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>排球</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>páiqiú</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>배구</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Volleyball</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr"/>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>排球</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>排球</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>20183</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>乒乓球</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>pīngpāngqiú</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>탁구</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Table tennis / Ping-pong</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr"/>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>乒乓球</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>乒乓球</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>20184</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>击剑</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>jījiàn</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>펜싱</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Fencing</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr"/>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>击剑</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>击剑</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>20185</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>网球</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>wǎngqiú</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>테니스</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Tennis</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr"/>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>网球</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>网球</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>20186</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>羽毛球</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>yǔmáoqiú</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>배드민턴</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Badminton</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr"/>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>羽毛球</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>羽毛球</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>20187</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>瑜伽</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>yújiā</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>"0000"</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>요가</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Yoga</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr"/>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>瑜伽</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr"/>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>高尔夫球</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>20188</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>游泳</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>yóuyǒng</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>수영</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Swimming</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr"/>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>游泳</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr"/>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>游泳</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>20189</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>pǎobù</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>달리기</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Running</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr"/>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr"/>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>跑步</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>20190</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>射箭</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>shèjiàn</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>양궁</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Archery</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr"/>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>射箭</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr"/>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>射箭</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>20191</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>举重</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>jǔzhòng</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>역도</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Weightlifting</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr"/>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>举重</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr"/>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>举重</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>20192</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>跆拳道</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>táiquándào</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Taekwondo</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr"/>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>跆拳道</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr"/>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>跆拳道</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>20193</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>滑雪</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>huáxuě</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>스키</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Skiing</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr"/>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>滑雪</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr"/>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>滑雪</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>20194</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>健身</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>jiànshēn</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>스포츠</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>헬스</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Fitness / Working out</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr"/>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>健身</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr"/>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>健身</t>
         </is>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -1257,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1323,8 +1323,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>50000</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1359,8 +1361,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>50001</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>50001</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1395,8 +1399,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>50002</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>50002</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1431,8 +1437,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>50003</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>50003</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1467,8 +1475,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>50004</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>50004</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
@@ -1478,17 +1488,23 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>0</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>0</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>50005</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>50005</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1527,8 +1543,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>50006</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>50006</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1567,8 +1585,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>50007</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>50007</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1607,8 +1627,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>50008</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>50008</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1647,8 +1669,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>50009</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>50009</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
@@ -1658,17 +1682,23 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>0</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>50010</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>50010</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
@@ -1678,17 +1708,23 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>0</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>50011</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>50011</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
@@ -1698,17 +1734,23 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>0</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>50012</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>50012</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
@@ -1718,17 +1760,23 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>0</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>0</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>50013</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>50013</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
@@ -1738,17 +1786,23 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>0</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>0</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>50014</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>50014</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
@@ -1758,17 +1812,23 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>0</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>0</v>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>50015</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>50015</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
@@ -1778,17 +1838,23 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>0</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>0</v>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>50016</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>50016</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
@@ -1798,17 +1864,23 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>0</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>0</v>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>50017</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>50017</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
@@ -1818,17 +1890,23 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>0</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>0</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>50018</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>50018</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
@@ -1838,17 +1916,23 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>0</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>0</v>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>50019</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>50019</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
@@ -1858,17 +1942,23 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>0</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>0</v>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>50020</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>50020</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
@@ -1882,12 +1972,108 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
-        <v>0</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
-        <v>0</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>50021</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>订阅</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dìngyuè</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>구독</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Subscribe</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>订阅</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>订阅</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>50022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>点赞</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>diǎnzàn</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>좋아요</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Like</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>点赞</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>点赞</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -1323,10 +1323,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+      <c r="A2" t="n">
+        <v>50000</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1361,10 +1359,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>50001</t>
-        </is>
+      <c r="A3" t="n">
+        <v>50001</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1399,10 +1395,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>50002</t>
-        </is>
+      <c r="A4" t="n">
+        <v>50002</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1437,10 +1431,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>50003</t>
-        </is>
+      <c r="A5" t="n">
+        <v>50003</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1475,10 +1467,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>50004</t>
-        </is>
+      <c r="A6" t="n">
+        <v>50004</v>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
@@ -1501,10 +1491,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>50005</t>
-        </is>
+      <c r="A7" t="n">
+        <v>50005</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1543,10 +1531,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>50006</t>
-        </is>
+      <c r="A8" t="n">
+        <v>50006</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1585,10 +1571,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>50007</t>
-        </is>
+      <c r="A9" t="n">
+        <v>50007</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1627,10 +1611,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>50008</t>
-        </is>
+      <c r="A10" t="n">
+        <v>50008</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1669,10 +1651,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>50009</t>
-        </is>
+      <c r="A11" t="n">
+        <v>50009</v>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
@@ -1695,10 +1675,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>50010</t>
-        </is>
+      <c r="A12" t="n">
+        <v>50010</v>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
@@ -1721,10 +1699,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>50011</t>
-        </is>
+      <c r="A13" t="n">
+        <v>50011</v>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
@@ -1747,10 +1723,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>50012</t>
-        </is>
+      <c r="A14" t="n">
+        <v>50012</v>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
@@ -1773,10 +1747,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>50013</t>
-        </is>
+      <c r="A15" t="n">
+        <v>50013</v>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
@@ -1799,10 +1771,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>50014</t>
-        </is>
+      <c r="A16" t="n">
+        <v>50014</v>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
@@ -1825,10 +1795,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>50015</t>
-        </is>
+      <c r="A17" t="n">
+        <v>50015</v>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
@@ -1851,10 +1819,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>50016</t>
-        </is>
+      <c r="A18" t="n">
+        <v>50016</v>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
@@ -1877,10 +1843,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>50017</t>
-        </is>
+      <c r="A19" t="n">
+        <v>50017</v>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
@@ -1903,10 +1867,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>50018</t>
-        </is>
+      <c r="A20" t="n">
+        <v>50018</v>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
@@ -1929,10 +1891,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>50019</t>
-        </is>
+      <c r="A21" t="n">
+        <v>50019</v>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
@@ -1955,10 +1915,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>50020</t>
-        </is>
+      <c r="A22" t="n">
+        <v>50020</v>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
@@ -1985,10 +1943,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>50021</t>
-        </is>
+      <c r="A23" t="n">
+        <v>50021</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2031,10 +1987,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>50022</t>
-        </is>
+      <c r="A24" t="n">
+        <v>50022</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8885,7 +8885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L580"/>
+  <dimension ref="A1:L603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9035,8 +9035,10 @@
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>20000</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9071,8 +9073,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>20001</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9107,8 +9111,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>20002</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20002</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9143,8 +9149,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>20003</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20003</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9179,8 +9187,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>20004</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20004</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -9215,8 +9225,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>20005</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20005</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -9251,8 +9263,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>20006</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20006</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -9287,8 +9301,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>20007</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20007</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -9323,8 +9339,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>20008</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20008</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -9359,8 +9377,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>20009</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20009</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -9395,8 +9415,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>20010</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20010</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -9447,8 +9469,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>20011</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20011</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -9483,8 +9507,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>20012</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20012</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -9519,8 +9545,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20013</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -9555,8 +9583,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>20014</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20014</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -9591,8 +9621,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>20015</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20015</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -9627,8 +9659,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>20016</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20016</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -9663,8 +9697,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>20017</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20017</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -9699,8 +9735,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>20018</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20018</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -9961,8 +9999,10 @@
       <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>20099</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20099</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -9997,8 +10037,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>20100</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20100</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -10033,8 +10075,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>20101</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20101</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -10083,28 +10127,46 @@
       <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>20102</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20102</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>书</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>shū</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>명사</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>책</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
@@ -10119,8 +10181,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>20103</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20103</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -10167,8 +10231,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>20104</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20104</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -10215,8 +10281,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>20105</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20105</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -10263,8 +10331,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>20106</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20106</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -10307,8 +10377,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>20107</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20107</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -10351,8 +10423,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>20108</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20108</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -10395,8 +10469,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>20109</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20109</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -10439,8 +10515,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>20110</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20110</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -10475,8 +10553,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>20111</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20111</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -10511,8 +10591,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>20112</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20112</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -10547,8 +10629,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>20113</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20113</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -10583,8 +10667,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>20114</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20114</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -10619,8 +10705,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>20115</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20115</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -10655,8 +10743,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>20116</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20116</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -10691,8 +10781,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>20117</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20117</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -10731,8 +10823,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>20118</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20118</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -10771,8 +10865,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>20119</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20119</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -10807,8 +10903,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>20120</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20120</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -10843,28 +10941,46 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>20121</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>shuǐ</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>명사</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>물</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
@@ -10879,28 +10995,46 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>20122</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20122</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>冰水</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>bīngshuǐ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>명사</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>찬물</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ice water</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
@@ -10915,8 +11049,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>20123</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20123</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -10951,8 +11087,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>20124</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20124</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -10987,8 +11125,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>20125</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20125</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -11023,8 +11163,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>20126</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20126</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -11059,8 +11201,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>20127</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20127</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -11095,8 +11239,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>20128</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20128</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -11131,8 +11277,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>20129</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20129</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -11171,8 +11319,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>20130</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20130</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -11211,8 +11361,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>20131</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20131</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -11247,8 +11399,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>20132</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20132</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -11283,8 +11437,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>20133</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20133</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -11319,8 +11475,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>20134</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20134</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -11355,8 +11513,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>20135</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20135</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -11391,8 +11551,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>20136</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20136</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -11427,8 +11589,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
-        <v>20137</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20137</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -11463,8 +11627,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>20138</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20138</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -11499,8 +11665,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>20139</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20139</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -11535,8 +11703,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>20140</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20140</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -11571,8 +11741,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>20141</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20141</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -11607,8 +11779,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>20142</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20142</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -11643,8 +11817,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>20143</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20143</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -11679,8 +11855,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>20144</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20144</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -11715,8 +11893,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>20145</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20145</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -11751,8 +11931,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v>20146</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20146</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -11829,8 +12011,10 @@
       <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v>20150</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20150</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -11842,19 +12026,31 @@
           <t>kělè</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>명사</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>콜라</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>cola</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
@@ -11869,28 +12065,46 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>20151</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20151</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>啤酒</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>píjiǔ</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>명사</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>맥주</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>beer</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
@@ -11905,28 +12119,46 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>20152</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20152</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>雪碧</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>xuěbì</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>명사</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>사이다(스프라이트)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>사이다</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sprite</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
@@ -16813,8 +17045,10 @@
       <c r="L444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" t="n">
-        <v>20501</v>
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>20501</t>
+        </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -16865,8 +17099,10 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="n">
-        <v>20502</v>
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>20502</t>
+        </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -16917,8 +17153,10 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="n">
-        <v>20503</v>
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>20503</t>
+        </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -16969,8 +17207,10 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="n">
-        <v>20504</v>
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>20504</t>
+        </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -17021,8 +17261,10 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="n">
-        <v>20505</v>
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>20505</t>
+        </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -17073,8 +17315,10 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="n">
-        <v>20506</v>
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>20506</t>
+        </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -17125,8 +17369,10 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="n">
-        <v>20507</v>
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>20507</t>
+        </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -17177,8 +17423,10 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="n">
-        <v>20508</v>
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>20508</t>
+        </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -17229,8 +17477,10 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="n">
-        <v>20509</v>
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>20509</t>
+        </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -17269,8 +17519,10 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="n">
-        <v>20510</v>
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>20510</t>
+        </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -17309,8 +17561,10 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="n">
-        <v>20511</v>
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>20511</t>
+        </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -17361,8 +17615,10 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="n">
-        <v>20019</v>
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>20019</t>
+        </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -17413,8 +17669,10 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="n">
-        <v>20020</v>
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>20020</t>
+        </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -17465,8 +17723,10 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="n">
-        <v>20021</v>
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>20021</t>
+        </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -17517,8 +17777,10 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="n">
-        <v>20022</v>
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>20022</t>
+        </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -17569,8 +17831,10 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="n">
-        <v>20023</v>
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>20023</t>
+        </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -17621,8 +17885,10 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="n">
-        <v>20024</v>
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>20024</t>
+        </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -17673,8 +17939,10 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="n">
-        <v>20025</v>
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>20025</t>
+        </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -17725,8 +17993,10 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="n">
-        <v>20026</v>
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>20026</t>
+        </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -17777,8 +18047,10 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="n">
-        <v>20027</v>
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>20027</t>
+        </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -17829,8 +18101,10 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="n">
-        <v>20028</v>
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>20028</t>
+        </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -17881,8 +18155,10 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="n">
-        <v>20029</v>
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>20029</t>
+        </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -17933,8 +18209,10 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="n">
-        <v>20030</v>
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>20030</t>
+        </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -17985,8 +18263,10 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="n">
-        <v>20031</v>
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>20031</t>
+        </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -18037,8 +18317,10 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="n">
-        <v>20032</v>
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>20032</t>
+        </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -18089,8 +18371,10 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="n">
-        <v>20033</v>
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>20033</t>
+        </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -18141,8 +18425,10 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="n">
-        <v>20034</v>
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>20034</t>
+        </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -18193,8 +18479,10 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="n">
-        <v>20035</v>
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>20035</t>
+        </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -18245,8 +18533,10 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="n">
-        <v>20036</v>
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>20036</t>
+        </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -18297,8 +18587,10 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="n">
-        <v>20037</v>
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>20037</t>
+        </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -18349,8 +18641,10 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="n">
-        <v>20038</v>
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>20038</t>
+        </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -18401,8 +18695,10 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="n">
-        <v>20039</v>
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>20039</t>
+        </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -18453,8 +18749,10 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="n">
-        <v>20040</v>
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>20040</t>
+        </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -18505,8 +18803,10 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="n">
-        <v>20041</v>
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -18557,8 +18857,10 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="n">
-        <v>20042</v>
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>20042</t>
+        </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -18609,8 +18911,10 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="n">
-        <v>20043</v>
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -18661,8 +18965,10 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="n">
-        <v>20044</v>
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -18713,8 +19019,10 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="n">
-        <v>20045</v>
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>20045</t>
+        </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -18765,8 +19073,10 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="n">
-        <v>20046</v>
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>20046</t>
+        </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -18817,8 +19127,10 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="n">
-        <v>20047</v>
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>20047</t>
+        </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -18869,8 +19181,10 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="n">
-        <v>20048</v>
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>20048</t>
+        </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -18921,8 +19235,10 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="n">
-        <v>20049</v>
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>20049</t>
+        </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -18973,8 +19289,10 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="n">
-        <v>20050</v>
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>20050</t>
+        </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -19025,8 +19343,10 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="n">
-        <v>20051</v>
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>20051</t>
+        </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -19077,8 +19397,10 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="n">
-        <v>20052</v>
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>20052</t>
+        </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -19129,8 +19451,10 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="n">
-        <v>20054</v>
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>20054</t>
+        </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -19181,8 +19505,10 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="n">
-        <v>20055</v>
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>20055</t>
+        </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -19233,8 +19559,10 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="n">
-        <v>20056</v>
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>20056</t>
+        </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -19285,8 +19613,10 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="n">
-        <v>20057</v>
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>20057</t>
+        </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -19337,8 +19667,10 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="n">
-        <v>20058</v>
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>20058</t>
+        </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -19389,8 +19721,10 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="n">
-        <v>20053</v>
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>20053</t>
+        </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -19441,8 +19775,10 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="n">
-        <v>20059</v>
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>20059</t>
+        </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -19493,8 +19829,10 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="n">
-        <v>20060</v>
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>20060</t>
+        </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -19545,8 +19883,10 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="n">
-        <v>20061</v>
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>20061</t>
+        </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -19597,8 +19937,10 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="n">
-        <v>20062</v>
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>20062</t>
+        </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -19649,8 +19991,10 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="n">
-        <v>20063</v>
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>20063</t>
+        </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -19701,8 +20045,10 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="n">
-        <v>20064</v>
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>20064</t>
+        </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -19753,8 +20099,10 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="n">
-        <v>20065</v>
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>20065</t>
+        </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -19805,8 +20153,10 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="n">
-        <v>20066</v>
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>20066</t>
+        </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -19857,8 +20207,10 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="n">
-        <v>20067</v>
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>20067</t>
+        </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -19909,8 +20261,10 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="n">
-        <v>20068</v>
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>20068</t>
+        </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -19961,8 +20315,10 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="n">
-        <v>20069</v>
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>20069</t>
+        </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -20013,8 +20369,10 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="n">
-        <v>20070</v>
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>20070</t>
+        </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -20065,8 +20423,10 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="n">
-        <v>20071</v>
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>20071</t>
+        </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -20117,8 +20477,10 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="n">
-        <v>20072</v>
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>20072</t>
+        </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -20169,8 +20531,10 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="n">
-        <v>20073</v>
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>20073</t>
+        </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -20221,8 +20585,10 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="n">
-        <v>20074</v>
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>20074</t>
+        </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -20273,8 +20639,10 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="n">
-        <v>20075</v>
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>20075</t>
+        </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -20325,8 +20693,10 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="n">
-        <v>20076</v>
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>20076</t>
+        </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -20377,8 +20747,10 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="n">
-        <v>20077</v>
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>20077</t>
+        </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -20429,8 +20801,10 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="n">
-        <v>20078</v>
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>20078</t>
+        </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -20481,8 +20855,10 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="n">
-        <v>20079</v>
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>20079</t>
+        </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -20533,8 +20909,10 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="n">
-        <v>20080</v>
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>20080</t>
+        </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -20585,8 +20963,10 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="n">
-        <v>20081</v>
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>20081</t>
+        </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -20637,8 +21017,10 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="n">
-        <v>20082</v>
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>20082</t>
+        </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -20689,8 +21071,10 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="n">
-        <v>20083</v>
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>20083</t>
+        </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -20741,8 +21125,10 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="n">
-        <v>20084</v>
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>20084</t>
+        </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -20793,8 +21179,10 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="n">
-        <v>20085</v>
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>20085</t>
+        </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -20845,8 +21233,10 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="n">
-        <v>20086</v>
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>20086</t>
+        </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -20889,8 +21279,10 @@
       <c r="L523" t="inlineStr"/>
     </row>
     <row r="524">
-      <c r="A524" t="n">
-        <v>20087</v>
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>20087</t>
+        </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -20941,8 +21333,10 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="n">
-        <v>20088</v>
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>20088</t>
+        </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -20993,8 +21387,10 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="n">
-        <v>20089</v>
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>20089</t>
+        </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -21045,8 +21441,10 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="n">
-        <v>20091</v>
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>20091</t>
+        </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -21097,8 +21495,10 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="n">
-        <v>20092</v>
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>20092</t>
+        </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -21149,8 +21549,10 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="n">
-        <v>20095</v>
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>20095</t>
+        </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -21201,8 +21603,10 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="n">
-        <v>20096</v>
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>20096</t>
+        </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -21253,8 +21657,10 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="n">
-        <v>20097</v>
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>20097</t>
+        </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -21278,7 +21684,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>dian</t>
+          <t>가구</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -21305,8 +21711,10 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="n">
-        <v>20098</v>
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>20098</t>
+        </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -21357,8 +21765,10 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="n">
-        <v>20147</v>
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>20147</t>
+        </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -21409,8 +21819,10 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="n">
-        <v>20149</v>
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>20149</t>
+        </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -21461,8 +21873,10 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="n">
-        <v>20153</v>
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>20153</t>
+        </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -21513,8 +21927,10 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="n">
-        <v>20154</v>
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>20154</t>
+        </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -21565,8 +21981,10 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="n">
-        <v>20155</v>
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>20155</t>
+        </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -21617,8 +22035,10 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="n">
-        <v>20156</v>
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>20156</t>
+        </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -21669,8 +22089,10 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="n">
-        <v>20157</v>
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>20157</t>
+        </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -21694,7 +22116,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>dian</t>
+          <t>가구</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -21721,8 +22143,10 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="n">
-        <v>20158</v>
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>20158</t>
+        </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -21773,8 +22197,10 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="n">
-        <v>20090</v>
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>20090</t>
+        </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -21825,8 +22251,10 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="n">
-        <v>20093</v>
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>20093</t>
+        </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -21877,8 +22305,10 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="n">
-        <v>20094</v>
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>20094</t>
+        </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -21929,8 +22359,10 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="n">
-        <v>20148</v>
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>20148</t>
+        </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -21981,8 +22413,10 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="n">
-        <v>20159</v>
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>20159</t>
+        </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -22033,8 +22467,10 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" t="n">
-        <v>20160</v>
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>20160</t>
+        </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -22085,8 +22521,10 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="n">
-        <v>20161</v>
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>20161</t>
+        </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -22137,8 +22575,10 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="n">
-        <v>20162</v>
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>20162</t>
+        </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -22189,8 +22629,10 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="n">
-        <v>20163</v>
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>20163</t>
+        </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -22241,8 +22683,10 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="n">
-        <v>20164</v>
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>20164</t>
+        </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -22293,8 +22737,10 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="n">
-        <v>20165</v>
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>20165</t>
+        </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -22345,8 +22791,10 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" t="n">
-        <v>20166</v>
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>20166</t>
+        </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -22397,8 +22845,10 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" t="n">
-        <v>20167</v>
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>20167</t>
+        </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -22445,8 +22895,10 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" t="n">
-        <v>20168</v>
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>20168</t>
+        </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -22497,8 +22949,10 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="n">
-        <v>20169</v>
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>20169</t>
+        </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -22549,8 +23003,10 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" t="n">
-        <v>20170</v>
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>20170</t>
+        </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -22601,8 +23057,10 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" t="n">
-        <v>20171</v>
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>20171</t>
+        </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -22653,8 +23111,10 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" t="n">
-        <v>20172</v>
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>20172</t>
+        </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -22705,8 +23165,10 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" t="n">
-        <v>20173</v>
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>20173</t>
+        </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -22757,8 +23219,10 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="n">
-        <v>20174</v>
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>20174</t>
+        </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -22809,8 +23273,10 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="n">
-        <v>20175</v>
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>20175</t>
+        </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -22861,8 +23327,10 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="n">
-        <v>20176</v>
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>20176</t>
+        </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -22913,8 +23381,10 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="n">
-        <v>20177</v>
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>20177</t>
+        </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -22965,8 +23435,10 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="n">
-        <v>20178</v>
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>20178</t>
+        </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -23017,8 +23489,10 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="n">
-        <v>20179</v>
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>20179</t>
+        </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -23069,8 +23543,10 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="n">
-        <v>20180</v>
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>20180</t>
+        </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -23121,8 +23597,10 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="n">
-        <v>20181</v>
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>20181</t>
+        </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -23173,8 +23651,10 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="n">
-        <v>20182</v>
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>20182</t>
+        </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -23225,8 +23705,10 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="n">
-        <v>20183</v>
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>20183</t>
+        </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -23277,8 +23759,10 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="n">
-        <v>20184</v>
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>20184</t>
+        </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -23329,8 +23813,10 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="n">
-        <v>20185</v>
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>20185</t>
+        </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -23381,8 +23867,10 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="n">
-        <v>20186</v>
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>20186</t>
+        </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -23433,8 +23921,10 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="n">
-        <v>20187</v>
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>20187</t>
+        </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -23485,8 +23975,10 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="n">
-        <v>20188</v>
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>20188</t>
+        </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -23537,8 +24029,10 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="n">
-        <v>20189</v>
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>20189</t>
+        </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -23589,8 +24083,10 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="n">
-        <v>20190</v>
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>20190</t>
+        </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -23641,8 +24137,10 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="n">
-        <v>20191</v>
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>20191</t>
+        </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -23693,8 +24191,10 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="n">
-        <v>20192</v>
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>20192</t>
+        </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -23745,8 +24245,10 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="n">
-        <v>20193</v>
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>20193</t>
+        </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -23797,8 +24299,10 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="n">
-        <v>20194</v>
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>20194</t>
+        </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -23845,6 +24349,1248 @@
       <c r="L580" t="inlineStr">
         <is>
           <t>健身</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>20195</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>床</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>chuáng</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>bed</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr"/>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>床</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr"/>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>床</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>20196</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>书桌</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>shūzhuō</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>책상</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>desk</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr"/>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>书桌</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr"/>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>书桌</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>20197</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>椅子</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>yǐzi</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>의자</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr"/>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>椅子</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr"/>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>椅子</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>20198</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>衣柜</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>yīguì</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>옷장</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>wardrobe / closet</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr"/>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>衣柜</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr"/>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>衣柜</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>20199</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>镜子</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>jìngzi</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>거울</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>mirror</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr"/>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>镜子</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr"/>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>镜子</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>20200</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>空调</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>kōngtiáo</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>에어컨</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>air conditioner</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr"/>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>空调</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr"/>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>空调</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>20201</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>冰箱</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>bīngxiāng</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>냉장고</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>refrigerator / fridge</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr"/>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>冰箱</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr"/>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>冰箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>20202</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>钟表</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>zhōngbiǎo</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>시계</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>clock / watch</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr"/>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>钟表</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr"/>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>钟表</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>20203</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>灯</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>dēng</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>전등</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>light / lamp</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr"/>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>灯</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr"/>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>灯</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>20204</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>mén</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>문</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>door</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr"/>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr"/>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>20205</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>窗户</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>chuānghu</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>창문</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr"/>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>窗户</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr"/>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>窗户</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>20206</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>枕头</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>zhěntou</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>베개</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>pillow</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr"/>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>枕头</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr"/>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>枕头</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>20207</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>被子</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>bèizi</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>이불</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>quilt / blanket</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>被子</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr"/>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>被子</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>20208</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>热水</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>rèshuǐ</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>따뜻한 물</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>hot water</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr"/>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>热水</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr"/>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>热水</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>20209</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>咖啡</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>kāfēi</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>coffee</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr"/>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>咖啡</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr"/>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>咖啡</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>20210</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>美式咖啡</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>měishì kāfēi</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>"0000"</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>아메리카노</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Americano</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr"/>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>美式咖啡</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr"/>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>美式咖啡</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>20211</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>拿铁</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>nátiě</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>라떼</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Latte</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr"/>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>拿铁</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr"/>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>拿铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>20212</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>茶</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>chá</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>차</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr"/>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>茶</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr"/>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>茶</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>20213</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>绿茶</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>lǜchá</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>녹차</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>green tea</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr"/>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>绿茶</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr"/>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>绿茶</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>20214</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>红茶</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>hóngchá</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>홍차</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>black tea</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr"/>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>红茶</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr"/>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>红茶</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>20215</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>nǎichá</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>밀크티</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>milk tea</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr"/>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr"/>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>20216</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>果汁</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>guǒzhī</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>과일 주스</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>juice</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr"/>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>果汁</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr"/>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>果汁</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>20217</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>牛奶</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>niúnǎi</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>음료</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>우유</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>milk</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr"/>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>牛奶</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr"/>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>牛奶</t>
         </is>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -8885,7 +8885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L603"/>
+  <dimension ref="A1:L604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9035,10 +9035,8 @@
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="A8" t="n">
+        <v>20000</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9073,10 +9071,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20001</t>
-        </is>
+      <c r="A9" t="n">
+        <v>20001</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9111,10 +9107,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>20002</t>
-        </is>
+      <c r="A10" t="n">
+        <v>20002</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9149,10 +9143,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>20003</t>
-        </is>
+      <c r="A11" t="n">
+        <v>20003</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9187,10 +9179,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20004</t>
-        </is>
+      <c r="A12" t="n">
+        <v>20004</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -9225,10 +9215,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20005</t>
-        </is>
+      <c r="A13" t="n">
+        <v>20005</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -9263,10 +9251,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20006</t>
-        </is>
+      <c r="A14" t="n">
+        <v>20006</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -9301,10 +9287,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>20007</t>
-        </is>
+      <c r="A15" t="n">
+        <v>20007</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -9339,10 +9323,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>20008</t>
-        </is>
+      <c r="A16" t="n">
+        <v>20008</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -9377,10 +9359,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20009</t>
-        </is>
+      <c r="A17" t="n">
+        <v>20009</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -9415,10 +9395,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20010</t>
-        </is>
+      <c r="A18" t="n">
+        <v>20010</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -9469,10 +9447,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>20011</t>
-        </is>
+      <c r="A19" t="n">
+        <v>20011</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -9507,10 +9483,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20012</t>
-        </is>
+      <c r="A20" t="n">
+        <v>20012</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -9545,10 +9519,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20013</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -9583,10 +9555,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20014</t>
-        </is>
+      <c r="A22" t="n">
+        <v>20014</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -9621,10 +9591,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20015</t>
-        </is>
+      <c r="A23" t="n">
+        <v>20015</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -9659,10 +9627,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20016</t>
-        </is>
+      <c r="A24" t="n">
+        <v>20016</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -9697,10 +9663,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20017</t>
-        </is>
+      <c r="A25" t="n">
+        <v>20017</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -9735,10 +9699,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20018</t>
-        </is>
+      <c r="A26" t="n">
+        <v>20018</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -9999,10 +9961,8 @@
       <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>20099</t>
-        </is>
+      <c r="A42" t="n">
+        <v>20099</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -10037,10 +9997,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>20100</t>
-        </is>
+      <c r="A43" t="n">
+        <v>20100</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -10075,10 +10033,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>20101</t>
-        </is>
+      <c r="A44" t="n">
+        <v>20101</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -10127,10 +10083,8 @@
       <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>20102</t>
-        </is>
+      <c r="A46" t="n">
+        <v>20102</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -10181,10 +10135,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>20103</t>
-        </is>
+      <c r="A47" t="n">
+        <v>20103</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -10231,10 +10183,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>20104</t>
-        </is>
+      <c r="A48" t="n">
+        <v>20104</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -10281,10 +10231,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>20105</t>
-        </is>
+      <c r="A49" t="n">
+        <v>20105</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -10331,10 +10279,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>20106</t>
-        </is>
+      <c r="A50" t="n">
+        <v>20106</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -10377,10 +10323,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>20107</t>
-        </is>
+      <c r="A51" t="n">
+        <v>20107</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -10423,10 +10367,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>20108</t>
-        </is>
+      <c r="A52" t="n">
+        <v>20108</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -10469,10 +10411,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>20109</t>
-        </is>
+      <c r="A53" t="n">
+        <v>20109</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -10515,10 +10455,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>20110</t>
-        </is>
+      <c r="A54" t="n">
+        <v>20110</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -10553,10 +10491,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>20111</t>
-        </is>
+      <c r="A55" t="n">
+        <v>20111</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -10591,10 +10527,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>20112</t>
-        </is>
+      <c r="A56" t="n">
+        <v>20112</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -10629,10 +10563,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>20113</t>
-        </is>
+      <c r="A57" t="n">
+        <v>20113</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -10667,10 +10599,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>20114</t>
-        </is>
+      <c r="A58" t="n">
+        <v>20114</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -10705,10 +10635,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>20115</t>
-        </is>
+      <c r="A59" t="n">
+        <v>20115</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -10743,10 +10671,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>20116</t>
-        </is>
+      <c r="A60" t="n">
+        <v>20116</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -10781,10 +10707,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>20117</t>
-        </is>
+      <c r="A61" t="n">
+        <v>20117</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -10823,10 +10747,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>20118</t>
-        </is>
+      <c r="A62" t="n">
+        <v>20118</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -10865,10 +10787,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20119</t>
-        </is>
+      <c r="A63" t="n">
+        <v>20119</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -10903,10 +10823,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>20120</t>
-        </is>
+      <c r="A64" t="n">
+        <v>20120</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -10941,10 +10859,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20121</t>
-        </is>
+      <c r="A65" t="n">
+        <v>20121</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -10995,10 +10911,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20122</t>
-        </is>
+      <c r="A66" t="n">
+        <v>20122</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -11049,10 +10963,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>20123</t>
-        </is>
+      <c r="A67" t="n">
+        <v>20123</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -11087,10 +10999,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>20124</t>
-        </is>
+      <c r="A68" t="n">
+        <v>20124</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -11125,10 +11035,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>20125</t>
-        </is>
+      <c r="A69" t="n">
+        <v>20125</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -11163,10 +11071,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>20126</t>
-        </is>
+      <c r="A70" t="n">
+        <v>20126</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -11201,10 +11107,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>20127</t>
-        </is>
+      <c r="A71" t="n">
+        <v>20127</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -11239,10 +11143,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>20128</t>
-        </is>
+      <c r="A72" t="n">
+        <v>20128</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -11277,10 +11179,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>20129</t>
-        </is>
+      <c r="A73" t="n">
+        <v>20129</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -11319,10 +11219,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>20130</t>
-        </is>
+      <c r="A74" t="n">
+        <v>20130</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -11361,10 +11259,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>20131</t>
-        </is>
+      <c r="A75" t="n">
+        <v>20131</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -11399,10 +11295,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>20132</t>
-        </is>
+      <c r="A76" t="n">
+        <v>20132</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -11437,10 +11331,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>20133</t>
-        </is>
+      <c r="A77" t="n">
+        <v>20133</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -11475,10 +11367,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>20134</t>
-        </is>
+      <c r="A78" t="n">
+        <v>20134</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -11513,10 +11403,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>20135</t>
-        </is>
+      <c r="A79" t="n">
+        <v>20135</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -11551,10 +11439,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>20136</t>
-        </is>
+      <c r="A80" t="n">
+        <v>20136</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -11589,10 +11475,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>20137</t>
-        </is>
+      <c r="A81" t="n">
+        <v>20137</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -11627,10 +11511,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>20138</t>
-        </is>
+      <c r="A82" t="n">
+        <v>20138</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -11665,10 +11547,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>20139</t>
-        </is>
+      <c r="A83" t="n">
+        <v>20139</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -11703,10 +11583,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>20140</t>
-        </is>
+      <c r="A84" t="n">
+        <v>20140</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -11741,10 +11619,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>20141</t>
-        </is>
+      <c r="A85" t="n">
+        <v>20141</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -11779,10 +11655,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>20142</t>
-        </is>
+      <c r="A86" t="n">
+        <v>20142</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -11817,10 +11691,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>20143</t>
-        </is>
+      <c r="A87" t="n">
+        <v>20143</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -11855,10 +11727,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>20144</t>
-        </is>
+      <c r="A88" t="n">
+        <v>20144</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -11893,10 +11763,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>20145</t>
-        </is>
+      <c r="A89" t="n">
+        <v>20145</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -11931,10 +11799,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>20146</t>
-        </is>
+      <c r="A90" t="n">
+        <v>20146</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -12011,10 +11877,8 @@
       <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>20150</t>
-        </is>
+      <c r="A94" t="n">
+        <v>20150</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -12065,10 +11929,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>20151</t>
-        </is>
+      <c r="A95" t="n">
+        <v>20151</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -12119,10 +11981,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>20152</t>
-        </is>
+      <c r="A96" t="n">
+        <v>20152</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -17045,10 +16905,8 @@
       <c r="L444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>20501</t>
-        </is>
+      <c r="A445" t="n">
+        <v>20501</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -17099,10 +16957,8 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>20502</t>
-        </is>
+      <c r="A446" t="n">
+        <v>20502</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -17153,10 +17009,8 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>20503</t>
-        </is>
+      <c r="A447" t="n">
+        <v>20503</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -17207,10 +17061,8 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>20504</t>
-        </is>
+      <c r="A448" t="n">
+        <v>20504</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -17261,10 +17113,8 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>20505</t>
-        </is>
+      <c r="A449" t="n">
+        <v>20505</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -17315,10 +17165,8 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>20506</t>
-        </is>
+      <c r="A450" t="n">
+        <v>20506</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -17369,10 +17217,8 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>20507</t>
-        </is>
+      <c r="A451" t="n">
+        <v>20507</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -17423,10 +17269,8 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>20508</t>
-        </is>
+      <c r="A452" t="n">
+        <v>20508</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -17477,10 +17321,8 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>20509</t>
-        </is>
+      <c r="A453" t="n">
+        <v>20509</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -17519,10 +17361,8 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>20510</t>
-        </is>
+      <c r="A454" t="n">
+        <v>20510</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -17561,10 +17401,8 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>20511</t>
-        </is>
+      <c r="A455" t="n">
+        <v>20511</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -17615,10 +17453,8 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>20019</t>
-        </is>
+      <c r="A456" t="n">
+        <v>20019</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -17669,10 +17505,8 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>20020</t>
-        </is>
+      <c r="A457" t="n">
+        <v>20020</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -17723,10 +17557,8 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>20021</t>
-        </is>
+      <c r="A458" t="n">
+        <v>20021</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -17777,10 +17609,8 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>20022</t>
-        </is>
+      <c r="A459" t="n">
+        <v>20022</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -17831,10 +17661,8 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>20023</t>
-        </is>
+      <c r="A460" t="n">
+        <v>20023</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -17885,10 +17713,8 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>20024</t>
-        </is>
+      <c r="A461" t="n">
+        <v>20024</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -17939,10 +17765,8 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>20025</t>
-        </is>
+      <c r="A462" t="n">
+        <v>20025</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -17993,10 +17817,8 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>20026</t>
-        </is>
+      <c r="A463" t="n">
+        <v>20026</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -18047,10 +17869,8 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>20027</t>
-        </is>
+      <c r="A464" t="n">
+        <v>20027</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -18101,10 +17921,8 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>20028</t>
-        </is>
+      <c r="A465" t="n">
+        <v>20028</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -18155,10 +17973,8 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>20029</t>
-        </is>
+      <c r="A466" t="n">
+        <v>20029</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -18209,10 +18025,8 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>20030</t>
-        </is>
+      <c r="A467" t="n">
+        <v>20030</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -18263,10 +18077,8 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>20031</t>
-        </is>
+      <c r="A468" t="n">
+        <v>20031</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -18317,10 +18129,8 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>20032</t>
-        </is>
+      <c r="A469" t="n">
+        <v>20032</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -18371,10 +18181,8 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>20033</t>
-        </is>
+      <c r="A470" t="n">
+        <v>20033</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -18425,10 +18233,8 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>20034</t>
-        </is>
+      <c r="A471" t="n">
+        <v>20034</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -18479,10 +18285,8 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>20035</t>
-        </is>
+      <c r="A472" t="n">
+        <v>20035</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -18533,10 +18337,8 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>20036</t>
-        </is>
+      <c r="A473" t="n">
+        <v>20036</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -18587,10 +18389,8 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>20037</t>
-        </is>
+      <c r="A474" t="n">
+        <v>20037</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -18641,10 +18441,8 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>20038</t>
-        </is>
+      <c r="A475" t="n">
+        <v>20038</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -18695,10 +18493,8 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>20039</t>
-        </is>
+      <c r="A476" t="n">
+        <v>20039</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -18749,10 +18545,8 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>20040</t>
-        </is>
+      <c r="A477" t="n">
+        <v>20040</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -18803,10 +18597,8 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
+      <c r="A478" t="n">
+        <v>20041</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -18857,10 +18649,8 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>20042</t>
-        </is>
+      <c r="A479" t="n">
+        <v>20042</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -18911,10 +18701,8 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>20043</t>
-        </is>
+      <c r="A480" t="n">
+        <v>20043</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -18965,10 +18753,8 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
+      <c r="A481" t="n">
+        <v>20044</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -19019,10 +18805,8 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>20045</t>
-        </is>
+      <c r="A482" t="n">
+        <v>20045</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -19073,10 +18857,8 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>20046</t>
-        </is>
+      <c r="A483" t="n">
+        <v>20046</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -19127,10 +18909,8 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>20047</t>
-        </is>
+      <c r="A484" t="n">
+        <v>20047</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -19181,10 +18961,8 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>20048</t>
-        </is>
+      <c r="A485" t="n">
+        <v>20048</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -19235,10 +19013,8 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>20049</t>
-        </is>
+      <c r="A486" t="n">
+        <v>20049</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -19289,10 +19065,8 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>20050</t>
-        </is>
+      <c r="A487" t="n">
+        <v>20050</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -19343,10 +19117,8 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>20051</t>
-        </is>
+      <c r="A488" t="n">
+        <v>20051</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -19397,10 +19169,8 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>20052</t>
-        </is>
+      <c r="A489" t="n">
+        <v>20052</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -19451,10 +19221,8 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>20054</t>
-        </is>
+      <c r="A490" t="n">
+        <v>20054</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -19505,10 +19273,8 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>20055</t>
-        </is>
+      <c r="A491" t="n">
+        <v>20055</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -19559,10 +19325,8 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>20056</t>
-        </is>
+      <c r="A492" t="n">
+        <v>20056</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -19613,10 +19377,8 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>20057</t>
-        </is>
+      <c r="A493" t="n">
+        <v>20057</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -19667,10 +19429,8 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>20058</t>
-        </is>
+      <c r="A494" t="n">
+        <v>20058</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -19721,10 +19481,8 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>20053</t>
-        </is>
+      <c r="A495" t="n">
+        <v>20053</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -19775,10 +19533,8 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>20059</t>
-        </is>
+      <c r="A496" t="n">
+        <v>20059</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -19829,10 +19585,8 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>20060</t>
-        </is>
+      <c r="A497" t="n">
+        <v>20060</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -19883,10 +19637,8 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>20061</t>
-        </is>
+      <c r="A498" t="n">
+        <v>20061</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -19937,10 +19689,8 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>20062</t>
-        </is>
+      <c r="A499" t="n">
+        <v>20062</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -19991,10 +19741,8 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>20063</t>
-        </is>
+      <c r="A500" t="n">
+        <v>20063</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -20045,10 +19793,8 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>20064</t>
-        </is>
+      <c r="A501" t="n">
+        <v>20064</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -20099,10 +19845,8 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>20065</t>
-        </is>
+      <c r="A502" t="n">
+        <v>20065</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -20153,10 +19897,8 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>20066</t>
-        </is>
+      <c r="A503" t="n">
+        <v>20066</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -20207,10 +19949,8 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>20067</t>
-        </is>
+      <c r="A504" t="n">
+        <v>20067</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -20261,10 +20001,8 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>20068</t>
-        </is>
+      <c r="A505" t="n">
+        <v>20068</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -20315,10 +20053,8 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>20069</t>
-        </is>
+      <c r="A506" t="n">
+        <v>20069</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -20369,10 +20105,8 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>20070</t>
-        </is>
+      <c r="A507" t="n">
+        <v>20070</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -20423,10 +20157,8 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>20071</t>
-        </is>
+      <c r="A508" t="n">
+        <v>20071</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -20477,10 +20209,8 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>20072</t>
-        </is>
+      <c r="A509" t="n">
+        <v>20072</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -20531,10 +20261,8 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>20073</t>
-        </is>
+      <c r="A510" t="n">
+        <v>20073</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -20585,10 +20313,8 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>20074</t>
-        </is>
+      <c r="A511" t="n">
+        <v>20074</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -20639,10 +20365,8 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>20075</t>
-        </is>
+      <c r="A512" t="n">
+        <v>20075</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -20693,10 +20417,8 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>20076</t>
-        </is>
+      <c r="A513" t="n">
+        <v>20076</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -20747,10 +20469,8 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>20077</t>
-        </is>
+      <c r="A514" t="n">
+        <v>20077</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -20801,10 +20521,8 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>20078</t>
-        </is>
+      <c r="A515" t="n">
+        <v>20078</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -20855,10 +20573,8 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>20079</t>
-        </is>
+      <c r="A516" t="n">
+        <v>20079</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -20909,10 +20625,8 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>20080</t>
-        </is>
+      <c r="A517" t="n">
+        <v>20080</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -20963,10 +20677,8 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>20081</t>
-        </is>
+      <c r="A518" t="n">
+        <v>20081</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -21017,10 +20729,8 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>20082</t>
-        </is>
+      <c r="A519" t="n">
+        <v>20082</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -21071,10 +20781,8 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>20083</t>
-        </is>
+      <c r="A520" t="n">
+        <v>20083</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -21125,10 +20833,8 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>20084</t>
-        </is>
+      <c r="A521" t="n">
+        <v>20084</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -21179,10 +20885,8 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>20085</t>
-        </is>
+      <c r="A522" t="n">
+        <v>20085</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -21233,10 +20937,8 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>20086</t>
-        </is>
+      <c r="A523" t="n">
+        <v>20086</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -21279,10 +20981,8 @@
       <c r="L523" t="inlineStr"/>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>20087</t>
-        </is>
+      <c r="A524" t="n">
+        <v>20087</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -21333,10 +21033,8 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>20088</t>
-        </is>
+      <c r="A525" t="n">
+        <v>20088</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -21387,10 +21085,8 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>20089</t>
-        </is>
+      <c r="A526" t="n">
+        <v>20089</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -21441,10 +21137,8 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>20091</t>
-        </is>
+      <c r="A527" t="n">
+        <v>20091</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -21495,10 +21189,8 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>20092</t>
-        </is>
+      <c r="A528" t="n">
+        <v>20092</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -21549,10 +21241,8 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>20095</t>
-        </is>
+      <c r="A529" t="n">
+        <v>20095</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -21603,10 +21293,8 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>20096</t>
-        </is>
+      <c r="A530" t="n">
+        <v>20096</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -21657,10 +21345,8 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>20097</t>
-        </is>
+      <c r="A531" t="n">
+        <v>20097</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -21711,10 +21397,8 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>20098</t>
-        </is>
+      <c r="A532" t="n">
+        <v>20098</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -21765,10 +21449,8 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>20147</t>
-        </is>
+      <c r="A533" t="n">
+        <v>20147</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -21819,10 +21501,8 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>20149</t>
-        </is>
+      <c r="A534" t="n">
+        <v>20149</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -21873,10 +21553,8 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>20153</t>
-        </is>
+      <c r="A535" t="n">
+        <v>20153</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -21927,10 +21605,8 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>20154</t>
-        </is>
+      <c r="A536" t="n">
+        <v>20154</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -21981,10 +21657,8 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>20155</t>
-        </is>
+      <c r="A537" t="n">
+        <v>20155</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -22035,10 +21709,8 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>20156</t>
-        </is>
+      <c r="A538" t="n">
+        <v>20156</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -22089,10 +21761,8 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>20157</t>
-        </is>
+      <c r="A539" t="n">
+        <v>20157</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -22143,10 +21813,8 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>20158</t>
-        </is>
+      <c r="A540" t="n">
+        <v>20158</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -22197,10 +21865,8 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>20090</t>
-        </is>
+      <c r="A541" t="n">
+        <v>20090</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -22251,10 +21917,8 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>20093</t>
-        </is>
+      <c r="A542" t="n">
+        <v>20093</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -22305,10 +21969,8 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>20094</t>
-        </is>
+      <c r="A543" t="n">
+        <v>20094</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -22359,10 +22021,8 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>20148</t>
-        </is>
+      <c r="A544" t="n">
+        <v>20148</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -22413,10 +22073,8 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>20159</t>
-        </is>
+      <c r="A545" t="n">
+        <v>20159</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -22467,10 +22125,8 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>20160</t>
-        </is>
+      <c r="A546" t="n">
+        <v>20160</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -22521,10 +22177,8 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>20161</t>
-        </is>
+      <c r="A547" t="n">
+        <v>20161</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -22575,10 +22229,8 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>20162</t>
-        </is>
+      <c r="A548" t="n">
+        <v>20162</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -22629,10 +22281,8 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>20163</t>
-        </is>
+      <c r="A549" t="n">
+        <v>20163</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -22683,10 +22333,8 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>20164</t>
-        </is>
+      <c r="A550" t="n">
+        <v>20164</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -22737,10 +22385,8 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>20165</t>
-        </is>
+      <c r="A551" t="n">
+        <v>20165</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -22791,10 +22437,8 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>20166</t>
-        </is>
+      <c r="A552" t="n">
+        <v>20166</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -22845,10 +22489,8 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>20167</t>
-        </is>
+      <c r="A553" t="n">
+        <v>20167</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -22895,10 +22537,8 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>20168</t>
-        </is>
+      <c r="A554" t="n">
+        <v>20168</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -22949,10 +22589,8 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>20169</t>
-        </is>
+      <c r="A555" t="n">
+        <v>20169</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -23003,10 +22641,8 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>20170</t>
-        </is>
+      <c r="A556" t="n">
+        <v>20170</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -23057,10 +22693,8 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>20171</t>
-        </is>
+      <c r="A557" t="n">
+        <v>20171</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -23111,10 +22745,8 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>20172</t>
-        </is>
+      <c r="A558" t="n">
+        <v>20172</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -23165,10 +22797,8 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>20173</t>
-        </is>
+      <c r="A559" t="n">
+        <v>20173</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -23219,10 +22849,8 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>20174</t>
-        </is>
+      <c r="A560" t="n">
+        <v>20174</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -23273,10 +22901,8 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>20175</t>
-        </is>
+      <c r="A561" t="n">
+        <v>20175</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -23327,10 +22953,8 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>20176</t>
-        </is>
+      <c r="A562" t="n">
+        <v>20176</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -23381,10 +23005,8 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>20177</t>
-        </is>
+      <c r="A563" t="n">
+        <v>20177</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -23435,10 +23057,8 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>20178</t>
-        </is>
+      <c r="A564" t="n">
+        <v>20178</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -23489,10 +23109,8 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>20179</t>
-        </is>
+      <c r="A565" t="n">
+        <v>20179</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -23543,10 +23161,8 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>20180</t>
-        </is>
+      <c r="A566" t="n">
+        <v>20180</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -23597,10 +23213,8 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>20181</t>
-        </is>
+      <c r="A567" t="n">
+        <v>20181</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -23651,10 +23265,8 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>20182</t>
-        </is>
+      <c r="A568" t="n">
+        <v>20182</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -23705,10 +23317,8 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>20183</t>
-        </is>
+      <c r="A569" t="n">
+        <v>20183</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -23759,10 +23369,8 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>20184</t>
-        </is>
+      <c r="A570" t="n">
+        <v>20184</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -23813,10 +23421,8 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>20185</t>
-        </is>
+      <c r="A571" t="n">
+        <v>20185</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -23867,10 +23473,8 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>20186</t>
-        </is>
+      <c r="A572" t="n">
+        <v>20186</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -23921,10 +23525,8 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>20187</t>
-        </is>
+      <c r="A573" t="n">
+        <v>20187</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -23975,10 +23577,8 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>20188</t>
-        </is>
+      <c r="A574" t="n">
+        <v>20188</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -24029,10 +23629,8 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>20189</t>
-        </is>
+      <c r="A575" t="n">
+        <v>20189</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -24083,10 +23681,8 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>20190</t>
-        </is>
+      <c r="A576" t="n">
+        <v>20190</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -24137,10 +23733,8 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>20191</t>
-        </is>
+      <c r="A577" t="n">
+        <v>20191</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -24191,10 +23785,8 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>20192</t>
-        </is>
+      <c r="A578" t="n">
+        <v>20192</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -24245,10 +23837,8 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>20193</t>
-        </is>
+      <c r="A579" t="n">
+        <v>20193</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -24299,10 +23889,8 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>20194</t>
-        </is>
+      <c r="A580" t="n">
+        <v>20194</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -24353,10 +23941,8 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>20195</t>
-        </is>
+      <c r="A581" t="n">
+        <v>20195</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -24407,10 +23993,8 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>20196</t>
-        </is>
+      <c r="A582" t="n">
+        <v>20196</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -24461,10 +24045,8 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>20197</t>
-        </is>
+      <c r="A583" t="n">
+        <v>20197</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -24515,10 +24097,8 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>20198</t>
-        </is>
+      <c r="A584" t="n">
+        <v>20198</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -24569,10 +24149,8 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>20199</t>
-        </is>
+      <c r="A585" t="n">
+        <v>20199</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -24623,10 +24201,8 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>20200</t>
-        </is>
+      <c r="A586" t="n">
+        <v>20200</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -24677,10 +24253,8 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>20201</t>
-        </is>
+      <c r="A587" t="n">
+        <v>20201</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -24731,10 +24305,8 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
+      <c r="A588" t="n">
+        <v>20202</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -24785,10 +24357,8 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
+      <c r="A589" t="n">
+        <v>20203</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -24839,10 +24409,8 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>20204</t>
-        </is>
+      <c r="A590" t="n">
+        <v>20204</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -24893,10 +24461,8 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>20205</t>
-        </is>
+      <c r="A591" t="n">
+        <v>20205</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -24947,10 +24513,8 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>20206</t>
-        </is>
+      <c r="A592" t="n">
+        <v>20206</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -25001,10 +24565,8 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>20207</t>
-        </is>
+      <c r="A593" t="n">
+        <v>20207</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -25055,10 +24617,8 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>20208</t>
-        </is>
+      <c r="A594" t="n">
+        <v>20208</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -25109,10 +24669,8 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>20209</t>
-        </is>
+      <c r="A595" t="n">
+        <v>20209</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -25163,10 +24721,8 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>20210</t>
-        </is>
+      <c r="A596" t="n">
+        <v>20210</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -25217,10 +24773,8 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>20211</t>
-        </is>
+      <c r="A597" t="n">
+        <v>20211</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -25271,10 +24825,8 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>20212</t>
-        </is>
+      <c r="A598" t="n">
+        <v>20212</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -25325,10 +24877,8 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>20213</t>
-        </is>
+      <c r="A599" t="n">
+        <v>20213</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -25379,10 +24929,8 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>20214</t>
-        </is>
+      <c r="A600" t="n">
+        <v>20214</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -25433,10 +24981,8 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>20215</t>
-        </is>
+      <c r="A601" t="n">
+        <v>20215</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -25487,10 +25033,8 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>20216</t>
-        </is>
+      <c r="A602" t="n">
+        <v>20216</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -25541,10 +25085,8 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>20217</t>
-        </is>
+      <c r="A603" t="n">
+        <v>20217</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -25591,6 +25133,58 @@
       <c r="L603" t="inlineStr">
         <is>
           <t>牛奶</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>20218</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>洗衣机</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>xǐ yī jī</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>가구</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>세탁기</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>washing machine</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr"/>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>洗衣机</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr"/>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>洗衣机</t>
         </is>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -5705,7 +5705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>반대</t>
+          <t>회</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>반대</t>
+          <t>출</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8873,6 +8873,718 @@
           <t>跑</t>
         </is>
       </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>10063</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>出去</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>chūqù</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>출</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>나가다</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>to go out</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>出去</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>出去</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>10064</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>出发</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>chūfā</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>출</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>출발하다</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>to set off</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>出发</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>出发</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>10065</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>出生</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>chūshēng</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>출</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>태어나다</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>to be born</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>出生</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>出生</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>10066</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>出现</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>chūxiàn</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>출</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>나타나다</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>to appear</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>出现</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>出现</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>10067</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>出差</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>chūchā</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>출</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>출장가다</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>to go on a business trip</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>出差</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>出差</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>10068</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>chū</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>출</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>밖으로</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>10069</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>回家</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>huíjiā</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>집에가다</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>to go home</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>回家</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>回家</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>10070</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>回来</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>huílái</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>돌아오다</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>to come back</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>回来</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>回来</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>10071</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>回去</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>huíqù</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>돌아가다</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>to go back</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>回去</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>回去</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>10072</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>回忆</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>huíyì</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>회상하다</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>memory / to recall</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>回忆</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>回忆</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>10073</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>回复</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>huífù</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>답장하다</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>to reply</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>回复</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>10074</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>回国</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>huíguó</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>귀국하다</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>to return to one's country</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>回国</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>回国</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>10075</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>回本</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>huíběn</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>본전을 찾다</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>break even</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>回本</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>回本</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>10076</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>huí</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>동사</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>회</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>되돌아가다</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8885,7 +9597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L604"/>
+  <dimension ref="A1:L636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22614,7 +23326,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>탈것</t>
+          <t>출</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -25185,6 +25897,1670 @@
       <c r="L604" t="inlineStr">
         <is>
           <t>洗衣机</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>20219</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>出口</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>chūkǒu</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>출</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>출구</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>exit / export</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr"/>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>出口</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr"/>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>出口</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>20220</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>米饭</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>mǐfàn</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>쌀밥</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>cooked rice</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr"/>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>米饭</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr"/>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>米饭</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>20221</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>炒饭</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>chǎofàn</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>볶음밥</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>fried rice</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr"/>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>炒饭</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr"/>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>炒饭</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>20222</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>面条</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>miàntiáo</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>면</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>noodles</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr"/>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>面条</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr"/>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>面条</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>20223</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>炒面</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>chǎomiàn</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>볶음면</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>fried noodles</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr"/>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>炒面</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr"/>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>炒面</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>20224</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>面包</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>miànbāo</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>빵</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr"/>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>面包</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr"/>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>面包</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>20225</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>三明治</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>sānmíngzhì</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>샌드위치</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>sandwich</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr"/>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>三明治</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr"/>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>三明治</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>20226</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>汤</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>tāng</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>soup</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr"/>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>汤</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr"/>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>汤</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>20227</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>蛋花汤</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>dànhuātāng</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>계란국</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>egg drop soup</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr"/>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>蛋花汤</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr"/>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>蛋花汤</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>20228</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>浓汤</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>nóngtāng</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>수프</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>thick soup / cream soup</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr"/>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>浓汤</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr"/>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>浓汤</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>20229</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>粥</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>zhōu</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>죽</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>porridge / congee</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr"/>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>粥</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr"/>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>粥</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>20230</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>包子</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>bāozi</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>빠오즈</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>steamed bun</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr"/>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>包子</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr"/>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>包子</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>20231</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>饺子</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>jiǎozi</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>교자</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>dumplings</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr"/>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>饺子</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr"/>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>饺子</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>20232</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>馒头</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>mántou</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>만두</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>mantou / steamed bun</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr"/>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>馒头</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr"/>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>馒头</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>20233</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>方便面</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>fāngbiànmiàn</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>라면</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>instant noodles</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr"/>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>方便面</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr"/>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>方便面</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>20234</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>韩国</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>hánguó</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr"/>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>韩国</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr"/>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>韩国</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>20235</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>朝鲜</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>cháoxiǎn</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>북한</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>North Korea</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr"/>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>朝鲜</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr"/>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>朝鲜</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>20236</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>zhōngguó</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr"/>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr"/>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>20237</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>台湾</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>táiwān</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>대만</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr"/>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>台湾</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr"/>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>台湾</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>20238</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>měiguó</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr"/>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr"/>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>20239</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>rìběn</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr"/>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr"/>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>20240</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>yīngguó</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>영국</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr"/>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr"/>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>20241</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>fǎguó</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr"/>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr"/>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>20242</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>déguó</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr"/>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr"/>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>20243</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>俄罗斯</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>éluósī</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>러시아</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr"/>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>俄罗斯</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr"/>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>俄罗斯</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>20244</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>jiānádà</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>캐나다</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr"/>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr"/>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>20245</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>澳大利亚</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>àodàlìyà</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>"0000"</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>호주</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr"/>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>澳大利亚</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr"/>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>澳大利亚</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>20246</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>yìdàlì</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>이탈리아</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr"/>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr"/>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>20247</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>xībānyá</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>"000"</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>스페인</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr"/>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr"/>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>20248</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>tàiguó</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>태국</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr"/>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr"/>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>20249</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>yuènán</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>베트남</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr"/>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr"/>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>20250</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>yìndù</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>"00"</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>국</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>인도</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr"/>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr"/>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>印度</t>
         </is>
       </c>
     </row>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -525,6 +535,8 @@
           <t>一</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -561,6 +573,8 @@
           <t>两</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -597,6 +611,8 @@
           <t>二</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -633,6 +649,8 @@
           <t>三</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -669,6 +687,8 @@
           <t>四</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -705,6 +725,8 @@
           <t>五</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -741,6 +763,8 @@
           <t>六</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -777,6 +801,8 @@
           <t>七</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -813,6 +839,8 @@
           <t>八</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -849,6 +877,8 @@
           <t>九</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -885,6 +915,8 @@
           <t>十</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -921,6 +953,8 @@
           <t>十一</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -957,6 +991,8 @@
           <t>十二</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -993,6 +1029,8 @@
           <t>十三</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1029,6 +1067,8 @@
           <t>十四</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1065,6 +1105,8 @@
           <t>十五</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1101,6 +1143,8 @@
           <t>十六</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1137,6 +1181,8 @@
           <t>十七</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1173,6 +1219,8 @@
           <t>十八</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1209,6 +1257,8 @@
           <t>十九</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1245,6 +1295,8 @@
           <t>二十</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1257,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,6 +1371,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>sound_path</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
         </is>
       </c>
     </row>
@@ -1357,6 +1419,8 @@
           <t>床前明月光</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1393,6 +1457,8 @@
           <t>疑是地上霜</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1429,6 +1495,8 @@
           <t>举头望明月</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1465,6 +1533,8 @@
           <t>低头思故乡</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1489,6 +1559,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1529,6 +1601,8 @@
           <t>闲山岛月明夜</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1569,6 +1643,8 @@
           <t>上戍楼抚大刀</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1609,6 +1685,8 @@
           <t>深愁时何处</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1727,8 @@
           <t>一声羌笛更添愁</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1673,6 +1753,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1697,6 +1779,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1721,6 +1805,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1745,6 +1831,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1769,6 +1857,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1793,6 +1883,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1817,6 +1909,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1841,6 +1935,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1865,6 +1961,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1889,6 +1987,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1913,6 +2013,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1941,6 +2043,8 @@
           <t>0</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1985,6 +2089,8 @@
           <t>订阅</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2029,6 +2135,8 @@
           <t>点赞</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2041,7 +2149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2105,6 +2213,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2141,6 +2259,8 @@
           <t>贵</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2193,6 +2313,8 @@
           <t>好吃</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2229,6 +2351,8 @@
           <t>对</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2265,6 +2389,8 @@
           <t>错</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2301,6 +2427,8 @@
           <t>烫</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2337,6 +2465,8 @@
           <t>热</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2373,6 +2503,8 @@
           <t>凉</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2409,6 +2541,8 @@
           <t>冷</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2445,6 +2579,8 @@
           <t>冰</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2497,6 +2633,8 @@
           <t>好</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2549,6 +2687,8 @@
           <t>好喝</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2601,6 +2741,8 @@
           <t>好看</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2653,6 +2795,8 @@
           <t>好听</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2705,6 +2849,8 @@
           <t>好玩</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2757,6 +2903,8 @@
           <t>好用</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2809,6 +2957,8 @@
           <t>好笑</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2861,6 +3011,8 @@
           <t>好做</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2913,6 +3065,8 @@
           <t>好受</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2965,6 +3119,8 @@
           <t>好走</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3017,6 +3173,8 @@
           <t>好学</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3069,6 +3227,8 @@
           <t>好闻</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3121,6 +3281,8 @@
           <t>高兴</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3335,8 @@
           <t>快乐</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3225,6 +3389,8 @@
           <t>兴奋</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3277,6 +3443,8 @@
           <t>感动</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3329,6 +3497,8 @@
           <t>放心</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3381,6 +3551,8 @@
           <t>满意</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3433,6 +3605,8 @@
           <t>舒服</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3659,8 @@
           <t>轻松</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3537,6 +3713,8 @@
           <t>生气</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3589,6 +3767,8 @@
           <t>难过</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3641,6 +3821,8 @@
           <t>伤心</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3693,6 +3875,8 @@
           <t>担心</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3745,6 +3929,8 @@
           <t>紧张</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3797,6 +3983,8 @@
           <t>累</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3849,6 +4037,8 @@
           <t>害怕</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3901,6 +4091,8 @@
           <t>害羞</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3913,7 +4105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3977,6 +4169,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -4013,6 +4215,8 @@
           <t>往</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4025,7 +4229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4089,6 +4293,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -4125,6 +4339,8 @@
           <t>有点</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4161,6 +4377,8 @@
           <t>太</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4197,6 +4415,8 @@
           <t>请</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4209,7 +4429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4273,6 +4493,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -4309,6 +4539,8 @@
           <t>斤</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4345,6 +4577,8 @@
           <t>个</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4381,6 +4615,8 @@
           <t>本</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4421,6 +4657,8 @@
           <t>只</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4457,6 +4695,8 @@
           <t>瓶</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4493,6 +4733,8 @@
           <t>杯</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4529,6 +4771,8 @@
           <t>双</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4565,6 +4809,8 @@
           <t>罐</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4577,7 +4823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4641,6 +4887,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -4677,6 +4933,8 @@
           <t>吗</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4713,6 +4971,8 @@
           <t>不</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4749,6 +5009,8 @@
           <t>的</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4785,6 +5047,8 @@
           <t>了</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4797,7 +5061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4861,6 +5125,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -4897,6 +5171,8 @@
           <t>我</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4933,6 +5209,8 @@
           <t>你</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4969,6 +5247,8 @@
           <t>您</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5005,6 +5285,8 @@
           <t>他</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5041,6 +5323,8 @@
           <t>她</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5077,6 +5361,8 @@
           <t>我们</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5113,6 +5399,8 @@
           <t>你们</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5149,6 +5437,8 @@
           <t>他们</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5185,6 +5475,8 @@
           <t>她们</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5197,7 +5489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5261,6 +5553,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5297,6 +5599,8 @@
           <t>这</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5333,6 +5637,8 @@
           <t>那</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5369,6 +5675,8 @@
           <t>这个</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5405,6 +5713,8 @@
           <t>那个</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5441,6 +5751,8 @@
           <t>这儿</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5477,6 +5789,8 @@
           <t>那儿</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5513,6 +5827,8 @@
           <t>哪儿</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5549,6 +5865,8 @@
           <t>几</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5585,6 +5903,8 @@
           <t>这样</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5621,6 +5941,8 @@
           <t>那样</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5657,6 +5979,8 @@
           <t>哪样</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5693,6 +6017,8 @@
           <t>这种</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5705,7 +6031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5769,6 +6095,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -5805,6 +6141,8 @@
           <t>是</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5841,6 +6179,8 @@
           <t>在</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5893,6 +6233,8 @@
           <t>去</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5929,6 +6271,8 @@
           <t>有</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5965,6 +6309,8 @@
           <t>等</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -6017,6 +6363,8 @@
           <t>工作</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6053,6 +6401,8 @@
           <t>好</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6105,6 +6455,8 @@
           <t>吃</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6157,6 +6509,8 @@
           <t>坐</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6193,6 +6547,8 @@
           <t>骑</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6245,6 +6601,8 @@
           <t>走</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6281,6 +6639,8 @@
           <t>要</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6317,6 +6677,8 @@
           <t>放</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6369,6 +6731,8 @@
           <t>给</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6405,6 +6769,8 @@
           <t>刷</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6441,6 +6807,8 @@
           <t>扫</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6481,6 +6849,8 @@
           <t>付</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6533,6 +6903,8 @@
           <t>来</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6585,6 +6957,8 @@
           <t>买</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6637,6 +7011,8 @@
           <t>卖</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6689,6 +7065,8 @@
           <t>收</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6741,6 +7119,8 @@
           <t>问</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6793,6 +7173,8 @@
           <t>回答</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -6845,6 +7227,8 @@
           <t>看</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -6897,6 +7281,8 @@
           <t>听</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -6949,6 +7335,8 @@
           <t>说</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -7001,6 +7389,8 @@
           <t>学</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -7053,6 +7443,8 @@
           <t>教</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -7105,6 +7497,8 @@
           <t>赢</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -7157,6 +7551,8 @@
           <t>输</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -7209,6 +7605,8 @@
           <t>开</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -7261,6 +7659,8 @@
           <t>关</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -7313,6 +7713,8 @@
           <t>上</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -7365,6 +7767,8 @@
           <t>下</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -7417,6 +7821,8 @@
           <t>进</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -7469,6 +7875,8 @@
           <t>出</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -7521,6 +7929,8 @@
           <t>起</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -7573,6 +7983,8 @@
           <t>穿</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -7625,6 +8037,8 @@
           <t>脱</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -7677,6 +8091,8 @@
           <t>开始</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -7729,6 +8145,8 @@
           <t>结束</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -7781,6 +8199,8 @@
           <t>记得</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -7833,6 +8253,8 @@
           <t>忘记</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -7885,6 +8307,8 @@
           <t>喜欢</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7937,6 +8361,8 @@
           <t>讨厌</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7989,6 +8415,8 @@
           <t>爱</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -8041,6 +8469,8 @@
           <t>恨</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -8093,6 +8523,8 @@
           <t>休息</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8145,6 +8577,8 @@
           <t>借</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8197,6 +8631,8 @@
           <t>还</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8249,6 +8685,8 @@
           <t>送</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8301,6 +8739,8 @@
           <t>收到</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8353,6 +8793,8 @@
           <t>找</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8405,6 +8847,8 @@
           <t>丢</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8457,6 +8901,8 @@
           <t>停</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8509,6 +8955,8 @@
           <t>喝</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8561,6 +9009,8 @@
           <t>做</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8613,6 +9063,8 @@
           <t>用</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8665,6 +9117,8 @@
           <t>住</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8717,6 +9171,8 @@
           <t>离开</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8769,6 +9225,8 @@
           <t>进去</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8821,6 +9279,8 @@
           <t>出来</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8873,6 +9333,8 @@
           <t>跑</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8925,6 +9387,8 @@
           <t>出去</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8977,6 +9441,8 @@
           <t>出发</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9029,6 +9495,8 @@
           <t>出生</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9081,6 +9549,8 @@
           <t>出现</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9133,6 +9603,8 @@
           <t>出差</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9181,6 +9653,8 @@
           <t>出</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9233,6 +9707,8 @@
           <t>回家</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9285,6 +9761,8 @@
           <t>回来</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9337,6 +9815,8 @@
           <t>回去</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9389,6 +9869,8 @@
           <t>回忆</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9441,6 +9923,8 @@
           <t>回复</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9493,6 +9977,8 @@
           <t>回国</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9545,6 +10031,8 @@
           <t>回本</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9585,6 +10073,8 @@
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9597,7 +10087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L636"/>
+  <dimension ref="A1:N636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9659,6 +10149,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>sound_path</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
         </is>
       </c>
     </row>
@@ -9675,6 +10175,8 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -9689,6 +10191,8 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -9703,6 +10207,8 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -9717,6 +10223,8 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -9731,6 +10239,8 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -9745,6 +10255,8 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9781,6 +10293,8 @@
           <t>上班族</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9817,6 +10331,8 @@
           <t>公司职员</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9853,6 +10369,8 @@
           <t>毕业生</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9889,6 +10407,8 @@
           <t>厨师</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9925,6 +10445,8 @@
           <t>歌手</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9961,6 +10483,8 @@
           <t>韩国人</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9997,6 +10521,8 @@
           <t>中国人</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10033,6 +10559,8 @@
           <t>程序员</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10069,6 +10597,8 @@
           <t>学生</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10105,6 +10635,8 @@
           <t>程序员</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10157,6 +10689,8 @@
           <t>老师</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10193,6 +10727,8 @@
           <t>医生</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10229,6 +10765,8 @@
           <t>公务员</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10265,6 +10803,8 @@
           <t>设计师</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10301,6 +10841,8 @@
           <t>律师</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10337,6 +10879,8 @@
           <t>会计</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10373,6 +10917,8 @@
           <t>银行职员</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -10409,6 +10955,8 @@
           <t>服务员</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -10461,6 +11009,8 @@
           <t>老板</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -10475,6 +11025,8 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -10489,6 +11041,8 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -10503,6 +11057,8 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -10517,6 +11073,8 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -10531,6 +11089,8 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -10545,6 +11105,8 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -10559,6 +11121,8 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -10573,6 +11137,8 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -10587,6 +11153,8 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -10601,6 +11169,8 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -10615,6 +11185,8 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -10629,6 +11201,8 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -10643,6 +11217,8 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -10657,6 +11233,8 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -10671,6 +11249,8 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -10707,6 +11287,8 @@
           <t>手机</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -10743,6 +11325,8 @@
           <t>工作</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -10779,6 +11363,8 @@
           <t>银行</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -10793,6 +11379,8 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -10845,6 +11433,8 @@
           <t>书</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -10893,6 +11483,8 @@
           <t>狗</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -10941,6 +11533,8 @@
           <t>猫</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -10989,6 +11583,8 @@
           <t>鸡</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -11033,6 +11629,8 @@
           <t>猪</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -11077,6 +11675,8 @@
           <t>牛</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -11121,6 +11721,8 @@
           <t>鸭子</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -11165,6 +11767,8 @@
           <t>羊</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -11201,6 +11805,8 @@
           <t>猪肉</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -11237,6 +11843,8 @@
           <t>牛肉</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -11273,6 +11881,8 @@
           <t>鸭肉</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -11309,6 +11919,8 @@
           <t>羊肉</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -11345,6 +11957,8 @@
           <t>鸡肉</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -11381,6 +11995,8 @@
           <t>洗手间</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -11417,6 +12033,8 @@
           <t>地铁站</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -11457,6 +12075,8 @@
           <t>发型</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -11497,6 +12117,8 @@
           <t>短发</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -11533,6 +12155,8 @@
           <t>韩式</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -11569,6 +12193,8 @@
           <t>水温</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -11621,6 +12247,8 @@
           <t>水</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -11673,6 +12301,12 @@
           <t>冰水</t>
         </is>
       </c>
+      <c r="M66" t="n">
+        <v>100008</v>
+      </c>
+      <c r="N66" t="n">
+        <v>20121</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -11709,6 +12343,8 @@
           <t>边</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -11745,6 +12381,8 @@
           <t>方向</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -11781,6 +12419,8 @@
           <t>右</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -11817,6 +12457,8 @@
           <t>反</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -11853,6 +12495,8 @@
           <t>楼</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -11889,6 +12533,8 @@
           <t>香菜</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -11929,6 +12575,8 @@
           <t>麻辣</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -11969,6 +12617,8 @@
           <t>孜然</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -12005,6 +12655,8 @@
           <t>醋</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -12041,6 +12693,8 @@
           <t>蒜</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -12077,6 +12731,8 @@
           <t>葱</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -12113,6 +12769,8 @@
           <t>辣椒油</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -12149,6 +12807,8 @@
           <t>菜单</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -12185,6 +12845,8 @@
           <t>勺子</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -12221,6 +12883,8 @@
           <t>叉子</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -12257,6 +12921,8 @@
           <t>筷子</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12293,6 +12959,8 @@
           <t>汤勺</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12329,6 +12997,8 @@
           <t>纸巾</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12365,6 +13035,8 @@
           <t>围裙</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12401,6 +13073,8 @@
           <t>碟子</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12437,6 +13111,8 @@
           <t>打包盒</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12473,6 +13149,8 @@
           <t>卡</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12509,6 +13187,8 @@
           <t>微信支付</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12545,6 +13225,8 @@
           <t>支付宝</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
@@ -12559,6 +13241,8 @@
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -12573,6 +13257,8 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -12587,6 +13273,8 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12639,6 +13327,8 @@
           <t>可乐</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12691,6 +13381,8 @@
           <t>啤酒</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12743,6 +13435,8 @@
           <t>雪碧</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
@@ -12757,6 +13451,8 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
@@ -12771,6 +13467,8 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
@@ -12785,6 +13483,8 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -12799,6 +13499,8 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
@@ -12813,6 +13515,8 @@
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -12827,6 +13531,8 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
@@ -12841,6 +13547,8 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
@@ -12855,6 +13563,8 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
@@ -12869,6 +13579,8 @@
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -12883,6 +13595,8 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
@@ -12897,6 +13611,8 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -12911,6 +13627,8 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
@@ -12925,6 +13643,8 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
@@ -12939,6 +13659,8 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -12953,6 +13675,8 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
@@ -12967,6 +13691,8 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
@@ -12981,6 +13707,8 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
@@ -12995,6 +13723,8 @@
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
@@ -13009,6 +13739,8 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
@@ -13023,6 +13755,8 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -13037,6 +13771,8 @@
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
@@ -13051,6 +13787,8 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
@@ -13065,6 +13803,8 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -13079,6 +13819,8 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
@@ -13093,6 +13835,8 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
@@ -13107,6 +13851,8 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
@@ -13121,6 +13867,8 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
@@ -13135,6 +13883,8 @@
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
@@ -13149,6 +13899,8 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
@@ -13163,6 +13915,8 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
@@ -13177,6 +13931,8 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
@@ -13191,6 +13947,8 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
@@ -13205,6 +13963,8 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
@@ -13219,6 +13979,8 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
@@ -13233,6 +13995,8 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -13247,6 +14011,8 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
@@ -13261,6 +14027,8 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
@@ -13275,6 +14043,8 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
@@ -13289,6 +14059,8 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
@@ -13303,6 +14075,8 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
@@ -13317,6 +14091,8 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
@@ -13331,6 +14107,8 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
@@ -13345,6 +14123,8 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
@@ -13359,6 +14139,8 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -13373,6 +14155,8 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
@@ -13387,6 +14171,8 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
@@ -13401,6 +14187,8 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
@@ -13415,6 +14203,8 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -13429,6 +14219,8 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
@@ -13443,6 +14235,8 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
@@ -13457,6 +14251,8 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
@@ -13471,6 +14267,8 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
@@ -13485,6 +14283,8 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
@@ -13499,6 +14299,8 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
@@ -13513,6 +14315,8 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -13527,6 +14331,8 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
@@ -13541,6 +14347,8 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
@@ -13555,6 +14363,8 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
@@ -13569,6 +14379,8 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
@@ -13583,6 +14395,8 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
@@ -13597,6 +14411,8 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
@@ -13611,6 +14427,8 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
@@ -13625,6 +14443,8 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
@@ -13639,6 +14459,8 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
@@ -13653,6 +14475,8 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -13667,6 +14491,8 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
@@ -13681,6 +14507,8 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
@@ -13695,6 +14523,8 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -13709,6 +14539,8 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
@@ -13723,6 +14555,8 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -13737,6 +14571,8 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -13751,6 +14587,8 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -13765,6 +14603,8 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
@@ -13779,6 +14619,8 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -13793,6 +14635,8 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
@@ -13807,6 +14651,8 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
@@ -13821,6 +14667,8 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
@@ -13835,6 +14683,8 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
@@ -13849,6 +14699,8 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
@@ -13863,6 +14715,8 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
@@ -13877,6 +14731,8 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
@@ -13891,6 +14747,8 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
@@ -13905,6 +14763,8 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
@@ -13919,6 +14779,8 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
@@ -13933,6 +14795,8 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
@@ -13947,6 +14811,8 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
@@ -13961,6 +14827,8 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
@@ -13975,6 +14843,8 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
@@ -13989,6 +14859,8 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>
@@ -14003,6 +14875,8 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
@@ -14017,6 +14891,8 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
@@ -14031,6 +14907,8 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
@@ -14045,6 +14923,8 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
@@ -14059,6 +14939,8 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
@@ -14073,6 +14955,8 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
@@ -14087,6 +14971,8 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
@@ -14101,6 +14987,8 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
@@ -14115,6 +15003,8 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
@@ -14129,6 +15019,8 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>
@@ -14143,6 +15035,8 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
@@ -14157,6 +15051,8 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
@@ -14171,6 +15067,8 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
@@ -14185,6 +15083,8 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
@@ -14199,6 +15099,8 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
@@ -14213,6 +15115,8 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
@@ -14227,6 +15131,8 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
@@ -14241,6 +15147,8 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
@@ -14255,6 +15163,8 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
@@ -14269,6 +15179,8 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
@@ -14283,6 +15195,8 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
@@ -14297,6 +15211,8 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
@@ -14311,6 +15227,8 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
@@ -14325,6 +15243,8 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
@@ -14339,6 +15259,8 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
@@ -14353,6 +15275,8 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
@@ -14367,6 +15291,8 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr"/>
@@ -14381,6 +15307,8 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
@@ -14395,6 +15323,8 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr"/>
@@ -14409,6 +15339,8 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr"/>
@@ -14423,6 +15355,8 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr"/>
@@ -14437,6 +15371,8 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr"/>
@@ -14451,6 +15387,8 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
@@ -14465,6 +15403,8 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
@@ -14479,6 +15419,8 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr"/>
@@ -14493,6 +15435,8 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr"/>
@@ -14507,6 +15451,8 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr"/>
@@ -14521,6 +15467,8 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr"/>
@@ -14535,6 +15483,8 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr"/>
@@ -14549,6 +15499,8 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr"/>
@@ -14563,6 +15515,8 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr"/>
@@ -14577,6 +15531,8 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr"/>
@@ -14591,6 +15547,8 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr"/>
@@ -14605,6 +15563,8 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr"/>
@@ -14619,6 +15579,8 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
@@ -14633,6 +15595,8 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
@@ -14647,6 +15611,8 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr"/>
@@ -14661,6 +15627,8 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr"/>
@@ -14675,6 +15643,8 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr"/>
@@ -14689,6 +15659,8 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr"/>
@@ -14703,6 +15675,8 @@
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr"/>
@@ -14717,6 +15691,8 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr"/>
@@ -14731,6 +15707,8 @@
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr"/>
@@ -14745,6 +15723,8 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr"/>
@@ -14759,6 +15739,8 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr"/>
@@ -14773,6 +15755,8 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr"/>
@@ -14787,6 +15771,8 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr"/>
@@ -14801,6 +15787,8 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr"/>
@@ -14815,6 +15803,8 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr"/>
@@ -14829,6 +15819,8 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr"/>
@@ -14843,6 +15835,8 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr"/>
@@ -14857,6 +15851,8 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr"/>
@@ -14871,6 +15867,8 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr"/>
@@ -14885,6 +15883,8 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr"/>
@@ -14899,6 +15899,8 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr"/>
@@ -14913,6 +15915,8 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr"/>
@@ -14927,6 +15931,8 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr"/>
@@ -14941,6 +15947,8 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr"/>
@@ -14955,6 +15963,8 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr"/>
@@ -14969,6 +15979,8 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr"/>
@@ -14983,6 +15995,8 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr"/>
@@ -14997,6 +16011,8 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr"/>
@@ -15011,6 +16027,8 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
@@ -15025,6 +16043,8 @@
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr"/>
@@ -15039,6 +16059,8 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr"/>
@@ -15053,6 +16075,8 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr"/>
@@ -15067,6 +16091,8 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr"/>
@@ -15081,6 +16107,8 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr"/>
@@ -15095,6 +16123,8 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr"/>
@@ -15109,6 +16139,8 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr"/>
@@ -15123,6 +16155,8 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr"/>
@@ -15137,6 +16171,8 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr"/>
@@ -15151,6 +16187,8 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr"/>
@@ -15165,6 +16203,8 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr"/>
@@ -15179,6 +16219,8 @@
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr"/>
@@ -15193,6 +16235,8 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr"/>
@@ -15207,6 +16251,8 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr"/>
@@ -15221,6 +16267,8 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr"/>
@@ -15235,6 +16283,8 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
@@ -15249,6 +16299,8 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr"/>
@@ -15263,6 +16315,8 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr"/>
@@ -15277,6 +16331,8 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr"/>
@@ -15291,6 +16347,8 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr"/>
@@ -15305,6 +16363,8 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
@@ -15319,6 +16379,8 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr"/>
@@ -15333,6 +16395,8 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr"/>
@@ -15347,6 +16411,8 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr"/>
@@ -15361,6 +16427,8 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr"/>
@@ -15375,6 +16443,8 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr"/>
@@ -15389,6 +16459,8 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr"/>
@@ -15403,6 +16475,8 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr"/>
@@ -15417,6 +16491,8 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr"/>
@@ -15431,6 +16507,8 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr"/>
@@ -15445,6 +16523,8 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr"/>
@@ -15459,6 +16539,8 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr"/>
@@ -15473,6 +16555,8 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr"/>
@@ -15487,6 +16571,8 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr"/>
@@ -15501,6 +16587,8 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr"/>
@@ -15515,6 +16603,8 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr"/>
@@ -15529,6 +16619,8 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr"/>
@@ -15543,6 +16635,8 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr"/>
@@ -15557,6 +16651,8 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr"/>
@@ -15571,6 +16667,8 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
@@ -15585,6 +16683,8 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr"/>
@@ -15599,6 +16699,8 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr"/>
@@ -15613,6 +16715,8 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr"/>
@@ -15627,6 +16731,8 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr"/>
@@ -15641,6 +16747,8 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr"/>
@@ -15655,6 +16763,8 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr"/>
@@ -15669,6 +16779,8 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr"/>
@@ -15683,6 +16795,8 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr"/>
@@ -15697,6 +16811,8 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr"/>
@@ -15711,6 +16827,8 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr"/>
@@ -15725,6 +16843,8 @@
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr"/>
@@ -15739,6 +16859,8 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr"/>
@@ -15753,6 +16875,8 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr"/>
@@ -15767,6 +16891,8 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr"/>
@@ -15781,6 +16907,8 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr"/>
@@ -15795,6 +16923,8 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr"/>
@@ -15809,6 +16939,8 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr"/>
@@ -15823,6 +16955,8 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr"/>
@@ -15837,6 +16971,8 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr"/>
@@ -15851,6 +16987,8 @@
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr"/>
@@ -15865,6 +17003,8 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr"/>
@@ -15879,6 +17019,8 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr"/>
@@ -15893,6 +17035,8 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr"/>
@@ -15907,6 +17051,8 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr"/>
@@ -15921,6 +17067,8 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr"/>
@@ -15935,6 +17083,8 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr"/>
@@ -15949,6 +17099,8 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr"/>
@@ -15963,6 +17115,8 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr"/>
@@ -15977,6 +17131,8 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr"/>
@@ -15991,6 +17147,8 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr"/>
@@ -16005,6 +17163,8 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr"/>
@@ -16019,6 +17179,8 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr"/>
@@ -16033,6 +17195,8 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr"/>
@@ -16047,6 +17211,8 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr"/>
@@ -16061,6 +17227,8 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr"/>
@@ -16075,6 +17243,8 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr"/>
@@ -16089,6 +17259,8 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr"/>
@@ -16103,6 +17275,8 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr"/>
@@ -16117,6 +17291,8 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr"/>
@@ -16131,6 +17307,8 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr"/>
@@ -16145,6 +17323,8 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr"/>
@@ -16159,6 +17339,8 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr"/>
@@ -16173,6 +17355,8 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr"/>
@@ -16187,6 +17371,8 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr"/>
@@ -16201,6 +17387,8 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr"/>
@@ -16215,6 +17403,8 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr"/>
@@ -16229,6 +17419,8 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr"/>
@@ -16243,6 +17435,8 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr"/>
@@ -16257,6 +17451,8 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr"/>
@@ -16271,6 +17467,8 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr"/>
@@ -16285,6 +17483,8 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr"/>
@@ -16299,6 +17499,8 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr"/>
@@ -16313,6 +17515,8 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr"/>
@@ -16327,6 +17531,8 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr"/>
@@ -16341,6 +17547,8 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr"/>
@@ -16355,6 +17563,8 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr"/>
@@ -16369,6 +17579,8 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr"/>
@@ -16383,6 +17595,8 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr"/>
@@ -16397,6 +17611,8 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr"/>
@@ -16411,6 +17627,8 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr"/>
@@ -16425,6 +17643,8 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr"/>
@@ -16439,6 +17659,8 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr"/>
@@ -16453,6 +17675,8 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr"/>
@@ -16467,6 +17691,8 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr"/>
@@ -16481,6 +17707,8 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr"/>
@@ -16495,6 +17723,8 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr"/>
@@ -16509,6 +17739,8 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr"/>
@@ -16523,6 +17755,8 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr"/>
@@ -16537,6 +17771,8 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr"/>
@@ -16551,6 +17787,8 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr"/>
@@ -16565,6 +17803,8 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr"/>
@@ -16579,6 +17819,8 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr"/>
@@ -16593,6 +17835,8 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr"/>
@@ -16607,6 +17851,8 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr"/>
@@ -16621,6 +17867,8 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr"/>
@@ -16635,6 +17883,8 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr"/>
@@ -16649,6 +17899,8 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr"/>
@@ -16663,6 +17915,8 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr"/>
@@ -16677,6 +17931,8 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr"/>
@@ -16691,6 +17947,8 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr"/>
@@ -16705,6 +17963,8 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr"/>
@@ -16719,6 +17979,8 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr"/>
@@ -16733,6 +17995,8 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr"/>
@@ -16747,6 +18011,8 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr"/>
@@ -16761,6 +18027,8 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr"/>
@@ -16775,6 +18043,8 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr"/>
@@ -16789,6 +18059,8 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr"/>
@@ -16803,6 +18075,8 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr"/>
@@ -16817,6 +18091,8 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr"/>
@@ -16831,6 +18107,8 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr"/>
@@ -16845,6 +18123,8 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr"/>
@@ -16859,6 +18139,8 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr"/>
@@ -16873,6 +18155,8 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr"/>
@@ -16887,6 +18171,8 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr"/>
@@ -16901,6 +18187,8 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr"/>
@@ -16915,6 +18203,8 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr"/>
@@ -16929,6 +18219,8 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr"/>
@@ -16943,6 +18235,8 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr"/>
@@ -16957,6 +18251,8 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr"/>
@@ -16971,6 +18267,8 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr"/>
@@ -16985,6 +18283,8 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr"/>
@@ -16999,6 +18299,8 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr"/>
@@ -17013,6 +18315,8 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr"/>
@@ -17027,6 +18331,8 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr"/>
@@ -17041,6 +18347,8 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr"/>
@@ -17055,6 +18363,8 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr"/>
@@ -17069,6 +18379,8 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr"/>
@@ -17083,6 +18395,8 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr"/>
@@ -17097,6 +18411,8 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr"/>
@@ -17111,6 +18427,8 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr"/>
@@ -17125,6 +18443,8 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr"/>
@@ -17139,6 +18459,8 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr"/>
@@ -17153,6 +18475,8 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr"/>
@@ -17167,6 +18491,8 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr"/>
@@ -17181,6 +18507,8 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr"/>
@@ -17195,6 +18523,8 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr"/>
@@ -17209,6 +18539,8 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr"/>
@@ -17223,6 +18555,8 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr"/>
@@ -17237,6 +18571,8 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr"/>
@@ -17251,6 +18587,8 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr"/>
@@ -17265,6 +18603,8 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr"/>
@@ -17279,6 +18619,8 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr"/>
@@ -17293,6 +18635,8 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr"/>
@@ -17307,6 +18651,8 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr"/>
@@ -17321,6 +18667,8 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr"/>
@@ -17335,6 +18683,8 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr"/>
@@ -17349,6 +18699,8 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr"/>
@@ -17363,6 +18715,8 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr"/>
@@ -17377,6 +18731,8 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr"/>
@@ -17391,6 +18747,8 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr"/>
@@ -17405,6 +18763,8 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr"/>
@@ -17419,6 +18779,8 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr"/>
@@ -17433,6 +18795,8 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr"/>
       <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr"/>
@@ -17447,6 +18811,8 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr"/>
       <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr"/>
@@ -17461,6 +18827,8 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr"/>
       <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
+      <c r="N433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr"/>
@@ -17475,6 +18843,8 @@
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr"/>
       <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr"/>
@@ -17489,6 +18859,8 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
+      <c r="N435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr"/>
@@ -17503,6 +18875,8 @@
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr"/>
       <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
+      <c r="N436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr"/>
@@ -17517,6 +18891,8 @@
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr"/>
       <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr"/>
@@ -17531,6 +18907,8 @@
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr"/>
       <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr"/>
@@ -17545,6 +18923,8 @@
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr"/>
@@ -17559,6 +18939,8 @@
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr"/>
@@ -17573,6 +18955,8 @@
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr"/>
@@ -17587,6 +18971,8 @@
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr"/>
@@ -17601,6 +18987,8 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr"/>
@@ -17615,6 +19003,8 @@
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr"/>
       <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -17667,6 +19057,8 @@
           <t>苹果</t>
         </is>
       </c>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -17719,6 +19111,8 @@
           <t>芒果</t>
         </is>
       </c>
+      <c r="M446" t="inlineStr"/>
+      <c r="N446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -17771,6 +19165,8 @@
           <t>西瓜</t>
         </is>
       </c>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -17823,6 +19219,8 @@
           <t>菠萝</t>
         </is>
       </c>
+      <c r="M448" t="inlineStr"/>
+      <c r="N448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -17875,6 +19273,8 @@
           <t>草莓</t>
         </is>
       </c>
+      <c r="M449" t="inlineStr"/>
+      <c r="N449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -17927,6 +19327,8 @@
           <t>山竹</t>
         </is>
       </c>
+      <c r="M450" t="inlineStr"/>
+      <c r="N450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -17979,6 +19381,8 @@
           <t>樱桃</t>
         </is>
       </c>
+      <c r="M451" t="inlineStr"/>
+      <c r="N451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -18031,6 +19435,8 @@
           <t>香蕉</t>
         </is>
       </c>
+      <c r="M452" t="inlineStr"/>
+      <c r="N452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -18071,6 +19477,8 @@
           <t>现金</t>
         </is>
       </c>
+      <c r="M453" t="inlineStr"/>
+      <c r="N453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -18111,6 +19519,8 @@
           <t>机场</t>
         </is>
       </c>
+      <c r="M454" t="inlineStr"/>
+      <c r="N454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -18163,6 +19573,8 @@
           <t>酒店</t>
         </is>
       </c>
+      <c r="M455" t="inlineStr"/>
+      <c r="N455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -18215,6 +19627,8 @@
           <t>星期一</t>
         </is>
       </c>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -18267,6 +19681,8 @@
           <t>星期二</t>
         </is>
       </c>
+      <c r="M457" t="inlineStr"/>
+      <c r="N457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -18319,6 +19735,8 @@
           <t>星期三</t>
         </is>
       </c>
+      <c r="M458" t="inlineStr"/>
+      <c r="N458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -18371,6 +19789,8 @@
           <t>星期四</t>
         </is>
       </c>
+      <c r="M459" t="inlineStr"/>
+      <c r="N459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -18423,6 +19843,8 @@
           <t>星期五</t>
         </is>
       </c>
+      <c r="M460" t="inlineStr"/>
+      <c r="N460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -18475,6 +19897,8 @@
           <t>星期六</t>
         </is>
       </c>
+      <c r="M461" t="inlineStr"/>
+      <c r="N461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -18527,6 +19951,8 @@
           <t>星期天</t>
         </is>
       </c>
+      <c r="M462" t="inlineStr"/>
+      <c r="N462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -18579,6 +20005,8 @@
           <t>今天</t>
         </is>
       </c>
+      <c r="M463" t="inlineStr"/>
+      <c r="N463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -18631,6 +20059,8 @@
           <t>明天</t>
         </is>
       </c>
+      <c r="M464" t="inlineStr"/>
+      <c r="N464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -18683,6 +20113,8 @@
           <t>昨天</t>
         </is>
       </c>
+      <c r="M465" t="inlineStr"/>
+      <c r="N465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -18735,6 +20167,8 @@
           <t>上周</t>
         </is>
       </c>
+      <c r="M466" t="inlineStr"/>
+      <c r="N466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -18787,6 +20221,8 @@
           <t>这周</t>
         </is>
       </c>
+      <c r="M467" t="inlineStr"/>
+      <c r="N467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -18839,6 +20275,8 @@
           <t>下周</t>
         </is>
       </c>
+      <c r="M468" t="inlineStr"/>
+      <c r="N468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -18891,6 +20329,8 @@
           <t>去年</t>
         </is>
       </c>
+      <c r="M469" t="inlineStr"/>
+      <c r="N469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -18943,6 +20383,8 @@
           <t>今年</t>
         </is>
       </c>
+      <c r="M470" t="inlineStr"/>
+      <c r="N470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -18995,6 +20437,8 @@
           <t>明年</t>
         </is>
       </c>
+      <c r="M471" t="inlineStr"/>
+      <c r="N471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -19047,6 +20491,8 @@
           <t>前天</t>
         </is>
       </c>
+      <c r="M472" t="inlineStr"/>
+      <c r="N472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -19099,6 +20545,8 @@
           <t>后天</t>
         </is>
       </c>
+      <c r="M473" t="inlineStr"/>
+      <c r="N473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -19151,6 +20599,8 @@
           <t>上个月</t>
         </is>
       </c>
+      <c r="M474" t="inlineStr"/>
+      <c r="N474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -19203,6 +20653,8 @@
           <t>这个月</t>
         </is>
       </c>
+      <c r="M475" t="inlineStr"/>
+      <c r="N475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -19255,6 +20707,8 @@
           <t>下个月</t>
         </is>
       </c>
+      <c r="M476" t="inlineStr"/>
+      <c r="N476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -19307,6 +20761,8 @@
           <t>每天</t>
         </is>
       </c>
+      <c r="M477" t="inlineStr"/>
+      <c r="N477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -19359,6 +20815,8 @@
           <t>妈妈</t>
         </is>
       </c>
+      <c r="M478" t="inlineStr"/>
+      <c r="N478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -19411,6 +20869,8 @@
           <t>爸爸</t>
         </is>
       </c>
+      <c r="M479" t="inlineStr"/>
+      <c r="N479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -19463,6 +20923,8 @@
           <t>哥哥</t>
         </is>
       </c>
+      <c r="M480" t="inlineStr"/>
+      <c r="N480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -19515,6 +20977,8 @@
           <t>姐姐</t>
         </is>
       </c>
+      <c r="M481" t="inlineStr"/>
+      <c r="N481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -19567,6 +21031,8 @@
           <t>弟弟</t>
         </is>
       </c>
+      <c r="M482" t="inlineStr"/>
+      <c r="N482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -19619,6 +21085,8 @@
           <t>妹妹</t>
         </is>
       </c>
+      <c r="M483" t="inlineStr"/>
+      <c r="N483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -19671,6 +21139,8 @@
           <t>爷爷</t>
         </is>
       </c>
+      <c r="M484" t="inlineStr"/>
+      <c r="N484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -19723,6 +21193,8 @@
           <t>奶奶</t>
         </is>
       </c>
+      <c r="M485" t="inlineStr"/>
+      <c r="N485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -19775,6 +21247,8 @@
           <t>孩子</t>
         </is>
       </c>
+      <c r="M486" t="inlineStr"/>
+      <c r="N486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -19827,6 +21301,8 @@
           <t>鸟</t>
         </is>
       </c>
+      <c r="M487" t="inlineStr"/>
+      <c r="N487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -19879,6 +21355,8 @@
           <t>鱼</t>
         </is>
       </c>
+      <c r="M488" t="inlineStr"/>
+      <c r="N488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -19931,6 +21409,8 @@
           <t>马</t>
         </is>
       </c>
+      <c r="M489" t="inlineStr"/>
+      <c r="N489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -19983,6 +21463,8 @@
           <t>兔子</t>
         </is>
       </c>
+      <c r="M490" t="inlineStr"/>
+      <c r="N490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -20035,6 +21517,8 @@
           <t>老虎</t>
         </is>
       </c>
+      <c r="M491" t="inlineStr"/>
+      <c r="N491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -20087,6 +21571,8 @@
           <t>熊猫</t>
         </is>
       </c>
+      <c r="M492" t="inlineStr"/>
+      <c r="N492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -20139,6 +21625,8 @@
           <t>狮子</t>
         </is>
       </c>
+      <c r="M493" t="inlineStr"/>
+      <c r="N493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -20191,6 +21679,8 @@
           <t>老鼠</t>
         </is>
       </c>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -20243,6 +21733,8 @@
           <t>葡萄</t>
         </is>
       </c>
+      <c r="M495" t="inlineStr"/>
+      <c r="N495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -20295,6 +21787,8 @@
           <t>桃子</t>
         </is>
       </c>
+      <c r="M496" t="inlineStr"/>
+      <c r="N496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -20347,6 +21841,8 @@
           <t>橙子</t>
         </is>
       </c>
+      <c r="M497" t="inlineStr"/>
+      <c r="N497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -20399,6 +21895,8 @@
           <t>柠檬</t>
         </is>
       </c>
+      <c r="M498" t="inlineStr"/>
+      <c r="N498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -20451,6 +21949,8 @@
           <t>蓝莓</t>
         </is>
       </c>
+      <c r="M499" t="inlineStr"/>
+      <c r="N499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -20503,6 +22003,8 @@
           <t>哈密瓜</t>
         </is>
       </c>
+      <c r="M500" t="inlineStr"/>
+      <c r="N500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -20555,6 +22057,8 @@
           <t>梨</t>
         </is>
       </c>
+      <c r="M501" t="inlineStr"/>
+      <c r="N501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -20607,6 +22111,8 @@
           <t>猕猴桃</t>
         </is>
       </c>
+      <c r="M502" t="inlineStr"/>
+      <c r="N502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -20659,6 +22165,8 @@
           <t>榴莲</t>
         </is>
       </c>
+      <c r="M503" t="inlineStr"/>
+      <c r="N503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -20711,6 +22219,8 @@
           <t>火龙果</t>
         </is>
       </c>
+      <c r="M504" t="inlineStr"/>
+      <c r="N504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -20763,6 +22273,8 @@
           <t>百香果</t>
         </is>
       </c>
+      <c r="M505" t="inlineStr"/>
+      <c r="N505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -20815,6 +22327,8 @@
           <t>树莓</t>
         </is>
       </c>
+      <c r="M506" t="inlineStr"/>
+      <c r="N506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -20867,6 +22381,8 @@
           <t>蔓越莓</t>
         </is>
       </c>
+      <c r="M507" t="inlineStr"/>
+      <c r="N507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -20919,6 +22435,8 @@
           <t>黑莓</t>
         </is>
       </c>
+      <c r="M508" t="inlineStr"/>
+      <c r="N508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -20971,6 +22489,8 @@
           <t>木瓜</t>
         </is>
       </c>
+      <c r="M509" t="inlineStr"/>
+      <c r="N509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -21023,6 +22543,8 @@
           <t>香瓜</t>
         </is>
       </c>
+      <c r="M510" t="inlineStr"/>
+      <c r="N510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -21075,6 +22597,8 @@
           <t>橘子</t>
         </is>
       </c>
+      <c r="M511" t="inlineStr"/>
+      <c r="N511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -21127,6 +22651,8 @@
           <t>李子</t>
         </is>
       </c>
+      <c r="M512" t="inlineStr"/>
+      <c r="N512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -21179,6 +22705,8 @@
           <t>栗子</t>
         </is>
       </c>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -21231,6 +22759,8 @@
           <t>椰子</t>
         </is>
       </c>
+      <c r="M514" t="inlineStr"/>
+      <c r="N514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -21283,6 +22813,8 @@
           <t>老公</t>
         </is>
       </c>
+      <c r="M515" t="inlineStr"/>
+      <c r="N515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -21335,6 +22867,8 @@
           <t>老婆</t>
         </is>
       </c>
+      <c r="M516" t="inlineStr"/>
+      <c r="N516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -21387,6 +22921,8 @@
           <t>老人</t>
         </is>
       </c>
+      <c r="M517" t="inlineStr"/>
+      <c r="N517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -21439,6 +22975,8 @@
           <t>老外</t>
         </is>
       </c>
+      <c r="M518" t="inlineStr"/>
+      <c r="N518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -21491,6 +23029,8 @@
           <t>老样子</t>
         </is>
       </c>
+      <c r="M519" t="inlineStr"/>
+      <c r="N519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -21543,6 +23083,8 @@
           <t>老朋友</t>
         </is>
       </c>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -21595,6 +23137,8 @@
           <t>老家</t>
         </is>
       </c>
+      <c r="M521" t="inlineStr"/>
+      <c r="N521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -21647,6 +23191,8 @@
           <t>老百姓</t>
         </is>
       </c>
+      <c r="M522" t="inlineStr"/>
+      <c r="N522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -21691,6 +23237,8 @@
       </c>
       <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
+      <c r="N523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -21743,6 +23291,8 @@
           <t>博物馆</t>
         </is>
       </c>
+      <c r="M524" t="inlineStr"/>
+      <c r="N524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -21795,6 +23345,8 @@
           <t>美术馆</t>
         </is>
       </c>
+      <c r="M525" t="inlineStr"/>
+      <c r="N525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -21847,6 +23399,8 @@
           <t>科学馆</t>
         </is>
       </c>
+      <c r="M526" t="inlineStr"/>
+      <c r="N526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -21899,6 +23453,8 @@
           <t>宾馆</t>
         </is>
       </c>
+      <c r="M527" t="inlineStr"/>
+      <c r="N527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -21951,6 +23507,8 @@
           <t>大使馆</t>
         </is>
       </c>
+      <c r="M528" t="inlineStr"/>
+      <c r="N528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -22003,6 +23561,8 @@
           <t>图书馆</t>
         </is>
       </c>
+      <c r="M529" t="inlineStr"/>
+      <c r="N529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -22055,6 +23615,8 @@
           <t>体育馆</t>
         </is>
       </c>
+      <c r="M530" t="inlineStr"/>
+      <c r="N530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -22107,6 +23669,8 @@
           <t>电视</t>
         </is>
       </c>
+      <c r="M531" t="inlineStr"/>
+      <c r="N531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -22159,6 +23723,8 @@
           <t>电冰箱</t>
         </is>
       </c>
+      <c r="M532" t="inlineStr"/>
+      <c r="N532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -22211,6 +23777,8 @@
           <t>电风扇</t>
         </is>
       </c>
+      <c r="M533" t="inlineStr"/>
+      <c r="N533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -22263,6 +23831,8 @@
           <t>电池</t>
         </is>
       </c>
+      <c r="M534" t="inlineStr"/>
+      <c r="N534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -22315,6 +23885,8 @@
           <t>电饭煲</t>
         </is>
       </c>
+      <c r="M535" t="inlineStr"/>
+      <c r="N535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -22367,6 +23939,8 @@
           <t>电热水壶</t>
         </is>
       </c>
+      <c r="M536" t="inlineStr"/>
+      <c r="N536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -22419,6 +23993,8 @@
           <t>电动车</t>
         </is>
       </c>
+      <c r="M537" t="inlineStr"/>
+      <c r="N537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -22471,6 +24047,8 @@
           <t>饭馆</t>
         </is>
       </c>
+      <c r="M538" t="inlineStr"/>
+      <c r="N538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -22523,6 +24101,8 @@
           <t>电脑</t>
         </is>
       </c>
+      <c r="M539" t="inlineStr"/>
+      <c r="N539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -22575,6 +24155,8 @@
           <t>电话</t>
         </is>
       </c>
+      <c r="M540" t="inlineStr"/>
+      <c r="N540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -22627,6 +24209,8 @@
           <t>电</t>
         </is>
       </c>
+      <c r="M541" t="inlineStr"/>
+      <c r="N541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -22679,6 +24263,8 @@
           <t>馆</t>
         </is>
       </c>
+      <c r="M542" t="inlineStr"/>
+      <c r="N542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -22731,6 +24317,12 @@
           <t>电灯</t>
         </is>
       </c>
+      <c r="M543" t="n">
+        <v>20090</v>
+      </c>
+      <c r="N543" t="n">
+        <v>20203</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -22783,6 +24375,8 @@
           <t>电梯</t>
         </is>
       </c>
+      <c r="M544" t="inlineStr"/>
+      <c r="N544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -22835,6 +24429,8 @@
           <t>商店</t>
         </is>
       </c>
+      <c r="M545" t="inlineStr"/>
+      <c r="N545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -22887,6 +24483,8 @@
           <t>饭店</t>
         </is>
       </c>
+      <c r="M546" t="inlineStr"/>
+      <c r="N546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -22939,6 +24537,12 @@
           <t>书店</t>
         </is>
       </c>
+      <c r="M547" t="n">
+        <v>20102</v>
+      </c>
+      <c r="N547" t="n">
+        <v>20167</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -22991,6 +24595,8 @@
           <t>花店</t>
         </is>
       </c>
+      <c r="M548" t="inlineStr"/>
+      <c r="N548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -23043,6 +24649,8 @@
           <t>便利店</t>
         </is>
       </c>
+      <c r="M549" t="inlineStr"/>
+      <c r="N549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -23095,6 +24703,8 @@
           <t>药店</t>
         </is>
       </c>
+      <c r="M550" t="inlineStr"/>
+      <c r="N550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -23147,6 +24757,8 @@
           <t>服装店</t>
         </is>
       </c>
+      <c r="M551" t="inlineStr"/>
+      <c r="N551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -23199,6 +24811,8 @@
           <t>眼镜店</t>
         </is>
       </c>
+      <c r="M552" t="inlineStr"/>
+      <c r="N552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -23247,6 +24861,8 @@
           <t>店</t>
         </is>
       </c>
+      <c r="M553" t="inlineStr"/>
+      <c r="N553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -23299,6 +24915,8 @@
           <t>飞机</t>
         </is>
       </c>
+      <c r="M554" t="inlineStr"/>
+      <c r="N554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -23351,6 +24969,8 @@
           <t>出租车</t>
         </is>
       </c>
+      <c r="M555" t="inlineStr"/>
+      <c r="N555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -23403,6 +25023,8 @@
           <t>公交车</t>
         </is>
       </c>
+      <c r="M556" t="inlineStr"/>
+      <c r="N556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -23455,6 +25077,8 @@
           <t>自行车</t>
         </is>
       </c>
+      <c r="M557" t="inlineStr"/>
+      <c r="N557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -23507,6 +25131,8 @@
           <t>火车</t>
         </is>
       </c>
+      <c r="M558" t="inlineStr"/>
+      <c r="N558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -23559,6 +25185,8 @@
           <t>地铁</t>
         </is>
       </c>
+      <c r="M559" t="inlineStr"/>
+      <c r="N559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -23611,6 +25239,8 @@
           <t>船</t>
         </is>
       </c>
+      <c r="M560" t="inlineStr"/>
+      <c r="N560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -23663,6 +25293,8 @@
           <t>摩托车</t>
         </is>
       </c>
+      <c r="M561" t="inlineStr"/>
+      <c r="N561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -23715,6 +25347,8 @@
           <t>高铁</t>
         </is>
       </c>
+      <c r="M562" t="inlineStr"/>
+      <c r="N562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -23767,6 +25401,8 @@
           <t>共享单车</t>
         </is>
       </c>
+      <c r="M563" t="inlineStr"/>
+      <c r="N563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -23819,6 +25455,8 @@
           <t>步行</t>
         </is>
       </c>
+      <c r="M564" t="inlineStr"/>
+      <c r="N564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -23871,6 +25509,8 @@
           <t>足球</t>
         </is>
       </c>
+      <c r="M565" t="inlineStr"/>
+      <c r="N565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -23923,6 +25563,8 @@
           <t>篮球</t>
         </is>
       </c>
+      <c r="M566" t="inlineStr"/>
+      <c r="N566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -23975,6 +25617,8 @@
           <t>棒球</t>
         </is>
       </c>
+      <c r="M567" t="inlineStr"/>
+      <c r="N567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -24027,6 +25671,8 @@
           <t>排球</t>
         </is>
       </c>
+      <c r="M568" t="inlineStr"/>
+      <c r="N568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -24079,6 +25725,8 @@
           <t>乒乓球</t>
         </is>
       </c>
+      <c r="M569" t="inlineStr"/>
+      <c r="N569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -24131,6 +25779,8 @@
           <t>击剑</t>
         </is>
       </c>
+      <c r="M570" t="inlineStr"/>
+      <c r="N570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -24183,6 +25833,8 @@
           <t>网球</t>
         </is>
       </c>
+      <c r="M571" t="inlineStr"/>
+      <c r="N571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -24235,6 +25887,8 @@
           <t>羽毛球</t>
         </is>
       </c>
+      <c r="M572" t="inlineStr"/>
+      <c r="N572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -24287,6 +25941,8 @@
           <t>高尔夫球</t>
         </is>
       </c>
+      <c r="M573" t="inlineStr"/>
+      <c r="N573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -24339,6 +25995,8 @@
           <t>游泳</t>
         </is>
       </c>
+      <c r="M574" t="inlineStr"/>
+      <c r="N574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -24391,6 +26049,8 @@
           <t>跑步</t>
         </is>
       </c>
+      <c r="M575" t="inlineStr"/>
+      <c r="N575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -24443,6 +26103,8 @@
           <t>射箭</t>
         </is>
       </c>
+      <c r="M576" t="inlineStr"/>
+      <c r="N576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -24495,6 +26157,8 @@
           <t>举重</t>
         </is>
       </c>
+      <c r="M577" t="inlineStr"/>
+      <c r="N577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -24547,6 +26211,8 @@
           <t>跆拳道</t>
         </is>
       </c>
+      <c r="M578" t="inlineStr"/>
+      <c r="N578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -24599,6 +26265,8 @@
           <t>滑雪</t>
         </is>
       </c>
+      <c r="M579" t="inlineStr"/>
+      <c r="N579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -24651,6 +26319,8 @@
           <t>健身</t>
         </is>
       </c>
+      <c r="M580" t="inlineStr"/>
+      <c r="N580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -24703,6 +26373,8 @@
           <t>床</t>
         </is>
       </c>
+      <c r="M581" t="inlineStr"/>
+      <c r="N581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -24755,6 +26427,8 @@
           <t>书桌</t>
         </is>
       </c>
+      <c r="M582" t="inlineStr"/>
+      <c r="N582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -24807,6 +26481,8 @@
           <t>椅子</t>
         </is>
       </c>
+      <c r="M583" t="inlineStr"/>
+      <c r="N583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -24859,6 +26535,8 @@
           <t>衣柜</t>
         </is>
       </c>
+      <c r="M584" t="inlineStr"/>
+      <c r="N584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -24911,6 +26589,8 @@
           <t>镜子</t>
         </is>
       </c>
+      <c r="M585" t="inlineStr"/>
+      <c r="N585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -24963,6 +26643,8 @@
           <t>空调</t>
         </is>
       </c>
+      <c r="M586" t="inlineStr"/>
+      <c r="N586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -25015,6 +26697,8 @@
           <t>冰箱</t>
         </is>
       </c>
+      <c r="M587" t="inlineStr"/>
+      <c r="N587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -25067,6 +26751,8 @@
           <t>钟表</t>
         </is>
       </c>
+      <c r="M588" t="inlineStr"/>
+      <c r="N588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -25119,6 +26805,8 @@
           <t>灯</t>
         </is>
       </c>
+      <c r="M589" t="inlineStr"/>
+      <c r="N589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -25171,6 +26859,8 @@
           <t>门</t>
         </is>
       </c>
+      <c r="M590" t="inlineStr"/>
+      <c r="N590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -25223,6 +26913,8 @@
           <t>窗户</t>
         </is>
       </c>
+      <c r="M591" t="inlineStr"/>
+      <c r="N591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -25275,6 +26967,8 @@
           <t>枕头</t>
         </is>
       </c>
+      <c r="M592" t="inlineStr"/>
+      <c r="N592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -25327,6 +27021,8 @@
           <t>被子</t>
         </is>
       </c>
+      <c r="M593" t="inlineStr"/>
+      <c r="N593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -25379,6 +27075,8 @@
           <t>热水</t>
         </is>
       </c>
+      <c r="M594" t="inlineStr"/>
+      <c r="N594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -25431,6 +27129,8 @@
           <t>咖啡</t>
         </is>
       </c>
+      <c r="M595" t="inlineStr"/>
+      <c r="N595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -25483,6 +27183,8 @@
           <t>美式咖啡</t>
         </is>
       </c>
+      <c r="M596" t="inlineStr"/>
+      <c r="N596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -25535,6 +27237,8 @@
           <t>拿铁</t>
         </is>
       </c>
+      <c r="M597" t="inlineStr"/>
+      <c r="N597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -25587,6 +27291,8 @@
           <t>茶</t>
         </is>
       </c>
+      <c r="M598" t="inlineStr"/>
+      <c r="N598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -25639,6 +27345,8 @@
           <t>绿茶</t>
         </is>
       </c>
+      <c r="M599" t="inlineStr"/>
+      <c r="N599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -25691,6 +27399,8 @@
           <t>红茶</t>
         </is>
       </c>
+      <c r="M600" t="inlineStr"/>
+      <c r="N600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -25743,6 +27453,8 @@
           <t>奶茶</t>
         </is>
       </c>
+      <c r="M601" t="inlineStr"/>
+      <c r="N601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -25795,6 +27507,8 @@
           <t>果汁</t>
         </is>
       </c>
+      <c r="M602" t="inlineStr"/>
+      <c r="N602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -25847,6 +27561,8 @@
           <t>牛奶</t>
         </is>
       </c>
+      <c r="M603" t="inlineStr"/>
+      <c r="N603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -25899,6 +27615,8 @@
           <t>洗衣机</t>
         </is>
       </c>
+      <c r="M604" t="inlineStr"/>
+      <c r="N604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -25951,6 +27669,8 @@
           <t>出口</t>
         </is>
       </c>
+      <c r="M605" t="inlineStr"/>
+      <c r="N605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -26003,6 +27723,8 @@
           <t>米饭</t>
         </is>
       </c>
+      <c r="M606" t="inlineStr"/>
+      <c r="N606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -26055,6 +27777,8 @@
           <t>炒饭</t>
         </is>
       </c>
+      <c r="M607" t="inlineStr"/>
+      <c r="N607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -26107,6 +27831,8 @@
           <t>面条</t>
         </is>
       </c>
+      <c r="M608" t="inlineStr"/>
+      <c r="N608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -26159,6 +27885,8 @@
           <t>炒面</t>
         </is>
       </c>
+      <c r="M609" t="inlineStr"/>
+      <c r="N609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -26211,6 +27939,8 @@
           <t>面包</t>
         </is>
       </c>
+      <c r="M610" t="inlineStr"/>
+      <c r="N610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -26263,6 +27993,8 @@
           <t>三明治</t>
         </is>
       </c>
+      <c r="M611" t="inlineStr"/>
+      <c r="N611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -26315,6 +28047,8 @@
           <t>汤</t>
         </is>
       </c>
+      <c r="M612" t="inlineStr"/>
+      <c r="N612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -26367,6 +28101,8 @@
           <t>蛋花汤</t>
         </is>
       </c>
+      <c r="M613" t="inlineStr"/>
+      <c r="N613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -26419,6 +28155,8 @@
           <t>浓汤</t>
         </is>
       </c>
+      <c r="M614" t="inlineStr"/>
+      <c r="N614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -26471,6 +28209,8 @@
           <t>粥</t>
         </is>
       </c>
+      <c r="M615" t="inlineStr"/>
+      <c r="N615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -26523,6 +28263,8 @@
           <t>包子</t>
         </is>
       </c>
+      <c r="M616" t="inlineStr"/>
+      <c r="N616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -26575,6 +28317,8 @@
           <t>饺子</t>
         </is>
       </c>
+      <c r="M617" t="inlineStr"/>
+      <c r="N617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -26627,6 +28371,8 @@
           <t>馒头</t>
         </is>
       </c>
+      <c r="M618" t="inlineStr"/>
+      <c r="N618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -26679,6 +28425,8 @@
           <t>方便面</t>
         </is>
       </c>
+      <c r="M619" t="inlineStr"/>
+      <c r="N619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -26731,6 +28479,8 @@
           <t>韩国</t>
         </is>
       </c>
+      <c r="M620" t="inlineStr"/>
+      <c r="N620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -26783,6 +28533,8 @@
           <t>朝鲜</t>
         </is>
       </c>
+      <c r="M621" t="inlineStr"/>
+      <c r="N621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -26835,6 +28587,8 @@
           <t>中国</t>
         </is>
       </c>
+      <c r="M622" t="inlineStr"/>
+      <c r="N622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -26887,6 +28641,8 @@
           <t>台湾</t>
         </is>
       </c>
+      <c r="M623" t="inlineStr"/>
+      <c r="N623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -26939,6 +28695,8 @@
           <t>美国</t>
         </is>
       </c>
+      <c r="M624" t="inlineStr"/>
+      <c r="N624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -26991,6 +28749,8 @@
           <t>日本</t>
         </is>
       </c>
+      <c r="M625" t="inlineStr"/>
+      <c r="N625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -27043,6 +28803,8 @@
           <t>英国</t>
         </is>
       </c>
+      <c r="M626" t="inlineStr"/>
+      <c r="N626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -27095,6 +28857,8 @@
           <t>法国</t>
         </is>
       </c>
+      <c r="M627" t="inlineStr"/>
+      <c r="N627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -27147,6 +28911,8 @@
           <t>德国</t>
         </is>
       </c>
+      <c r="M628" t="inlineStr"/>
+      <c r="N628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -27199,6 +28965,8 @@
           <t>俄罗斯</t>
         </is>
       </c>
+      <c r="M629" t="inlineStr"/>
+      <c r="N629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -27251,6 +29019,8 @@
           <t>加拿大</t>
         </is>
       </c>
+      <c r="M630" t="inlineStr"/>
+      <c r="N630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -27303,6 +29073,8 @@
           <t>澳大利亚</t>
         </is>
       </c>
+      <c r="M631" t="inlineStr"/>
+      <c r="N631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -27355,6 +29127,8 @@
           <t>意大利</t>
         </is>
       </c>
+      <c r="M632" t="inlineStr"/>
+      <c r="N632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -27407,6 +29181,8 @@
           <t>西班牙</t>
         </is>
       </c>
+      <c r="M633" t="inlineStr"/>
+      <c r="N633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -27459,6 +29235,8 @@
           <t>泰国</t>
         </is>
       </c>
+      <c r="M634" t="inlineStr"/>
+      <c r="N634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -27511,6 +29289,8 @@
           <t>越南</t>
         </is>
       </c>
+      <c r="M635" t="inlineStr"/>
+      <c r="N635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -27563,6 +29343,8 @@
           <t>印度</t>
         </is>
       </c>
+      <c r="M636" t="inlineStr"/>
+      <c r="N636" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27575,7 +29357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27637,6 +29419,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>sound_path</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
         </is>
       </c>
     </row>
@@ -27655,6 +29447,8 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -27691,6 +29485,8 @@
           <t>地铁站</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -27727,6 +29523,8 @@
           <t>外滩</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -27763,6 +29561,8 @@
           <t>喜茶</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -27799,6 +29599,8 @@
           <t>海底捞</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -27835,6 +29637,8 @@
           <t>瑞幸咖啡</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -27871,6 +29675,8 @@
           <t>东方明珠</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -27907,6 +29713,8 @@
           <t>迪士尼乐园</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -27947,6 +29755,8 @@
           <t>福宝</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -27987,6 +29797,8 @@
           <t>爱宝</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -28027,6 +29839,8 @@
           <t>乐宝</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -28067,6 +29881,8 @@
           <t>睿宝</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -28107,6 +29923,8 @@
           <t>辉宝</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -28147,6 +29965,8 @@
           <t>宝家</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -28187,6 +30007,8 @@
           <t>毛泽东</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -28227,6 +30049,8 @@
           <t>邓小平</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -28267,6 +30091,8 @@
           <t>周恩来</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -28307,6 +30133,8 @@
           <t>邓小平</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -28347,6 +30175,8 @@
           <t>习近平</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -28383,6 +30213,8 @@
           <t>张元英</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -28419,6 +30251,8 @@
           <t>高胤祯</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -28455,6 +30289,8 @@
           <t>李舜臣</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28467,7 +30303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28531,6 +30367,16 @@
           <t>sound_path</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>component1_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>component2_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -28567,6 +30413,8 @@
           <t>太烫了</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -28603,6 +30451,8 @@
           <t>太凉了</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -28639,6 +30489,8 @@
           <t>多放点</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -28675,6 +30527,8 @@
           <t>少放点</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -28711,6 +30565,8 @@
           <t>你好</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -28747,6 +30603,8 @@
           <t>点</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -2402,10 +2402,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="A2" t="n">
+        <v>100000</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2445,10 +2443,8 @@
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>100001</t>
-        </is>
+      <c r="A3" t="n">
+        <v>100001</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2504,10 +2500,8 @@
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>100002</t>
-        </is>
+      <c r="A4" t="n">
+        <v>100002</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2547,10 +2541,8 @@
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>100003</t>
-        </is>
+      <c r="A5" t="n">
+        <v>100003</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2590,10 +2582,8 @@
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>100004</t>
-        </is>
+      <c r="A6" t="n">
+        <v>100004</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2633,10 +2623,8 @@
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>100005</t>
-        </is>
+      <c r="A7" t="n">
+        <v>100005</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2676,10 +2664,8 @@
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>100006</t>
-        </is>
+      <c r="A8" t="n">
+        <v>100006</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2719,10 +2705,8 @@
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>100007</t>
-        </is>
+      <c r="A9" t="n">
+        <v>100007</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2762,10 +2746,8 @@
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>100008</t>
-        </is>
+      <c r="A10" t="n">
+        <v>100008</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2805,10 +2787,8 @@
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>100009</t>
-        </is>
+      <c r="A11" t="n">
+        <v>100009</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2864,10 +2844,8 @@
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>100010</t>
-        </is>
+      <c r="A12" t="n">
+        <v>100010</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2923,10 +2901,8 @@
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>100011</t>
-        </is>
+      <c r="A13" t="n">
+        <v>100011</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2982,10 +2958,8 @@
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>100012</t>
-        </is>
+      <c r="A14" t="n">
+        <v>100012</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3041,10 +3015,8 @@
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>100013</t>
-        </is>
+      <c r="A15" t="n">
+        <v>100013</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3100,10 +3072,8 @@
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>100014</t>
-        </is>
+      <c r="A16" t="n">
+        <v>100014</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3159,10 +3129,8 @@
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>100015</t>
-        </is>
+      <c r="A17" t="n">
+        <v>100015</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3218,10 +3186,8 @@
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>100016</t>
-        </is>
+      <c r="A18" t="n">
+        <v>100016</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3277,10 +3243,8 @@
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>100017</t>
-        </is>
+      <c r="A19" t="n">
+        <v>100017</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3336,10 +3300,8 @@
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>100018</t>
-        </is>
+      <c r="A20" t="n">
+        <v>100018</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3395,10 +3357,8 @@
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>100019</t>
-        </is>
+      <c r="A21" t="n">
+        <v>100019</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3454,10 +3414,8 @@
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>100020</t>
-        </is>
+      <c r="A22" t="n">
+        <v>100020</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3513,10 +3471,8 @@
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>100021</t>
-        </is>
+      <c r="A23" t="n">
+        <v>100021</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3572,10 +3528,8 @@
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>100022</t>
-        </is>
+      <c r="A24" t="n">
+        <v>100022</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3631,10 +3585,8 @@
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>100023</t>
-        </is>
+      <c r="A25" t="n">
+        <v>100023</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3690,10 +3642,8 @@
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>100024</t>
-        </is>
+      <c r="A26" t="n">
+        <v>100024</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3749,10 +3699,8 @@
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>100025</t>
-        </is>
+      <c r="A27" t="n">
+        <v>100025</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3808,10 +3756,8 @@
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>100026</t>
-        </is>
+      <c r="A28" t="n">
+        <v>100026</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3867,10 +3813,8 @@
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>100027</t>
-        </is>
+      <c r="A29" t="n">
+        <v>100027</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3926,10 +3870,8 @@
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>100028</t>
-        </is>
+      <c r="A30" t="n">
+        <v>100028</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3985,10 +3927,8 @@
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>100029</t>
-        </is>
+      <c r="A31" t="n">
+        <v>100029</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4044,10 +3984,8 @@
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>100030</t>
-        </is>
+      <c r="A32" t="n">
+        <v>100030</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4103,10 +4041,8 @@
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>100031</t>
-        </is>
+      <c r="A33" t="n">
+        <v>100031</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4162,10 +4098,8 @@
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>100032</t>
-        </is>
+      <c r="A34" t="n">
+        <v>100032</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4221,10 +4155,8 @@
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>100033</t>
-        </is>
+      <c r="A35" t="n">
+        <v>100033</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4280,10 +4212,8 @@
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>100034</t>
-        </is>
+      <c r="A36" t="n">
+        <v>100034</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4339,10 +4269,8 @@
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>100035</t>
-        </is>
+      <c r="A37" t="n">
+        <v>100035</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4398,10 +4326,8 @@
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>100036</t>
-        </is>
+      <c r="A38" t="n">
+        <v>100036</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4457,10 +4383,8 @@
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>100037</t>
-        </is>
+      <c r="A39" t="n">
+        <v>100037</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -11090,7 +11014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q672"/>
+  <dimension ref="A1:Q675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26825,8 +26749,16 @@
           <t>电池</t>
         </is>
       </c>
-      <c r="M534" t="inlineStr"/>
-      <c r="N534" t="inlineStr"/>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>20090</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>20550</t>
+        </is>
+      </c>
       <c r="O534" t="inlineStr"/>
       <c r="P534" t="inlineStr"/>
       <c r="Q534" t="inlineStr"/>
@@ -27195,8 +27127,16 @@
           <t>电话</t>
         </is>
       </c>
-      <c r="M540" t="inlineStr"/>
-      <c r="N540" t="inlineStr"/>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>20090</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>20549</t>
+        </is>
+      </c>
       <c r="O540" t="inlineStr"/>
       <c r="P540" t="inlineStr"/>
       <c r="Q540" t="inlineStr"/>
@@ -34262,8 +34202,16 @@
       <c r="J661" t="inlineStr"/>
       <c r="K661" t="inlineStr"/>
       <c r="L661" t="inlineStr"/>
-      <c r="M661" t="inlineStr"/>
-      <c r="N661" t="inlineStr"/>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>20090</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>20548</t>
+        </is>
+      </c>
       <c r="O661" t="inlineStr"/>
       <c r="P661" t="inlineStr"/>
       <c r="Q661" t="inlineStr"/>
@@ -34868,6 +34816,147 @@
       <c r="O672" t="inlineStr"/>
       <c r="P672" t="inlineStr"/>
       <c r="Q672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>20548</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>影</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>yǐng</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr"/>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>전자제품</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>그림자</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>shadow</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr"/>
+      <c r="J673" t="inlineStr"/>
+      <c r="K673" t="inlineStr"/>
+      <c r="L673" t="inlineStr"/>
+      <c r="M673" t="inlineStr"/>
+      <c r="N673" t="inlineStr"/>
+      <c r="O673" t="inlineStr"/>
+      <c r="P673" t="inlineStr"/>
+      <c r="Q673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>20549</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>话</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>huà</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr"/>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>전자제품</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>말씀/이야기</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>speech, words</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr"/>
+      <c r="J674" t="inlineStr"/>
+      <c r="K674" t="inlineStr"/>
+      <c r="L674" t="inlineStr"/>
+      <c r="M674" t="inlineStr"/>
+      <c r="N674" t="inlineStr"/>
+      <c r="O674" t="inlineStr"/>
+      <c r="P674" t="inlineStr"/>
+      <c r="Q674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>20550</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>池</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>chí</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>전자제품</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>연못</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>pond</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr"/>
+      <c r="J675" t="inlineStr"/>
+      <c r="K675" t="inlineStr"/>
+      <c r="L675" t="inlineStr"/>
+      <c r="M675" t="inlineStr"/>
+      <c r="N675" t="inlineStr"/>
+      <c r="O675" t="inlineStr"/>
+      <c r="P675" t="inlineStr"/>
+      <c r="Q675" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resource/table/words.xlsx
+++ b/resource/table/words.xlsx
@@ -11219,10 +11219,8 @@
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="A8" t="n">
+        <v>20000</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -11262,10 +11260,8 @@
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20001</t>
-        </is>
+      <c r="A9" t="n">
+        <v>20001</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -11305,10 +11301,8 @@
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>20002</t>
-        </is>
+      <c r="A10" t="n">
+        <v>20002</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -11348,10 +11342,8 @@
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>20003</t>
-        </is>
+      <c r="A11" t="n">
+        <v>20003</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -11391,10 +11383,8 @@
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20004</t>
-        </is>
+      <c r="A12" t="n">
+        <v>20004</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -11434,10 +11424,8 @@
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20005</t>
-        </is>
+      <c r="A13" t="n">
+        <v>20005</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -11477,10 +11465,8 @@
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20006</t>
-        </is>
+      <c r="A14" t="n">
+        <v>20006</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -11520,10 +11506,8 @@
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>20007</t>
-        </is>
+      <c r="A15" t="n">
+        <v>20007</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -11563,10 +11547,8 @@
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>20008</t>
-        </is>
+      <c r="A16" t="n">
+        <v>20008</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -11606,10 +11588,8 @@
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20009</t>
-        </is>
+      <c r="A17" t="n">
+        <v>20009</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -11649,10 +11629,8 @@
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20010</t>
-        </is>
+      <c r="A18" t="n">
+        <v>20010</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -11708,10 +11686,8 @@
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>20011</t>
-        </is>
+      <c r="A19" t="n">
+        <v>20011</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -11751,10 +11727,8 @@
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20012</t>
-        </is>
+      <c r="A20" t="n">
+        <v>20012</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -11794,10 +11768,8 @@
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20013</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -11837,10 +11809,8 @@
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20014</t>
-        </is>
+      <c r="A22" t="n">
+        <v>20014</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -11880,10 +11850,8 @@
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20015</t>
-        </is>
+      <c r="A23" t="n">
+        <v>20015</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -11923,10 +11891,8 @@
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20016</t>
-        </is>
+      <c r="A24" t="n">
+        <v>20016</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -11966,10 +11932,8 @@
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20017</t>
-        </is>
+      <c r="A25" t="n">
+        <v>20017</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -12009,10 +11973,8 @@
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20018</t>
-        </is>
+      <c r="A26" t="n">
+        <v>20018</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -12353,10 +12315,8 @@
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>20099</t>
-        </is>
+      <c r="A42" t="n">
+        <v>20099</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -12396,10 +12356,8 @@
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>20100</t>
-        </is>
+      <c r="A43" t="n">
+        <v>20100</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -12439,10 +12397,8 @@
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>20101</t>
-        </is>
+      <c r="A44" t="n">
+        <v>20101</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -12501,10 +12457,8 @@
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>20102</t>
-        </is>
+      <c r="A46" t="n">
+        <v>20102</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -12560,10 +12514,8 @@
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>20103</t>
-        </is>
+      <c r="A47" t="n">
+        <v>20103</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -12615,10 +12567,8 @@
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>20104</t>
-        </is>
+      <c r="A48" t="n">
+        <v>20104</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -12670,10 +12620,8 @@
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>20105</t>
-        </is>
+      <c r="A49" t="n">
+        <v>20105</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -12725,10 +12673,8 @@
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>20106</t>
-        </is>
+      <c r="A50" t="n">
+        <v>20106</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -12776,10 +12722,8 @@
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>20107</t>
-        </is>
+      <c r="A51" t="n">
+        <v>20107</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -12827,10 +12771,8 @@
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>20108</t>
-        </is>
+      <c r="A52" t="n">
+        <v>20108</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -12878,10 +12820,8 @@
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>20109</t>
-        </is>
+      <c r="A53" t="n">
+        <v>20109</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -12929,10 +12869,8 @@
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>20110</t>
-        </is>
+      <c r="A54" t="n">
+        <v>20110</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -12972,10 +12910,8 @@
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>20111</t>
-        </is>
+      <c r="A55" t="n">
+        <v>20111</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -13015,10 +12951,8 @@
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>20112</t>
-        </is>
+      <c r="A56" t="n">
+        <v>20112</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -13058,10 +12992,8 @@
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>20113</t>
-        </is>
+      <c r="A57" t="n">
+        <v>20113</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -13101,10 +13033,8 @@
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>20114</t>
-        </is>
+      <c r="A58" t="n">
+        <v>20114</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -13144,10 +13074,8 @@
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>20115</t>
-        </is>
+      <c r="A59" t="n">
+        <v>20115</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -13187,10 +13115,8 @@
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>20116</t>
-        </is>
+      <c r="A60" t="n">
+        <v>20116</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -13230,10 +13156,8 @@
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>20117</t>
-        </is>
+      <c r="A61" t="n">
+        <v>20117</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -13277,10 +13201,8 @@
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>20118</t>
-        </is>
+      <c r="A62" t="n">
+        <v>20118</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -13324,10 +13246,8 @@
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20119</t>
-        </is>
+      <c r="A63" t="n">
+        <v>20119</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -13367,10 +13287,8 @@
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>20120</t>
-        </is>
+      <c r="A64" t="n">
+        <v>20120</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -13410,10 +13328,8 @@
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20121</t>
-        </is>
+      <c r="A65" t="n">
+        <v>20121</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -13469,10 +13385,8 @@
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20122</t>
-        </is>
+      <c r="A66" t="n">
+        <v>20122</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -13521,15 +13435,11 @@
           <t>冰水</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>100008</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>20121</t>
-        </is>
+      <c r="M66" t="n">
+        <v>100008</v>
+      </c>
+      <c r="N66" t="n">
+        <v>20121</v>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -13544,10 +13454,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>20123</t>
-        </is>
+      <c r="A67" t="n">
+        <v>20123</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -13587,10 +13495,8 @@
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>20124</t>
-        </is>
+      <c r="A68" t="n">
+        <v>20124</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -13630,10 +13536,8 @@
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>20125</t>
-        </is>
+      <c r="A69" t="n">
+        <v>20125</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -13673,10 +13577,8 @@
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>20126</t>
-        </is>
+      <c r="A70" t="n">
+        <v>20126</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -13716,10 +13618,8 @@
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>20127</t>
-        </is>
+      <c r="A71" t="n">
+        <v>20127</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -13759,10 +13659,8 @@
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>20128</t>
-        </is>
+      <c r="A72" t="n">
+        <v>20128</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -13802,10 +13700,8 @@
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>20129</t>
-        </is>
+      <c r="A73" t="n">
+        <v>20129</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -13849,10 +13745,8 @@
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>20130</t>
-        </is>
+      <c r="A74" t="n">
+        <v>20130</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -13896,10 +13790,8 @@
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>20131</t>
-        </is>
+      <c r="A75" t="n">
+        <v>20131</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -13939,10 +13831,8 @@
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>20132</t>
-        </is>
+      <c r="A76" t="n">
+        <v>20132</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -13982,10 +13872,8 @@
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>20133</t>
-        </is>
+      <c r="A77" t="n">
+        <v>20133</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -14025,10 +13913,8 @@
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>20134</t>
-        </is>
+      <c r="A78" t="n">
+        <v>20134</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -14068,10 +13954,8 @@
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>20135</t>
-        </is>
+      <c r="A79" t="n">
+        <v>20135</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -14111,10 +13995,8 @@
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>20136</t>
-        </is>
+      <c r="A80" t="n">
+        <v>20136</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -14154,10 +14036,8 @@
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>20137</t>
-        </is>
+      <c r="A81" t="n">
+        <v>20137</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -14197,10 +14077,8 @@
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>20138</t>
-        </is>
+      <c r="A82" t="n">
+        <v>20138</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -14240,10 +14118,8 @@
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>20139</t>
-        </is>
+      <c r="A83" t="n">
+        <v>20139</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -14283,10 +14159,8 @@
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>20140</t>
-        </is>
+      <c r="A84" t="n">
+        <v>20140</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -14326,10 +14200,8 @@
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>20141</t>
-        </is>
+      <c r="A85" t="n">
+        <v>20141</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -14369,10 +14241,8 @@
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>20142</t>
-        </is>
+      <c r="A86" t="n">
+        <v>20142</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -14412,10 +14282,8 @@
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>20143</t>
-        </is>
+      <c r="A87" t="n">
+        <v>20143</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -14455,10 +14323,8 @@
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>20144</t>
-        </is>
+      <c r="A88" t="n">
+        <v>20144</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -14498,10 +14364,8 @@
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>20145</t>
-        </is>
+      <c r="A89" t="n">
+        <v>20145</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -14541,10 +14405,8 @@
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>20146</t>
-        </is>
+      <c r="A90" t="n">
+        <v>20146</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -14641,10 +14503,8 @@
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>20150</t>
-        </is>
+      <c r="A94" t="n">
+        <v>20150</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -14700,10 +14560,8 @@
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>20151</t>
-        </is>
+      <c r="A95" t="n">
+        <v>20151</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -14759,10 +14617,8 @@
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>20152</t>
-        </is>
+      <c r="A96" t="n">
+        <v>20152</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -21430,10 +21286,8 @@
       <c r="Q444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>20501</t>
-        </is>
+      <c r="A445" t="n">
+        <v>20501</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -21489,10 +21343,8 @@
       <c r="Q445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>20502</t>
-        </is>
+      <c r="A446" t="n">
+        <v>20502</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -21548,10 +21400,8 @@
       <c r="Q446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>20503</t>
-        </is>
+      <c r="A447" t="n">
+        <v>20503</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -21607,10 +21457,8 @@
       <c r="Q447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>20504</t>
-        </is>
+      <c r="A448" t="n">
+        <v>20504</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -21666,10 +21514,8 @@
       <c r="Q448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>20505</t>
-        </is>
+      <c r="A449" t="n">
+        <v>20505</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -21725,10 +21571,8 @@
       <c r="Q449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>20506</t>
-        </is>
+      <c r="A450" t="n">
+        <v>20506</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -21784,10 +21628,8 @@
       <c r="Q450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>20507</t>
-        </is>
+      <c r="A451" t="n">
+        <v>20507</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -21843,10 +21685,8 @@
       <c r="Q451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>20508</t>
-        </is>
+      <c r="A452" t="n">
+        <v>20508</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -21902,10 +21742,8 @@
       <c r="Q452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>20509</t>
-        </is>
+      <c r="A453" t="n">
+        <v>20509</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -21949,10 +21787,8 @@
       <c r="Q453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>20510</t>
-        </is>
+      <c r="A454" t="n">
+        <v>20510</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -21996,10 +21832,8 @@
       <c r="Q454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>20511</t>
-        </is>
+      <c r="A455" t="n">
+        <v>20511</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -22055,10 +21889,8 @@
       <c r="Q455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>20019</t>
-        </is>
+      <c r="A456" t="n">
+        <v>20019</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -22114,10 +21946,8 @@
       <c r="Q456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>20020</t>
-        </is>
+      <c r="A457" t="n">
+        <v>20020</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -22173,10 +22003,8 @@
       <c r="Q457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>20021</t>
-        </is>
+      <c r="A458" t="n">
+        <v>20021</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -22232,10 +22060,8 @@
       <c r="Q458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>20022</t>
-        </is>
+      <c r="A459" t="n">
+        <v>20022</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -22291,10 +22117,8 @@
       <c r="Q459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>20023</t>
-        </is>
+      <c r="A460" t="n">
+        <v>20023</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -22350,10 +22174,8 @@
       <c r="Q460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>20024</t>
-        </is>
+      <c r="A461" t="n">
+        <v>20024</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -22409,10 +22231,8 @@
       <c r="Q461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>20025</t>
-        </is>
+      <c r="A462" t="n">
+        <v>20025</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -22468,10 +22288,8 @@
       <c r="Q462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>20026</t>
-        </is>
+      <c r="A463" t="n">
+        <v>20026</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -22527,10 +22345,8 @@
       <c r="Q463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>20027</t>
-        </is>
+      <c r="A464" t="n">
+        <v>20027</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -22586,10 +22402,8 @@
       <c r="Q464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>20028</t>
-        </is>
+      <c r="A465" t="n">
+        <v>20028</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -22645,10 +22459,8 @@
       <c r="Q465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>20029</t>
-        </is>
+      <c r="A466" t="n">
+        <v>20029</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -22704,10 +22516,8 @@
       <c r="Q466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>20030</t>
-        </is>
+      <c r="A467" t="n">
+        <v>20030</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -22763,10 +22573,8 @@
       <c r="Q467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>20031</t>
-        </is>
+      <c r="A468" t="n">
+        <v>20031</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -22822,10 +22630,8 @@
       <c r="Q468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>20032</t>
-        </is>
+      <c r="A469" t="n">
+        <v>20032</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -22881,10 +22687,8 @@
       <c r="Q469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>20033</t>
-        </is>
+      <c r="A470" t="n">
+        <v>20033</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -22940,10 +22744,8 @@
       <c r="Q470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>20034</t>
-        </is>
+      <c r="A471" t="n">
+        <v>20034</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -22999,10 +22801,8 @@
       <c r="Q471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>20035</t>
-        </is>
+      <c r="A472" t="n">
+        <v>20035</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -23058,10 +22858,8 @@
       <c r="Q472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>20036</t>
-        </is>
+      <c r="A473" t="n">
+        <v>20036</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -23117,10 +22915,8 @@
       <c r="Q473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>20037</t>
-        </is>
+      <c r="A474" t="n">
+        <v>20037</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -23176,10 +22972,8 @@
       <c r="Q474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>20038</t>
-        </is>
+      <c r="A475" t="n">
+        <v>20038</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -23235,10 +23029,8 @@
       <c r="Q475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>20039</t>
-        </is>
+      <c r="A476" t="n">
+        <v>20039</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -23294,10 +23086,8 @@
       <c r="Q476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>20040</t>
-        </is>
+      <c r="A477" t="n">
+        <v>20040</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -23353,10 +23143,8 @@
       <c r="Q477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
+      <c r="A478" t="n">
+        <v>20041</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -23412,10 +23200,8 @@
       <c r="Q478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>20042</t>
-        </is>
+      <c r="A479" t="n">
+        <v>20042</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -23471,10 +23257,8 @@
       <c r="Q479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>20043</t>
-        </is>
+      <c r="A480" t="n">
+        <v>20043</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -23530,10 +23314,8 @@
       <c r="Q480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
+      <c r="A481" t="n">
+        <v>20044</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -23589,10 +23371,8 @@
       <c r="Q481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>20045</t>
-        </is>
+      <c r="A482" t="n">
+        <v>20045</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -23648,10 +23428,8 @@
       <c r="Q482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>20046</t>
-        </is>
+      <c r="A483" t="n">
+        <v>20046</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -23707,10 +23485,8 @@
       <c r="Q483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>20047</t>
-        </is>
+      <c r="A484" t="n">
+        <v>20047</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -23766,10 +23542,8 @@
       <c r="Q484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>20048</t>
-        </is>
+      <c r="A485" t="n">
+        <v>20048</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -23825,10 +23599,8 @@
       <c r="Q485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>20049</t>
-        </is>
+      <c r="A486" t="n">
+        <v>20049</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -23884,10 +23656,8 @@
       <c r="Q486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>20050</t>
-        </is>
+      <c r="A487" t="n">
+        <v>20050</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -23943,10 +23713,8 @@
       <c r="Q487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>20051</t>
-        </is>
+      <c r="A488" t="n">
+        <v>20051</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -24002,10 +23770,8 @@
       <c r="Q488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>20052</t>
-        </is>
+      <c r="A489" t="n">
+        <v>20052</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -24061,10 +23827,8 @@
       <c r="Q489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>20054</t>
-        </is>
+      <c r="A490" t="n">
+        <v>20054</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -24120,10 +23884,8 @@
       <c r="Q490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>20055</t>
-        </is>
+      <c r="A491" t="n">
+        <v>20055</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -24179,10 +23941,8 @@
       <c r="Q491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>20056</t>
-        </is>
+      <c r="A492" t="n">
+        <v>20056</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>熊猫</t>
         </is>
       </c>
-      <c r="M492" t="inlineStr">
-        <is>
-          <t>20542</t>
-        </is>
-      </c>
-      <c r="N492" t="inlineStr">
-        <is>
-          <t>20104</t>
-        </is>
+      <c r="M492" t="n">
+        <v>20542</v>
+      </c>
+      <c r="N492" t="n">
+        <v>20104</v>
       </c>
       <c r="O492" t="inlineStr"/>
       <c r="P492" t="inlineStr">
@@ -24254,10 +24010,8 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>20057</t>
-        </is>
+      <c r="A493" t="n">
+        <v>20057</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -24313,10 +24067,8 @@
       <c r="Q493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>20058</t>
-        </is>
+      <c r="A494" t="n">
+        <v>20058</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -24372,10 +24124,8 @@
       <c r="Q494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>20053</t>
-        </is>
+      <c r="A495" t="n">
+        <v>20053</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -24431,10 +24181,8 @@
       <c r="Q495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>20059</t>
-        </is>
+      <c r="A496" t="n">
+        <v>20059</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -24490,10 +24238,8 @@
       <c r="Q496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>20060</t>
-        </is>
+      <c r="A497" t="n">
+        <v>20060</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -24549,10 +24295,8 @@
       <c r="Q497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>20061</t>
-        </is>
+      <c r="A498" t="n">
+        <v>20061</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -24608,10 +24352,8 @@
       <c r="Q498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>20062</t>
-        </is>
+      <c r="A499" t="n">
+        <v>20062</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -24667,10 +24409,8 @@
       <c r="Q499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>20063</t>
-        </is>
+      <c r="A500" t="n">
+        <v>20063</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -24726,10 +24466,8 @@
       <c r="Q500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>20064</t>
-        </is>
+      <c r="A501" t="n">
+        <v>20064</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -24785,10 +24523,8 @@
       <c r="Q501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>20065</t>
-        </is>
+      <c r="A502" t="n">
+        <v>20065</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -24844,10 +24580,8 @@
       <c r="Q502" t="inlineStr"/>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>20066</t>
-        </is>
+      <c r="A503" t="n">
+        <v>20066</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -24903,10 +24637,8 @@
       <c r="Q503" t="inlineStr"/>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>20067</t>
-        </is>
+      <c r="A504" t="n">
+        <v>20067</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -24962,10 +24694,8 @@
       <c r="Q504" t="inlineStr"/>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>20068</t>
-        </is>
+      <c r="A505" t="n">
+        <v>20068</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -25021,10 +24751,8 @@
       <c r="Q505" t="inlineStr"/>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>20069</t>
-        </is>
+      <c r="A506" t="n">
+        <v>20069</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -25080,10 +24808,8 @@
       <c r="Q506" t="inlineStr"/>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>20070</t>
-        </is>
+      <c r="A507" t="n">
+        <v>20070</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -25139,10 +24865,8 @@
       <c r="Q507" t="inlineStr"/>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>20071</t>
-        </is>
+      <c r="A508" t="n">
+        <v>20071</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -25198,10 +24922,8 @@
       <c r="Q508" t="inlineStr"/>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>20072</t>
-        </is>
+      <c r="A509" t="n">
+        <v>20072</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -25257,10 +24979,8 @@
       <c r="Q509" t="inlineStr"/>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>20073</t>
-        </is>
+      <c r="A510" t="n">
+        <v>20073</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -25316,10 +25036,8 @@
       <c r="Q510" t="inlineStr"/>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>20074</t>
-        </is>
+      <c r="A511" t="n">
+        <v>20074</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -25375,10 +25093,8 @@
       <c r="Q511" t="inlineStr"/>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>20075</t>
-        </is>
+      <c r="A512" t="n">
+        <v>20075</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -25434,10 +25150,8 @@
       <c r="Q512" t="inlineStr"/>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>20076</t>
-        </is>
+      <c r="A513" t="n">
+        <v>20076</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -25493,10 +25207,8 @@
       <c r="Q513" t="inlineStr"/>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>20077</t>
-        </is>
+      <c r="A514" t="n">
+        <v>20077</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -25552,10 +25264,8 @@
       <c r="Q514" t="inlineStr"/>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>20078</t>
-        </is>
+      <c r="A515" t="n">
+        <v>20078</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -25611,10 +25321,8 @@
       <c r="Q515" t="inlineStr"/>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>20079</t>
-        </is>
+      <c r="A516" t="n">
+        <v>20079</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -25670,10 +25378,8 @@
       <c r="Q516" t="inlineStr"/>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>20080</t>
-        </is>
+      <c r="A517" t="n">
+        <v>20080</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -25729,10 +25435,8 @@
       <c r="Q517" t="inlineStr"/>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>20081</t>
-        </is>
+      <c r="A518" t="n">
+        <v>20081</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -25788,10 +25492,8 @@
       <c r="Q518" t="inlineStr"/>
     </row>
     <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>20082</t>
-        </is>
+      <c r="A519" t="n">
+        <v>20082</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -25847,10 +25549,8 @@
       <c r="Q519" t="inlineStr"/>
     </row>
     <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>20083</t>
-        </is>
+      <c r="A520" t="n">
+        <v>20083</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -25906,10 +25606,8 @@
       <c r="Q520" t="inlineStr"/>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>20084</t>
-        </is>
+      <c r="A521" t="n">
+        <v>20084</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -25965,10 +25663,8 @@
       <c r="Q521" t="inlineStr"/>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>20085</t>
-        </is>
+      <c r="A522" t="n">
+        <v>20085</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -26024,10 +25720,8 @@
       <c r="Q522" t="inlineStr"/>
     </row>
     <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>20086</t>
-        </is>
+      <c r="A523" t="n">
+        <v>20086</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -26075,10 +25769,8 @@
       <c r="Q523" t="inlineStr"/>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>20087</t>
-        </is>
+      <c r="A524" t="n">
+        <v>20087</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -26134,10 +25826,8 @@
       <c r="Q524" t="inlineStr"/>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>20088</t>
-        </is>
+      <c r="A525" t="n">
+        <v>20088</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -26193,10 +25883,8 @@
       <c r="Q525" t="inlineStr"/>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>20089</t>
-        </is>
+      <c r="A526" t="n">
+        <v>20089</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -26252,10 +25940,8 @@
       <c r="Q526" t="inlineStr"/>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>20091</t>
-        </is>
+      <c r="A527" t="n">
+        <v>20091</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -26311,10 +25997,8 @@
       <c r="Q527" t="inlineStr"/>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>20092</t>
-        </is>
+      <c r="A528" t="n">
+        <v>20092</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -26370,10 +26054,8 @@
       <c r="Q528" t="inlineStr"/>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>20095</t>
-        </is>
+      <c r="A529" t="n">
+        <v>20095</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -26422,15 +26104,11 @@
           <t>图书馆</t>
         </is>
       </c>
-      <c r="M529" t="inlineStr">
-        <is>
-          <t>20538</t>
-        </is>
-      </c>
-      <c r="N529" t="inlineStr">
-        <is>
-          <t>20093</t>
-        </is>
+      <c r="M529" t="n">
+        <v>20538</v>
+      </c>
+      <c r="N529" t="n">
+        <v>20093</v>
       </c>
       <c r="O529" t="inlineStr"/>
       <c r="P529" t="inlineStr">
@@ -26445,10 +26123,8 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>20096</t>
-        </is>
+      <c r="A530" t="n">
+        <v>20096</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -26504,10 +26180,8 @@
       <c r="Q530" t="inlineStr"/>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>20097</t>
-        </is>
+      <c r="A531" t="n">
+        <v>20097</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -26556,15 +26230,11 @@
           <t>电视</t>
         </is>
       </c>
-      <c r="M531" t="inlineStr">
-        <is>
-          <t>20090</t>
-        </is>
-      </c>
-      <c r="N531" t="inlineStr">
-        <is>
-          <t>10078</t>
-        </is>
+      <c r="M531" t="n">
+        <v>20090</v>
+      </c>
+      <c r="N531" t="n">
+        <v>10078</v>
       </c>
       <c r="O531" t="inlineStr"/>
       <c r="P531" t="inlineStr">
@@ -26579,10 +26249,8 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>20098</t>
-        </is>
+      <c r="A532" t="n">
+        <v>20098</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -26638,10 +26306,8 @@
       <c r="Q532" t="inlineStr"/>
     </row>
     <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>20147</t>
-        </is>
+      <c r="A533" t="n">
+        <v>20147</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -26697,10 +26363,8 @@
       <c r="Q533" t="inlineStr"/>
     </row>
     <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>20149</t>
-        </is>
+      <c r="A534" t="n">
+        <v>20149</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -26749,25 +26413,19 @@
           <t>电池</t>
         </is>
       </c>
-      <c r="M534" t="inlineStr">
-        <is>
-          <t>20090</t>
-        </is>
-      </c>
-      <c r="N534" t="inlineStr">
-        <is>
-          <t>20550</t>
-        </is>
+      <c r="M534" t="n">
+        <v>20090</v>
+      </c>
+      <c r="N534" t="n">
+        <v>20550</v>
       </c>
       <c r="O534" t="inlineStr"/>
       <c r="P534" t="inlineStr"/>
       <c r="Q534" t="inlineStr"/>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>20153</t>
-        </is>
+      <c r="A535" t="n">
+        <v>20153</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -26823,10 +26481,8 @@
       <c r="Q535" t="inlineStr"/>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>20154</t>
-        </is>
+      <c r="A536" t="n">
+        <v>20154</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -26882,10 +26538,8 @@
       <c r="Q536" t="inlineStr"/>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>20155</t>
-        </is>
+      <c r="A537" t="n">
+        <v>20155</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -26941,10 +26595,8 @@
       <c r="Q537" t="inlineStr"/>
     </row>
     <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>20156</t>
-        </is>
+      <c r="A538" t="n">
+        <v>20156</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -27000,10 +26652,8 @@
       <c r="Q538" t="inlineStr"/>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>20157</t>
-        </is>
+      <c r="A539" t="n">
+        <v>20157</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -27052,15 +26702,11 @@
           <t>电脑</t>
         </is>
       </c>
-      <c r="M539" t="inlineStr">
-        <is>
-          <t>20090</t>
-        </is>
-      </c>
-      <c r="N539" t="inlineStr">
-        <is>
-          <t>20525</t>
-        </is>
+      <c r="M539" t="n">
+        <v>20090</v>
+      </c>
+      <c r="N539" t="n">
+        <v>20525</v>
       </c>
       <c r="O539" t="inlineStr"/>
       <c r="P539" t="inlineStr">
@@ -27075,10 +26721,8 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>20158</t>
-        </is>
+      <c r="A540" t="n">
+        <v>20158</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -27127,25 +26771,19 @@
           <t>电话</t>
         </is>
       </c>
-      <c r="M540" t="inlineStr">
-        <is>
-          <t>20090</t>
-        </is>
-      </c>
-      <c r="N540" t="inlineStr">
-        <is>
-          <t>20549</t>
-        </is>
+      <c r="M540" t="n">
+        <v>20090</v>
+      </c>
+      <c r="N540" t="n">
+        <v>20549</v>
       </c>
       <c r="O540" t="inlineStr"/>
       <c r="P540" t="inlineStr"/>
       <c r="Q540" t="inlineStr"/>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>20090</t>
-        </is>
+      <c r="A541" t="n">
+        <v>20090</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -27201,10 +26839,8 @@
       <c r="Q541" t="inlineStr"/>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>20093</t>
-        </is>
+      <c r="A542" t="n">
+        <v>20093</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -27260,10 +26896,8 @@
       <c r="Q542" t="inlineStr"/>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>20094</t>
-        </is>
+      <c r="A543" t="n">
+        <v>20094</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -27312,15 +26946,11 @@
           <t>电灯</t>
         </is>
       </c>
-      <c r="M543" t="inlineStr">
-        <is>
-          <t>20090</t>
-        </is>
-      </c>
-      <c r="N543" t="inlineStr">
-        <is>
-          <t>20203</t>
-        </is>
+      <c r="M543" t="n">
+        <v>20090</v>
+      </c>
+      <c r="N543" t="n">
+        <v>20203</v>
       </c>
       <c r="O543" t="inlineStr"/>
       <c r="P543" t="inlineStr">
@@ -27335,10 +26965,8 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>20148</t>
-        </is>
+      <c r="A544" t="n">
+        <v>20148</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -27394,10 +27022,8 @@
       <c r="Q544" t="inlineStr"/>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>20159</t>
-        </is>
+      <c r="A545" t="n">
+        <v>20159</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -27453,10 +27079,8 @@
       <c r="Q545" t="inlineStr"/>
     </row>
     <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>20160</t>
-        </is>
+      <c r="A546" t="n">
+        <v>20160</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -27512,10 +27136,8 @@
       <c r="Q546" t="inlineStr"/>
     </row>
     <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>20161</t>
-        </is>
+      <c r="A547" t="n">
+        <v>20161</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -27564,15 +27186,11 @@
           <t>书店</t>
         </is>
       </c>
-      <c r="M547" t="inlineStr">
-        <is>
-          <t>20102</t>
-        </is>
-      </c>
-      <c r="N547" t="inlineStr">
-        <is>
-          <t>20167</t>
-        </is>
+      <c r="M547" t="n">
+        <v>20102</v>
+      </c>
+      <c r="N547" t="n">
+        <v>20167</v>
       </c>
       <c r="O547" t="inlineStr"/>
       <c r="P547" t="inlineStr">
@@ -27587,10 +27205,8 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>20162</t>
-        </is>
+      <c r="A548" t="n">
+        <v>20162</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -27646,10 +27262,8 @@
       <c r="Q548" t="inlineStr"/>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>20163</t>
-        </is>
+      <c r="A549" t="n">
+        <v>20163</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -27705,10 +27319,8 @@
       <c r="Q549" t="inlineStr"/>
     </row>
     <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>20164</t>
-        </is>
+      <c r="A550" t="n">
+        <v>20164</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -27764,10 +27376,8 @@
       <c r="Q550" t="inlineStr"/>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>20165</t>
-        </is>
+      <c r="A551" t="n">
+        <v>20165</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -27823,10 +27433,8 @@
       <c r="Q551" t="inlineStr"/>
     </row>
     <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>20166</t>
-        </is>
+      <c r="A552" t="n">
+        <v>20166</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -27882,10 +27490,8 @@
       <c r="Q552" t="inlineStr"/>
     </row>
     <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>20167</t>
-        </is>
+      <c r="A553" t="n">
+        <v>20167</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -27937,10 +27543,8 @@
       <c r="Q553" t="inlineStr"/>
     </row>
     <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>20168</t>
-        </is>
+      <c r="A554" t="n">
+        <v>20168</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -27989,15 +27593,11 @@
           <t>飞机</t>
         </is>
       </c>
-      <c r="M554" t="inlineStr">
-        <is>
-          <t>10077</t>
-        </is>
-      </c>
-      <c r="N554" t="inlineStr">
-        <is>
-          <t>20522</t>
-        </is>
+      <c r="M554" t="n">
+        <v>10077</v>
+      </c>
+      <c r="N554" t="n">
+        <v>20522</v>
       </c>
       <c r="O554" t="inlineStr"/>
       <c r="P554" t="inlineStr">
@@ -28012,10 +27612,8 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>20169</t>
-        </is>
+      <c r="A555" t="n">
+        <v>20169</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -28071,10 +27669,8 @@
       <c r="Q555" t="inlineStr"/>
     </row>
     <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>20170</t>
-        </is>
+      <c r="A556" t="n">
+        <v>20170</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -28130,10 +27726,8 @@
       <c r="Q556" t="inlineStr"/>
     </row>
     <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>20171</t>
-        </is>
+      <c r="A557" t="n">
+        <v>20171</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -28189,10 +27783,8 @@
       <c r="Q557" t="inlineStr"/>
     </row>
     <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>20172</t>
-        </is>
+      <c r="A558" t="n">
+        <v>20172</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -28241,15 +27833,11 @@
           <t>火车</t>
         </is>
       </c>
-      <c r="M558" t="inlineStr">
-        <is>
-          <t>20523</t>
-        </is>
-      </c>
-      <c r="N558" t="inlineStr">
-        <is>
-          <t>20521</t>
-        </is>
+      <c r="M558" t="n">
+        <v>20523</v>
+      </c>
+      <c r="N558" t="n">
+        <v>20521</v>
       </c>
       <c r="O558" t="inlineStr"/>
       <c r="P558" t="inlineStr">
@@ -28264,10 +27852,8 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>20173</t>
-        </is>
+      <c r="A559" t="n">
+        <v>20173</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -28323,10 +27909,8 @@
       <c r="Q559" t="inlineStr"/>
     </row>
     <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>20174</t>
-        </is>
+      <c r="A560" t="n">
+        <v>20174</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -28382,10 +27966,8 @@
       <c r="Q560" t="inlineStr"/>
     </row>
     <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>20175</t>
-        </is>
+      <c r="A561" t="n">
+        <v>20175</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -28441,10 +28023,8 @@
       <c r="Q561" t="inlineStr"/>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>20176</t>
-        </is>
+      <c r="A562" t="n">
+        <v>20176</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -28500,10 +28080,8 @@
       <c r="Q562" t="inlineStr"/>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>20177</t>
-        </is>
+      <c r="A563" t="n">
+        <v>20177</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -28559,10 +2813